--- a/WIP/月茗/LAN阿斯特莱雅/阿斯特莱雅-军事人员配置表.xlsx
+++ b/WIP/月茗/LAN阿斯特莱雅/阿斯特莱雅-军事人员配置表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" firstSheet="2"/>
+    <workbookView windowWidth="21810" windowHeight="12375" firstSheet="2"/>
   </bookViews>
   <sheets>
     <sheet name="PCR" sheetId="3" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="325">
   <si>
     <t>阿斯特莱雅</t>
   </si>
@@ -186,7 +186,7 @@
     <t>伊莉亚·奥恩斯坦</t>
   </si>
   <si>
-    <t>夜间行动（大师）</t>
+    <t>对地支援（专家）</t>
   </si>
   <si>
     <t>天野铃莓</t>
@@ -259,6 +259,9 @@
     <t>战术轰炸（大师）</t>
   </si>
   <si>
+    <t>厄里斯</t>
+  </si>
+  <si>
     <t>佐佐木咲恋</t>
   </si>
   <si>
@@ -304,6 +307,12 @@
     <t>美波铃奈</t>
   </si>
   <si>
+    <t>涅比亚</t>
+  </si>
+  <si>
+    <t>1级海军工程</t>
+  </si>
+  <si>
     <t>百地希留耶</t>
   </si>
   <si>
@@ -334,6 +343,12 @@
     <t>陆军士气（奇才）</t>
   </si>
   <si>
+    <t>久央璃亚</t>
+  </si>
+  <si>
+    <t>夜间行动（大师）</t>
+  </si>
+  <si>
     <t>丹野七七香</t>
   </si>
   <si>
@@ -343,6 +358,12 @@
     <t>千里真那</t>
   </si>
   <si>
+    <t>爱梅斯</t>
+  </si>
+  <si>
+    <t>1级陆军工程</t>
+  </si>
+  <si>
     <t>威权主义-贵族保守主义</t>
   </si>
   <si>
@@ -517,6 +538,12 @@
     <t>桥本环奈</t>
   </si>
   <si>
+    <t>德川莉莉</t>
+  </si>
+  <si>
+    <t>轰炸机拦截（大师）</t>
+  </si>
+  <si>
     <t>织原茉莉</t>
   </si>
   <si>
@@ -688,9 +715,6 @@
     <t>战略破坏</t>
   </si>
   <si>
-    <t>轰炸机拦截（大师）</t>
-  </si>
-  <si>
     <t>贸易袭击（大师）</t>
   </si>
   <si>
@@ -722,9 +746,6 @@
   </si>
   <si>
     <t>步兵部队（专家）</t>
-  </si>
-  <si>
-    <t>对地支援（专家）</t>
   </si>
   <si>
     <t>空中优势（专家）</t>
@@ -2145,7 +2166,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2182,9 +2203,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -2194,9 +2212,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -2216,15 +2231,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1">
@@ -2269,27 +2275,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2356,42 +2347,12 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2420,9 +2381,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2956,2354 +2914,2373 @@
   <dimension ref="B2:Z100"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="35" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="9" style="31"/>
-    <col min="2" max="21" width="20.625" style="31" customWidth="1"/>
-    <col min="22" max="22" width="9" style="31"/>
-    <col min="23" max="23" width="17.25" style="31" customWidth="1"/>
-    <col min="24" max="24" width="27.875" style="31" customWidth="1"/>
-    <col min="25" max="25" width="27.25" style="31" customWidth="1"/>
-    <col min="26" max="26" width="29.625" style="31" customWidth="1"/>
-    <col min="27" max="16384" width="9" style="31"/>
+    <col min="1" max="1" width="9" style="26"/>
+    <col min="2" max="21" width="20.625" style="26" customWidth="1"/>
+    <col min="22" max="22" width="9" style="26"/>
+    <col min="23" max="23" width="17.25" style="26" customWidth="1"/>
+    <col min="24" max="24" width="27.875" style="26" customWidth="1"/>
+    <col min="25" max="25" width="27.25" style="26" customWidth="1"/>
+    <col min="26" max="26" width="29.625" style="26" customWidth="1"/>
+    <col min="27" max="16384" width="9" style="26"/>
   </cols>
   <sheetData>
     <row r="2" customHeight="1" spans="2:26">
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="33"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="33"/>
-      <c r="M2" s="33"/>
-      <c r="N2" s="33"/>
-      <c r="O2" s="33"/>
-      <c r="P2" s="33"/>
-      <c r="Q2" s="33"/>
-      <c r="R2" s="33"/>
-      <c r="S2" s="33"/>
-      <c r="T2" s="33"/>
-      <c r="U2" s="34"/>
-      <c r="W2" s="35" t="s">
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
+      <c r="N2" s="28"/>
+      <c r="O2" s="28"/>
+      <c r="P2" s="28"/>
+      <c r="Q2" s="28"/>
+      <c r="R2" s="28"/>
+      <c r="S2" s="28"/>
+      <c r="T2" s="28"/>
+      <c r="U2" s="29"/>
+      <c r="W2" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="X2" s="36"/>
-      <c r="Y2" s="36"/>
-      <c r="Z2" s="37"/>
+      <c r="X2" s="31"/>
+      <c r="Y2" s="31"/>
+      <c r="Z2" s="32"/>
     </row>
     <row r="3" customHeight="1" spans="2:26">
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="39"/>
-      <c r="D3" s="40" t="s">
+      <c r="C3" s="34"/>
+      <c r="D3" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="41"/>
-      <c r="F3" s="42" t="s">
+      <c r="E3" s="35"/>
+      <c r="F3" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="39"/>
-      <c r="H3" s="43" t="s">
+      <c r="G3" s="34"/>
+      <c r="H3" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="44"/>
-      <c r="J3" s="42" t="s">
+      <c r="I3" s="35"/>
+      <c r="J3" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="K3" s="39"/>
-      <c r="L3" s="43" t="s">
+      <c r="K3" s="34"/>
+      <c r="L3" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="M3" s="44"/>
-      <c r="N3" s="42" t="s">
+      <c r="M3" s="35"/>
+      <c r="N3" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="O3" s="39"/>
-      <c r="P3" s="40" t="s">
+      <c r="O3" s="34"/>
+      <c r="P3" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="Q3" s="41"/>
-      <c r="R3" s="45"/>
-      <c r="S3" s="46" t="s">
+      <c r="Q3" s="35"/>
+      <c r="R3" s="36"/>
+      <c r="S3" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="T3" s="47"/>
-      <c r="U3" s="48"/>
-      <c r="W3" s="49" t="s">
+      <c r="T3" s="37"/>
+      <c r="U3" s="38"/>
+      <c r="W3" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="X3" s="50" t="s">
+      <c r="X3" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="Y3" s="50" t="s">
+      <c r="Y3" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="Z3" s="51" t="s">
+      <c r="Z3" s="41" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="2:26">
-      <c r="B4" s="52" t="s">
+      <c r="B4" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="53" t="s">
+      <c r="C4" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="53" t="s">
+      <c r="D4" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="53" t="s">
+      <c r="E4" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="53" t="s">
+      <c r="F4" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="53" t="s">
+      <c r="G4" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="53" t="s">
+      <c r="H4" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="I4" s="53" t="s">
+      <c r="I4" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="J4" s="53" t="s">
+      <c r="J4" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="53" t="s">
+      <c r="K4" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="L4" s="53" t="s">
+      <c r="L4" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="M4" s="53" t="s">
+      <c r="M4" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="N4" s="53" t="s">
+      <c r="N4" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="O4" s="54" t="s">
+      <c r="O4" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="P4" s="53" t="s">
+      <c r="P4" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="Q4" s="55" t="s">
+      <c r="Q4" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="R4" s="56" t="s">
+      <c r="R4" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="S4" s="57" t="s">
+      <c r="S4" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="T4" s="57" t="s">
+      <c r="T4" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="U4" s="58" t="s">
+      <c r="U4" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="W4" s="59" t="s">
+      <c r="W4" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="X4" s="60" t="s">
+      <c r="X4" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="Y4" s="60" t="s">
+      <c r="Y4" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="Z4" s="61" t="s">
+      <c r="Z4" s="51" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="2:26">
-      <c r="B5" s="62" t="s">
+      <c r="B5" s="52" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="63" t="s">
+      <c r="C5" s="53" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="64" t="s">
+      <c r="D5" s="54" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="63" t="s">
+      <c r="E5" s="53" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="64" t="s">
+      <c r="F5" s="54" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="63" t="s">
+      <c r="G5" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="H5" s="64" t="s">
+      <c r="H5" s="54" t="s">
         <v>29</v>
       </c>
-      <c r="I5" s="63" t="s">
+      <c r="I5" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="J5" s="64" t="s">
+      <c r="J5" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="K5" s="63" t="s">
+      <c r="K5" s="53" t="s">
         <v>32</v>
       </c>
-      <c r="L5" s="64" t="s">
+      <c r="L5" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="M5" s="63" t="s">
+      <c r="M5" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="N5" s="64" t="s">
+      <c r="N5" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="O5" s="63" t="s">
+      <c r="O5" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="P5" s="64" t="s">
+      <c r="P5" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="Q5" s="63" t="s">
+      <c r="Q5" s="53" t="s">
         <v>37</v>
       </c>
-      <c r="R5" s="65">
+      <c r="R5" s="55">
         <v>11111</v>
       </c>
-      <c r="S5" s="66" t="s">
+      <c r="S5" s="56" t="s">
         <v>38</v>
       </c>
-      <c r="T5" s="67" t="s">
+      <c r="T5" s="57" t="s">
         <v>39</v>
       </c>
-      <c r="U5" s="68" t="s">
+      <c r="U5" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="W5" s="59" t="s">
+      <c r="W5" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="X5" s="60" t="s">
+      <c r="X5" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="Y5" s="60" t="s">
+      <c r="Y5" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="Z5" s="61" t="s">
+      <c r="Z5" s="51" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="2:26">
-      <c r="B6" s="62" t="s">
+      <c r="B6" s="52" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="63" t="s">
+      <c r="C6" s="53" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="64" t="s">
+      <c r="D6" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="63" t="s">
+      <c r="E6" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="F6" s="64" t="s">
+      <c r="F6" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="G6" s="63" t="s">
+      <c r="G6" s="53" t="s">
         <v>46</v>
       </c>
-      <c r="H6" s="64" t="s">
+      <c r="H6" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="I6" s="63" t="s">
+      <c r="I6" s="53" t="s">
         <v>48</v>
       </c>
-      <c r="J6" s="69" t="s">
+      <c r="J6" s="59" t="s">
         <v>49</v>
       </c>
-      <c r="K6" s="63" t="s">
+      <c r="K6" s="53" t="s">
         <v>50</v>
       </c>
-      <c r="L6" s="69" t="s">
+      <c r="L6" s="59" t="s">
         <v>51</v>
       </c>
-      <c r="M6" s="63" t="s">
+      <c r="M6" s="53" t="s">
         <v>52</v>
       </c>
-      <c r="N6" s="64" t="s">
+      <c r="N6" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="O6" s="63" t="s">
+      <c r="O6" s="53" t="s">
         <v>54</v>
       </c>
-      <c r="P6" s="64" t="s">
+      <c r="P6" s="54" t="s">
         <v>55</v>
       </c>
-      <c r="Q6" s="63" t="s">
+      <c r="Q6" s="53" t="s">
         <v>37</v>
       </c>
-      <c r="R6" s="65">
+      <c r="R6" s="55">
         <v>11111</v>
       </c>
-      <c r="S6" s="66" t="s">
+      <c r="S6" s="56" t="s">
         <v>56</v>
       </c>
-      <c r="T6" s="67" t="s">
+      <c r="T6" s="57" t="s">
         <v>57</v>
       </c>
-      <c r="U6" s="68" t="s">
+      <c r="U6" s="58" t="s">
         <v>58</v>
       </c>
-      <c r="W6" s="59" t="s">
+      <c r="W6" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="X6" s="60" t="s">
+      <c r="X6" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="Y6" s="60" t="s">
+      <c r="Y6" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="Z6" s="61" t="s">
+      <c r="Z6" s="51" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="2:26">
-      <c r="B7" s="62" t="s">
+      <c r="B7" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="63" t="s">
+      <c r="C7" s="53" t="s">
         <v>63</v>
       </c>
-      <c r="D7" s="64" t="s">
+      <c r="D7" s="54" t="s">
         <v>64</v>
       </c>
-      <c r="E7" s="63" t="s">
+      <c r="E7" s="53" t="s">
         <v>65</v>
       </c>
-      <c r="F7" s="64" t="s">
+      <c r="F7" s="54" t="s">
         <v>66</v>
       </c>
-      <c r="G7" s="63" t="s">
+      <c r="G7" s="53" t="s">
         <v>67</v>
       </c>
-      <c r="H7" s="64" t="s">
+      <c r="H7" s="54" t="s">
         <v>68</v>
       </c>
-      <c r="I7" s="63" t="s">
+      <c r="I7" s="53" t="s">
         <v>69</v>
       </c>
-      <c r="J7" s="64" t="s">
+      <c r="J7" s="54" t="s">
         <v>70</v>
       </c>
-      <c r="K7" s="63" t="s">
+      <c r="K7" s="53" t="s">
         <v>71</v>
       </c>
-      <c r="L7" s="64" t="s">
+      <c r="L7" s="54" t="s">
         <v>72</v>
       </c>
-      <c r="M7" s="63" t="s">
+      <c r="M7" s="53" t="s">
         <v>73</v>
       </c>
-      <c r="N7" s="64" t="s">
+      <c r="N7" s="54" t="s">
         <v>74</v>
       </c>
-      <c r="O7" s="63" t="s">
+      <c r="O7" s="53" t="s">
         <v>75</v>
       </c>
-      <c r="P7" s="64" t="s">
+      <c r="P7" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="Q7" s="63" t="s">
+      <c r="Q7" s="53" t="s">
         <v>37</v>
       </c>
-      <c r="R7" s="65">
+      <c r="R7" s="55">
         <v>11111</v>
       </c>
-      <c r="S7" s="66"/>
-      <c r="T7" s="67"/>
-      <c r="U7" s="68"/>
-      <c r="W7" s="59" t="s">
+      <c r="S7" s="56" t="s">
         <v>76</v>
       </c>
-      <c r="X7" s="60" t="s">
+      <c r="T7" s="57" t="s">
+        <v>39</v>
+      </c>
+      <c r="U7" s="58"/>
+      <c r="W7" s="49" t="s">
         <v>77</v>
       </c>
-      <c r="Y7" s="60" t="s">
+      <c r="X7" s="50" t="s">
         <v>78</v>
       </c>
-      <c r="Z7" s="61" t="s">
+      <c r="Y7" s="50" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z7" s="51" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="2:26">
-      <c r="B8" s="62" t="s">
+      <c r="B8" s="52" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="63" t="s">
-        <v>79</v>
-      </c>
-      <c r="D8" s="64" t="s">
+      <c r="C8" s="53" t="s">
         <v>80</v>
       </c>
-      <c r="E8" s="63" t="s">
+      <c r="D8" s="54" t="s">
         <v>81</v>
       </c>
-      <c r="F8" s="64" t="s">
+      <c r="E8" s="53" t="s">
         <v>82</v>
       </c>
-      <c r="G8" s="63" t="s">
+      <c r="F8" s="54" t="s">
         <v>83</v>
       </c>
-      <c r="H8" s="64" t="s">
+      <c r="G8" s="53" t="s">
         <v>84</v>
       </c>
-      <c r="I8" s="63" t="s">
+      <c r="H8" s="54" t="s">
         <v>85</v>
       </c>
-      <c r="J8" s="70"/>
-      <c r="K8" s="63"/>
-      <c r="L8" s="64" t="s">
+      <c r="I8" s="53" t="s">
         <v>86</v>
       </c>
-      <c r="M8" s="63" t="s">
+      <c r="J8" s="54"/>
+      <c r="K8" s="53"/>
+      <c r="L8" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="N8" s="64" t="s">
+      <c r="M8" s="53" t="s">
         <v>88</v>
       </c>
-      <c r="O8" s="63" t="s">
+      <c r="N8" s="54" t="s">
         <v>89</v>
       </c>
-      <c r="P8" s="64" t="s">
+      <c r="O8" s="53" t="s">
         <v>90</v>
       </c>
-      <c r="Q8" s="63" t="s">
+      <c r="P8" s="54" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q8" s="53" t="s">
         <v>37</v>
       </c>
-      <c r="R8" s="65">
+      <c r="R8" s="55">
         <v>11111</v>
       </c>
-      <c r="S8" s="66"/>
-      <c r="T8" s="67"/>
-      <c r="U8" s="68"/>
-      <c r="W8" s="59" t="s">
+      <c r="S8" s="56" t="s">
+        <v>92</v>
+      </c>
+      <c r="T8" s="57" t="s">
+        <v>93</v>
+      </c>
+      <c r="U8" s="58"/>
+      <c r="W8" s="49" t="s">
+        <v>94</v>
+      </c>
+      <c r="X8" s="50" t="s">
+        <v>95</v>
+      </c>
+      <c r="Y8" s="50" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z8" s="51" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="2:26">
+      <c r="B9" s="52" t="s">
+        <v>94</v>
+      </c>
+      <c r="C9" s="53" t="s">
+        <v>97</v>
+      </c>
+      <c r="D9" s="54" t="s">
+        <v>98</v>
+      </c>
+      <c r="E9" s="53" t="s">
+        <v>99</v>
+      </c>
+      <c r="F9" s="54" t="s">
+        <v>100</v>
+      </c>
+      <c r="G9" s="53" t="s">
+        <v>101</v>
+      </c>
+      <c r="H9" s="54" t="s">
+        <v>102</v>
+      </c>
+      <c r="I9" s="53" t="s">
+        <v>103</v>
+      </c>
+      <c r="J9" s="54"/>
+      <c r="K9" s="53"/>
+      <c r="L9" s="59" t="s">
+        <v>104</v>
+      </c>
+      <c r="M9" s="53" t="s">
+        <v>105</v>
+      </c>
+      <c r="N9" s="54" t="s">
+        <v>106</v>
+      </c>
+      <c r="O9" s="53" t="s">
+        <v>107</v>
+      </c>
+      <c r="P9" s="54" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q9" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="R9" s="55">
+        <v>11111</v>
+      </c>
+      <c r="S9" s="56" t="s">
+        <v>109</v>
+      </c>
+      <c r="T9" s="57" t="s">
+        <v>110</v>
+      </c>
+      <c r="U9" s="58"/>
+      <c r="W9" s="49" t="s">
+        <v>94</v>
+      </c>
+      <c r="X9" s="50" t="s">
+        <v>95</v>
+      </c>
+      <c r="Y9" s="50" t="s">
+        <v>111</v>
+      </c>
+      <c r="Z9" s="51" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="2:26">
+      <c r="B10" s="52" t="s">
+        <v>113</v>
+      </c>
+      <c r="C10" s="53" t="s">
+        <v>114</v>
+      </c>
+      <c r="D10" s="54" t="s">
+        <v>115</v>
+      </c>
+      <c r="E10" s="53" t="s">
+        <v>116</v>
+      </c>
+      <c r="F10" s="54" t="s">
+        <v>117</v>
+      </c>
+      <c r="G10" s="53" t="s">
+        <v>118</v>
+      </c>
+      <c r="H10" s="54" t="s">
+        <v>55</v>
+      </c>
+      <c r="I10" s="53" t="s">
+        <v>119</v>
+      </c>
+      <c r="J10" s="54"/>
+      <c r="K10" s="53"/>
+      <c r="L10" s="54"/>
+      <c r="M10" s="53"/>
+      <c r="N10" s="54" t="s">
+        <v>120</v>
+      </c>
+      <c r="O10" s="53" t="s">
+        <v>121</v>
+      </c>
+      <c r="P10" s="59" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q10" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="R10" s="55">
+        <v>11111</v>
+      </c>
+      <c r="S10" s="56"/>
+      <c r="T10" s="57"/>
+      <c r="U10" s="58"/>
+      <c r="W10" s="49" t="s">
+        <v>108</v>
+      </c>
+      <c r="X10" s="50" t="s">
+        <v>122</v>
+      </c>
+      <c r="Y10" s="50" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z10" s="51" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="2:26">
+      <c r="B11" s="52" t="s">
+        <v>77</v>
+      </c>
+      <c r="C11" s="53" t="s">
+        <v>125</v>
+      </c>
+      <c r="D11" s="54" t="s">
+        <v>126</v>
+      </c>
+      <c r="E11" s="53" t="s">
+        <v>127</v>
+      </c>
+      <c r="F11" s="54" t="s">
+        <v>128</v>
+      </c>
+      <c r="G11" s="53" t="s">
+        <v>129</v>
+      </c>
+      <c r="H11" s="54"/>
+      <c r="I11" s="53"/>
+      <c r="J11" s="54"/>
+      <c r="K11" s="53"/>
+      <c r="L11" s="54"/>
+      <c r="M11" s="53"/>
+      <c r="N11" s="59" t="s">
+        <v>130</v>
+      </c>
+      <c r="O11" s="53" t="s">
+        <v>131</v>
+      </c>
+      <c r="P11" s="54" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q11" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="R11" s="55">
+        <v>11111</v>
+      </c>
+      <c r="S11" s="56"/>
+      <c r="T11" s="57"/>
+      <c r="U11" s="58"/>
+      <c r="W11" s="49" t="s">
+        <v>113</v>
+      </c>
+      <c r="X11" s="50" t="s">
+        <v>95</v>
+      </c>
+      <c r="Y11" s="50" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z11" s="51" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="2:26">
+      <c r="B12" s="52" t="s">
+        <v>108</v>
+      </c>
+      <c r="C12" s="53" t="s">
+        <v>134</v>
+      </c>
+      <c r="D12" s="54" t="s">
+        <v>94</v>
+      </c>
+      <c r="E12" s="60" t="s">
+        <v>135</v>
+      </c>
+      <c r="F12" s="54"/>
+      <c r="G12" s="53"/>
+      <c r="H12" s="54"/>
+      <c r="I12" s="53"/>
+      <c r="J12" s="54"/>
+      <c r="K12" s="53"/>
+      <c r="L12" s="54"/>
+      <c r="M12" s="53"/>
+      <c r="N12" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="O12" s="53" t="s">
+        <v>137</v>
+      </c>
+      <c r="P12" s="54" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q12" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="R12" s="55">
+        <v>11111</v>
+      </c>
+      <c r="S12" s="56"/>
+      <c r="T12" s="57"/>
+      <c r="U12" s="58"/>
+      <c r="W12" s="49" t="s">
+        <v>19</v>
+      </c>
+      <c r="X12" s="50" t="s">
+        <v>138</v>
+      </c>
+      <c r="Y12" s="50" t="s">
+        <v>139</v>
+      </c>
+      <c r="Z12" s="51" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="2:26">
+      <c r="B13" s="52"/>
+      <c r="C13" s="53"/>
+      <c r="D13" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="E13" s="60" t="s">
+        <v>142</v>
+      </c>
+      <c r="F13" s="54"/>
+      <c r="G13" s="53"/>
+      <c r="H13" s="54"/>
+      <c r="I13" s="53"/>
+      <c r="J13" s="54"/>
+      <c r="K13" s="53"/>
+      <c r="L13" s="54"/>
+      <c r="M13" s="53"/>
+      <c r="N13" s="54" t="s">
+        <v>143</v>
+      </c>
+      <c r="O13" s="53" t="s">
+        <v>144</v>
+      </c>
+      <c r="P13" s="54" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q13" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="R13" s="55">
+        <v>11111</v>
+      </c>
+      <c r="S13" s="56"/>
+      <c r="T13" s="57"/>
+      <c r="U13" s="58"/>
+      <c r="W13" s="49"/>
+      <c r="X13" s="50"/>
+      <c r="Y13" s="50"/>
+      <c r="Z13" s="51"/>
+    </row>
+    <row r="14" customHeight="1" spans="2:26">
+      <c r="B14" s="52"/>
+      <c r="C14" s="53"/>
+      <c r="D14" s="54" t="s">
+        <v>145</v>
+      </c>
+      <c r="E14" s="60" t="s">
+        <v>146</v>
+      </c>
+      <c r="F14" s="61"/>
+      <c r="G14" s="53"/>
+      <c r="H14" s="54"/>
+      <c r="I14" s="53"/>
+      <c r="J14" s="54"/>
+      <c r="K14" s="53"/>
+      <c r="L14" s="54"/>
+      <c r="M14" s="53"/>
+      <c r="N14" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="O14" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="P14" s="54" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q14" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="R14" s="55">
+        <v>11111</v>
+      </c>
+      <c r="S14" s="56"/>
+      <c r="T14" s="57"/>
+      <c r="U14" s="58"/>
+      <c r="W14" s="49"/>
+      <c r="X14" s="50"/>
+      <c r="Y14" s="50"/>
+      <c r="Z14" s="51"/>
+    </row>
+    <row r="15" customHeight="1" spans="2:26">
+      <c r="B15" s="52"/>
+      <c r="C15" s="53"/>
+      <c r="D15" s="54" t="s">
+        <v>149</v>
+      </c>
+      <c r="E15" s="60" t="s">
+        <v>150</v>
+      </c>
+      <c r="F15" s="61"/>
+      <c r="G15" s="53"/>
+      <c r="H15" s="54"/>
+      <c r="I15" s="53"/>
+      <c r="J15" s="54"/>
+      <c r="K15" s="53"/>
+      <c r="L15" s="54"/>
+      <c r="M15" s="53"/>
+      <c r="N15" s="54" t="s">
         <v>91</v>
       </c>
-      <c r="X8" s="60" t="s">
-        <v>92</v>
-      </c>
-      <c r="Y8" s="60" t="s">
-        <v>93</v>
-      </c>
-      <c r="Z8" s="61" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="2:26">
-      <c r="B9" s="62" t="s">
-        <v>91</v>
-      </c>
-      <c r="C9" s="63" t="s">
-        <v>94</v>
-      </c>
-      <c r="D9" s="64" t="s">
-        <v>95</v>
-      </c>
-      <c r="E9" s="63" t="s">
-        <v>96</v>
-      </c>
-      <c r="F9" s="64" t="s">
-        <v>97</v>
-      </c>
-      <c r="G9" s="63" t="s">
-        <v>98</v>
-      </c>
-      <c r="H9" s="64" t="s">
-        <v>99</v>
-      </c>
-      <c r="I9" s="63" t="s">
-        <v>100</v>
-      </c>
-      <c r="J9" s="70"/>
-      <c r="K9" s="63"/>
-      <c r="L9" s="70"/>
-      <c r="M9" s="63"/>
-      <c r="N9" s="64" t="s">
-        <v>101</v>
-      </c>
-      <c r="O9" s="63" t="s">
+      <c r="O15" s="53" t="s">
+        <v>151</v>
+      </c>
+      <c r="P15" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q15" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="R15" s="55">
+        <v>11111</v>
+      </c>
+      <c r="S15" s="56"/>
+      <c r="T15" s="57"/>
+      <c r="U15" s="58"/>
+      <c r="W15" s="49"/>
+      <c r="X15" s="50"/>
+      <c r="Y15" s="50"/>
+      <c r="Z15" s="51"/>
+    </row>
+    <row r="16" customHeight="1" spans="2:26">
+      <c r="B16" s="52"/>
+      <c r="C16" s="53"/>
+      <c r="D16" s="54" t="s">
+        <v>152</v>
+      </c>
+      <c r="E16" s="60" t="s">
+        <v>153</v>
+      </c>
+      <c r="F16" s="61"/>
+      <c r="G16" s="53"/>
+      <c r="H16" s="54"/>
+      <c r="I16" s="53"/>
+      <c r="J16" s="54"/>
+      <c r="K16" s="53"/>
+      <c r="L16" s="54"/>
+      <c r="M16" s="53"/>
+      <c r="N16" s="54" t="s">
+        <v>77</v>
+      </c>
+      <c r="O16" s="53" t="s">
+        <v>154</v>
+      </c>
+      <c r="P16" s="54" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q16" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="R16" s="55">
+        <v>11111</v>
+      </c>
+      <c r="S16" s="56"/>
+      <c r="T16" s="57"/>
+      <c r="U16" s="58"/>
+      <c r="W16" s="49"/>
+      <c r="X16" s="50"/>
+      <c r="Y16" s="50"/>
+      <c r="Z16" s="51"/>
+    </row>
+    <row r="17" customHeight="1" spans="2:26">
+      <c r="B17" s="52"/>
+      <c r="C17" s="53"/>
+      <c r="D17" s="54" t="s">
+        <v>156</v>
+      </c>
+      <c r="E17" s="60" t="s">
+        <v>157</v>
+      </c>
+      <c r="F17" s="61"/>
+      <c r="G17" s="53"/>
+      <c r="H17" s="54"/>
+      <c r="I17" s="53"/>
+      <c r="J17" s="54"/>
+      <c r="K17" s="53"/>
+      <c r="L17" s="54"/>
+      <c r="M17" s="53"/>
+      <c r="N17" s="54" t="s">
+        <v>158</v>
+      </c>
+      <c r="O17" s="53" t="s">
+        <v>159</v>
+      </c>
+      <c r="P17" s="54" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q17" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="R17" s="55">
+        <v>11111</v>
+      </c>
+      <c r="S17" s="56"/>
+      <c r="T17" s="57"/>
+      <c r="U17" s="58"/>
+      <c r="W17" s="49"/>
+      <c r="X17" s="50"/>
+      <c r="Y17" s="50"/>
+      <c r="Z17" s="51"/>
+    </row>
+    <row r="18" customHeight="1" spans="2:26">
+      <c r="B18" s="52"/>
+      <c r="C18" s="53"/>
+      <c r="D18" s="54" t="s">
+        <v>42</v>
+      </c>
+      <c r="E18" s="60" t="s">
+        <v>160</v>
+      </c>
+      <c r="F18" s="61"/>
+      <c r="G18" s="53"/>
+      <c r="H18" s="54"/>
+      <c r="I18" s="53"/>
+      <c r="J18" s="54"/>
+      <c r="K18" s="53"/>
+      <c r="L18" s="54"/>
+      <c r="M18" s="53"/>
+      <c r="N18" s="54" t="s">
+        <v>161</v>
+      </c>
+      <c r="O18" s="53" t="s">
+        <v>162</v>
+      </c>
+      <c r="P18" s="54" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q18" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="R18" s="55">
+        <v>11111</v>
+      </c>
+      <c r="S18" s="56"/>
+      <c r="T18" s="57"/>
+      <c r="U18" s="58"/>
+      <c r="W18" s="49"/>
+      <c r="X18" s="50"/>
+      <c r="Y18" s="50"/>
+      <c r="Z18" s="51"/>
+    </row>
+    <row r="19" customHeight="1" spans="2:26">
+      <c r="B19" s="52"/>
+      <c r="C19" s="53"/>
+      <c r="D19" s="54"/>
+      <c r="E19" s="60"/>
+      <c r="F19" s="61"/>
+      <c r="G19" s="53"/>
+      <c r="H19" s="54"/>
+      <c r="I19" s="53"/>
+      <c r="J19" s="54"/>
+      <c r="K19" s="53"/>
+      <c r="L19" s="54"/>
+      <c r="M19" s="53"/>
+      <c r="N19" s="54" t="s">
+        <v>163</v>
+      </c>
+      <c r="O19" s="53" t="s">
+        <v>164</v>
+      </c>
+      <c r="P19" s="54" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q19" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="R19" s="55">
+        <v>11111</v>
+      </c>
+      <c r="S19" s="56"/>
+      <c r="T19" s="57"/>
+      <c r="U19" s="58"/>
+      <c r="W19" s="49"/>
+      <c r="X19" s="50"/>
+      <c r="Y19" s="50"/>
+      <c r="Z19" s="51"/>
+    </row>
+    <row r="20" customHeight="1" spans="2:26">
+      <c r="B20" s="52"/>
+      <c r="C20" s="53"/>
+      <c r="D20" s="54"/>
+      <c r="E20" s="60"/>
+      <c r="F20" s="61"/>
+      <c r="G20" s="53"/>
+      <c r="H20" s="54"/>
+      <c r="I20" s="53"/>
+      <c r="J20" s="54"/>
+      <c r="K20" s="53"/>
+      <c r="L20" s="54"/>
+      <c r="M20" s="53"/>
+      <c r="N20" s="59" t="s">
+        <v>166</v>
+      </c>
+      <c r="O20" s="53" t="s">
+        <v>167</v>
+      </c>
+      <c r="P20" s="54" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q20" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="R20" s="55">
+        <v>11111</v>
+      </c>
+      <c r="S20" s="56"/>
+      <c r="T20" s="57"/>
+      <c r="U20" s="58"/>
+      <c r="W20" s="49"/>
+      <c r="X20" s="50"/>
+      <c r="Y20" s="50"/>
+      <c r="Z20" s="51"/>
+    </row>
+    <row r="21" customHeight="1" spans="2:26">
+      <c r="B21" s="52"/>
+      <c r="C21" s="53"/>
+      <c r="D21" s="54"/>
+      <c r="E21" s="60"/>
+      <c r="F21" s="61"/>
+      <c r="G21" s="53"/>
+      <c r="H21" s="54"/>
+      <c r="I21" s="53"/>
+      <c r="J21" s="54"/>
+      <c r="K21" s="53"/>
+      <c r="L21" s="54"/>
+      <c r="M21" s="53"/>
+      <c r="N21" s="54" t="s">
+        <v>169</v>
+      </c>
+      <c r="O21" s="53" t="s">
+        <v>170</v>
+      </c>
+      <c r="P21" s="54" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q21" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="R21" s="55">
+        <v>11111</v>
+      </c>
+      <c r="S21" s="56"/>
+      <c r="T21" s="57"/>
+      <c r="U21" s="58"/>
+      <c r="W21" s="49"/>
+      <c r="X21" s="50"/>
+      <c r="Y21" s="50"/>
+      <c r="Z21" s="51"/>
+    </row>
+    <row r="22" customHeight="1" spans="2:26">
+      <c r="B22" s="52"/>
+      <c r="C22" s="53"/>
+      <c r="D22" s="54"/>
+      <c r="E22" s="60"/>
+      <c r="F22" s="61"/>
+      <c r="G22" s="53"/>
+      <c r="H22" s="54"/>
+      <c r="I22" s="53"/>
+      <c r="J22" s="54"/>
+      <c r="K22" s="53"/>
+      <c r="L22" s="54"/>
+      <c r="M22" s="53"/>
+      <c r="N22" s="54"/>
+      <c r="O22" s="53"/>
+      <c r="P22" s="54" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q22" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="R22" s="55">
+        <v>11111</v>
+      </c>
+      <c r="S22" s="56"/>
+      <c r="T22" s="57"/>
+      <c r="U22" s="58"/>
+      <c r="W22" s="49"/>
+      <c r="X22" s="50"/>
+      <c r="Y22" s="50"/>
+      <c r="Z22" s="51"/>
+    </row>
+    <row r="23" customHeight="1" spans="2:26">
+      <c r="B23" s="52"/>
+      <c r="C23" s="53"/>
+      <c r="D23" s="54"/>
+      <c r="E23" s="60"/>
+      <c r="F23" s="61"/>
+      <c r="G23" s="53"/>
+      <c r="H23" s="54"/>
+      <c r="I23" s="53"/>
+      <c r="J23" s="54"/>
+      <c r="K23" s="53"/>
+      <c r="L23" s="54"/>
+      <c r="M23" s="53"/>
+      <c r="N23" s="54"/>
+      <c r="O23" s="53"/>
+      <c r="P23" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="P9" s="64" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q9" s="63" t="s">
-        <v>37</v>
-      </c>
-      <c r="R9" s="65">
+      <c r="Q23" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="R23" s="55">
         <v>11111</v>
       </c>
-      <c r="S9" s="66"/>
-      <c r="T9" s="67"/>
-      <c r="U9" s="68"/>
-      <c r="W9" s="59" t="s">
-        <v>91</v>
-      </c>
-      <c r="X9" s="60" t="s">
-        <v>92</v>
-      </c>
-      <c r="Y9" s="60" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z9" s="61" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="10" customHeight="1" spans="2:26">
-      <c r="B10" s="62" t="s">
-        <v>106</v>
-      </c>
-      <c r="C10" s="63" t="s">
-        <v>107</v>
-      </c>
-      <c r="D10" s="64" t="s">
-        <v>108</v>
-      </c>
-      <c r="E10" s="63" t="s">
-        <v>109</v>
-      </c>
-      <c r="F10" s="64" t="s">
-        <v>110</v>
-      </c>
-      <c r="G10" s="63" t="s">
-        <v>111</v>
-      </c>
-      <c r="H10" s="64" t="s">
-        <v>55</v>
-      </c>
-      <c r="I10" s="63" t="s">
-        <v>112</v>
-      </c>
-      <c r="J10" s="70"/>
-      <c r="K10" s="63"/>
-      <c r="L10" s="70"/>
-      <c r="M10" s="63"/>
-      <c r="N10" s="64" t="s">
-        <v>113</v>
-      </c>
-      <c r="O10" s="63" t="s">
-        <v>114</v>
-      </c>
-      <c r="P10" s="69" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q10" s="63" t="s">
-        <v>37</v>
-      </c>
-      <c r="R10" s="65">
+      <c r="S23" s="56"/>
+      <c r="T23" s="57"/>
+      <c r="U23" s="58"/>
+      <c r="W23" s="49"/>
+      <c r="X23" s="50"/>
+      <c r="Y23" s="50"/>
+      <c r="Z23" s="51"/>
+    </row>
+    <row r="24" customHeight="1" spans="2:26">
+      <c r="B24" s="52"/>
+      <c r="C24" s="53"/>
+      <c r="D24" s="54"/>
+      <c r="E24" s="60"/>
+      <c r="F24" s="61"/>
+      <c r="G24" s="53"/>
+      <c r="H24" s="54"/>
+      <c r="I24" s="53"/>
+      <c r="J24" s="54"/>
+      <c r="K24" s="53"/>
+      <c r="L24" s="54"/>
+      <c r="M24" s="53"/>
+      <c r="N24" s="54"/>
+      <c r="O24" s="53"/>
+      <c r="P24" s="54" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q24" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="R24" s="55">
         <v>11111</v>
       </c>
-      <c r="S10" s="66"/>
-      <c r="T10" s="67"/>
-      <c r="U10" s="68"/>
-      <c r="W10" s="59" t="s">
-        <v>103</v>
-      </c>
-      <c r="X10" s="60" t="s">
-        <v>115</v>
-      </c>
-      <c r="Y10" s="60" t="s">
-        <v>116</v>
-      </c>
-      <c r="Z10" s="61" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="11" customHeight="1" spans="2:26">
-      <c r="B11" s="62" t="s">
-        <v>76</v>
-      </c>
-      <c r="C11" s="63" t="s">
-        <v>118</v>
-      </c>
-      <c r="D11" s="64" t="s">
-        <v>119</v>
-      </c>
-      <c r="E11" s="63" t="s">
-        <v>120</v>
-      </c>
-      <c r="F11" s="64" t="s">
-        <v>121</v>
-      </c>
-      <c r="G11" s="63" t="s">
-        <v>122</v>
-      </c>
-      <c r="H11" s="70"/>
-      <c r="I11" s="63"/>
-      <c r="J11" s="70"/>
-      <c r="K11" s="63"/>
-      <c r="L11" s="70"/>
-      <c r="M11" s="63"/>
-      <c r="N11" s="69" t="s">
-        <v>123</v>
-      </c>
-      <c r="O11" s="63" t="s">
-        <v>124</v>
-      </c>
-      <c r="P11" s="64" t="s">
-        <v>91</v>
-      </c>
-      <c r="Q11" s="63" t="s">
-        <v>125</v>
-      </c>
-      <c r="R11" s="65">
+      <c r="S24" s="56"/>
+      <c r="T24" s="57"/>
+      <c r="U24" s="58"/>
+      <c r="W24" s="49"/>
+      <c r="X24" s="50"/>
+      <c r="Y24" s="50"/>
+      <c r="Z24" s="51"/>
+    </row>
+    <row r="25" customHeight="1" spans="2:26">
+      <c r="B25" s="52"/>
+      <c r="C25" s="61"/>
+      <c r="D25" s="54"/>
+      <c r="E25" s="60"/>
+      <c r="F25" s="61"/>
+      <c r="G25" s="61"/>
+      <c r="H25" s="54"/>
+      <c r="I25" s="61"/>
+      <c r="J25" s="54"/>
+      <c r="K25" s="61"/>
+      <c r="L25" s="54"/>
+      <c r="M25" s="61"/>
+      <c r="N25" s="54"/>
+      <c r="O25" s="61"/>
+      <c r="P25" s="54" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q25" s="61" t="s">
+        <v>132</v>
+      </c>
+      <c r="R25" s="55">
         <v>11111</v>
       </c>
-      <c r="S11" s="66"/>
-      <c r="T11" s="67"/>
-      <c r="U11" s="68"/>
-      <c r="W11" s="59" t="s">
-        <v>106</v>
-      </c>
-      <c r="X11" s="60" t="s">
-        <v>92</v>
-      </c>
-      <c r="Y11" s="60" t="s">
-        <v>93</v>
-      </c>
-      <c r="Z11" s="61" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="12" customHeight="1" spans="2:26">
-      <c r="B12" s="71" t="s">
-        <v>103</v>
-      </c>
-      <c r="C12" s="63" t="s">
-        <v>127</v>
-      </c>
-      <c r="D12" s="64" t="s">
-        <v>91</v>
-      </c>
-      <c r="E12" s="72" t="s">
-        <v>128</v>
-      </c>
-      <c r="F12" s="70"/>
-      <c r="G12" s="63"/>
-      <c r="H12" s="70"/>
-      <c r="I12" s="63"/>
-      <c r="J12" s="70"/>
-      <c r="K12" s="63"/>
-      <c r="L12" s="70"/>
-      <c r="M12" s="63"/>
-      <c r="N12" s="69" t="s">
-        <v>129</v>
-      </c>
-      <c r="O12" s="63" t="s">
-        <v>130</v>
-      </c>
-      <c r="P12" s="64" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q12" s="63" t="s">
-        <v>125</v>
-      </c>
-      <c r="R12" s="65">
+      <c r="S25" s="56"/>
+      <c r="T25" s="57"/>
+      <c r="U25" s="58"/>
+    </row>
+    <row r="26" customHeight="1" spans="2:26">
+      <c r="B26" s="52"/>
+      <c r="C26" s="61"/>
+      <c r="D26" s="54"/>
+      <c r="E26" s="60"/>
+      <c r="F26" s="61"/>
+      <c r="G26" s="61"/>
+      <c r="H26" s="54"/>
+      <c r="I26" s="61"/>
+      <c r="J26" s="54"/>
+      <c r="K26" s="61"/>
+      <c r="L26" s="54"/>
+      <c r="M26" s="61"/>
+      <c r="N26" s="54"/>
+      <c r="O26" s="61"/>
+      <c r="P26" s="54" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q26" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="R26" s="55">
         <v>11111</v>
       </c>
-      <c r="S12" s="66"/>
-      <c r="T12" s="67"/>
-      <c r="U12" s="68"/>
-      <c r="W12" s="59" t="s">
-        <v>19</v>
-      </c>
-      <c r="X12" s="60" t="s">
-        <v>131</v>
-      </c>
-      <c r="Y12" s="60" t="s">
+      <c r="S26" s="56"/>
+      <c r="T26" s="57"/>
+      <c r="U26" s="58"/>
+    </row>
+    <row r="27" customHeight="1" spans="2:26">
+      <c r="B27" s="52"/>
+      <c r="C27" s="53"/>
+      <c r="D27" s="54"/>
+      <c r="E27" s="60"/>
+      <c r="F27" s="61"/>
+      <c r="G27" s="53"/>
+      <c r="H27" s="54"/>
+      <c r="I27" s="53"/>
+      <c r="J27" s="54"/>
+      <c r="K27" s="53"/>
+      <c r="L27" s="54"/>
+      <c r="M27" s="53"/>
+      <c r="N27" s="54"/>
+      <c r="O27" s="53"/>
+      <c r="P27" s="54" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q27" s="53" t="s">
         <v>132</v>
       </c>
-      <c r="Z12" s="61" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="2:26">
-      <c r="B13" s="71"/>
-      <c r="C13" s="63"/>
-      <c r="D13" s="64" t="s">
-        <v>134</v>
-      </c>
-      <c r="E13" s="72" t="s">
-        <v>135</v>
-      </c>
-      <c r="F13" s="70"/>
-      <c r="G13" s="63"/>
-      <c r="H13" s="70"/>
-      <c r="I13" s="63"/>
-      <c r="J13" s="70"/>
-      <c r="K13" s="63"/>
-      <c r="L13" s="70"/>
-      <c r="M13" s="63"/>
-      <c r="N13" s="64" t="s">
-        <v>136</v>
-      </c>
-      <c r="O13" s="63" t="s">
-        <v>137</v>
-      </c>
-      <c r="P13" s="64" t="s">
-        <v>110</v>
-      </c>
-      <c r="Q13" s="63" t="s">
-        <v>125</v>
-      </c>
-      <c r="R13" s="65">
+      <c r="R27" s="55">
         <v>11111</v>
       </c>
-      <c r="S13" s="66"/>
-      <c r="T13" s="67"/>
-      <c r="U13" s="68"/>
-      <c r="W13" s="59"/>
-      <c r="X13" s="60"/>
-      <c r="Y13" s="60"/>
-      <c r="Z13" s="61"/>
-    </row>
-    <row r="14" customHeight="1" spans="2:26">
-      <c r="B14" s="71"/>
-      <c r="C14" s="63"/>
-      <c r="D14" s="64" t="s">
-        <v>138</v>
-      </c>
-      <c r="E14" s="72" t="s">
-        <v>139</v>
-      </c>
-      <c r="F14" s="73"/>
-      <c r="G14" s="63"/>
-      <c r="H14" s="70"/>
-      <c r="I14" s="63"/>
-      <c r="J14" s="70"/>
-      <c r="K14" s="63"/>
-      <c r="L14" s="70"/>
-      <c r="M14" s="63"/>
-      <c r="N14" s="64" t="s">
-        <v>140</v>
-      </c>
-      <c r="O14" s="63" t="s">
+      <c r="S27" s="56"/>
+      <c r="T27" s="57"/>
+      <c r="U27" s="58"/>
+    </row>
+    <row r="28" customHeight="1" spans="2:26">
+      <c r="B28" s="52"/>
+      <c r="C28" s="53"/>
+      <c r="D28" s="54"/>
+      <c r="E28" s="60"/>
+      <c r="F28" s="61"/>
+      <c r="G28" s="53"/>
+      <c r="H28" s="54"/>
+      <c r="I28" s="53"/>
+      <c r="J28" s="54"/>
+      <c r="K28" s="53"/>
+      <c r="L28" s="54"/>
+      <c r="M28" s="53"/>
+      <c r="N28" s="54"/>
+      <c r="O28" s="53"/>
+      <c r="P28" s="54" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q28" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="R28" s="55">
+        <v>11111</v>
+      </c>
+      <c r="S28" s="56"/>
+      <c r="T28" s="57"/>
+      <c r="U28" s="58"/>
+    </row>
+    <row r="29" customHeight="1" spans="2:26">
+      <c r="B29" s="52"/>
+      <c r="C29" s="53"/>
+      <c r="D29" s="54"/>
+      <c r="E29" s="60"/>
+      <c r="F29" s="53"/>
+      <c r="G29" s="53"/>
+      <c r="H29" s="54"/>
+      <c r="I29" s="60"/>
+      <c r="J29" s="53"/>
+      <c r="K29" s="53"/>
+      <c r="L29" s="54"/>
+      <c r="M29" s="60"/>
+      <c r="N29" s="53"/>
+      <c r="O29" s="53"/>
+      <c r="P29" s="59" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q29" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="R29" s="55">
+        <v>11111</v>
+      </c>
+      <c r="S29" s="56"/>
+      <c r="T29" s="57"/>
+      <c r="U29" s="58"/>
+    </row>
+    <row r="30" customHeight="1" spans="2:26">
+      <c r="B30" s="52"/>
+      <c r="C30" s="53"/>
+      <c r="D30" s="54"/>
+      <c r="E30" s="60"/>
+      <c r="F30" s="53"/>
+      <c r="G30" s="53"/>
+      <c r="H30" s="54"/>
+      <c r="I30" s="60"/>
+      <c r="J30" s="53"/>
+      <c r="K30" s="53"/>
+      <c r="L30" s="54"/>
+      <c r="M30" s="60"/>
+      <c r="N30" s="53"/>
+      <c r="O30" s="53"/>
+      <c r="P30" s="54" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q30" s="53" t="s">
+        <v>172</v>
+      </c>
+      <c r="R30" s="55">
+        <v>11111</v>
+      </c>
+      <c r="S30" s="56"/>
+      <c r="T30" s="57"/>
+      <c r="U30" s="58"/>
+    </row>
+    <row r="31" customHeight="1" spans="2:26">
+      <c r="B31" s="52"/>
+      <c r="C31" s="53"/>
+      <c r="D31" s="54"/>
+      <c r="E31" s="60"/>
+      <c r="F31" s="53"/>
+      <c r="G31" s="53"/>
+      <c r="H31" s="54"/>
+      <c r="I31" s="60"/>
+      <c r="J31" s="53"/>
+      <c r="K31" s="53"/>
+      <c r="L31" s="54"/>
+      <c r="M31" s="60"/>
+      <c r="N31" s="53"/>
+      <c r="O31" s="53"/>
+      <c r="P31" s="59" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q31" s="53" t="s">
+        <v>172</v>
+      </c>
+      <c r="R31" s="55">
+        <v>11111</v>
+      </c>
+      <c r="S31" s="56"/>
+      <c r="T31" s="57"/>
+      <c r="U31" s="58"/>
+    </row>
+    <row r="32" customHeight="1" spans="2:26">
+      <c r="B32" s="52"/>
+      <c r="C32" s="53"/>
+      <c r="D32" s="54"/>
+      <c r="E32" s="60"/>
+      <c r="F32" s="53"/>
+      <c r="G32" s="53"/>
+      <c r="H32" s="54"/>
+      <c r="I32" s="60"/>
+      <c r="J32" s="53"/>
+      <c r="K32" s="53"/>
+      <c r="L32" s="54"/>
+      <c r="M32" s="60"/>
+      <c r="N32" s="53"/>
+      <c r="O32" s="53"/>
+      <c r="P32" s="54" t="s">
         <v>141</v>
       </c>
-      <c r="P14" s="64" t="s">
-        <v>108</v>
-      </c>
-      <c r="Q14" s="63" t="s">
-        <v>125</v>
-      </c>
-      <c r="R14" s="65">
+      <c r="Q32" s="53" t="s">
+        <v>172</v>
+      </c>
+      <c r="R32" s="55">
         <v>11111</v>
       </c>
-      <c r="S14" s="66"/>
-      <c r="T14" s="67"/>
-      <c r="U14" s="68"/>
-      <c r="W14" s="59"/>
-      <c r="X14" s="60"/>
-      <c r="Y14" s="60"/>
-      <c r="Z14" s="61"/>
-    </row>
-    <row r="15" customHeight="1" spans="2:26">
-      <c r="B15" s="71"/>
-      <c r="C15" s="63"/>
-      <c r="D15" s="64" t="s">
-        <v>142</v>
-      </c>
-      <c r="E15" s="72" t="s">
-        <v>143</v>
-      </c>
-      <c r="F15" s="73"/>
-      <c r="G15" s="63"/>
-      <c r="H15" s="70"/>
-      <c r="I15" s="63"/>
-      <c r="J15" s="70"/>
-      <c r="K15" s="63"/>
-      <c r="L15" s="70"/>
-      <c r="M15" s="63"/>
-      <c r="N15" s="64" t="s">
-        <v>90</v>
-      </c>
-      <c r="O15" s="63" t="s">
-        <v>144</v>
-      </c>
-      <c r="P15" s="64" t="s">
-        <v>140</v>
-      </c>
-      <c r="Q15" s="63" t="s">
-        <v>125</v>
-      </c>
-      <c r="R15" s="65">
+      <c r="S32" s="56"/>
+      <c r="T32" s="57"/>
+      <c r="U32" s="58"/>
+    </row>
+    <row r="33" customHeight="1" spans="2:21">
+      <c r="B33" s="52"/>
+      <c r="C33" s="53"/>
+      <c r="D33" s="54"/>
+      <c r="E33" s="60"/>
+      <c r="F33" s="53"/>
+      <c r="G33" s="53"/>
+      <c r="H33" s="54"/>
+      <c r="I33" s="60"/>
+      <c r="J33" s="53"/>
+      <c r="K33" s="53"/>
+      <c r="L33" s="54"/>
+      <c r="M33" s="60"/>
+      <c r="N33" s="53"/>
+      <c r="O33" s="53"/>
+      <c r="P33" s="54" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q33" s="53" t="s">
+        <v>172</v>
+      </c>
+      <c r="R33" s="55">
         <v>11111</v>
       </c>
-      <c r="S15" s="66"/>
-      <c r="T15" s="67"/>
-      <c r="U15" s="68"/>
-      <c r="W15" s="59"/>
-      <c r="X15" s="60"/>
-      <c r="Y15" s="60"/>
-      <c r="Z15" s="61"/>
-    </row>
-    <row r="16" customHeight="1" spans="2:26">
-      <c r="B16" s="71"/>
-      <c r="C16" s="63"/>
-      <c r="D16" s="64" t="s">
-        <v>145</v>
-      </c>
-      <c r="E16" s="72" t="s">
-        <v>146</v>
-      </c>
-      <c r="F16" s="73"/>
-      <c r="G16" s="63"/>
-      <c r="H16" s="70"/>
-      <c r="I16" s="63"/>
-      <c r="J16" s="70"/>
-      <c r="K16" s="63"/>
-      <c r="L16" s="70"/>
-      <c r="M16" s="63"/>
-      <c r="N16" s="64" t="s">
-        <v>76</v>
-      </c>
-      <c r="O16" s="63" t="s">
-        <v>147</v>
-      </c>
-      <c r="P16" s="64" t="s">
-        <v>148</v>
-      </c>
-      <c r="Q16" s="63" t="s">
-        <v>125</v>
-      </c>
-      <c r="R16" s="65">
+      <c r="S33" s="56"/>
+      <c r="T33" s="57"/>
+      <c r="U33" s="58"/>
+    </row>
+    <row r="34" customHeight="1" spans="2:21">
+      <c r="B34" s="52"/>
+      <c r="C34" s="53"/>
+      <c r="D34" s="54"/>
+      <c r="E34" s="60"/>
+      <c r="F34" s="53"/>
+      <c r="G34" s="53"/>
+      <c r="H34" s="54"/>
+      <c r="I34" s="60"/>
+      <c r="J34" s="53"/>
+      <c r="K34" s="53"/>
+      <c r="L34" s="54"/>
+      <c r="M34" s="60"/>
+      <c r="N34" s="53"/>
+      <c r="O34" s="53"/>
+      <c r="P34" s="54" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q34" s="53" t="s">
+        <v>172</v>
+      </c>
+      <c r="R34" s="55">
         <v>11111</v>
       </c>
-      <c r="S16" s="66"/>
-      <c r="T16" s="67"/>
-      <c r="U16" s="68"/>
-      <c r="W16" s="59"/>
-      <c r="X16" s="60"/>
-      <c r="Y16" s="60"/>
-      <c r="Z16" s="61"/>
-    </row>
-    <row r="17" customHeight="1" spans="2:26">
-      <c r="B17" s="71"/>
-      <c r="C17" s="63"/>
-      <c r="D17" s="64" t="s">
-        <v>149</v>
-      </c>
-      <c r="E17" s="72" t="s">
-        <v>150</v>
-      </c>
-      <c r="F17" s="73"/>
-      <c r="G17" s="63"/>
-      <c r="H17" s="70"/>
-      <c r="I17" s="63"/>
-      <c r="J17" s="70"/>
-      <c r="K17" s="63"/>
-      <c r="L17" s="70"/>
-      <c r="M17" s="63"/>
-      <c r="N17" s="64" t="s">
-        <v>151</v>
-      </c>
-      <c r="O17" s="63" t="s">
-        <v>152</v>
-      </c>
-      <c r="P17" s="64" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q17" s="63" t="s">
-        <v>125</v>
-      </c>
-      <c r="R17" s="65">
+      <c r="S34" s="56"/>
+      <c r="T34" s="57"/>
+      <c r="U34" s="58"/>
+    </row>
+    <row r="35" customHeight="1" spans="2:21">
+      <c r="B35" s="52"/>
+      <c r="C35" s="53"/>
+      <c r="D35" s="54"/>
+      <c r="E35" s="60"/>
+      <c r="F35" s="53"/>
+      <c r="G35" s="53"/>
+      <c r="H35" s="54"/>
+      <c r="I35" s="60"/>
+      <c r="J35" s="53"/>
+      <c r="K35" s="53"/>
+      <c r="L35" s="54"/>
+      <c r="M35" s="60"/>
+      <c r="N35" s="53"/>
+      <c r="O35" s="53"/>
+      <c r="P35" s="54" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q35" s="53" t="s">
+        <v>172</v>
+      </c>
+      <c r="R35" s="55">
         <v>11111</v>
       </c>
-      <c r="S17" s="66"/>
-      <c r="T17" s="67"/>
-      <c r="U17" s="68"/>
-      <c r="W17" s="59"/>
-      <c r="X17" s="60"/>
-      <c r="Y17" s="60"/>
-      <c r="Z17" s="61"/>
-    </row>
-    <row r="18" customHeight="1" spans="2:26">
-      <c r="B18" s="71"/>
-      <c r="C18" s="63"/>
-      <c r="D18" s="64" t="s">
-        <v>42</v>
-      </c>
-      <c r="E18" s="74" t="s">
-        <v>153</v>
-      </c>
-      <c r="F18" s="73"/>
-      <c r="G18" s="63"/>
-      <c r="H18" s="70"/>
-      <c r="I18" s="63"/>
-      <c r="J18" s="70"/>
-      <c r="K18" s="63"/>
-      <c r="L18" s="70"/>
-      <c r="M18" s="63"/>
-      <c r="N18" s="64" t="s">
-        <v>154</v>
-      </c>
-      <c r="O18" s="63" t="s">
-        <v>155</v>
-      </c>
-      <c r="P18" s="64" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q18" s="63" t="s">
-        <v>125</v>
-      </c>
-      <c r="R18" s="65">
-        <v>11111</v>
-      </c>
-      <c r="S18" s="66"/>
-      <c r="T18" s="67"/>
-      <c r="U18" s="68"/>
-      <c r="W18" s="59"/>
-      <c r="X18" s="60"/>
-      <c r="Y18" s="60"/>
-      <c r="Z18" s="61"/>
-    </row>
-    <row r="19" customHeight="1" spans="2:26">
-      <c r="B19" s="71"/>
-      <c r="C19" s="63"/>
-      <c r="D19" s="64"/>
-      <c r="E19" s="72"/>
-      <c r="F19" s="73"/>
-      <c r="G19" s="63"/>
-      <c r="H19" s="70"/>
-      <c r="I19" s="63"/>
-      <c r="J19" s="70"/>
-      <c r="K19" s="63"/>
-      <c r="L19" s="70"/>
-      <c r="M19" s="63"/>
-      <c r="N19" s="64" t="s">
-        <v>156</v>
-      </c>
-      <c r="O19" s="63" t="s">
-        <v>157</v>
-      </c>
-      <c r="P19" s="64" t="s">
-        <v>158</v>
-      </c>
-      <c r="Q19" s="63" t="s">
-        <v>125</v>
-      </c>
-      <c r="R19" s="65">
-        <v>11111</v>
-      </c>
-      <c r="S19" s="66"/>
-      <c r="T19" s="67"/>
-      <c r="U19" s="68"/>
-      <c r="W19" s="59"/>
-      <c r="X19" s="60"/>
-      <c r="Y19" s="60"/>
-      <c r="Z19" s="61"/>
-    </row>
-    <row r="20" customHeight="1" spans="2:26">
-      <c r="B20" s="71"/>
-      <c r="C20" s="63"/>
-      <c r="D20" s="64"/>
-      <c r="E20" s="72"/>
-      <c r="F20" s="73"/>
-      <c r="G20" s="63"/>
-      <c r="H20" s="70"/>
-      <c r="I20" s="63"/>
-      <c r="J20" s="70"/>
-      <c r="K20" s="63"/>
-      <c r="L20" s="70"/>
-      <c r="M20" s="63"/>
-      <c r="N20" s="69" t="s">
-        <v>159</v>
-      </c>
-      <c r="O20" s="63" t="s">
-        <v>160</v>
-      </c>
-      <c r="P20" s="64" t="s">
-        <v>161</v>
-      </c>
-      <c r="Q20" s="63" t="s">
-        <v>125</v>
-      </c>
-      <c r="R20" s="65">
-        <v>11111</v>
-      </c>
-      <c r="S20" s="66"/>
-      <c r="T20" s="67"/>
-      <c r="U20" s="68"/>
-      <c r="W20" s="59"/>
-      <c r="X20" s="60"/>
-      <c r="Y20" s="60"/>
-      <c r="Z20" s="61"/>
-    </row>
-    <row r="21" customHeight="1" spans="2:26">
-      <c r="B21" s="71"/>
-      <c r="C21" s="63"/>
-      <c r="D21" s="64"/>
-      <c r="E21" s="74"/>
-      <c r="F21" s="73"/>
-      <c r="G21" s="63"/>
-      <c r="H21" s="70"/>
-      <c r="I21" s="63"/>
-      <c r="J21" s="70"/>
-      <c r="K21" s="63"/>
-      <c r="L21" s="70"/>
-      <c r="M21" s="63"/>
-      <c r="N21" s="70"/>
-      <c r="O21" s="63"/>
-      <c r="P21" s="64" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q21" s="63" t="s">
-        <v>125</v>
-      </c>
-      <c r="R21" s="65">
-        <v>11111</v>
-      </c>
-      <c r="S21" s="66"/>
-      <c r="T21" s="67"/>
-      <c r="U21" s="68"/>
-      <c r="W21" s="59"/>
-      <c r="X21" s="60"/>
-      <c r="Y21" s="60"/>
-      <c r="Z21" s="61"/>
-    </row>
-    <row r="22" customHeight="1" spans="2:26">
-      <c r="B22" s="71"/>
-      <c r="C22" s="63"/>
-      <c r="D22" s="70"/>
-      <c r="E22" s="74"/>
-      <c r="F22" s="73"/>
-      <c r="G22" s="63"/>
-      <c r="H22" s="70"/>
-      <c r="I22" s="63"/>
-      <c r="J22" s="70"/>
-      <c r="K22" s="63"/>
-      <c r="L22" s="70"/>
-      <c r="M22" s="63"/>
-      <c r="N22" s="70"/>
-      <c r="O22" s="63"/>
-      <c r="P22" s="64" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q22" s="63" t="s">
-        <v>125</v>
-      </c>
-      <c r="R22" s="65">
-        <v>11111</v>
-      </c>
-      <c r="S22" s="66"/>
-      <c r="T22" s="67"/>
-      <c r="U22" s="68"/>
-      <c r="W22" s="59"/>
-      <c r="X22" s="60"/>
-      <c r="Y22" s="60"/>
-      <c r="Z22" s="61"/>
-    </row>
-    <row r="23" customHeight="1" spans="2:26">
-      <c r="B23" s="71"/>
-      <c r="C23" s="63"/>
-      <c r="D23" s="70"/>
-      <c r="E23" s="74"/>
-      <c r="F23" s="73"/>
-      <c r="G23" s="63"/>
-      <c r="H23" s="70"/>
-      <c r="I23" s="63"/>
-      <c r="J23" s="70"/>
-      <c r="K23" s="63"/>
-      <c r="L23" s="70"/>
-      <c r="M23" s="63"/>
-      <c r="N23" s="70"/>
-      <c r="O23" s="63"/>
-      <c r="P23" s="64" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q23" s="63" t="s">
-        <v>125</v>
-      </c>
-      <c r="R23" s="65">
-        <v>11111</v>
-      </c>
-      <c r="S23" s="66"/>
-      <c r="T23" s="67"/>
-      <c r="U23" s="68"/>
-      <c r="W23" s="59"/>
-      <c r="X23" s="60"/>
-      <c r="Y23" s="60"/>
-      <c r="Z23" s="61"/>
-    </row>
-    <row r="24" customHeight="1" spans="2:26">
-      <c r="B24" s="71"/>
-      <c r="C24" s="63"/>
-      <c r="D24" s="70"/>
-      <c r="E24" s="74"/>
-      <c r="F24" s="73"/>
-      <c r="G24" s="63"/>
-      <c r="H24" s="70"/>
-      <c r="I24" s="63"/>
-      <c r="J24" s="70"/>
-      <c r="K24" s="63"/>
-      <c r="L24" s="70"/>
-      <c r="M24" s="63"/>
-      <c r="N24" s="70"/>
-      <c r="O24" s="63"/>
-      <c r="P24" s="64" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q24" s="63" t="s">
-        <v>125</v>
-      </c>
-      <c r="R24" s="65">
-        <v>11111</v>
-      </c>
-      <c r="S24" s="66"/>
-      <c r="T24" s="67"/>
-      <c r="U24" s="68"/>
-      <c r="W24" s="59"/>
-      <c r="X24" s="60"/>
-      <c r="Y24" s="60"/>
-      <c r="Z24" s="61"/>
-    </row>
-    <row r="25" customHeight="1" spans="2:26">
-      <c r="B25" s="71"/>
-      <c r="C25" s="73"/>
-      <c r="D25" s="70"/>
-      <c r="E25" s="74"/>
-      <c r="F25" s="73"/>
-      <c r="G25" s="73"/>
-      <c r="H25" s="70"/>
-      <c r="I25" s="73"/>
-      <c r="J25" s="70"/>
-      <c r="K25" s="73"/>
-      <c r="L25" s="70"/>
-      <c r="M25" s="73"/>
-      <c r="N25" s="70"/>
-      <c r="O25" s="73"/>
-      <c r="P25" s="64" t="s">
-        <v>151</v>
-      </c>
-      <c r="Q25" s="75" t="s">
-        <v>125</v>
-      </c>
-      <c r="R25" s="65">
-        <v>11111</v>
-      </c>
-      <c r="S25" s="66"/>
-      <c r="T25" s="67"/>
-      <c r="U25" s="68"/>
-    </row>
-    <row r="26" customHeight="1" spans="2:26">
-      <c r="B26" s="76"/>
-      <c r="C26" s="75"/>
-      <c r="D26" s="77"/>
-      <c r="E26" s="74"/>
-      <c r="F26" s="73"/>
-      <c r="G26" s="75"/>
-      <c r="H26" s="70"/>
-      <c r="I26" s="75"/>
-      <c r="J26" s="70"/>
-      <c r="K26" s="75"/>
-      <c r="L26" s="70"/>
-      <c r="M26" s="75"/>
-      <c r="N26" s="70"/>
-      <c r="O26" s="75"/>
-      <c r="P26" s="64" t="s">
-        <v>162</v>
-      </c>
-      <c r="Q26" s="63" t="s">
-        <v>125</v>
-      </c>
-      <c r="R26" s="65">
-        <v>11111</v>
-      </c>
-      <c r="S26" s="66"/>
-      <c r="T26" s="67"/>
-      <c r="U26" s="68"/>
-    </row>
-    <row r="27" customHeight="1" spans="2:26">
-      <c r="B27" s="78"/>
-      <c r="C27" s="63"/>
-      <c r="D27" s="70"/>
-      <c r="E27" s="74"/>
-      <c r="F27" s="73"/>
-      <c r="G27" s="63"/>
-      <c r="H27" s="70"/>
-      <c r="I27" s="63"/>
-      <c r="J27" s="70"/>
-      <c r="K27" s="63"/>
-      <c r="L27" s="70"/>
-      <c r="M27" s="63"/>
-      <c r="N27" s="70"/>
-      <c r="O27" s="63"/>
-      <c r="P27" s="64" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q27" s="63" t="s">
-        <v>125</v>
-      </c>
-      <c r="R27" s="65">
-        <v>11111</v>
-      </c>
-      <c r="S27" s="66"/>
-      <c r="T27" s="67"/>
-      <c r="U27" s="68"/>
-    </row>
-    <row r="28" customHeight="1" spans="2:26">
-      <c r="B28" s="78"/>
-      <c r="C28" s="63"/>
-      <c r="D28" s="70"/>
-      <c r="E28" s="74"/>
-      <c r="F28" s="73"/>
-      <c r="G28" s="63"/>
-      <c r="H28" s="70"/>
-      <c r="I28" s="63"/>
-      <c r="J28" s="70"/>
-      <c r="K28" s="63"/>
-      <c r="L28" s="70"/>
-      <c r="M28" s="63"/>
-      <c r="N28" s="70"/>
-      <c r="O28" s="63"/>
-      <c r="P28" s="79" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q28" s="63" t="s">
-        <v>125</v>
-      </c>
-      <c r="R28" s="65">
-        <v>11111</v>
-      </c>
-      <c r="S28" s="66"/>
-      <c r="T28" s="67"/>
-      <c r="U28" s="68"/>
-    </row>
-    <row r="29" customHeight="1" spans="2:26">
-      <c r="B29" s="78"/>
-      <c r="C29" s="63"/>
-      <c r="D29" s="80"/>
-      <c r="E29" s="72"/>
-      <c r="F29" s="63"/>
-      <c r="G29" s="63"/>
-      <c r="H29" s="80"/>
-      <c r="I29" s="72"/>
-      <c r="J29" s="63"/>
-      <c r="K29" s="63"/>
-      <c r="L29" s="80"/>
-      <c r="M29" s="72"/>
-      <c r="N29" s="63"/>
-      <c r="O29" s="63"/>
-      <c r="P29" s="81" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q29" s="63" t="s">
-        <v>125</v>
-      </c>
-      <c r="R29" s="65">
-        <v>11111</v>
-      </c>
-      <c r="S29" s="66"/>
-      <c r="T29" s="67"/>
-      <c r="U29" s="68"/>
-    </row>
-    <row r="30" customHeight="1" spans="2:26">
-      <c r="B30" s="78"/>
-      <c r="C30" s="63"/>
-      <c r="D30" s="80"/>
-      <c r="E30" s="72"/>
-      <c r="F30" s="63"/>
-      <c r="G30" s="63"/>
-      <c r="H30" s="80"/>
-      <c r="I30" s="72"/>
-      <c r="J30" s="63"/>
-      <c r="K30" s="63"/>
-      <c r="L30" s="80"/>
-      <c r="M30" s="72"/>
-      <c r="N30" s="63"/>
-      <c r="O30" s="63"/>
-      <c r="P30" s="64" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q30" s="63" t="s">
-        <v>163</v>
-      </c>
-      <c r="R30" s="65">
-        <v>11111</v>
-      </c>
-      <c r="S30" s="66"/>
-      <c r="T30" s="67"/>
-      <c r="U30" s="68"/>
-    </row>
-    <row r="31" customHeight="1" spans="2:26">
-      <c r="B31" s="78"/>
-      <c r="C31" s="63"/>
-      <c r="D31" s="80"/>
-      <c r="E31" s="72"/>
-      <c r="F31" s="63"/>
-      <c r="G31" s="63"/>
-      <c r="H31" s="80"/>
-      <c r="I31" s="72"/>
-      <c r="J31" s="63"/>
-      <c r="K31" s="63"/>
-      <c r="L31" s="80"/>
-      <c r="M31" s="72"/>
-      <c r="N31" s="63"/>
-      <c r="O31" s="63"/>
-      <c r="P31" s="69" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q31" s="63" t="s">
-        <v>163</v>
-      </c>
-      <c r="R31" s="65">
-        <v>11111</v>
-      </c>
-      <c r="S31" s="66"/>
-      <c r="T31" s="67"/>
-      <c r="U31" s="68"/>
-    </row>
-    <row r="32" customHeight="1" spans="2:26">
-      <c r="B32" s="78"/>
-      <c r="C32" s="63"/>
-      <c r="D32" s="80"/>
-      <c r="E32" s="72"/>
-      <c r="F32" s="63"/>
-      <c r="G32" s="63"/>
-      <c r="H32" s="80"/>
-      <c r="I32" s="72"/>
-      <c r="J32" s="63"/>
-      <c r="K32" s="63"/>
-      <c r="L32" s="80"/>
-      <c r="M32" s="72"/>
-      <c r="N32" s="63"/>
-      <c r="O32" s="63"/>
-      <c r="P32" s="64" t="s">
-        <v>134</v>
-      </c>
-      <c r="Q32" s="63" t="s">
-        <v>163</v>
-      </c>
-      <c r="R32" s="65">
-        <v>11111</v>
-      </c>
-      <c r="S32" s="66"/>
-      <c r="T32" s="67"/>
-      <c r="U32" s="68"/>
-    </row>
-    <row r="33" customHeight="1" spans="2:21">
-      <c r="B33" s="78"/>
-      <c r="C33" s="63"/>
-      <c r="D33" s="80"/>
-      <c r="E33" s="72"/>
-      <c r="F33" s="63"/>
-      <c r="G33" s="63"/>
-      <c r="H33" s="80"/>
-      <c r="I33" s="72"/>
-      <c r="J33" s="63"/>
-      <c r="K33" s="63"/>
-      <c r="L33" s="80"/>
-      <c r="M33" s="72"/>
-      <c r="N33" s="63"/>
-      <c r="O33" s="63"/>
-      <c r="P33" s="64" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q33" s="63" t="s">
-        <v>163</v>
-      </c>
-      <c r="R33" s="65">
-        <v>11111</v>
-      </c>
-      <c r="S33" s="66"/>
-      <c r="T33" s="67"/>
-      <c r="U33" s="68"/>
-    </row>
-    <row r="34" customHeight="1" spans="2:21">
-      <c r="B34" s="78"/>
-      <c r="C34" s="63"/>
-      <c r="D34" s="80"/>
-      <c r="E34" s="72"/>
-      <c r="F34" s="63"/>
-      <c r="G34" s="63"/>
-      <c r="H34" s="80"/>
-      <c r="I34" s="72"/>
-      <c r="J34" s="63"/>
-      <c r="K34" s="63"/>
-      <c r="L34" s="80"/>
-      <c r="M34" s="72"/>
-      <c r="N34" s="63"/>
-      <c r="O34" s="63"/>
-      <c r="P34" s="64" t="s">
-        <v>154</v>
-      </c>
-      <c r="Q34" s="63" t="s">
-        <v>163</v>
-      </c>
-      <c r="R34" s="65">
-        <v>11111</v>
-      </c>
-      <c r="S34" s="66"/>
-      <c r="T34" s="67"/>
-      <c r="U34" s="68"/>
-    </row>
-    <row r="35" customHeight="1" spans="2:21">
-      <c r="B35" s="78"/>
-      <c r="C35" s="63"/>
-      <c r="D35" s="80"/>
-      <c r="E35" s="72"/>
-      <c r="F35" s="63"/>
-      <c r="G35" s="63"/>
-      <c r="H35" s="80"/>
-      <c r="I35" s="72"/>
-      <c r="J35" s="63"/>
-      <c r="K35" s="63"/>
-      <c r="L35" s="80"/>
-      <c r="M35" s="72"/>
-      <c r="N35" s="63"/>
-      <c r="O35" s="63"/>
-      <c r="P35" s="64" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q35" s="63" t="s">
-        <v>163</v>
-      </c>
-      <c r="R35" s="65">
-        <v>11111</v>
-      </c>
-      <c r="S35" s="66"/>
-      <c r="T35" s="67"/>
-      <c r="U35" s="68"/>
+      <c r="S35" s="56"/>
+      <c r="T35" s="57"/>
+      <c r="U35" s="58"/>
     </row>
     <row r="36" customHeight="1" spans="2:21">
-      <c r="B36" s="78"/>
-      <c r="C36" s="63"/>
-      <c r="D36" s="80"/>
-      <c r="E36" s="72"/>
-      <c r="F36" s="63"/>
-      <c r="G36" s="63"/>
-      <c r="H36" s="80"/>
-      <c r="I36" s="72"/>
-      <c r="J36" s="63"/>
-      <c r="K36" s="63"/>
-      <c r="L36" s="80"/>
-      <c r="M36" s="72"/>
-      <c r="N36" s="63"/>
-      <c r="O36" s="63"/>
-      <c r="P36" s="64"/>
-      <c r="Q36" s="63"/>
-      <c r="R36" s="65"/>
-      <c r="S36" s="66"/>
-      <c r="T36" s="67"/>
-      <c r="U36" s="68"/>
+      <c r="B36" s="52"/>
+      <c r="C36" s="53"/>
+      <c r="D36" s="54"/>
+      <c r="E36" s="60"/>
+      <c r="F36" s="53"/>
+      <c r="G36" s="53"/>
+      <c r="H36" s="54"/>
+      <c r="I36" s="60"/>
+      <c r="J36" s="53"/>
+      <c r="K36" s="53"/>
+      <c r="L36" s="54"/>
+      <c r="M36" s="60"/>
+      <c r="N36" s="53"/>
+      <c r="O36" s="53"/>
+      <c r="P36" s="54"/>
+      <c r="Q36" s="53"/>
+      <c r="R36" s="55"/>
+      <c r="S36" s="56"/>
+      <c r="T36" s="57"/>
+      <c r="U36" s="58"/>
     </row>
     <row r="37" customHeight="1" spans="2:21">
-      <c r="B37" s="82"/>
-      <c r="D37" s="83"/>
-      <c r="E37" s="84"/>
-      <c r="H37" s="83"/>
-      <c r="I37" s="84"/>
-      <c r="L37" s="83"/>
-      <c r="M37" s="84"/>
-      <c r="P37" s="83"/>
-      <c r="Q37" s="31"/>
-      <c r="R37" s="85"/>
-      <c r="S37" s="66"/>
-      <c r="T37" s="67"/>
-      <c r="U37" s="68"/>
+      <c r="B37" s="62"/>
+      <c r="D37" s="63"/>
+      <c r="E37" s="64"/>
+      <c r="H37" s="63"/>
+      <c r="I37" s="64"/>
+      <c r="L37" s="63"/>
+      <c r="M37" s="64"/>
+      <c r="P37" s="63"/>
+      <c r="R37" s="65"/>
+      <c r="S37" s="56"/>
+      <c r="T37" s="57"/>
+      <c r="U37" s="58"/>
     </row>
     <row r="38" customHeight="1" spans="2:21">
-      <c r="B38" s="82"/>
-      <c r="D38" s="83"/>
-      <c r="E38" s="84"/>
-      <c r="H38" s="83"/>
-      <c r="I38" s="84"/>
-      <c r="L38" s="83"/>
-      <c r="M38" s="84"/>
-      <c r="P38" s="83"/>
-      <c r="R38" s="85"/>
-      <c r="S38" s="66"/>
-      <c r="T38" s="67"/>
-      <c r="U38" s="68"/>
+      <c r="B38" s="62"/>
+      <c r="D38" s="63"/>
+      <c r="E38" s="64"/>
+      <c r="H38" s="63"/>
+      <c r="I38" s="64"/>
+      <c r="L38" s="63"/>
+      <c r="M38" s="64"/>
+      <c r="P38" s="63"/>
+      <c r="R38" s="65"/>
+      <c r="S38" s="56"/>
+      <c r="T38" s="57"/>
+      <c r="U38" s="58"/>
     </row>
     <row r="39" customHeight="1" spans="2:21">
-      <c r="B39" s="82"/>
-      <c r="D39" s="83"/>
-      <c r="E39" s="84"/>
-      <c r="H39" s="83"/>
-      <c r="I39" s="84"/>
-      <c r="L39" s="83"/>
-      <c r="M39" s="84"/>
-      <c r="P39" s="83"/>
-      <c r="R39" s="85"/>
-      <c r="S39" s="66"/>
-      <c r="T39" s="67"/>
-      <c r="U39" s="68"/>
+      <c r="B39" s="62"/>
+      <c r="D39" s="63"/>
+      <c r="E39" s="64"/>
+      <c r="H39" s="63"/>
+      <c r="I39" s="64"/>
+      <c r="L39" s="63"/>
+      <c r="M39" s="64"/>
+      <c r="P39" s="63"/>
+      <c r="R39" s="65"/>
+      <c r="S39" s="56"/>
+      <c r="T39" s="57"/>
+      <c r="U39" s="58"/>
     </row>
     <row r="40" customHeight="1" spans="2:21">
-      <c r="B40" s="82"/>
-      <c r="D40" s="83"/>
-      <c r="E40" s="84"/>
-      <c r="H40" s="83"/>
-      <c r="I40" s="84"/>
-      <c r="L40" s="83"/>
-      <c r="M40" s="84"/>
-      <c r="P40" s="83"/>
-      <c r="R40" s="85"/>
-      <c r="S40" s="66"/>
-      <c r="T40" s="67"/>
-      <c r="U40" s="68"/>
+      <c r="B40" s="62"/>
+      <c r="D40" s="63"/>
+      <c r="E40" s="64"/>
+      <c r="H40" s="63"/>
+      <c r="I40" s="64"/>
+      <c r="L40" s="63"/>
+      <c r="M40" s="64"/>
+      <c r="P40" s="63"/>
+      <c r="R40" s="65"/>
+      <c r="S40" s="56"/>
+      <c r="T40" s="57"/>
+      <c r="U40" s="58"/>
     </row>
     <row r="41" customHeight="1" spans="2:21">
-      <c r="B41" s="82"/>
-      <c r="D41" s="83"/>
-      <c r="E41" s="84"/>
-      <c r="H41" s="83"/>
-      <c r="I41" s="84"/>
-      <c r="L41" s="83"/>
-      <c r="M41" s="84"/>
-      <c r="P41" s="83"/>
-      <c r="R41" s="85"/>
-      <c r="S41" s="66"/>
-      <c r="T41" s="67"/>
-      <c r="U41" s="68"/>
+      <c r="B41" s="62"/>
+      <c r="D41" s="63"/>
+      <c r="E41" s="64"/>
+      <c r="H41" s="63"/>
+      <c r="I41" s="64"/>
+      <c r="L41" s="63"/>
+      <c r="M41" s="64"/>
+      <c r="P41" s="63"/>
+      <c r="R41" s="65"/>
+      <c r="S41" s="56"/>
+      <c r="T41" s="57"/>
+      <c r="U41" s="58"/>
     </row>
     <row r="42" customHeight="1" spans="2:21">
-      <c r="B42" s="82"/>
-      <c r="D42" s="83"/>
-      <c r="E42" s="84"/>
-      <c r="H42" s="83"/>
-      <c r="I42" s="84"/>
-      <c r="L42" s="83"/>
-      <c r="M42" s="84"/>
-      <c r="P42" s="83"/>
-      <c r="R42" s="85"/>
-      <c r="S42" s="66"/>
-      <c r="T42" s="67"/>
-      <c r="U42" s="68"/>
+      <c r="B42" s="62"/>
+      <c r="D42" s="63"/>
+      <c r="E42" s="64"/>
+      <c r="H42" s="63"/>
+      <c r="I42" s="64"/>
+      <c r="L42" s="63"/>
+      <c r="M42" s="64"/>
+      <c r="P42" s="63"/>
+      <c r="R42" s="65"/>
+      <c r="S42" s="56"/>
+      <c r="T42" s="57"/>
+      <c r="U42" s="58"/>
     </row>
     <row r="43" customHeight="1" spans="2:21">
-      <c r="B43" s="82"/>
-      <c r="D43" s="83"/>
-      <c r="E43" s="84"/>
-      <c r="H43" s="83"/>
-      <c r="I43" s="84"/>
-      <c r="L43" s="83"/>
-      <c r="M43" s="84"/>
-      <c r="P43" s="83"/>
-      <c r="R43" s="85"/>
-      <c r="S43" s="66"/>
-      <c r="T43" s="67"/>
-      <c r="U43" s="68"/>
+      <c r="B43" s="62"/>
+      <c r="D43" s="63"/>
+      <c r="E43" s="64"/>
+      <c r="H43" s="63"/>
+      <c r="I43" s="64"/>
+      <c r="L43" s="63"/>
+      <c r="M43" s="64"/>
+      <c r="P43" s="63"/>
+      <c r="R43" s="65"/>
+      <c r="S43" s="56"/>
+      <c r="T43" s="57"/>
+      <c r="U43" s="58"/>
     </row>
     <row r="44" customHeight="1" spans="2:21">
-      <c r="B44" s="82"/>
-      <c r="D44" s="83"/>
-      <c r="E44" s="84"/>
-      <c r="H44" s="83"/>
-      <c r="I44" s="84"/>
-      <c r="L44" s="83"/>
-      <c r="M44" s="84"/>
-      <c r="P44" s="83"/>
-      <c r="R44" s="85"/>
-      <c r="S44" s="66"/>
-      <c r="T44" s="67"/>
-      <c r="U44" s="68"/>
+      <c r="B44" s="62"/>
+      <c r="D44" s="63"/>
+      <c r="E44" s="64"/>
+      <c r="H44" s="63"/>
+      <c r="I44" s="64"/>
+      <c r="L44" s="63"/>
+      <c r="M44" s="64"/>
+      <c r="P44" s="63"/>
+      <c r="R44" s="65"/>
+      <c r="S44" s="56"/>
+      <c r="T44" s="57"/>
+      <c r="U44" s="58"/>
     </row>
     <row r="45" customHeight="1" spans="2:21">
-      <c r="B45" s="82"/>
-      <c r="D45" s="83"/>
-      <c r="E45" s="84"/>
-      <c r="H45" s="83"/>
-      <c r="I45" s="84"/>
-      <c r="L45" s="83"/>
-      <c r="M45" s="84"/>
-      <c r="P45" s="83"/>
-      <c r="R45" s="85"/>
-      <c r="S45" s="66"/>
-      <c r="T45" s="67"/>
-      <c r="U45" s="68"/>
+      <c r="B45" s="62"/>
+      <c r="D45" s="63"/>
+      <c r="E45" s="64"/>
+      <c r="H45" s="63"/>
+      <c r="I45" s="64"/>
+      <c r="L45" s="63"/>
+      <c r="M45" s="64"/>
+      <c r="P45" s="63"/>
+      <c r="R45" s="65"/>
+      <c r="S45" s="56"/>
+      <c r="T45" s="57"/>
+      <c r="U45" s="58"/>
     </row>
     <row r="46" customHeight="1" spans="2:21">
-      <c r="B46" s="82"/>
-      <c r="D46" s="83"/>
-      <c r="E46" s="84"/>
-      <c r="H46" s="83"/>
-      <c r="I46" s="84"/>
-      <c r="L46" s="83"/>
-      <c r="M46" s="84"/>
-      <c r="P46" s="83"/>
-      <c r="R46" s="85"/>
-      <c r="S46" s="66"/>
-      <c r="T46" s="67"/>
-      <c r="U46" s="68"/>
+      <c r="B46" s="62"/>
+      <c r="D46" s="63"/>
+      <c r="E46" s="64"/>
+      <c r="H46" s="63"/>
+      <c r="I46" s="64"/>
+      <c r="L46" s="63"/>
+      <c r="M46" s="64"/>
+      <c r="P46" s="63"/>
+      <c r="R46" s="65"/>
+      <c r="S46" s="56"/>
+      <c r="T46" s="57"/>
+      <c r="U46" s="58"/>
     </row>
     <row r="47" customHeight="1" spans="2:21">
-      <c r="B47" s="82"/>
-      <c r="D47" s="83"/>
-      <c r="E47" s="84"/>
-      <c r="H47" s="83"/>
-      <c r="I47" s="84"/>
-      <c r="L47" s="83"/>
-      <c r="M47" s="84"/>
-      <c r="P47" s="83"/>
-      <c r="R47" s="85"/>
-      <c r="S47" s="66"/>
-      <c r="T47" s="67"/>
-      <c r="U47" s="68"/>
+      <c r="B47" s="62"/>
+      <c r="D47" s="63"/>
+      <c r="E47" s="64"/>
+      <c r="H47" s="63"/>
+      <c r="I47" s="64"/>
+      <c r="L47" s="63"/>
+      <c r="M47" s="64"/>
+      <c r="P47" s="63"/>
+      <c r="R47" s="65"/>
+      <c r="S47" s="56"/>
+      <c r="T47" s="57"/>
+      <c r="U47" s="58"/>
     </row>
     <row r="48" customHeight="1" spans="2:21">
-      <c r="B48" s="82"/>
-      <c r="D48" s="83"/>
-      <c r="E48" s="84"/>
-      <c r="H48" s="83"/>
-      <c r="I48" s="84"/>
-      <c r="L48" s="83"/>
-      <c r="M48" s="84"/>
-      <c r="P48" s="83"/>
-      <c r="R48" s="85"/>
-      <c r="S48" s="66"/>
-      <c r="T48" s="67"/>
-      <c r="U48" s="68"/>
+      <c r="B48" s="62"/>
+      <c r="D48" s="63"/>
+      <c r="E48" s="64"/>
+      <c r="H48" s="63"/>
+      <c r="I48" s="64"/>
+      <c r="L48" s="63"/>
+      <c r="M48" s="64"/>
+      <c r="P48" s="63"/>
+      <c r="R48" s="65"/>
+      <c r="S48" s="56"/>
+      <c r="T48" s="57"/>
+      <c r="U48" s="58"/>
     </row>
     <row r="49" customHeight="1" spans="2:21">
-      <c r="B49" s="82"/>
-      <c r="D49" s="83"/>
-      <c r="E49" s="84"/>
-      <c r="H49" s="83"/>
-      <c r="I49" s="84"/>
-      <c r="L49" s="83"/>
-      <c r="M49" s="84"/>
-      <c r="P49" s="83"/>
-      <c r="R49" s="85"/>
-      <c r="S49" s="66"/>
-      <c r="T49" s="67"/>
-      <c r="U49" s="68"/>
+      <c r="B49" s="62"/>
+      <c r="D49" s="63"/>
+      <c r="E49" s="64"/>
+      <c r="H49" s="63"/>
+      <c r="I49" s="64"/>
+      <c r="L49" s="63"/>
+      <c r="M49" s="64"/>
+      <c r="P49" s="63"/>
+      <c r="R49" s="65"/>
+      <c r="S49" s="56"/>
+      <c r="T49" s="57"/>
+      <c r="U49" s="58"/>
     </row>
     <row r="50" customHeight="1" spans="2:21">
-      <c r="B50" s="82"/>
-      <c r="D50" s="83"/>
-      <c r="E50" s="84"/>
-      <c r="H50" s="83"/>
-      <c r="I50" s="84"/>
-      <c r="L50" s="83"/>
-      <c r="M50" s="84"/>
-      <c r="P50" s="83"/>
-      <c r="R50" s="85"/>
-      <c r="S50" s="66"/>
-      <c r="T50" s="67"/>
-      <c r="U50" s="68"/>
+      <c r="B50" s="62"/>
+      <c r="D50" s="63"/>
+      <c r="E50" s="64"/>
+      <c r="H50" s="63"/>
+      <c r="I50" s="64"/>
+      <c r="L50" s="63"/>
+      <c r="M50" s="64"/>
+      <c r="P50" s="63"/>
+      <c r="R50" s="65"/>
+      <c r="S50" s="56"/>
+      <c r="T50" s="57"/>
+      <c r="U50" s="58"/>
     </row>
     <row r="51" customHeight="1" spans="2:21">
-      <c r="B51" s="82"/>
-      <c r="D51" s="83"/>
-      <c r="E51" s="84"/>
-      <c r="H51" s="83"/>
-      <c r="I51" s="84"/>
-      <c r="L51" s="83"/>
-      <c r="M51" s="84"/>
-      <c r="P51" s="83"/>
-      <c r="R51" s="85"/>
-      <c r="S51" s="66"/>
-      <c r="T51" s="67"/>
-      <c r="U51" s="68"/>
+      <c r="B51" s="62"/>
+      <c r="D51" s="63"/>
+      <c r="E51" s="64"/>
+      <c r="H51" s="63"/>
+      <c r="I51" s="64"/>
+      <c r="L51" s="63"/>
+      <c r="M51" s="64"/>
+      <c r="P51" s="63"/>
+      <c r="R51" s="65"/>
+      <c r="S51" s="56"/>
+      <c r="T51" s="57"/>
+      <c r="U51" s="58"/>
     </row>
     <row r="52" customHeight="1" spans="2:21">
-      <c r="B52" s="82"/>
-      <c r="D52" s="83"/>
-      <c r="E52" s="84"/>
-      <c r="H52" s="83"/>
-      <c r="I52" s="84"/>
-      <c r="L52" s="83"/>
-      <c r="M52" s="84"/>
-      <c r="P52" s="83"/>
-      <c r="R52" s="85"/>
-      <c r="S52" s="66"/>
-      <c r="T52" s="67"/>
-      <c r="U52" s="68"/>
+      <c r="B52" s="62"/>
+      <c r="D52" s="63"/>
+      <c r="E52" s="64"/>
+      <c r="H52" s="63"/>
+      <c r="I52" s="64"/>
+      <c r="L52" s="63"/>
+      <c r="M52" s="64"/>
+      <c r="P52" s="63"/>
+      <c r="R52" s="65"/>
+      <c r="S52" s="56"/>
+      <c r="T52" s="57"/>
+      <c r="U52" s="58"/>
     </row>
     <row r="53" customHeight="1" spans="2:21">
-      <c r="B53" s="82"/>
-      <c r="D53" s="83"/>
-      <c r="E53" s="84"/>
-      <c r="H53" s="83"/>
-      <c r="I53" s="84"/>
-      <c r="L53" s="83"/>
-      <c r="M53" s="84"/>
-      <c r="P53" s="83"/>
-      <c r="R53" s="85"/>
-      <c r="S53" s="66"/>
-      <c r="T53" s="67"/>
-      <c r="U53" s="68"/>
+      <c r="B53" s="62"/>
+      <c r="D53" s="63"/>
+      <c r="E53" s="64"/>
+      <c r="H53" s="63"/>
+      <c r="I53" s="64"/>
+      <c r="L53" s="63"/>
+      <c r="M53" s="64"/>
+      <c r="P53" s="63"/>
+      <c r="R53" s="65"/>
+      <c r="S53" s="56"/>
+      <c r="T53" s="57"/>
+      <c r="U53" s="58"/>
     </row>
     <row r="54" customHeight="1" spans="2:21">
-      <c r="B54" s="82"/>
-      <c r="D54" s="83"/>
-      <c r="E54" s="84"/>
-      <c r="H54" s="83"/>
-      <c r="I54" s="84"/>
-      <c r="L54" s="83"/>
-      <c r="M54" s="84"/>
-      <c r="P54" s="83"/>
-      <c r="R54" s="85"/>
-      <c r="S54" s="66"/>
-      <c r="T54" s="67"/>
-      <c r="U54" s="68"/>
+      <c r="B54" s="62"/>
+      <c r="D54" s="63"/>
+      <c r="E54" s="64"/>
+      <c r="H54" s="63"/>
+      <c r="I54" s="64"/>
+      <c r="L54" s="63"/>
+      <c r="M54" s="64"/>
+      <c r="P54" s="63"/>
+      <c r="R54" s="65"/>
+      <c r="S54" s="56"/>
+      <c r="T54" s="57"/>
+      <c r="U54" s="58"/>
     </row>
     <row r="55" customHeight="1" spans="2:21">
-      <c r="B55" s="82"/>
-      <c r="D55" s="83"/>
-      <c r="E55" s="84"/>
-      <c r="H55" s="83"/>
-      <c r="I55" s="84"/>
-      <c r="L55" s="83"/>
-      <c r="M55" s="84"/>
-      <c r="P55" s="83"/>
-      <c r="R55" s="85"/>
-      <c r="S55" s="66"/>
-      <c r="T55" s="67"/>
-      <c r="U55" s="68"/>
+      <c r="B55" s="62"/>
+      <c r="D55" s="63"/>
+      <c r="E55" s="64"/>
+      <c r="H55" s="63"/>
+      <c r="I55" s="64"/>
+      <c r="L55" s="63"/>
+      <c r="M55" s="64"/>
+      <c r="P55" s="63"/>
+      <c r="R55" s="65"/>
+      <c r="S55" s="56"/>
+      <c r="T55" s="57"/>
+      <c r="U55" s="58"/>
     </row>
     <row r="56" customHeight="1" spans="2:21">
-      <c r="B56" s="82"/>
-      <c r="D56" s="83"/>
-      <c r="E56" s="84"/>
-      <c r="H56" s="83"/>
-      <c r="I56" s="84"/>
-      <c r="L56" s="83"/>
-      <c r="M56" s="84"/>
-      <c r="P56" s="83"/>
-      <c r="R56" s="85"/>
-      <c r="S56" s="66"/>
-      <c r="T56" s="67"/>
-      <c r="U56" s="68"/>
+      <c r="B56" s="62"/>
+      <c r="D56" s="63"/>
+      <c r="E56" s="64"/>
+      <c r="H56" s="63"/>
+      <c r="I56" s="64"/>
+      <c r="L56" s="63"/>
+      <c r="M56" s="64"/>
+      <c r="P56" s="63"/>
+      <c r="R56" s="65"/>
+      <c r="S56" s="56"/>
+      <c r="T56" s="57"/>
+      <c r="U56" s="58"/>
     </row>
     <row r="57" customHeight="1" spans="2:21">
-      <c r="B57" s="82"/>
-      <c r="D57" s="83"/>
-      <c r="E57" s="84"/>
-      <c r="H57" s="83"/>
-      <c r="I57" s="84"/>
-      <c r="L57" s="83"/>
-      <c r="M57" s="84"/>
-      <c r="P57" s="83"/>
-      <c r="R57" s="85"/>
-      <c r="S57" s="66"/>
-      <c r="T57" s="67"/>
-      <c r="U57" s="68"/>
+      <c r="B57" s="62"/>
+      <c r="D57" s="63"/>
+      <c r="E57" s="64"/>
+      <c r="H57" s="63"/>
+      <c r="I57" s="64"/>
+      <c r="L57" s="63"/>
+      <c r="M57" s="64"/>
+      <c r="P57" s="63"/>
+      <c r="R57" s="65"/>
+      <c r="S57" s="56"/>
+      <c r="T57" s="57"/>
+      <c r="U57" s="58"/>
     </row>
     <row r="58" customHeight="1" spans="2:21">
-      <c r="B58" s="82"/>
-      <c r="D58" s="83"/>
-      <c r="E58" s="84"/>
-      <c r="H58" s="83"/>
-      <c r="I58" s="84"/>
-      <c r="L58" s="83"/>
-      <c r="M58" s="84"/>
-      <c r="P58" s="83"/>
-      <c r="R58" s="85"/>
-      <c r="S58" s="66"/>
-      <c r="T58" s="67"/>
-      <c r="U58" s="68"/>
+      <c r="B58" s="62"/>
+      <c r="D58" s="63"/>
+      <c r="E58" s="64"/>
+      <c r="H58" s="63"/>
+      <c r="I58" s="64"/>
+      <c r="L58" s="63"/>
+      <c r="M58" s="64"/>
+      <c r="P58" s="63"/>
+      <c r="R58" s="65"/>
+      <c r="S58" s="56"/>
+      <c r="T58" s="57"/>
+      <c r="U58" s="58"/>
     </row>
     <row r="59" customHeight="1" spans="2:21">
-      <c r="B59" s="82"/>
-      <c r="D59" s="83"/>
-      <c r="E59" s="84"/>
-      <c r="H59" s="83"/>
-      <c r="I59" s="84"/>
-      <c r="L59" s="83"/>
-      <c r="M59" s="84"/>
-      <c r="P59" s="83"/>
-      <c r="R59" s="85"/>
-      <c r="S59" s="66"/>
-      <c r="T59" s="67"/>
-      <c r="U59" s="68"/>
+      <c r="B59" s="62"/>
+      <c r="D59" s="63"/>
+      <c r="E59" s="64"/>
+      <c r="H59" s="63"/>
+      <c r="I59" s="64"/>
+      <c r="L59" s="63"/>
+      <c r="M59" s="64"/>
+      <c r="P59" s="63"/>
+      <c r="R59" s="65"/>
+      <c r="S59" s="56"/>
+      <c r="T59" s="57"/>
+      <c r="U59" s="58"/>
     </row>
     <row r="60" customHeight="1" spans="2:21">
-      <c r="B60" s="82"/>
-      <c r="D60" s="83"/>
-      <c r="E60" s="84"/>
-      <c r="H60" s="83"/>
-      <c r="I60" s="84"/>
-      <c r="L60" s="83"/>
-      <c r="M60" s="84"/>
-      <c r="P60" s="83"/>
-      <c r="R60" s="85"/>
-      <c r="S60" s="66"/>
-      <c r="T60" s="67"/>
-      <c r="U60" s="68"/>
+      <c r="B60" s="62"/>
+      <c r="D60" s="63"/>
+      <c r="E60" s="64"/>
+      <c r="H60" s="63"/>
+      <c r="I60" s="64"/>
+      <c r="L60" s="63"/>
+      <c r="M60" s="64"/>
+      <c r="P60" s="63"/>
+      <c r="R60" s="65"/>
+      <c r="S60" s="56"/>
+      <c r="T60" s="57"/>
+      <c r="U60" s="58"/>
     </row>
     <row r="61" customHeight="1" spans="2:21">
-      <c r="B61" s="82"/>
-      <c r="D61" s="83"/>
-      <c r="E61" s="84"/>
-      <c r="H61" s="83"/>
-      <c r="I61" s="84"/>
-      <c r="L61" s="83"/>
-      <c r="M61" s="84"/>
-      <c r="P61" s="83"/>
-      <c r="R61" s="85"/>
-      <c r="S61" s="66"/>
-      <c r="T61" s="67"/>
-      <c r="U61" s="68"/>
+      <c r="B61" s="62"/>
+      <c r="D61" s="63"/>
+      <c r="E61" s="64"/>
+      <c r="H61" s="63"/>
+      <c r="I61" s="64"/>
+      <c r="L61" s="63"/>
+      <c r="M61" s="64"/>
+      <c r="P61" s="63"/>
+      <c r="R61" s="65"/>
+      <c r="S61" s="56"/>
+      <c r="T61" s="57"/>
+      <c r="U61" s="58"/>
     </row>
     <row r="62" customHeight="1" spans="2:21">
-      <c r="B62" s="82"/>
-      <c r="D62" s="83"/>
-      <c r="E62" s="84"/>
-      <c r="H62" s="83"/>
-      <c r="I62" s="84"/>
-      <c r="L62" s="83"/>
-      <c r="M62" s="84"/>
-      <c r="P62" s="83"/>
-      <c r="R62" s="85"/>
-      <c r="S62" s="66"/>
-      <c r="T62" s="67"/>
-      <c r="U62" s="68"/>
+      <c r="B62" s="62"/>
+      <c r="D62" s="63"/>
+      <c r="E62" s="64"/>
+      <c r="H62" s="63"/>
+      <c r="I62" s="64"/>
+      <c r="L62" s="63"/>
+      <c r="M62" s="64"/>
+      <c r="P62" s="63"/>
+      <c r="R62" s="65"/>
+      <c r="S62" s="56"/>
+      <c r="T62" s="57"/>
+      <c r="U62" s="58"/>
     </row>
     <row r="63" customHeight="1" spans="2:21">
-      <c r="B63" s="82"/>
-      <c r="D63" s="83"/>
-      <c r="E63" s="84"/>
-      <c r="H63" s="83"/>
-      <c r="I63" s="84"/>
-      <c r="L63" s="83"/>
-      <c r="M63" s="84"/>
-      <c r="P63" s="83"/>
-      <c r="R63" s="85"/>
-      <c r="S63" s="66"/>
-      <c r="T63" s="67"/>
-      <c r="U63" s="68"/>
+      <c r="B63" s="62"/>
+      <c r="D63" s="63"/>
+      <c r="E63" s="64"/>
+      <c r="H63" s="63"/>
+      <c r="I63" s="64"/>
+      <c r="L63" s="63"/>
+      <c r="M63" s="64"/>
+      <c r="P63" s="63"/>
+      <c r="R63" s="65"/>
+      <c r="S63" s="56"/>
+      <c r="T63" s="57"/>
+      <c r="U63" s="58"/>
     </row>
     <row r="64" customHeight="1" spans="2:21">
-      <c r="B64" s="82"/>
-      <c r="D64" s="83"/>
-      <c r="E64" s="84"/>
-      <c r="H64" s="83"/>
-      <c r="I64" s="84"/>
-      <c r="L64" s="83"/>
-      <c r="M64" s="84"/>
-      <c r="P64" s="83"/>
-      <c r="R64" s="85"/>
-      <c r="S64" s="66"/>
-      <c r="T64" s="67"/>
-      <c r="U64" s="68"/>
+      <c r="B64" s="62"/>
+      <c r="D64" s="63"/>
+      <c r="E64" s="64"/>
+      <c r="H64" s="63"/>
+      <c r="I64" s="64"/>
+      <c r="L64" s="63"/>
+      <c r="M64" s="64"/>
+      <c r="P64" s="63"/>
+      <c r="R64" s="65"/>
+      <c r="S64" s="56"/>
+      <c r="T64" s="57"/>
+      <c r="U64" s="58"/>
     </row>
     <row r="65" customHeight="1" spans="2:21">
-      <c r="B65" s="82"/>
-      <c r="D65" s="83"/>
-      <c r="E65" s="84"/>
-      <c r="H65" s="83"/>
-      <c r="I65" s="84"/>
-      <c r="L65" s="83"/>
-      <c r="M65" s="84"/>
-      <c r="P65" s="83"/>
-      <c r="R65" s="85"/>
-      <c r="S65" s="66"/>
-      <c r="T65" s="67"/>
-      <c r="U65" s="68"/>
+      <c r="B65" s="62"/>
+      <c r="D65" s="63"/>
+      <c r="E65" s="64"/>
+      <c r="H65" s="63"/>
+      <c r="I65" s="64"/>
+      <c r="L65" s="63"/>
+      <c r="M65" s="64"/>
+      <c r="P65" s="63"/>
+      <c r="R65" s="65"/>
+      <c r="S65" s="56"/>
+      <c r="T65" s="57"/>
+      <c r="U65" s="58"/>
     </row>
     <row r="66" customHeight="1" spans="2:21">
-      <c r="B66" s="82"/>
-      <c r="D66" s="83"/>
-      <c r="E66" s="84"/>
-      <c r="H66" s="83"/>
-      <c r="I66" s="84"/>
-      <c r="L66" s="83"/>
-      <c r="M66" s="84"/>
-      <c r="P66" s="83"/>
-      <c r="R66" s="85"/>
-      <c r="S66" s="66"/>
-      <c r="T66" s="67"/>
-      <c r="U66" s="68"/>
+      <c r="B66" s="62"/>
+      <c r="D66" s="63"/>
+      <c r="E66" s="64"/>
+      <c r="H66" s="63"/>
+      <c r="I66" s="64"/>
+      <c r="L66" s="63"/>
+      <c r="M66" s="64"/>
+      <c r="P66" s="63"/>
+      <c r="R66" s="65"/>
+      <c r="S66" s="56"/>
+      <c r="T66" s="57"/>
+      <c r="U66" s="58"/>
     </row>
     <row r="67" customHeight="1" spans="2:21">
-      <c r="B67" s="82"/>
-      <c r="D67" s="83"/>
-      <c r="E67" s="84"/>
-      <c r="H67" s="83"/>
-      <c r="I67" s="84"/>
-      <c r="L67" s="83"/>
-      <c r="M67" s="84"/>
-      <c r="P67" s="83"/>
-      <c r="R67" s="85"/>
-      <c r="S67" s="66"/>
-      <c r="T67" s="67"/>
-      <c r="U67" s="68"/>
+      <c r="B67" s="62"/>
+      <c r="D67" s="63"/>
+      <c r="E67" s="64"/>
+      <c r="H67" s="63"/>
+      <c r="I67" s="64"/>
+      <c r="L67" s="63"/>
+      <c r="M67" s="64"/>
+      <c r="P67" s="63"/>
+      <c r="R67" s="65"/>
+      <c r="S67" s="56"/>
+      <c r="T67" s="57"/>
+      <c r="U67" s="58"/>
     </row>
     <row r="68" customHeight="1" spans="2:21">
-      <c r="B68" s="82"/>
-      <c r="D68" s="83"/>
-      <c r="E68" s="84"/>
-      <c r="H68" s="83"/>
-      <c r="I68" s="84"/>
-      <c r="L68" s="83"/>
-      <c r="M68" s="84"/>
-      <c r="P68" s="83"/>
-      <c r="R68" s="85"/>
-      <c r="S68" s="66"/>
-      <c r="T68" s="67"/>
-      <c r="U68" s="68"/>
+      <c r="B68" s="62"/>
+      <c r="D68" s="63"/>
+      <c r="E68" s="64"/>
+      <c r="H68" s="63"/>
+      <c r="I68" s="64"/>
+      <c r="L68" s="63"/>
+      <c r="M68" s="64"/>
+      <c r="P68" s="63"/>
+      <c r="R68" s="65"/>
+      <c r="S68" s="56"/>
+      <c r="T68" s="57"/>
+      <c r="U68" s="58"/>
     </row>
     <row r="69" customHeight="1" spans="2:21">
-      <c r="B69" s="82"/>
-      <c r="D69" s="83"/>
-      <c r="E69" s="84"/>
-      <c r="H69" s="83"/>
-      <c r="I69" s="84"/>
-      <c r="L69" s="83"/>
-      <c r="M69" s="84"/>
-      <c r="P69" s="83"/>
-      <c r="R69" s="85"/>
-      <c r="S69" s="66"/>
-      <c r="T69" s="67"/>
-      <c r="U69" s="68"/>
+      <c r="B69" s="62"/>
+      <c r="D69" s="63"/>
+      <c r="E69" s="64"/>
+      <c r="H69" s="63"/>
+      <c r="I69" s="64"/>
+      <c r="L69" s="63"/>
+      <c r="M69" s="64"/>
+      <c r="P69" s="63"/>
+      <c r="R69" s="65"/>
+      <c r="S69" s="56"/>
+      <c r="T69" s="57"/>
+      <c r="U69" s="58"/>
     </row>
     <row r="70" customHeight="1" spans="2:21">
-      <c r="B70" s="82"/>
-      <c r="D70" s="83"/>
-      <c r="E70" s="84"/>
-      <c r="H70" s="83"/>
-      <c r="I70" s="84"/>
-      <c r="L70" s="83"/>
-      <c r="M70" s="84"/>
-      <c r="P70" s="83"/>
-      <c r="R70" s="85"/>
-      <c r="S70" s="66"/>
-      <c r="T70" s="67"/>
-      <c r="U70" s="68"/>
+      <c r="B70" s="62"/>
+      <c r="D70" s="63"/>
+      <c r="E70" s="64"/>
+      <c r="H70" s="63"/>
+      <c r="I70" s="64"/>
+      <c r="L70" s="63"/>
+      <c r="M70" s="64"/>
+      <c r="P70" s="63"/>
+      <c r="R70" s="65"/>
+      <c r="S70" s="56"/>
+      <c r="T70" s="57"/>
+      <c r="U70" s="58"/>
     </row>
     <row r="71" customHeight="1" spans="2:21">
-      <c r="B71" s="82"/>
-      <c r="D71" s="83"/>
-      <c r="E71" s="84"/>
-      <c r="H71" s="83"/>
-      <c r="I71" s="84"/>
-      <c r="L71" s="83"/>
-      <c r="M71" s="84"/>
-      <c r="P71" s="83"/>
-      <c r="R71" s="85"/>
-      <c r="S71" s="66"/>
-      <c r="T71" s="67"/>
-      <c r="U71" s="68"/>
+      <c r="B71" s="62"/>
+      <c r="D71" s="63"/>
+      <c r="E71" s="64"/>
+      <c r="H71" s="63"/>
+      <c r="I71" s="64"/>
+      <c r="L71" s="63"/>
+      <c r="M71" s="64"/>
+      <c r="P71" s="63"/>
+      <c r="R71" s="65"/>
+      <c r="S71" s="56"/>
+      <c r="T71" s="57"/>
+      <c r="U71" s="58"/>
     </row>
     <row r="72" customHeight="1" spans="2:21">
-      <c r="B72" s="82"/>
-      <c r="D72" s="83"/>
-      <c r="E72" s="84"/>
-      <c r="H72" s="83"/>
-      <c r="I72" s="84"/>
-      <c r="L72" s="83"/>
-      <c r="M72" s="84"/>
-      <c r="P72" s="83"/>
-      <c r="R72" s="85"/>
-      <c r="S72" s="66"/>
-      <c r="T72" s="67"/>
-      <c r="U72" s="68"/>
+      <c r="B72" s="62"/>
+      <c r="D72" s="63"/>
+      <c r="E72" s="64"/>
+      <c r="H72" s="63"/>
+      <c r="I72" s="64"/>
+      <c r="L72" s="63"/>
+      <c r="M72" s="64"/>
+      <c r="P72" s="63"/>
+      <c r="R72" s="65"/>
+      <c r="S72" s="56"/>
+      <c r="T72" s="57"/>
+      <c r="U72" s="58"/>
     </row>
     <row r="73" customHeight="1" spans="2:21">
-      <c r="B73" s="82"/>
-      <c r="D73" s="83"/>
-      <c r="E73" s="84"/>
-      <c r="H73" s="83"/>
-      <c r="I73" s="84"/>
-      <c r="L73" s="83"/>
-      <c r="M73" s="84"/>
-      <c r="P73" s="83"/>
-      <c r="R73" s="85"/>
-      <c r="S73" s="66"/>
-      <c r="T73" s="67"/>
-      <c r="U73" s="68"/>
+      <c r="B73" s="62"/>
+      <c r="D73" s="63"/>
+      <c r="E73" s="64"/>
+      <c r="H73" s="63"/>
+      <c r="I73" s="64"/>
+      <c r="L73" s="63"/>
+      <c r="M73" s="64"/>
+      <c r="P73" s="63"/>
+      <c r="R73" s="65"/>
+      <c r="S73" s="56"/>
+      <c r="T73" s="57"/>
+      <c r="U73" s="58"/>
     </row>
     <row r="74" customHeight="1" spans="2:21">
-      <c r="B74" s="82"/>
-      <c r="D74" s="83"/>
-      <c r="E74" s="84"/>
-      <c r="H74" s="83"/>
-      <c r="I74" s="84"/>
-      <c r="L74" s="83"/>
-      <c r="M74" s="84"/>
-      <c r="P74" s="83"/>
-      <c r="R74" s="85"/>
-      <c r="S74" s="66"/>
-      <c r="T74" s="67"/>
-      <c r="U74" s="68"/>
+      <c r="B74" s="62"/>
+      <c r="D74" s="63"/>
+      <c r="E74" s="64"/>
+      <c r="H74" s="63"/>
+      <c r="I74" s="64"/>
+      <c r="L74" s="63"/>
+      <c r="M74" s="64"/>
+      <c r="P74" s="63"/>
+      <c r="R74" s="65"/>
+      <c r="S74" s="56"/>
+      <c r="T74" s="57"/>
+      <c r="U74" s="58"/>
     </row>
     <row r="75" customHeight="1" spans="2:21">
-      <c r="B75" s="82"/>
-      <c r="D75" s="83"/>
-      <c r="E75" s="84"/>
-      <c r="H75" s="83"/>
-      <c r="I75" s="84"/>
-      <c r="L75" s="83"/>
-      <c r="M75" s="84"/>
-      <c r="P75" s="83"/>
-      <c r="R75" s="85"/>
-      <c r="S75" s="66"/>
-      <c r="T75" s="67"/>
-      <c r="U75" s="68"/>
+      <c r="B75" s="62"/>
+      <c r="D75" s="63"/>
+      <c r="E75" s="64"/>
+      <c r="H75" s="63"/>
+      <c r="I75" s="64"/>
+      <c r="L75" s="63"/>
+      <c r="M75" s="64"/>
+      <c r="P75" s="63"/>
+      <c r="R75" s="65"/>
+      <c r="S75" s="56"/>
+      <c r="T75" s="57"/>
+      <c r="U75" s="58"/>
     </row>
     <row r="76" customHeight="1" spans="2:21">
-      <c r="B76" s="82"/>
-      <c r="D76" s="83"/>
-      <c r="E76" s="84"/>
-      <c r="H76" s="83"/>
-      <c r="I76" s="84"/>
-      <c r="L76" s="83"/>
-      <c r="M76" s="84"/>
-      <c r="P76" s="83"/>
-      <c r="R76" s="85"/>
-      <c r="S76" s="66"/>
-      <c r="T76" s="67"/>
-      <c r="U76" s="68"/>
+      <c r="B76" s="62"/>
+      <c r="D76" s="63"/>
+      <c r="E76" s="64"/>
+      <c r="H76" s="63"/>
+      <c r="I76" s="64"/>
+      <c r="L76" s="63"/>
+      <c r="M76" s="64"/>
+      <c r="P76" s="63"/>
+      <c r="R76" s="65"/>
+      <c r="S76" s="56"/>
+      <c r="T76" s="57"/>
+      <c r="U76" s="58"/>
     </row>
     <row r="77" customHeight="1" spans="2:21">
-      <c r="B77" s="82"/>
-      <c r="D77" s="83"/>
-      <c r="E77" s="84"/>
-      <c r="H77" s="83"/>
-      <c r="I77" s="84"/>
-      <c r="L77" s="83"/>
-      <c r="M77" s="84"/>
-      <c r="P77" s="83"/>
-      <c r="R77" s="85"/>
-      <c r="S77" s="66"/>
-      <c r="T77" s="67"/>
-      <c r="U77" s="68"/>
+      <c r="B77" s="62"/>
+      <c r="D77" s="63"/>
+      <c r="E77" s="64"/>
+      <c r="H77" s="63"/>
+      <c r="I77" s="64"/>
+      <c r="L77" s="63"/>
+      <c r="M77" s="64"/>
+      <c r="P77" s="63"/>
+      <c r="R77" s="65"/>
+      <c r="S77" s="56"/>
+      <c r="T77" s="57"/>
+      <c r="U77" s="58"/>
     </row>
     <row r="78" customHeight="1" spans="2:21">
-      <c r="B78" s="82"/>
-      <c r="D78" s="83"/>
-      <c r="E78" s="84"/>
-      <c r="H78" s="83"/>
-      <c r="I78" s="84"/>
-      <c r="L78" s="83"/>
-      <c r="M78" s="84"/>
-      <c r="P78" s="83"/>
-      <c r="R78" s="85"/>
-      <c r="S78" s="66"/>
-      <c r="T78" s="67"/>
-      <c r="U78" s="68"/>
+      <c r="B78" s="62"/>
+      <c r="D78" s="63"/>
+      <c r="E78" s="64"/>
+      <c r="H78" s="63"/>
+      <c r="I78" s="64"/>
+      <c r="L78" s="63"/>
+      <c r="M78" s="64"/>
+      <c r="P78" s="63"/>
+      <c r="R78" s="65"/>
+      <c r="S78" s="56"/>
+      <c r="T78" s="57"/>
+      <c r="U78" s="58"/>
     </row>
     <row r="79" customHeight="1" spans="2:21">
-      <c r="B79" s="82"/>
-      <c r="D79" s="83"/>
-      <c r="E79" s="84"/>
-      <c r="H79" s="83"/>
-      <c r="I79" s="84"/>
-      <c r="L79" s="83"/>
-      <c r="M79" s="84"/>
-      <c r="P79" s="83"/>
-      <c r="R79" s="85"/>
-      <c r="S79" s="66"/>
-      <c r="T79" s="67"/>
-      <c r="U79" s="68"/>
+      <c r="B79" s="62"/>
+      <c r="D79" s="63"/>
+      <c r="E79" s="64"/>
+      <c r="H79" s="63"/>
+      <c r="I79" s="64"/>
+      <c r="L79" s="63"/>
+      <c r="M79" s="64"/>
+      <c r="P79" s="63"/>
+      <c r="R79" s="65"/>
+      <c r="S79" s="56"/>
+      <c r="T79" s="57"/>
+      <c r="U79" s="58"/>
     </row>
     <row r="80" customHeight="1" spans="2:21">
-      <c r="B80" s="82"/>
-      <c r="D80" s="83"/>
-      <c r="E80" s="84"/>
-      <c r="H80" s="83"/>
-      <c r="I80" s="84"/>
-      <c r="L80" s="83"/>
-      <c r="M80" s="84"/>
-      <c r="P80" s="83"/>
-      <c r="R80" s="85"/>
-      <c r="S80" s="66"/>
-      <c r="T80" s="67"/>
-      <c r="U80" s="68"/>
+      <c r="B80" s="62"/>
+      <c r="D80" s="63"/>
+      <c r="E80" s="64"/>
+      <c r="H80" s="63"/>
+      <c r="I80" s="64"/>
+      <c r="L80" s="63"/>
+      <c r="M80" s="64"/>
+      <c r="P80" s="63"/>
+      <c r="R80" s="65"/>
+      <c r="S80" s="56"/>
+      <c r="T80" s="57"/>
+      <c r="U80" s="58"/>
     </row>
     <row r="81" customHeight="1" spans="2:21">
-      <c r="B81" s="82"/>
-      <c r="D81" s="83"/>
-      <c r="E81" s="84"/>
-      <c r="H81" s="83"/>
-      <c r="I81" s="84"/>
-      <c r="L81" s="83"/>
-      <c r="M81" s="84"/>
-      <c r="P81" s="83"/>
-      <c r="R81" s="85"/>
-      <c r="S81" s="66"/>
-      <c r="T81" s="67"/>
-      <c r="U81" s="68"/>
+      <c r="B81" s="62"/>
+      <c r="D81" s="63"/>
+      <c r="E81" s="64"/>
+      <c r="H81" s="63"/>
+      <c r="I81" s="64"/>
+      <c r="L81" s="63"/>
+      <c r="M81" s="64"/>
+      <c r="P81" s="63"/>
+      <c r="R81" s="65"/>
+      <c r="S81" s="56"/>
+      <c r="T81" s="57"/>
+      <c r="U81" s="58"/>
     </row>
     <row r="82" customHeight="1" spans="2:21">
-      <c r="B82" s="82"/>
-      <c r="D82" s="83"/>
-      <c r="E82" s="84"/>
-      <c r="H82" s="83"/>
-      <c r="I82" s="84"/>
-      <c r="L82" s="83"/>
-      <c r="M82" s="84"/>
-      <c r="P82" s="83"/>
-      <c r="R82" s="85"/>
-      <c r="S82" s="66"/>
-      <c r="T82" s="67"/>
-      <c r="U82" s="68"/>
+      <c r="B82" s="62"/>
+      <c r="D82" s="63"/>
+      <c r="E82" s="64"/>
+      <c r="H82" s="63"/>
+      <c r="I82" s="64"/>
+      <c r="L82" s="63"/>
+      <c r="M82" s="64"/>
+      <c r="P82" s="63"/>
+      <c r="R82" s="65"/>
+      <c r="S82" s="56"/>
+      <c r="T82" s="57"/>
+      <c r="U82" s="58"/>
     </row>
     <row r="83" customHeight="1" spans="2:21">
-      <c r="B83" s="82"/>
-      <c r="D83" s="83"/>
-      <c r="E83" s="84"/>
-      <c r="H83" s="83"/>
-      <c r="I83" s="84"/>
-      <c r="L83" s="83"/>
-      <c r="M83" s="84"/>
-      <c r="P83" s="83"/>
-      <c r="R83" s="85"/>
-      <c r="S83" s="66"/>
-      <c r="T83" s="67"/>
-      <c r="U83" s="68"/>
+      <c r="B83" s="62"/>
+      <c r="D83" s="63"/>
+      <c r="E83" s="64"/>
+      <c r="H83" s="63"/>
+      <c r="I83" s="64"/>
+      <c r="L83" s="63"/>
+      <c r="M83" s="64"/>
+      <c r="P83" s="63"/>
+      <c r="R83" s="65"/>
+      <c r="S83" s="56"/>
+      <c r="T83" s="57"/>
+      <c r="U83" s="58"/>
     </row>
     <row r="84" customHeight="1" spans="2:21">
-      <c r="B84" s="82"/>
-      <c r="D84" s="83"/>
-      <c r="E84" s="84"/>
-      <c r="H84" s="83"/>
-      <c r="I84" s="84"/>
-      <c r="L84" s="83"/>
-      <c r="M84" s="84"/>
-      <c r="P84" s="83"/>
-      <c r="R84" s="85"/>
-      <c r="S84" s="66"/>
-      <c r="T84" s="67"/>
-      <c r="U84" s="68"/>
+      <c r="B84" s="62"/>
+      <c r="D84" s="63"/>
+      <c r="E84" s="64"/>
+      <c r="H84" s="63"/>
+      <c r="I84" s="64"/>
+      <c r="L84" s="63"/>
+      <c r="M84" s="64"/>
+      <c r="P84" s="63"/>
+      <c r="R84" s="65"/>
+      <c r="S84" s="56"/>
+      <c r="T84" s="57"/>
+      <c r="U84" s="58"/>
     </row>
     <row r="85" customHeight="1" spans="2:21">
-      <c r="B85" s="82"/>
-      <c r="D85" s="83"/>
-      <c r="E85" s="84"/>
-      <c r="H85" s="83"/>
-      <c r="I85" s="84"/>
-      <c r="L85" s="83"/>
-      <c r="M85" s="84"/>
-      <c r="P85" s="83"/>
-      <c r="R85" s="85"/>
-      <c r="S85" s="66"/>
-      <c r="T85" s="67"/>
-      <c r="U85" s="68"/>
+      <c r="B85" s="62"/>
+      <c r="D85" s="63"/>
+      <c r="E85" s="64"/>
+      <c r="H85" s="63"/>
+      <c r="I85" s="64"/>
+      <c r="L85" s="63"/>
+      <c r="M85" s="64"/>
+      <c r="P85" s="63"/>
+      <c r="R85" s="65"/>
+      <c r="S85" s="56"/>
+      <c r="T85" s="57"/>
+      <c r="U85" s="58"/>
     </row>
     <row r="86" customHeight="1" spans="2:21">
-      <c r="B86" s="82"/>
-      <c r="D86" s="83"/>
-      <c r="E86" s="84"/>
-      <c r="H86" s="83"/>
-      <c r="I86" s="84"/>
-      <c r="L86" s="83"/>
-      <c r="M86" s="84"/>
-      <c r="P86" s="83"/>
-      <c r="R86" s="85"/>
-      <c r="S86" s="66"/>
-      <c r="T86" s="67"/>
-      <c r="U86" s="68"/>
+      <c r="B86" s="62"/>
+      <c r="D86" s="63"/>
+      <c r="E86" s="64"/>
+      <c r="H86" s="63"/>
+      <c r="I86" s="64"/>
+      <c r="L86" s="63"/>
+      <c r="M86" s="64"/>
+      <c r="P86" s="63"/>
+      <c r="R86" s="65"/>
+      <c r="S86" s="56"/>
+      <c r="T86" s="57"/>
+      <c r="U86" s="58"/>
     </row>
     <row r="87" customHeight="1" spans="2:21">
-      <c r="B87" s="82"/>
-      <c r="D87" s="83"/>
-      <c r="E87" s="84"/>
-      <c r="H87" s="83"/>
-      <c r="I87" s="84"/>
-      <c r="L87" s="83"/>
-      <c r="M87" s="84"/>
-      <c r="P87" s="83"/>
-      <c r="R87" s="85"/>
-      <c r="S87" s="66"/>
-      <c r="T87" s="67"/>
-      <c r="U87" s="68"/>
+      <c r="B87" s="62"/>
+      <c r="D87" s="63"/>
+      <c r="E87" s="64"/>
+      <c r="H87" s="63"/>
+      <c r="I87" s="64"/>
+      <c r="L87" s="63"/>
+      <c r="M87" s="64"/>
+      <c r="P87" s="63"/>
+      <c r="R87" s="65"/>
+      <c r="S87" s="56"/>
+      <c r="T87" s="57"/>
+      <c r="U87" s="58"/>
     </row>
     <row r="88" customHeight="1" spans="2:21">
-      <c r="B88" s="82"/>
-      <c r="D88" s="83"/>
-      <c r="E88" s="84"/>
-      <c r="H88" s="83"/>
-      <c r="I88" s="84"/>
-      <c r="L88" s="83"/>
-      <c r="M88" s="84"/>
-      <c r="P88" s="83"/>
-      <c r="R88" s="85"/>
-      <c r="S88" s="66"/>
-      <c r="T88" s="67"/>
-      <c r="U88" s="68"/>
+      <c r="B88" s="62"/>
+      <c r="D88" s="63"/>
+      <c r="E88" s="64"/>
+      <c r="H88" s="63"/>
+      <c r="I88" s="64"/>
+      <c r="L88" s="63"/>
+      <c r="M88" s="64"/>
+      <c r="P88" s="63"/>
+      <c r="R88" s="65"/>
+      <c r="S88" s="56"/>
+      <c r="T88" s="57"/>
+      <c r="U88" s="58"/>
     </row>
     <row r="89" customHeight="1" spans="2:21">
-      <c r="B89" s="82"/>
-      <c r="D89" s="83"/>
-      <c r="E89" s="84"/>
-      <c r="H89" s="83"/>
-      <c r="I89" s="84"/>
-      <c r="L89" s="83"/>
-      <c r="M89" s="84"/>
-      <c r="P89" s="83"/>
-      <c r="R89" s="85"/>
-      <c r="S89" s="66"/>
-      <c r="T89" s="67"/>
-      <c r="U89" s="68"/>
+      <c r="B89" s="62"/>
+      <c r="D89" s="63"/>
+      <c r="E89" s="64"/>
+      <c r="H89" s="63"/>
+      <c r="I89" s="64"/>
+      <c r="L89" s="63"/>
+      <c r="M89" s="64"/>
+      <c r="P89" s="63"/>
+      <c r="R89" s="65"/>
+      <c r="S89" s="56"/>
+      <c r="T89" s="57"/>
+      <c r="U89" s="58"/>
     </row>
     <row r="90" customHeight="1" spans="2:21">
-      <c r="B90" s="82"/>
-      <c r="D90" s="83"/>
-      <c r="E90" s="84"/>
-      <c r="H90" s="83"/>
-      <c r="I90" s="84"/>
-      <c r="L90" s="83"/>
-      <c r="M90" s="84"/>
-      <c r="P90" s="83"/>
-      <c r="R90" s="85"/>
-      <c r="S90" s="66"/>
-      <c r="T90" s="67"/>
-      <c r="U90" s="68"/>
+      <c r="B90" s="62"/>
+      <c r="D90" s="63"/>
+      <c r="E90" s="64"/>
+      <c r="H90" s="63"/>
+      <c r="I90" s="64"/>
+      <c r="L90" s="63"/>
+      <c r="M90" s="64"/>
+      <c r="P90" s="63"/>
+      <c r="R90" s="65"/>
+      <c r="S90" s="56"/>
+      <c r="T90" s="57"/>
+      <c r="U90" s="58"/>
     </row>
     <row r="91" customHeight="1" spans="2:21">
-      <c r="B91" s="82"/>
-      <c r="D91" s="83"/>
-      <c r="E91" s="84"/>
-      <c r="H91" s="83"/>
-      <c r="I91" s="84"/>
-      <c r="L91" s="83"/>
-      <c r="M91" s="84"/>
-      <c r="P91" s="83"/>
-      <c r="R91" s="85"/>
-      <c r="S91" s="66"/>
-      <c r="T91" s="67"/>
-      <c r="U91" s="68"/>
+      <c r="B91" s="62"/>
+      <c r="D91" s="63"/>
+      <c r="E91" s="64"/>
+      <c r="H91" s="63"/>
+      <c r="I91" s="64"/>
+      <c r="L91" s="63"/>
+      <c r="M91" s="64"/>
+      <c r="P91" s="63"/>
+      <c r="R91" s="65"/>
+      <c r="S91" s="56"/>
+      <c r="T91" s="57"/>
+      <c r="U91" s="58"/>
     </row>
     <row r="92" customHeight="1" spans="2:21">
-      <c r="B92" s="82"/>
-      <c r="D92" s="83"/>
-      <c r="E92" s="84"/>
-      <c r="H92" s="83"/>
-      <c r="I92" s="84"/>
-      <c r="L92" s="83"/>
-      <c r="M92" s="84"/>
-      <c r="P92" s="83"/>
-      <c r="R92" s="85"/>
-      <c r="S92" s="66"/>
-      <c r="T92" s="67"/>
-      <c r="U92" s="68"/>
+      <c r="B92" s="62"/>
+      <c r="D92" s="63"/>
+      <c r="E92" s="64"/>
+      <c r="H92" s="63"/>
+      <c r="I92" s="64"/>
+      <c r="L92" s="63"/>
+      <c r="M92" s="64"/>
+      <c r="P92" s="63"/>
+      <c r="R92" s="65"/>
+      <c r="S92" s="56"/>
+      <c r="T92" s="57"/>
+      <c r="U92" s="58"/>
     </row>
     <row r="93" customHeight="1" spans="2:21">
-      <c r="B93" s="82"/>
-      <c r="D93" s="83"/>
-      <c r="E93" s="84"/>
-      <c r="H93" s="83"/>
-      <c r="I93" s="84"/>
-      <c r="L93" s="83"/>
-      <c r="M93" s="84"/>
-      <c r="P93" s="83"/>
-      <c r="R93" s="85"/>
-      <c r="S93" s="66"/>
-      <c r="T93" s="67"/>
-      <c r="U93" s="68"/>
+      <c r="B93" s="62"/>
+      <c r="D93" s="63"/>
+      <c r="E93" s="64"/>
+      <c r="H93" s="63"/>
+      <c r="I93" s="64"/>
+      <c r="L93" s="63"/>
+      <c r="M93" s="64"/>
+      <c r="P93" s="63"/>
+      <c r="R93" s="65"/>
+      <c r="S93" s="56"/>
+      <c r="T93" s="57"/>
+      <c r="U93" s="58"/>
     </row>
     <row r="94" customHeight="1" spans="2:21">
-      <c r="B94" s="82"/>
-      <c r="D94" s="83"/>
-      <c r="E94" s="84"/>
-      <c r="H94" s="83"/>
-      <c r="I94" s="84"/>
-      <c r="L94" s="83"/>
-      <c r="M94" s="84"/>
-      <c r="P94" s="83"/>
-      <c r="R94" s="85"/>
-      <c r="S94" s="66"/>
-      <c r="T94" s="67"/>
-      <c r="U94" s="68"/>
+      <c r="B94" s="62"/>
+      <c r="D94" s="63"/>
+      <c r="E94" s="64"/>
+      <c r="H94" s="63"/>
+      <c r="I94" s="64"/>
+      <c r="L94" s="63"/>
+      <c r="M94" s="64"/>
+      <c r="P94" s="63"/>
+      <c r="R94" s="65"/>
+      <c r="S94" s="56"/>
+      <c r="T94" s="57"/>
+      <c r="U94" s="58"/>
     </row>
     <row r="95" customHeight="1" spans="2:21">
-      <c r="B95" s="82"/>
-      <c r="D95" s="83"/>
-      <c r="E95" s="84"/>
-      <c r="H95" s="83"/>
-      <c r="I95" s="84"/>
-      <c r="L95" s="83"/>
-      <c r="M95" s="84"/>
-      <c r="P95" s="83"/>
-      <c r="R95" s="85"/>
-      <c r="S95" s="66"/>
-      <c r="T95" s="67"/>
-      <c r="U95" s="68"/>
+      <c r="B95" s="62"/>
+      <c r="D95" s="63"/>
+      <c r="E95" s="64"/>
+      <c r="H95" s="63"/>
+      <c r="I95" s="64"/>
+      <c r="L95" s="63"/>
+      <c r="M95" s="64"/>
+      <c r="P95" s="63"/>
+      <c r="R95" s="65"/>
+      <c r="S95" s="56"/>
+      <c r="T95" s="57"/>
+      <c r="U95" s="58"/>
     </row>
     <row r="96" customHeight="1" spans="2:21">
-      <c r="B96" s="82"/>
-      <c r="D96" s="83"/>
-      <c r="E96" s="84"/>
-      <c r="H96" s="83"/>
-      <c r="I96" s="84"/>
-      <c r="L96" s="83"/>
-      <c r="M96" s="84"/>
-      <c r="P96" s="83"/>
-      <c r="R96" s="85"/>
-      <c r="S96" s="66"/>
-      <c r="T96" s="67"/>
-      <c r="U96" s="68"/>
+      <c r="B96" s="62"/>
+      <c r="D96" s="63"/>
+      <c r="E96" s="64"/>
+      <c r="H96" s="63"/>
+      <c r="I96" s="64"/>
+      <c r="L96" s="63"/>
+      <c r="M96" s="64"/>
+      <c r="P96" s="63"/>
+      <c r="R96" s="65"/>
+      <c r="S96" s="56"/>
+      <c r="T96" s="57"/>
+      <c r="U96" s="58"/>
     </row>
     <row r="97" customHeight="1" spans="2:21">
-      <c r="B97" s="82"/>
-      <c r="D97" s="83"/>
-      <c r="E97" s="84"/>
-      <c r="H97" s="83"/>
-      <c r="I97" s="84"/>
-      <c r="L97" s="83"/>
-      <c r="M97" s="84"/>
-      <c r="P97" s="83"/>
-      <c r="R97" s="85"/>
-      <c r="S97" s="66"/>
-      <c r="T97" s="67"/>
-      <c r="U97" s="68"/>
+      <c r="B97" s="62"/>
+      <c r="D97" s="63"/>
+      <c r="E97" s="64"/>
+      <c r="H97" s="63"/>
+      <c r="I97" s="64"/>
+      <c r="L97" s="63"/>
+      <c r="M97" s="64"/>
+      <c r="P97" s="63"/>
+      <c r="R97" s="65"/>
+      <c r="S97" s="56"/>
+      <c r="T97" s="57"/>
+      <c r="U97" s="58"/>
     </row>
     <row r="98" customHeight="1" spans="2:21">
-      <c r="B98" s="82"/>
-      <c r="D98" s="83"/>
-      <c r="E98" s="84"/>
-      <c r="H98" s="83"/>
-      <c r="I98" s="84"/>
-      <c r="L98" s="83"/>
-      <c r="M98" s="84"/>
-      <c r="P98" s="83"/>
-      <c r="R98" s="85"/>
-      <c r="S98" s="66"/>
-      <c r="T98" s="67"/>
-      <c r="U98" s="68"/>
+      <c r="B98" s="62"/>
+      <c r="D98" s="63"/>
+      <c r="E98" s="64"/>
+      <c r="H98" s="63"/>
+      <c r="I98" s="64"/>
+      <c r="L98" s="63"/>
+      <c r="M98" s="64"/>
+      <c r="P98" s="63"/>
+      <c r="R98" s="65"/>
+      <c r="S98" s="56"/>
+      <c r="T98" s="57"/>
+      <c r="U98" s="58"/>
     </row>
     <row r="99" customHeight="1" spans="2:21">
-      <c r="B99" s="82"/>
-      <c r="D99" s="83"/>
-      <c r="E99" s="84"/>
-      <c r="H99" s="83"/>
-      <c r="I99" s="84"/>
-      <c r="L99" s="83"/>
-      <c r="M99" s="84"/>
-      <c r="P99" s="83"/>
-      <c r="R99" s="85"/>
-      <c r="S99" s="66"/>
-      <c r="T99" s="67"/>
-      <c r="U99" s="68"/>
+      <c r="B99" s="62"/>
+      <c r="D99" s="63"/>
+      <c r="E99" s="64"/>
+      <c r="H99" s="63"/>
+      <c r="I99" s="64"/>
+      <c r="L99" s="63"/>
+      <c r="M99" s="64"/>
+      <c r="P99" s="63"/>
+      <c r="R99" s="65"/>
+      <c r="S99" s="56"/>
+      <c r="T99" s="57"/>
+      <c r="U99" s="58"/>
     </row>
     <row r="100" customHeight="1" spans="2:21">
-      <c r="B100" s="86"/>
-      <c r="C100" s="87"/>
-      <c r="D100" s="88"/>
-      <c r="E100" s="89"/>
-      <c r="F100" s="87"/>
-      <c r="G100" s="87"/>
-      <c r="H100" s="88"/>
-      <c r="I100" s="89"/>
-      <c r="J100" s="87"/>
-      <c r="K100" s="87"/>
-      <c r="L100" s="88"/>
-      <c r="M100" s="89"/>
-      <c r="N100" s="87"/>
-      <c r="O100" s="87"/>
-      <c r="P100" s="88"/>
-      <c r="Q100" s="87"/>
-      <c r="R100" s="90"/>
-      <c r="S100" s="91"/>
-      <c r="T100" s="92"/>
-      <c r="U100" s="93"/>
+      <c r="B100" s="66"/>
+      <c r="C100" s="67"/>
+      <c r="D100" s="68"/>
+      <c r="E100" s="69"/>
+      <c r="F100" s="67"/>
+      <c r="G100" s="67"/>
+      <c r="H100" s="68"/>
+      <c r="I100" s="69"/>
+      <c r="J100" s="67"/>
+      <c r="K100" s="67"/>
+      <c r="L100" s="68"/>
+      <c r="M100" s="69"/>
+      <c r="N100" s="67"/>
+      <c r="O100" s="67"/>
+      <c r="P100" s="68"/>
+      <c r="Q100" s="67"/>
+      <c r="R100" s="70"/>
+      <c r="S100" s="71"/>
+      <c r="T100" s="70"/>
+      <c r="U100" s="72"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -5320,7 +5297,7 @@
     <mergeCell ref="S3:U3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q35 Q5:Q20 Q21:Q34 Q36:Q37">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q5:Q37">
       <formula1>"陆军上将,陆军元帅,海军上将"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5333,7 +5310,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:O35"/>
+  <dimension ref="B1:O35"/>
   <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="3" width="18.6666666666667" customWidth="1"/>
@@ -5349,479 +5326,480 @@
     <col min="17" max="17" width="23.1083333333333" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" ht="14.25"/>
     <row r="2" ht="14.25" spans="2:15">
       <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3" spans="2:15">
       <c r="B3" s="5" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="F3" s="8"/>
       <c r="G3" s="7" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="H3" s="8"/>
       <c r="I3" s="7" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="J3" s="8"/>
       <c r="K3" s="7" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="L3" s="8"/>
       <c r="M3" s="9" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="N3" s="8"/>
       <c r="O3" s="7" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
     </row>
     <row r="4" spans="2:15">
       <c r="B4" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>112</v>
+        <v>187</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>119</v>
       </c>
       <c r="F4" s="8"/>
-      <c r="G4" s="12" t="s">
-        <v>179</v>
+      <c r="G4" s="7" t="s">
+        <v>188</v>
       </c>
       <c r="H4" s="8"/>
-      <c r="I4" s="12" t="s">
-        <v>180</v>
+      <c r="I4" s="7" t="s">
+        <v>189</v>
       </c>
       <c r="J4" s="8"/>
-      <c r="K4" s="12" t="s">
-        <v>181</v>
+      <c r="K4" s="7" t="s">
+        <v>190</v>
       </c>
       <c r="L4" s="8"/>
-      <c r="M4" s="13" t="s">
+      <c r="M4" s="12" t="s">
         <v>71</v>
       </c>
       <c r="N4" s="8"/>
-      <c r="O4" s="12" t="s">
-        <v>182</v>
+      <c r="O4" s="7" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="5" spans="2:15">
-      <c r="B5" s="14" t="s">
-        <v>183</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>184</v>
+      <c r="B5" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>193</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="F5" s="8"/>
       <c r="G5" s="7" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="H5" s="8"/>
       <c r="I5" s="7" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="J5" s="8"/>
       <c r="K5" s="7" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="L5" s="8"/>
-      <c r="M5" s="16" t="s">
-        <v>189</v>
+      <c r="M5" s="12" t="s">
+        <v>198</v>
       </c>
       <c r="N5" s="8"/>
       <c r="O5" s="7" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
     </row>
     <row r="6" spans="2:15">
-      <c r="B6" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>191</v>
-      </c>
-      <c r="E6" s="19" t="s">
-        <v>192</v>
+      <c r="B6" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>201</v>
       </c>
       <c r="F6" s="8"/>
-      <c r="G6" s="19" t="s">
-        <v>193</v>
+      <c r="G6" s="17" t="s">
+        <v>202</v>
       </c>
       <c r="H6" s="8"/>
-      <c r="I6" s="19" t="s">
-        <v>194</v>
+      <c r="I6" s="17" t="s">
+        <v>203</v>
       </c>
       <c r="J6" s="8"/>
-      <c r="K6" s="19" t="s">
-        <v>195</v>
+      <c r="K6" s="17" t="s">
+        <v>204</v>
       </c>
       <c r="L6" s="8"/>
-      <c r="M6" s="20" t="s">
-        <v>196</v>
+      <c r="M6" s="18" t="s">
+        <v>205</v>
       </c>
       <c r="N6" s="8"/>
-      <c r="O6" s="19" t="s">
-        <v>197</v>
+      <c r="O6" s="17" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="7" spans="2:15">
-      <c r="B7" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>198</v>
-      </c>
-      <c r="E7" s="19" t="s">
+      <c r="B7" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="E7" s="17" t="s">
         <v>30</v>
       </c>
       <c r="F7" s="8"/>
-      <c r="G7" s="19" t="s">
-        <v>144</v>
+      <c r="G7" s="17" t="s">
+        <v>151</v>
       </c>
       <c r="H7" s="8"/>
-      <c r="I7" s="19" t="s">
-        <v>199</v>
+      <c r="I7" s="17" t="s">
+        <v>208</v>
       </c>
       <c r="J7" s="8"/>
-      <c r="K7" s="19" t="s">
-        <v>200</v>
+      <c r="K7" s="17" t="s">
+        <v>209</v>
       </c>
       <c r="L7" s="8"/>
-      <c r="M7" s="20" t="s">
+      <c r="M7" s="18" t="s">
         <v>32</v>
       </c>
       <c r="N7" s="8"/>
-      <c r="O7" s="19" t="s">
-        <v>201</v>
+      <c r="O7" s="17" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="8" spans="2:15">
-      <c r="B8" s="17" t="s">
-        <v>202</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>203</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>204</v>
+      <c r="B8" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>213</v>
       </c>
       <c r="F8" s="8"/>
-      <c r="G8" s="19" t="s">
-        <v>205</v>
+      <c r="G8" s="17" t="s">
+        <v>214</v>
       </c>
       <c r="H8" s="8"/>
-      <c r="I8" s="19" t="s">
-        <v>87</v>
+      <c r="I8" s="17" t="s">
+        <v>88</v>
       </c>
       <c r="J8" s="8"/>
-      <c r="K8" s="19" t="s">
-        <v>206</v>
+      <c r="K8" s="17" t="s">
+        <v>215</v>
       </c>
       <c r="L8" s="8"/>
-      <c r="M8" s="20" t="s">
-        <v>207</v>
+      <c r="M8" s="18" t="s">
+        <v>216</v>
       </c>
       <c r="N8" s="8"/>
-      <c r="O8" s="19" t="s">
-        <v>208</v>
+      <c r="O8" s="17" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="9" spans="2:15">
-      <c r="B9" s="14" t="s">
-        <v>209</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>210</v>
+      <c r="B9" s="13" t="s">
+        <v>218</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>219</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="F9" s="8"/>
       <c r="G9" s="7" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="H9" s="8"/>
       <c r="I9" s="7" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="J9" s="8"/>
       <c r="K9" s="7" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="L9" s="8"/>
-      <c r="M9" s="16" t="s">
-        <v>215</v>
+      <c r="M9" s="12" t="s">
+        <v>224</v>
       </c>
       <c r="N9" s="8"/>
       <c r="O9" s="7" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
     </row>
     <row r="10" spans="2:15">
-      <c r="B10" s="17" t="s">
-        <v>217</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>218</v>
-      </c>
-      <c r="E10" s="12" t="s">
+      <c r="B10" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="E10" s="7" t="s">
         <v>48</v>
       </c>
       <c r="F10" s="8"/>
-      <c r="G10" s="12" t="s">
-        <v>114</v>
+      <c r="G10" s="7" t="s">
+        <v>121</v>
       </c>
       <c r="H10" s="8"/>
-      <c r="I10" s="12" t="s">
-        <v>52</v>
+      <c r="I10" s="7" t="s">
+        <v>105</v>
       </c>
       <c r="J10" s="8"/>
-      <c r="K10" s="12" t="s">
-        <v>219</v>
+      <c r="K10" s="7" t="s">
+        <v>170</v>
       </c>
       <c r="L10" s="8"/>
-      <c r="M10" s="13" t="s">
-        <v>220</v>
+      <c r="M10" s="12" t="s">
+        <v>228</v>
       </c>
       <c r="N10" s="8"/>
-      <c r="O10" s="12" t="s">
-        <v>221</v>
+      <c r="O10" s="7" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="11" spans="2:15">
-      <c r="B11" s="14" t="s">
-        <v>222</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>223</v>
+      <c r="B11" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>231</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="F11" s="8"/>
       <c r="G11" s="7" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="H11" s="8"/>
       <c r="I11" s="7" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="J11" s="8"/>
       <c r="K11" s="7" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="L11" s="8"/>
-      <c r="M11" s="16" t="s">
+      <c r="M11" s="12" t="s">
         <v>50</v>
       </c>
       <c r="N11" s="8"/>
       <c r="O11" s="7" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
     </row>
     <row r="12" spans="2:15">
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="18" t="s">
-        <v>229</v>
-      </c>
-      <c r="E12" s="19" t="s">
+      <c r="C12" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="E12" s="17" t="s">
         <v>69</v>
       </c>
       <c r="F12" s="8"/>
-      <c r="G12" s="19" t="s">
-        <v>230</v>
+      <c r="G12" s="17" t="s">
+        <v>238</v>
       </c>
       <c r="H12" s="8"/>
-      <c r="I12" s="19" t="s">
-        <v>231</v>
+      <c r="I12" s="17" t="s">
+        <v>52</v>
       </c>
       <c r="J12" s="8"/>
-      <c r="K12" s="19" t="s">
-        <v>232</v>
+      <c r="K12" s="17" t="s">
+        <v>239</v>
       </c>
       <c r="L12" s="8"/>
-      <c r="M12" s="20" t="s">
-        <v>233</v>
+      <c r="M12" s="18" t="s">
+        <v>240</v>
       </c>
       <c r="N12" s="8"/>
-      <c r="O12" s="19" t="s">
-        <v>234</v>
+      <c r="O12" s="17" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="13" spans="2:15">
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="15" t="s">
-        <v>235</v>
-      </c>
-      <c r="E13" s="19" t="s">
-        <v>236</v>
+      <c r="C13" s="14" t="s">
+        <v>242</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>243</v>
       </c>
       <c r="F13" s="8"/>
-      <c r="G13" s="19" t="s">
-        <v>152</v>
+      <c r="G13" s="17" t="s">
+        <v>159</v>
       </c>
       <c r="H13" s="8"/>
-      <c r="I13" s="19" t="s">
+      <c r="I13" s="17" t="s">
         <v>73</v>
       </c>
       <c r="J13" s="8"/>
-      <c r="K13" s="19" t="s">
+      <c r="K13" s="17" t="s">
         <v>54</v>
       </c>
       <c r="L13" s="8"/>
-      <c r="M13" s="20" t="s">
-        <v>237</v>
+      <c r="M13" s="18" t="s">
+        <v>244</v>
       </c>
       <c r="N13" s="8"/>
-      <c r="O13" s="19" t="s">
-        <v>124</v>
+      <c r="O13" s="17" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="14" spans="2:15">
-      <c r="B14" s="17" t="s">
-        <v>238</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>239</v>
-      </c>
-      <c r="E14" s="19" t="s">
-        <v>240</v>
+      <c r="B14" s="15" t="s">
+        <v>245</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>246</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>247</v>
       </c>
       <c r="F14" s="8"/>
-      <c r="G14" s="19" t="s">
-        <v>241</v>
+      <c r="G14" s="17" t="s">
+        <v>248</v>
       </c>
       <c r="H14" s="8"/>
-      <c r="I14" s="19" t="s">
-        <v>242</v>
+      <c r="I14" s="17" t="s">
+        <v>249</v>
       </c>
       <c r="J14" s="8"/>
-      <c r="K14" s="19" t="s">
-        <v>243</v>
+      <c r="K14" s="17" t="s">
+        <v>250</v>
       </c>
       <c r="L14" s="8"/>
-      <c r="M14" s="20" t="s">
-        <v>244</v>
+      <c r="M14" s="18" t="s">
+        <v>251</v>
       </c>
       <c r="N14" s="8"/>
-      <c r="O14" s="19" t="s">
-        <v>245</v>
+      <c r="O14" s="17" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="15" spans="2:15">
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C15" s="15" t="s">
-        <v>246</v>
+      <c r="C15" s="14" t="s">
+        <v>253</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="F15" s="8"/>
       <c r="G15" s="7" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="H15" s="8"/>
       <c r="I15" s="7" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="J15" s="8"/>
       <c r="K15" s="7" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="L15" s="8"/>
-      <c r="M15" s="16" t="s">
-        <v>251</v>
+      <c r="M15" s="12" t="s">
+        <v>258</v>
       </c>
       <c r="N15" s="8"/>
       <c r="O15" s="7" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
     </row>
     <row r="16" spans="2:15">
-      <c r="B16" s="17" t="s">
-        <v>253</v>
-      </c>
-      <c r="C16" s="18" t="s">
-        <v>254</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>255</v>
+      <c r="B16" s="15" t="s">
+        <v>260</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>261</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>262</v>
       </c>
       <c r="F16" s="8"/>
-      <c r="G16" s="12" t="s">
-        <v>141</v>
+      <c r="G16" s="7" t="s">
+        <v>148</v>
       </c>
       <c r="H16" s="8"/>
-      <c r="I16" s="12" t="s">
-        <v>256</v>
+      <c r="I16" s="7" t="s">
+        <v>263</v>
       </c>
       <c r="J16" s="8"/>
-      <c r="K16" s="12" t="s">
-        <v>102</v>
+      <c r="K16" s="7" t="s">
+        <v>107</v>
       </c>
       <c r="L16" s="8"/>
-      <c r="M16" s="13" t="s">
-        <v>257</v>
+      <c r="M16" s="12" t="s">
+        <v>264</v>
       </c>
       <c r="N16" s="8"/>
-      <c r="O16" s="12" t="s">
-        <v>258</v>
+      <c r="O16" s="7" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="17" spans="2:15">
-      <c r="B17" s="21" t="s">
-        <v>259</v>
-      </c>
-      <c r="C17" s="22" t="s">
-        <v>260</v>
+      <c r="B17" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>267</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="F17" s="8"/>
       <c r="G17" s="7" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="H17" s="8"/>
       <c r="I17" s="7" t="s">
@@ -5829,259 +5807,259 @@
       </c>
       <c r="J17" s="8"/>
       <c r="K17" s="7" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="L17" s="8"/>
-      <c r="M17" s="16" t="s">
-        <v>264</v>
+      <c r="M17" s="12" t="s">
+        <v>271</v>
       </c>
       <c r="N17" s="8"/>
       <c r="O17" s="7" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
     </row>
     <row r="18" ht="14.25" spans="2:15">
-      <c r="B18" s="17" t="s">
-        <v>266</v>
-      </c>
-      <c r="C18" s="18" t="s">
-        <v>267</v>
-      </c>
-      <c r="E18" s="19" t="s">
-        <v>268</v>
+      <c r="B18" s="15" t="s">
+        <v>273</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>274</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>275</v>
       </c>
       <c r="F18" s="8"/>
-      <c r="G18" s="19" t="s">
-        <v>269</v>
+      <c r="G18" s="17" t="s">
+        <v>276</v>
       </c>
       <c r="H18" s="8"/>
-      <c r="I18" s="23" t="s">
-        <v>270</v>
+      <c r="I18" s="21" t="s">
+        <v>277</v>
       </c>
       <c r="J18" s="8"/>
-      <c r="K18" s="19" t="s">
-        <v>271</v>
+      <c r="K18" s="17" t="s">
+        <v>278</v>
       </c>
       <c r="L18" s="8"/>
-      <c r="M18" s="24" t="s">
-        <v>270</v>
+      <c r="M18" s="18" t="s">
+        <v>277</v>
       </c>
       <c r="N18" s="8"/>
-      <c r="O18" s="19" t="s">
-        <v>272</v>
+      <c r="O18" s="17" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="19" spans="2:15">
-      <c r="B19" s="14" t="s">
-        <v>273</v>
-      </c>
-      <c r="C19" s="15" t="s">
-        <v>274</v>
-      </c>
-      <c r="E19" s="19" t="s">
-        <v>275</v>
+      <c r="B19" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>281</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>282</v>
       </c>
       <c r="F19" s="8"/>
-      <c r="G19" s="19" t="s">
-        <v>276</v>
+      <c r="G19" s="17" t="s">
+        <v>283</v>
       </c>
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
       <c r="J19" s="8"/>
-      <c r="K19" s="19" t="s">
-        <v>277</v>
+      <c r="K19" s="17" t="s">
+        <v>284</v>
       </c>
       <c r="L19" s="8"/>
-      <c r="M19" s="25" t="s">
-        <v>278</v>
+      <c r="M19" s="12" t="s">
+        <v>285</v>
       </c>
       <c r="N19" s="8"/>
-      <c r="O19" s="19" t="s">
-        <v>130</v>
+      <c r="O19" s="17" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="20" spans="2:15">
-      <c r="B20" s="17" t="s">
-        <v>279</v>
-      </c>
-      <c r="C20" s="18" t="s">
-        <v>280</v>
-      </c>
-      <c r="E20" s="19" t="s">
-        <v>281</v>
+      <c r="B20" s="15" t="s">
+        <v>286</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>288</v>
       </c>
       <c r="F20" s="8"/>
-      <c r="G20" s="19" t="s">
-        <v>282</v>
+      <c r="G20" s="17" t="s">
+        <v>289</v>
       </c>
       <c r="H20" s="8"/>
       <c r="I20" s="8"/>
       <c r="J20" s="8"/>
-      <c r="K20" s="19" t="s">
-        <v>283</v>
+      <c r="K20" s="17" t="s">
+        <v>290</v>
       </c>
       <c r="L20" s="8"/>
-      <c r="M20" s="26" t="s">
-        <v>284</v>
+      <c r="M20" s="12" t="s">
+        <v>291</v>
       </c>
       <c r="N20" s="8"/>
-      <c r="O20" s="19" t="s">
-        <v>285</v>
+      <c r="O20" s="17" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="21" ht="14.25" spans="2:15">
-      <c r="B21" s="14" t="s">
-        <v>286</v>
-      </c>
-      <c r="C21" s="15" t="s">
-        <v>274</v>
+      <c r="B21" s="13" t="s">
+        <v>293</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>281</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="F21" s="8"/>
       <c r="G21" s="7" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="H21" s="8"/>
       <c r="I21" s="8"/>
       <c r="J21" s="8"/>
       <c r="K21" s="7" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="L21" s="8"/>
-      <c r="M21" s="27" t="s">
-        <v>289</v>
+      <c r="M21" s="22" t="s">
+        <v>296</v>
       </c>
       <c r="N21" s="8"/>
       <c r="O21" s="7" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
     </row>
     <row r="22" ht="14.25" spans="2:15">
-      <c r="B22" s="28" t="s">
-        <v>291</v>
-      </c>
-      <c r="C22" s="29" t="s">
-        <v>280</v>
-      </c>
-      <c r="E22" s="12" t="s">
-        <v>292</v>
+      <c r="B22" s="23" t="s">
+        <v>298</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>287</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>299</v>
       </c>
       <c r="F22" s="8"/>
-      <c r="G22" s="12" t="s">
-        <v>293</v>
+      <c r="G22" s="7" t="s">
+        <v>300</v>
       </c>
       <c r="H22" s="8"/>
       <c r="I22" s="8"/>
       <c r="J22" s="8"/>
-      <c r="K22" s="12" t="s">
+      <c r="K22" s="7" t="s">
         <v>75</v>
       </c>
       <c r="L22" s="8"/>
       <c r="M22" s="8"/>
       <c r="N22" s="8"/>
-      <c r="O22" s="12" t="s">
-        <v>137</v>
+      <c r="O22" s="7" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="23" spans="2:15">
       <c r="E23" s="7" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F23" s="8"/>
       <c r="G23" s="7" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="H23" s="8"/>
       <c r="I23" s="8"/>
       <c r="J23" s="8"/>
       <c r="K23" s="7" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="L23" s="8"/>
       <c r="M23" s="8"/>
       <c r="N23" s="8"/>
       <c r="O23" s="7" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
     </row>
     <row r="24" spans="2:15">
-      <c r="E24" s="19" t="s">
-        <v>297</v>
+      <c r="E24" s="17" t="s">
+        <v>304</v>
       </c>
       <c r="F24" s="8"/>
-      <c r="G24" s="19" t="s">
-        <v>298</v>
+      <c r="G24" s="17" t="s">
+        <v>305</v>
       </c>
       <c r="H24" s="8"/>
       <c r="I24" s="8"/>
       <c r="J24" s="8"/>
-      <c r="K24" s="19" t="s">
-        <v>299</v>
+      <c r="K24" s="17" t="s">
+        <v>306</v>
       </c>
       <c r="L24" s="8"/>
       <c r="M24" s="8"/>
       <c r="N24" s="8"/>
-      <c r="O24" s="19" t="s">
-        <v>300</v>
+      <c r="O24" s="17" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="25" spans="2:15">
-      <c r="E25" s="19" t="s">
-        <v>85</v>
+      <c r="E25" s="17" t="s">
+        <v>86</v>
       </c>
       <c r="F25" s="8"/>
-      <c r="G25" s="19" t="s">
-        <v>147</v>
+      <c r="G25" s="17" t="s">
+        <v>154</v>
       </c>
       <c r="H25" s="8"/>
       <c r="I25" s="8"/>
       <c r="J25" s="8"/>
-      <c r="K25" s="19" t="s">
-        <v>301</v>
+      <c r="K25" s="17" t="s">
+        <v>308</v>
       </c>
       <c r="L25" s="8"/>
       <c r="M25" s="8"/>
       <c r="N25" s="8"/>
-      <c r="O25" s="19" t="s">
-        <v>302</v>
+      <c r="O25" s="17" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="26" ht="14.25" spans="2:15">
-      <c r="E26" s="19" t="s">
-        <v>303</v>
+      <c r="E26" s="17" t="s">
+        <v>310</v>
       </c>
       <c r="F26" s="8"/>
-      <c r="G26" s="19" t="s">
-        <v>304</v>
+      <c r="G26" s="17" t="s">
+        <v>311</v>
       </c>
       <c r="H26" s="8"/>
       <c r="I26" s="8"/>
       <c r="J26" s="8"/>
-      <c r="K26" s="19" t="s">
-        <v>305</v>
+      <c r="K26" s="17" t="s">
+        <v>312</v>
       </c>
       <c r="L26" s="8"/>
       <c r="M26" s="8"/>
       <c r="N26" s="8"/>
-      <c r="O26" s="23" t="s">
-        <v>155</v>
+      <c r="O26" s="21" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="27" spans="2:15">
       <c r="E27" s="7" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="F27" s="8"/>
       <c r="G27" s="7" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="H27" s="8"/>
       <c r="I27" s="8"/>
       <c r="J27" s="8"/>
       <c r="K27" s="7" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="L27" s="8"/>
       <c r="M27" s="8"/>
@@ -6089,18 +6067,18 @@
       <c r="O27" s="8"/>
     </row>
     <row r="28" spans="2:15">
-      <c r="E28" s="12" t="s">
-        <v>309</v>
+      <c r="E28" s="7" t="s">
+        <v>316</v>
       </c>
       <c r="F28" s="8"/>
-      <c r="G28" s="12" t="s">
-        <v>310</v>
+      <c r="G28" s="7" t="s">
+        <v>317</v>
       </c>
       <c r="H28" s="8"/>
       <c r="I28" s="8"/>
       <c r="J28" s="8"/>
-      <c r="K28" s="12" t="s">
-        <v>311</v>
+      <c r="K28" s="7" t="s">
+        <v>318</v>
       </c>
       <c r="L28" s="8"/>
       <c r="M28" s="8"/>
@@ -6109,17 +6087,17 @@
     </row>
     <row r="29" ht="14.25" spans="2:15">
       <c r="E29" s="7" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="F29" s="8"/>
       <c r="G29" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H29" s="8"/>
       <c r="I29" s="8"/>
       <c r="J29" s="8"/>
-      <c r="K29" s="30" t="s">
-        <v>313</v>
+      <c r="K29" s="25" t="s">
+        <v>320</v>
       </c>
       <c r="L29" s="8"/>
       <c r="M29" s="8"/>
@@ -6127,12 +6105,12 @@
       <c r="O29" s="8"/>
     </row>
     <row r="30" ht="14.25" spans="2:15">
-      <c r="E30" s="23" t="s">
-        <v>270</v>
+      <c r="E30" s="21" t="s">
+        <v>277</v>
       </c>
       <c r="F30" s="8"/>
-      <c r="G30" s="19" t="s">
-        <v>314</v>
+      <c r="G30" s="17" t="s">
+        <v>321</v>
       </c>
       <c r="H30" s="8"/>
       <c r="I30" s="8"/>
@@ -6146,8 +6124,8 @@
     <row r="31" spans="2:15">
       <c r="E31" s="8"/>
       <c r="F31" s="8"/>
-      <c r="G31" s="19" t="s">
-        <v>315</v>
+      <c r="G31" s="17" t="s">
+        <v>322</v>
       </c>
       <c r="H31" s="8"/>
       <c r="I31" s="8"/>
@@ -6161,7 +6139,7 @@
     <row r="32" spans="2:15">
       <c r="E32" s="8"/>
       <c r="F32" s="8"/>
-      <c r="G32" s="19" t="s">
+      <c r="G32" s="17" t="s">
         <v>36</v>
       </c>
       <c r="H32" s="8"/>
@@ -6177,7 +6155,7 @@
       <c r="E33" s="8"/>
       <c r="F33" s="8"/>
       <c r="G33" s="7" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="H33" s="8"/>
       <c r="I33" s="8"/>
@@ -6191,8 +6169,8 @@
     <row r="34" spans="5:15">
       <c r="E34" s="8"/>
       <c r="F34" s="8"/>
-      <c r="G34" s="12" t="s">
-        <v>316</v>
+      <c r="G34" s="7" t="s">
+        <v>323</v>
       </c>
       <c r="H34" s="8"/>
       <c r="I34" s="8"/>
@@ -6206,8 +6184,8 @@
     <row r="35" ht="14.25" spans="5:15">
       <c r="E35" s="8"/>
       <c r="F35" s="8"/>
-      <c r="G35" s="30" t="s">
-        <v>317</v>
+      <c r="G35" s="25" t="s">
+        <v>324</v>
       </c>
       <c r="H35" s="8"/>
       <c r="I35" s="8"/>

--- a/WIP/月茗/LAN阿斯特莱雅/阿斯特莱雅-军事人员配置表.xlsx
+++ b/WIP/月茗/LAN阿斯特莱雅/阿斯特莱雅-军事人员配置表.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="353">
   <si>
     <t>阿斯特莱雅</t>
   </si>
@@ -244,649 +244,733 @@
     <t>三角千歌</t>
   </si>
   <si>
+    <t>海军航空（专家）</t>
+  </si>
+  <si>
+    <t>古蕾雅</t>
+  </si>
+  <si>
+    <t>对地支援（大师）</t>
+  </si>
+  <si>
+    <t>亚里莎</t>
+  </si>
+  <si>
+    <t>战术轰炸（大师）</t>
+  </si>
+  <si>
+    <t>厄里斯</t>
+  </si>
+  <si>
+    <t>佐佐木咲恋</t>
+  </si>
+  <si>
+    <t>咲恋救济院</t>
+  </si>
+  <si>
+    <t>革新主义-社会民主主义</t>
+  </si>
+  <si>
+    <t>沉默的实干家</t>
+  </si>
+  <si>
+    <t>姬宫真步</t>
+  </si>
+  <si>
+    <t>红色动员者</t>
+  </si>
+  <si>
+    <t>柊杏奈</t>
+  </si>
+  <si>
+    <t>闪电战理论家</t>
+  </si>
+  <si>
+    <t>莉玛</t>
+  </si>
+  <si>
+    <t>陆军机动（大师）</t>
+  </si>
+  <si>
+    <t>风宫依里</t>
+  </si>
+  <si>
+    <t>海军机动（大师）</t>
+  </si>
+  <si>
+    <t>九朗千恵</t>
+  </si>
+  <si>
+    <t>航空安全（奇才）</t>
+  </si>
+  <si>
+    <t>双叶碧</t>
+  </si>
+  <si>
+    <t>陆军隐匿（奇才）</t>
+  </si>
+  <si>
+    <t>美波铃奈</t>
+  </si>
+  <si>
+    <t>涅比亚</t>
+  </si>
+  <si>
+    <t>1级海军工程</t>
+  </si>
+  <si>
+    <t>百地希留耶</t>
+  </si>
+  <si>
+    <t>美食殿堂</t>
+  </si>
+  <si>
+    <t>保守主义-威权保守主义</t>
+  </si>
+  <si>
+    <t>勋爵阁下</t>
+  </si>
+  <si>
+    <t>雾原霞</t>
+  </si>
+  <si>
+    <t>王宫名侦探</t>
+  </si>
+  <si>
+    <t>衣之咲璃乃</t>
+  </si>
+  <si>
+    <t>优势火力学说专家</t>
+  </si>
+  <si>
+    <t>樱井望</t>
+  </si>
+  <si>
+    <t>陆军士气（奇才）</t>
+  </si>
+  <si>
+    <t>茧宫纺希</t>
+  </si>
+  <si>
+    <t>久央璃亚</t>
+  </si>
+  <si>
+    <t>夜间行动（大师）</t>
+  </si>
+  <si>
+    <t>丹野七七香</t>
+  </si>
+  <si>
+    <t>密接支援（大师）</t>
+  </si>
+  <si>
+    <t>千里真那</t>
+  </si>
+  <si>
+    <t>爱梅斯</t>
+  </si>
+  <si>
+    <t>1级陆军工程</t>
+  </si>
+  <si>
+    <t>威权主义-贵族保守主义</t>
+  </si>
+  <si>
+    <t>军队胜利，凯露说服霸瞳</t>
+  </si>
+  <si>
+    <t>枣可萝</t>
+  </si>
+  <si>
+    <t>小小的引导者</t>
+  </si>
+  <si>
+    <t>仓石惠理子</t>
+  </si>
+  <si>
+    <t>恐怖的巨头</t>
+  </si>
+  <si>
+    <t>柏崎栞</t>
+  </si>
+  <si>
+    <t>决战计划学说专家</t>
+  </si>
+  <si>
+    <t>陆军防御（大师）</t>
+  </si>
+  <si>
+    <t>柏崎初音</t>
+  </si>
+  <si>
+    <t>炮兵部队（大师）</t>
+  </si>
+  <si>
+    <t>蛮出井布武机</t>
+  </si>
+  <si>
+    <t>七冠</t>
+  </si>
+  <si>
+    <t>霸权主义-个人独裁</t>
+  </si>
+  <si>
+    <t>军队胜利，霸瞳收拢权力</t>
+  </si>
+  <si>
+    <t>明日之星</t>
+  </si>
+  <si>
+    <t>宫坂珠希</t>
+  </si>
+  <si>
+    <t>幻影猫</t>
+  </si>
+  <si>
+    <t>太刀洗流夏</t>
+  </si>
+  <si>
+    <t>军事理论家</t>
+  </si>
+  <si>
+    <t>茜美美</t>
+  </si>
+  <si>
+    <t>风宫茜里</t>
+  </si>
+  <si>
+    <t>两栖作战（大师）</t>
+  </si>
+  <si>
+    <t>陆军上将</t>
+  </si>
+  <si>
+    <t>宵滨深月</t>
+  </si>
+  <si>
+    <t>军队胜利，共和派政变成功，成立共和国</t>
+  </si>
+  <si>
+    <t>国家社会主义先锋</t>
+  </si>
+  <si>
+    <t>财政紧缩专家</t>
+  </si>
+  <si>
+    <t>一之濑祈梨</t>
+  </si>
+  <si>
+    <t>蛮出井若菜</t>
+  </si>
+  <si>
+    <t>阿斯特莱雅家族</t>
+  </si>
+  <si>
+    <t>威权主义-绝对君主制</t>
+  </si>
+  <si>
+    <t>军队胜利，联邦派政变成功，重建王国</t>
+  </si>
+  <si>
+    <t>模索路晶</t>
+  </si>
+  <si>
+    <t>大神美冬</t>
+  </si>
+  <si>
+    <t>效率至上</t>
+  </si>
+  <si>
+    <t>栗林胡桃</t>
+  </si>
+  <si>
+    <t>屏卫舰作战（大师）</t>
+  </si>
+  <si>
+    <t>观崎佳凛</t>
+  </si>
+  <si>
+    <t>士条怜</t>
+  </si>
+  <si>
+    <t>军需主官</t>
+  </si>
+  <si>
+    <t>黑江花子</t>
+  </si>
+  <si>
+    <t>特种部队（大师）</t>
+  </si>
+  <si>
+    <t>真行寺由仁</t>
+  </si>
+  <si>
+    <t>网络巨人</t>
+  </si>
+  <si>
+    <t>装甲部队（大师）</t>
+  </si>
+  <si>
+    <t>藤堂秋乃</t>
+  </si>
+  <si>
+    <t>财团千金</t>
+  </si>
+  <si>
+    <t>陆军重组（大师）</t>
+  </si>
+  <si>
+    <t>虹村雪</t>
+  </si>
+  <si>
+    <t>北条绫音</t>
+  </si>
+  <si>
+    <t>无畏的冒险家</t>
+  </si>
+  <si>
+    <t>园上矛依未</t>
+  </si>
+  <si>
+    <t>步兵部队（大师）</t>
+  </si>
+  <si>
+    <t>野户真阳</t>
+  </si>
+  <si>
+    <t>自由市场经济学家</t>
+  </si>
+  <si>
+    <t>现士实似似花</t>
+  </si>
+  <si>
+    <t>航空母舰作战（奇才）</t>
+  </si>
+  <si>
+    <t>普雷西娅·怀斯曼</t>
+  </si>
+  <si>
+    <t>远野帆稀</t>
+  </si>
+  <si>
+    <t>步坦协同（专家）</t>
+  </si>
+  <si>
+    <t>妮隆·朱贝尔</t>
+  </si>
+  <si>
+    <t>琳德</t>
+  </si>
+  <si>
+    <t>上喜忍</t>
+  </si>
+  <si>
+    <t>无线电情报（专家）</t>
+  </si>
+  <si>
+    <t>桥本环奈</t>
+  </si>
+  <si>
+    <t>玉泉美咲</t>
+  </si>
+  <si>
+    <t>德川莉莉</t>
+  </si>
+  <si>
+    <t>轰炸机拦截（大师）</t>
+  </si>
+  <si>
+    <t>爱川美里</t>
+  </si>
+  <si>
+    <t>库露露</t>
+  </si>
+  <si>
+    <t>石桥步美</t>
+  </si>
+  <si>
+    <t>穗高未奏希</t>
+  </si>
+  <si>
+    <t>露易丝玛丽</t>
+  </si>
+  <si>
+    <t>卯之花兰</t>
+  </si>
+  <si>
+    <t>鬼道嘉夜</t>
+  </si>
+  <si>
+    <t>志木场寝亚</t>
+  </si>
+  <si>
+    <t>志木场祢罗</t>
+  </si>
+  <si>
+    <t>流魅空</t>
+  </si>
+  <si>
+    <t>织原茉莉</t>
+  </si>
+  <si>
+    <t>幽野霞</t>
+  </si>
+  <si>
+    <t>海军上将</t>
+  </si>
+  <si>
+    <t>蛮出井倭</t>
+  </si>
+  <si>
+    <t>森近铃</t>
+  </si>
+  <si>
+    <t>风间千爱瑠</t>
+  </si>
+  <si>
+    <t>远见空花</t>
+  </si>
+  <si>
+    <t>一华牡丹</t>
+  </si>
+  <si>
+    <t>对应学说</t>
+  </si>
+  <si>
+    <t>陆军部长职位</t>
+  </si>
+  <si>
+    <t>陆军总司令职位</t>
+  </si>
+  <si>
+    <t>空军部长职位</t>
+  </si>
+  <si>
+    <t>空军总司令职位</t>
+  </si>
+  <si>
+    <t>海军部长职位</t>
+  </si>
+  <si>
+    <t>海军总司令职位</t>
+  </si>
+  <si>
+    <t>陆军</t>
+  </si>
+  <si>
+    <t>陆军防御（专家）</t>
+  </si>
+  <si>
+    <t>堑壕作战（专家）</t>
+  </si>
+  <si>
+    <t>空军改革（专家）</t>
+  </si>
+  <si>
+    <t>空军战斗训练（专家）</t>
+  </si>
+  <si>
+    <t>反潜作战（专家）</t>
+  </si>
+  <si>
+    <t>机动作战+装甲速度</t>
+  </si>
+  <si>
+    <t>堑壕作战（大师）</t>
+  </si>
+  <si>
+    <t>空军改革（大师）</t>
+  </si>
+  <si>
+    <t>空军战斗训练（大师）</t>
+  </si>
+  <si>
     <t>海军航空（大师）</t>
   </si>
   <si>
-    <t>古蕾雅</t>
-  </si>
-  <si>
-    <t>对地支援（大师）</t>
-  </si>
-  <si>
-    <t>亚里莎</t>
-  </si>
-  <si>
-    <t>战术轰炸（大师）</t>
-  </si>
-  <si>
-    <t>厄里斯</t>
-  </si>
-  <si>
-    <t>佐佐木咲恋</t>
-  </si>
-  <si>
-    <t>咲恋救济院</t>
-  </si>
-  <si>
-    <t>革新主义-社会民主主义</t>
-  </si>
-  <si>
-    <t>沉默的实干家</t>
-  </si>
-  <si>
-    <t>姬宫真步</t>
-  </si>
-  <si>
-    <t>红色动员者</t>
-  </si>
-  <si>
-    <t>柊杏奈</t>
-  </si>
-  <si>
-    <t>闪电战理论家</t>
-  </si>
-  <si>
-    <t>莉玛</t>
-  </si>
-  <si>
-    <t>陆军机动（大师）</t>
-  </si>
-  <si>
-    <t>九朗千恵</t>
-  </si>
-  <si>
-    <t>航空安全（奇才）</t>
-  </si>
-  <si>
-    <t>双叶碧</t>
-  </si>
-  <si>
-    <t>陆军隐匿（奇才）</t>
-  </si>
-  <si>
-    <t>美波铃奈</t>
-  </si>
-  <si>
-    <t>涅比亚</t>
-  </si>
-  <si>
-    <t>1级海军工程</t>
-  </si>
-  <si>
-    <t>百地希留耶</t>
-  </si>
-  <si>
-    <t>美食殿堂</t>
-  </si>
-  <si>
-    <t>保守主义-威权保守主义</t>
-  </si>
-  <si>
-    <t>勋爵阁下</t>
-  </si>
-  <si>
-    <t>雾原霞</t>
-  </si>
-  <si>
-    <t>王宫名侦探</t>
-  </si>
-  <si>
-    <t>衣之咲璃乃</t>
-  </si>
-  <si>
-    <t>优势火力学说专家</t>
-  </si>
-  <si>
-    <t>樱井望</t>
-  </si>
-  <si>
-    <t>陆军士气（奇才）</t>
-  </si>
-  <si>
-    <t>久央璃亚</t>
-  </si>
-  <si>
-    <t>夜间行动（大师）</t>
-  </si>
-  <si>
-    <t>丹野七七香</t>
-  </si>
-  <si>
-    <t>密接支援（大师）</t>
-  </si>
-  <si>
-    <t>千里真那</t>
-  </si>
-  <si>
-    <t>爱梅斯</t>
-  </si>
-  <si>
-    <t>1级陆军工程</t>
-  </si>
-  <si>
-    <t>威权主义-贵族保守主义</t>
-  </si>
-  <si>
-    <t>军队胜利，凯露说服霸瞳</t>
-  </si>
-  <si>
-    <t>枣可萝</t>
-  </si>
-  <si>
-    <t>小小的引导者</t>
-  </si>
-  <si>
-    <t>仓石惠理子</t>
-  </si>
-  <si>
-    <t>恐怖的巨头</t>
-  </si>
-  <si>
-    <t>柏崎栞</t>
-  </si>
-  <si>
-    <t>决战计划学说专家</t>
-  </si>
-  <si>
-    <t>陆军防御（大师）</t>
-  </si>
-  <si>
-    <t>柏崎初音</t>
-  </si>
-  <si>
-    <t>炮兵部队（大师）</t>
-  </si>
-  <si>
-    <t>七冠</t>
-  </si>
-  <si>
-    <t>霸权主义-个人独裁</t>
-  </si>
-  <si>
-    <t>军队胜利，霸瞳收拢权力</t>
-  </si>
-  <si>
-    <t>明日之星</t>
-  </si>
-  <si>
-    <t>宫坂珠希</t>
-  </si>
-  <si>
-    <t>幻影猫</t>
-  </si>
-  <si>
-    <t>太刀洗流夏</t>
-  </si>
-  <si>
-    <t>军事理论家</t>
-  </si>
-  <si>
-    <t>风宫茜里</t>
-  </si>
-  <si>
-    <t>两栖作战（大师）</t>
-  </si>
-  <si>
-    <t>陆军上将</t>
-  </si>
-  <si>
-    <t>军队胜利，共和派政变成功，成立共和国</t>
-  </si>
-  <si>
-    <t>国家社会主义先锋</t>
-  </si>
-  <si>
-    <t>财政紧缩专家</t>
-  </si>
-  <si>
-    <t>风宫依里</t>
+    <t>反潜作战（大师）</t>
+  </si>
+  <si>
+    <t>机动作战学说专家</t>
+  </si>
+  <si>
+    <t>机动作战</t>
+  </si>
+  <si>
+    <t>陆军防御（奇才）</t>
+  </si>
+  <si>
+    <t>堑壕作战（奇才）</t>
+  </si>
+  <si>
+    <t>空军改革（奇才）</t>
+  </si>
+  <si>
+    <t>空军战斗训练（奇才）</t>
+  </si>
+  <si>
+    <t>海军航空（奇才）</t>
+  </si>
+  <si>
+    <t>反潜作战（奇才）</t>
+  </si>
+  <si>
+    <t>优势火力</t>
+  </si>
+  <si>
+    <t>陆军进攻（专家）</t>
+  </si>
+  <si>
+    <t>装甲部队（专家）</t>
+  </si>
+  <si>
+    <t>航空安全（专家）</t>
+  </si>
+  <si>
+    <t>海军袭击（专家）</t>
+  </si>
+  <si>
+    <t>舰队决战（专家）</t>
+  </si>
+  <si>
+    <t>海军对空防御（专家）</t>
+  </si>
+  <si>
+    <t>决战计划</t>
+  </si>
+  <si>
+    <t>航空安全（大师）</t>
+  </si>
+  <si>
+    <t>海军袭击（大师）</t>
+  </si>
+  <si>
+    <t>海军对空防御（大师）</t>
+  </si>
+  <si>
+    <t>人海突击学说专家</t>
+  </si>
+  <si>
+    <t>人海突击</t>
+  </si>
+  <si>
+    <t>陆军进攻（奇才）</t>
+  </si>
+  <si>
+    <t>装甲部队（奇才）</t>
+  </si>
+  <si>
+    <t>海军袭击（奇才）</t>
+  </si>
+  <si>
+    <t>舰队决战（奇才）</t>
+  </si>
+  <si>
+    <t>海军对空防御（奇才）</t>
+  </si>
+  <si>
+    <t>空战理论家</t>
+  </si>
+  <si>
+    <t>空军</t>
+  </si>
+  <si>
+    <t>陆军计划（专家）</t>
+  </si>
+  <si>
+    <t>炮兵部队（专家）</t>
+  </si>
+  <si>
+    <t>夜间行动（专家）</t>
+  </si>
+  <si>
+    <t>轰炸机拦截（专家）</t>
+  </si>
+  <si>
+    <t>贸易袭击（专家）</t>
+  </si>
+  <si>
+    <t>舰队后勤（专家）</t>
+  </si>
+  <si>
+    <t>空中制胜</t>
+  </si>
+  <si>
+    <t>战略破坏</t>
+  </si>
+  <si>
+    <t>贸易袭击（大师）</t>
+  </si>
+  <si>
+    <t>舰队后勤（大师）</t>
+  </si>
+  <si>
+    <t>密接支援拥护者</t>
+  </si>
+  <si>
+    <t>战场支援</t>
+  </si>
+  <si>
+    <t>陆军计划（奇才）</t>
+  </si>
+  <si>
+    <t>炮兵部队（奇才）</t>
+  </si>
+  <si>
+    <t>夜间行动（奇才）</t>
+  </si>
+  <si>
+    <t>轰炸机拦截（奇才）</t>
+  </si>
+  <si>
+    <t>舰队后勤（奇才）</t>
+  </si>
+  <si>
+    <t>连续作战</t>
+  </si>
+  <si>
+    <t>步兵部队（专家）</t>
+  </si>
+  <si>
+    <t>空中优势（专家）</t>
+  </si>
+  <si>
+    <t>海军改革（专家）</t>
+  </si>
+  <si>
+    <t>两栖作战（专家）</t>
+  </si>
+  <si>
+    <t>空军+CAS伤害修正</t>
+  </si>
+  <si>
+    <t>陆军演习（大师）</t>
+  </si>
+  <si>
+    <t>海军改革（大师）</t>
+  </si>
+  <si>
+    <t>海军理论家</t>
+  </si>
+  <si>
+    <t>海军</t>
+  </si>
+  <si>
+    <t>陆军演习（奇才）</t>
+  </si>
+  <si>
+    <t>步兵部队（奇才）</t>
+  </si>
+  <si>
+    <t>对地支援（奇才）</t>
+  </si>
+  <si>
+    <t>空中优势（奇才）</t>
+  </si>
+  <si>
+    <t>海军改革（奇才）</t>
+  </si>
+  <si>
+    <t>两栖作战（奇才）</t>
+  </si>
+  <si>
+    <t>基地打击</t>
+  </si>
+  <si>
+    <t>陆军改革（专家）</t>
+  </si>
+  <si>
+    <t>特种部队（专家）</t>
+  </si>
+  <si>
+    <t>全天候作战（专家）</t>
+  </si>
+  <si>
+    <t>密接支援（专家）</t>
+  </si>
+  <si>
+    <t>海军机动（专家）</t>
+  </si>
+  <si>
+    <t>潜艇作战（专家）</t>
+  </si>
+  <si>
+    <t>大舰队拥护者</t>
+  </si>
+  <si>
+    <t>存在舰队</t>
+  </si>
+  <si>
+    <t>陆军改革（大师）</t>
+  </si>
+  <si>
+    <t>全天候作战（大师）</t>
+  </si>
+  <si>
+    <t>潜艇作战（大师）</t>
+  </si>
+  <si>
+    <t>潜艇专家</t>
+  </si>
+  <si>
+    <t>贸易阻断</t>
+  </si>
+  <si>
+    <t>陆军改革（奇才）</t>
+  </si>
+  <si>
+    <t>特种部队（奇才）</t>
+  </si>
+  <si>
+    <t>密接支援（奇才）</t>
+  </si>
+  <si>
+    <t>海军机动（奇才）</t>
+  </si>
+  <si>
+    <t>潜艇作战（奇才）</t>
+  </si>
+  <si>
+    <t>理论派议会</t>
+  </si>
+  <si>
+    <t>全部</t>
+  </si>
+  <si>
+    <t>陆军组织（专家）</t>
+  </si>
+  <si>
+    <t>骑兵部队（专家）</t>
+  </si>
+  <si>
+    <t>保守派</t>
+  </si>
+  <si>
+    <t>战略轰炸（专家）</t>
+  </si>
+  <si>
+    <t>主力舰作战（专家）</t>
+  </si>
+  <si>
+    <t>火箭科学家</t>
+  </si>
+  <si>
+    <t>火箭科技</t>
+  </si>
+  <si>
+    <t>陆军组织（大师）</t>
+  </si>
+  <si>
+    <t>骑兵部队（大师）</t>
+  </si>
+  <si>
+    <t>战略轰炸（大师）</t>
+  </si>
+  <si>
+    <t>海军火炮制造商（专家）</t>
   </si>
   <si>
     <t>主力舰作战（大师）</t>
-  </si>
-  <si>
-    <t>阿斯特莱雅家族</t>
-  </si>
-  <si>
-    <t>威权主义-绝对君主制</t>
-  </si>
-  <si>
-    <t>军队胜利，联邦派政变成功，重建王国</t>
-  </si>
-  <si>
-    <t>大神美冬</t>
-  </si>
-  <si>
-    <t>效率至上</t>
-  </si>
-  <si>
-    <t>栗林胡桃</t>
-  </si>
-  <si>
-    <t>屏卫舰作战（大师）</t>
-  </si>
-  <si>
-    <t>士条怜</t>
-  </si>
-  <si>
-    <t>军需主官</t>
-  </si>
-  <si>
-    <t>黑江花子</t>
-  </si>
-  <si>
-    <t>特种部队（大师）</t>
-  </si>
-  <si>
-    <t>真行寺由仁</t>
-  </si>
-  <si>
-    <t>网络巨人</t>
-  </si>
-  <si>
-    <t>装甲部队（大师）</t>
-  </si>
-  <si>
-    <t>藤堂秋乃</t>
-  </si>
-  <si>
-    <t>财团千金</t>
-  </si>
-  <si>
-    <t>陆军重组（大师）</t>
-  </si>
-  <si>
-    <t>虹村雪</t>
-  </si>
-  <si>
-    <t>北条绫音</t>
-  </si>
-  <si>
-    <t>无畏的冒险家</t>
-  </si>
-  <si>
-    <t>园上矛依未</t>
-  </si>
-  <si>
-    <t>步兵部队（大师）</t>
-  </si>
-  <si>
-    <t>自由市场经济学家</t>
-  </si>
-  <si>
-    <t>现士实似似花</t>
-  </si>
-  <si>
-    <t>航空母舰作战（奇才）</t>
-  </si>
-  <si>
-    <t>远野帆稀</t>
-  </si>
-  <si>
-    <t>步坦协同（专家）</t>
-  </si>
-  <si>
-    <t>妮隆·朱贝尔</t>
-  </si>
-  <si>
-    <t>上喜忍</t>
-  </si>
-  <si>
-    <t>无线电情报（专家）</t>
-  </si>
-  <si>
-    <t>桥本环奈</t>
-  </si>
-  <si>
-    <t>德川莉莉</t>
-  </si>
-  <si>
-    <t>轰炸机拦截（大师）</t>
-  </si>
-  <si>
-    <t>织原茉莉</t>
-  </si>
-  <si>
-    <t>海军上将</t>
-  </si>
-  <si>
-    <t>对应学说</t>
-  </si>
-  <si>
-    <t>陆军部长职位</t>
-  </si>
-  <si>
-    <t>陆军总司令职位</t>
-  </si>
-  <si>
-    <t>空军部长职位</t>
-  </si>
-  <si>
-    <t>空军总司令职位</t>
-  </si>
-  <si>
-    <t>海军部长职位</t>
-  </si>
-  <si>
-    <t>海军总司令职位</t>
-  </si>
-  <si>
-    <t>陆军</t>
-  </si>
-  <si>
-    <t>陆军防御（专家）</t>
-  </si>
-  <si>
-    <t>堑壕作战（专家）</t>
-  </si>
-  <si>
-    <t>空军改革（专家）</t>
-  </si>
-  <si>
-    <t>空军战斗训练（专家）</t>
-  </si>
-  <si>
-    <t>海军航空（专家）</t>
-  </si>
-  <si>
-    <t>反潜作战（专家）</t>
-  </si>
-  <si>
-    <t>机动作战+装甲速度</t>
-  </si>
-  <si>
-    <t>堑壕作战（大师）</t>
-  </si>
-  <si>
-    <t>空军改革（大师）</t>
-  </si>
-  <si>
-    <t>空军战斗训练（大师）</t>
-  </si>
-  <si>
-    <t>反潜作战（大师）</t>
-  </si>
-  <si>
-    <t>机动作战学说专家</t>
-  </si>
-  <si>
-    <t>机动作战</t>
-  </si>
-  <si>
-    <t>陆军防御（奇才）</t>
-  </si>
-  <si>
-    <t>堑壕作战（奇才）</t>
-  </si>
-  <si>
-    <t>空军改革（奇才）</t>
-  </si>
-  <si>
-    <t>空军战斗训练（奇才）</t>
-  </si>
-  <si>
-    <t>海军航空（奇才）</t>
-  </si>
-  <si>
-    <t>反潜作战（奇才）</t>
-  </si>
-  <si>
-    <t>优势火力</t>
-  </si>
-  <si>
-    <t>陆军进攻（专家）</t>
-  </si>
-  <si>
-    <t>装甲部队（专家）</t>
-  </si>
-  <si>
-    <t>航空安全（专家）</t>
-  </si>
-  <si>
-    <t>海军袭击（专家）</t>
-  </si>
-  <si>
-    <t>舰队决战（专家）</t>
-  </si>
-  <si>
-    <t>海军对空防御（专家）</t>
-  </si>
-  <si>
-    <t>决战计划</t>
-  </si>
-  <si>
-    <t>航空安全（大师）</t>
-  </si>
-  <si>
-    <t>海军袭击（大师）</t>
-  </si>
-  <si>
-    <t>海军对空防御（大师）</t>
-  </si>
-  <si>
-    <t>人海突击学说专家</t>
-  </si>
-  <si>
-    <t>人海突击</t>
-  </si>
-  <si>
-    <t>陆军进攻（奇才）</t>
-  </si>
-  <si>
-    <t>装甲部队（奇才）</t>
-  </si>
-  <si>
-    <t>海军袭击（奇才）</t>
-  </si>
-  <si>
-    <t>舰队决战（奇才）</t>
-  </si>
-  <si>
-    <t>海军对空防御（奇才）</t>
-  </si>
-  <si>
-    <t>空战理论家</t>
-  </si>
-  <si>
-    <t>空军</t>
-  </si>
-  <si>
-    <t>陆军计划（专家）</t>
-  </si>
-  <si>
-    <t>炮兵部队（专家）</t>
-  </si>
-  <si>
-    <t>夜间行动（专家）</t>
-  </si>
-  <si>
-    <t>轰炸机拦截（专家）</t>
-  </si>
-  <si>
-    <t>贸易袭击（专家）</t>
-  </si>
-  <si>
-    <t>舰队后勤（专家）</t>
-  </si>
-  <si>
-    <t>空中制胜</t>
-  </si>
-  <si>
-    <t>战略破坏</t>
-  </si>
-  <si>
-    <t>贸易袭击（大师）</t>
-  </si>
-  <si>
-    <t>舰队后勤（大师）</t>
-  </si>
-  <si>
-    <t>密接支援拥护者</t>
-  </si>
-  <si>
-    <t>战场支援</t>
-  </si>
-  <si>
-    <t>陆军计划（奇才）</t>
-  </si>
-  <si>
-    <t>炮兵部队（奇才）</t>
-  </si>
-  <si>
-    <t>夜间行动（奇才）</t>
-  </si>
-  <si>
-    <t>轰炸机拦截（奇才）</t>
-  </si>
-  <si>
-    <t>舰队后勤（奇才）</t>
-  </si>
-  <si>
-    <t>连续作战</t>
-  </si>
-  <si>
-    <t>步兵部队（专家）</t>
-  </si>
-  <si>
-    <t>空中优势（专家）</t>
-  </si>
-  <si>
-    <t>海军改革（专家）</t>
-  </si>
-  <si>
-    <t>两栖作战（专家）</t>
-  </si>
-  <si>
-    <t>空军+CAS伤害修正</t>
-  </si>
-  <si>
-    <t>陆军演习（大师）</t>
-  </si>
-  <si>
-    <t>海军改革（大师）</t>
-  </si>
-  <si>
-    <t>海军理论家</t>
-  </si>
-  <si>
-    <t>海军</t>
-  </si>
-  <si>
-    <t>陆军演习（奇才）</t>
-  </si>
-  <si>
-    <t>步兵部队（奇才）</t>
-  </si>
-  <si>
-    <t>对地支援（奇才）</t>
-  </si>
-  <si>
-    <t>空中优势（奇才）</t>
-  </si>
-  <si>
-    <t>海军改革（奇才）</t>
-  </si>
-  <si>
-    <t>两栖作战（奇才）</t>
-  </si>
-  <si>
-    <t>基地打击</t>
-  </si>
-  <si>
-    <t>陆军改革（专家）</t>
-  </si>
-  <si>
-    <t>特种部队（专家）</t>
-  </si>
-  <si>
-    <t>全天候作战（专家）</t>
-  </si>
-  <si>
-    <t>密接支援（专家）</t>
-  </si>
-  <si>
-    <t>海军机动（专家）</t>
-  </si>
-  <si>
-    <t>潜艇作战（专家）</t>
-  </si>
-  <si>
-    <t>大舰队拥护者</t>
-  </si>
-  <si>
-    <t>存在舰队</t>
-  </si>
-  <si>
-    <t>陆军改革（大师）</t>
-  </si>
-  <si>
-    <t>全天候作战（大师）</t>
-  </si>
-  <si>
-    <t>海军机动（大师）</t>
-  </si>
-  <si>
-    <t>潜艇作战（大师）</t>
-  </si>
-  <si>
-    <t>潜艇专家</t>
-  </si>
-  <si>
-    <t>贸易阻断</t>
-  </si>
-  <si>
-    <t>陆军改革（奇才）</t>
-  </si>
-  <si>
-    <t>特种部队（奇才）</t>
-  </si>
-  <si>
-    <t>密接支援（奇才）</t>
-  </si>
-  <si>
-    <t>海军机动（奇才）</t>
-  </si>
-  <si>
-    <t>潜艇作战（奇才）</t>
-  </si>
-  <si>
-    <t>理论派议会</t>
-  </si>
-  <si>
-    <t>全部</t>
-  </si>
-  <si>
-    <t>陆军组织（专家）</t>
-  </si>
-  <si>
-    <t>骑兵部队（专家）</t>
-  </si>
-  <si>
-    <t>保守派</t>
-  </si>
-  <si>
-    <t>战略轰炸（专家）</t>
-  </si>
-  <si>
-    <t>主力舰作战（专家）</t>
-  </si>
-  <si>
-    <t>火箭科学家</t>
-  </si>
-  <si>
-    <t>火箭科技</t>
-  </si>
-  <si>
-    <t>陆军组织（大师）</t>
-  </si>
-  <si>
-    <t>骑兵部队（大师）</t>
-  </si>
-  <si>
-    <t>战略轰炸（大师）</t>
-  </si>
-  <si>
-    <t>海军火炮制造商（专家）</t>
   </si>
   <si>
     <t>核物理学家</t>
@@ -3325,22 +3409,26 @@
       <c r="I8" s="53" t="s">
         <v>86</v>
       </c>
-      <c r="J8" s="54"/>
-      <c r="K8" s="53"/>
+      <c r="J8" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="K8" s="53" t="s">
+        <v>88</v>
+      </c>
       <c r="L8" s="54" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M8" s="53" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="N8" s="54" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="O8" s="53" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="P8" s="54" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="Q8" s="53" t="s">
         <v>37</v>
@@ -3349,20 +3437,20 @@
         <v>11111</v>
       </c>
       <c r="S8" s="56" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="T8" s="57" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="U8" s="58"/>
       <c r="W8" s="49" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="X8" s="50" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="Y8" s="50" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Z8" s="51" t="s">
         <v>62</v>
@@ -3370,45 +3458,47 @@
     </row>
     <row r="9" customHeight="1" spans="2:26">
       <c r="B9" s="52" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C9" s="53" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D9" s="54" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E9" s="53" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F9" s="54" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G9" s="53" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H9" s="54" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I9" s="53" t="s">
-        <v>103</v>
-      </c>
-      <c r="J9" s="54"/>
+        <v>105</v>
+      </c>
+      <c r="J9" s="54" t="s">
+        <v>106</v>
+      </c>
       <c r="K9" s="53"/>
       <c r="L9" s="59" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="M9" s="53" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="N9" s="54" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="O9" s="53" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="P9" s="54" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="Q9" s="53" t="s">
         <v>37</v>
@@ -3417,59 +3507,59 @@
         <v>11111</v>
       </c>
       <c r="S9" s="56" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="T9" s="57" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="U9" s="58"/>
       <c r="W9" s="49" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="X9" s="50" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="Y9" s="50" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="Z9" s="51" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="2:26">
       <c r="B10" s="52" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C10" s="53" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D10" s="54" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E10" s="53" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F10" s="54" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G10" s="53" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H10" s="54" t="s">
         <v>55</v>
       </c>
       <c r="I10" s="53" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J10" s="54"/>
       <c r="K10" s="53"/>
       <c r="L10" s="54"/>
       <c r="M10" s="53"/>
       <c r="N10" s="54" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="O10" s="53" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="P10" s="59" t="s">
         <v>51</v>
@@ -3480,20 +3570,22 @@
       <c r="R10" s="55">
         <v>11111</v>
       </c>
-      <c r="S10" s="56"/>
+      <c r="S10" s="56" t="s">
+        <v>125</v>
+      </c>
       <c r="T10" s="57"/>
       <c r="U10" s="58"/>
       <c r="W10" s="49" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="X10" s="50" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="Y10" s="50" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="Z10" s="51" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="2:26">
@@ -3501,89 +3593,93 @@
         <v>77</v>
       </c>
       <c r="C11" s="53" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D11" s="54" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E11" s="53" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F11" s="54" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="G11" s="53" t="s">
-        <v>129</v>
-      </c>
-      <c r="H11" s="54"/>
+        <v>133</v>
+      </c>
+      <c r="H11" s="54" t="s">
+        <v>134</v>
+      </c>
       <c r="I11" s="53"/>
       <c r="J11" s="54"/>
       <c r="K11" s="53"/>
       <c r="L11" s="54"/>
       <c r="M11" s="53"/>
       <c r="N11" s="59" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="O11" s="53" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="P11" s="54" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="Q11" s="53" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="R11" s="55">
         <v>11111</v>
       </c>
-      <c r="S11" s="56"/>
+      <c r="S11" s="56" t="s">
+        <v>138</v>
+      </c>
       <c r="T11" s="57"/>
       <c r="U11" s="58"/>
       <c r="W11" s="49" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="X11" s="50" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="Y11" s="50" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Z11" s="51" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="2:26">
       <c r="B12" s="52" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C12" s="53" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="D12" s="54" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E12" s="60" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="F12" s="54"/>
       <c r="G12" s="53"/>
-      <c r="H12" s="54"/>
+      <c r="H12" s="59" t="s">
+        <v>142</v>
+      </c>
       <c r="I12" s="53"/>
       <c r="J12" s="54"/>
       <c r="K12" s="53"/>
       <c r="L12" s="54"/>
       <c r="M12" s="53"/>
       <c r="N12" s="59" t="s">
-        <v>136</v>
-      </c>
-      <c r="O12" s="53" t="s">
+        <v>143</v>
+      </c>
+      <c r="O12" s="53"/>
+      <c r="P12" s="54" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q12" s="53" t="s">
         <v>137</v>
-      </c>
-      <c r="P12" s="54" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q12" s="53" t="s">
-        <v>132</v>
       </c>
       <c r="R12" s="55">
         <v>11111</v>
@@ -3595,23 +3691,25 @@
         <v>19</v>
       </c>
       <c r="X12" s="50" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="Y12" s="50" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="Z12" s="51" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="2:26">
-      <c r="B13" s="52"/>
+      <c r="B13" s="52" t="s">
+        <v>147</v>
+      </c>
       <c r="C13" s="53"/>
       <c r="D13" s="54" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="E13" s="60" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="F13" s="54"/>
       <c r="G13" s="53"/>
@@ -3622,16 +3720,16 @@
       <c r="L13" s="54"/>
       <c r="M13" s="53"/>
       <c r="N13" s="54" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="O13" s="53" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="P13" s="54" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="Q13" s="53" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="R13" s="55">
         <v>11111</v>
@@ -3645,13 +3743,15 @@
       <c r="Z13" s="51"/>
     </row>
     <row r="14" customHeight="1" spans="2:26">
-      <c r="B14" s="52"/>
+      <c r="B14" s="52" t="s">
+        <v>152</v>
+      </c>
       <c r="C14" s="53"/>
       <c r="D14" s="54" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="E14" s="60" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="F14" s="61"/>
       <c r="G14" s="53"/>
@@ -3662,16 +3762,16 @@
       <c r="L14" s="54"/>
       <c r="M14" s="53"/>
       <c r="N14" s="54" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="O14" s="53" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="P14" s="54" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="Q14" s="53" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="R14" s="55">
         <v>11111</v>
@@ -3688,10 +3788,10 @@
       <c r="B15" s="52"/>
       <c r="C15" s="53"/>
       <c r="D15" s="54" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="E15" s="60" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="F15" s="61"/>
       <c r="G15" s="53"/>
@@ -3702,16 +3802,16 @@
       <c r="L15" s="54"/>
       <c r="M15" s="53"/>
       <c r="N15" s="54" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="O15" s="53" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="P15" s="54" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="Q15" s="53" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="R15" s="55">
         <v>11111</v>
@@ -3728,10 +3828,10 @@
       <c r="B16" s="52"/>
       <c r="C16" s="53"/>
       <c r="D16" s="54" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="E16" s="60" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="F16" s="61"/>
       <c r="G16" s="53"/>
@@ -3745,13 +3845,13 @@
         <v>77</v>
       </c>
       <c r="O16" s="53" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="P16" s="54" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="Q16" s="53" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="R16" s="55">
         <v>11111</v>
@@ -3768,10 +3868,10 @@
       <c r="B17" s="52"/>
       <c r="C17" s="53"/>
       <c r="D17" s="54" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="E17" s="60" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="F17" s="61"/>
       <c r="G17" s="53"/>
@@ -3782,20 +3882,16 @@
       <c r="L17" s="54"/>
       <c r="M17" s="53"/>
       <c r="N17" s="54" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="O17" s="53" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="P17" s="54" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q17" s="53" t="s">
-        <v>132</v>
-      </c>
-      <c r="R17" s="55">
-        <v>11111</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="Q17" s="53"/>
+      <c r="R17" s="55"/>
       <c r="S17" s="56"/>
       <c r="T17" s="57"/>
       <c r="U17" s="58"/>
@@ -3811,7 +3907,7 @@
         <v>42</v>
       </c>
       <c r="E18" s="60" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="F18" s="61"/>
       <c r="G18" s="53"/>
@@ -3822,16 +3918,16 @@
       <c r="L18" s="54"/>
       <c r="M18" s="53"/>
       <c r="N18" s="54" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="O18" s="53" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="P18" s="54" t="s">
         <v>68</v>
       </c>
       <c r="Q18" s="53" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="R18" s="55">
         <v>11111</v>
@@ -3847,7 +3943,9 @@
     <row r="19" customHeight="1" spans="2:26">
       <c r="B19" s="52"/>
       <c r="C19" s="53"/>
-      <c r="D19" s="54"/>
+      <c r="D19" s="54" t="s">
+        <v>172</v>
+      </c>
       <c r="E19" s="60"/>
       <c r="F19" s="61"/>
       <c r="G19" s="53"/>
@@ -3858,16 +3956,16 @@
       <c r="L19" s="54"/>
       <c r="M19" s="53"/>
       <c r="N19" s="54" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="O19" s="53" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="P19" s="54" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="Q19" s="53" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="R19" s="55">
         <v>11111</v>
@@ -3883,7 +3981,9 @@
     <row r="20" customHeight="1" spans="2:26">
       <c r="B20" s="52"/>
       <c r="C20" s="53"/>
-      <c r="D20" s="54"/>
+      <c r="D20" s="54" t="s">
+        <v>176</v>
+      </c>
       <c r="E20" s="60"/>
       <c r="F20" s="61"/>
       <c r="G20" s="53"/>
@@ -3894,16 +3994,16 @@
       <c r="L20" s="54"/>
       <c r="M20" s="53"/>
       <c r="N20" s="59" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="O20" s="53" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="P20" s="54" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="Q20" s="53" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="R20" s="55">
         <v>11111</v>
@@ -3919,7 +4019,9 @@
     <row r="21" customHeight="1" spans="2:26">
       <c r="B21" s="52"/>
       <c r="C21" s="53"/>
-      <c r="D21" s="54"/>
+      <c r="D21" s="54" t="s">
+        <v>180</v>
+      </c>
       <c r="E21" s="60"/>
       <c r="F21" s="61"/>
       <c r="G21" s="53"/>
@@ -3929,17 +4031,17 @@
       <c r="K21" s="53"/>
       <c r="L21" s="54"/>
       <c r="M21" s="53"/>
-      <c r="N21" s="54" t="s">
-        <v>169</v>
+      <c r="N21" s="59" t="s">
+        <v>181</v>
       </c>
       <c r="O21" s="53" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="P21" s="54" t="s">
         <v>33</v>
       </c>
       <c r="Q21" s="53" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="R21" s="55">
         <v>11111</v>
@@ -3955,7 +4057,9 @@
     <row r="22" customHeight="1" spans="2:26">
       <c r="B22" s="52"/>
       <c r="C22" s="53"/>
-      <c r="D22" s="54"/>
+      <c r="D22" s="54" t="s">
+        <v>183</v>
+      </c>
       <c r="E22" s="60"/>
       <c r="F22" s="61"/>
       <c r="G22" s="53"/>
@@ -3965,13 +4069,15 @@
       <c r="K22" s="53"/>
       <c r="L22" s="54"/>
       <c r="M22" s="53"/>
-      <c r="N22" s="54"/>
+      <c r="N22" s="54" t="s">
+        <v>184</v>
+      </c>
       <c r="O22" s="53"/>
       <c r="P22" s="54" t="s">
         <v>74</v>
       </c>
       <c r="Q22" s="53" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="R22" s="55">
         <v>11111</v>
@@ -3987,7 +4093,9 @@
     <row r="23" customHeight="1" spans="2:26">
       <c r="B23" s="52"/>
       <c r="C23" s="53"/>
-      <c r="D23" s="54"/>
+      <c r="D23" s="54" t="s">
+        <v>185</v>
+      </c>
       <c r="E23" s="60"/>
       <c r="F23" s="61"/>
       <c r="G23" s="53"/>
@@ -3997,13 +4105,15 @@
       <c r="K23" s="53"/>
       <c r="L23" s="54"/>
       <c r="M23" s="53"/>
-      <c r="N23" s="54"/>
+      <c r="N23" s="54" t="s">
+        <v>186</v>
+      </c>
       <c r="O23" s="53"/>
       <c r="P23" s="54" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="Q23" s="53" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="R23" s="55">
         <v>11111</v>
@@ -4019,7 +4129,9 @@
     <row r="24" customHeight="1" spans="2:26">
       <c r="B24" s="52"/>
       <c r="C24" s="53"/>
-      <c r="D24" s="54"/>
+      <c r="D24" s="54" t="s">
+        <v>187</v>
+      </c>
       <c r="E24" s="60"/>
       <c r="F24" s="61"/>
       <c r="G24" s="53"/>
@@ -4029,13 +4141,15 @@
       <c r="K24" s="53"/>
       <c r="L24" s="54"/>
       <c r="M24" s="53"/>
-      <c r="N24" s="54"/>
+      <c r="N24" s="59" t="s">
+        <v>188</v>
+      </c>
       <c r="O24" s="53"/>
       <c r="P24" s="54" t="s">
         <v>47</v>
       </c>
       <c r="Q24" s="53" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="R24" s="55">
         <v>11111</v>
@@ -4051,7 +4165,9 @@
     <row r="25" customHeight="1" spans="2:26">
       <c r="B25" s="52"/>
       <c r="C25" s="61"/>
-      <c r="D25" s="54"/>
+      <c r="D25" s="54" t="s">
+        <v>189</v>
+      </c>
       <c r="E25" s="60"/>
       <c r="F25" s="61"/>
       <c r="G25" s="61"/>
@@ -4061,13 +4177,15 @@
       <c r="K25" s="61"/>
       <c r="L25" s="54"/>
       <c r="M25" s="61"/>
-      <c r="N25" s="54"/>
+      <c r="N25" s="59" t="s">
+        <v>190</v>
+      </c>
       <c r="O25" s="61"/>
       <c r="P25" s="54" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="Q25" s="61" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="R25" s="55">
         <v>11111</v>
@@ -4079,7 +4197,9 @@
     <row r="26" customHeight="1" spans="2:26">
       <c r="B26" s="52"/>
       <c r="C26" s="61"/>
-      <c r="D26" s="54"/>
+      <c r="D26" s="54" t="s">
+        <v>191</v>
+      </c>
       <c r="E26" s="60"/>
       <c r="F26" s="61"/>
       <c r="G26" s="61"/>
@@ -4089,13 +4209,15 @@
       <c r="K26" s="61"/>
       <c r="L26" s="54"/>
       <c r="M26" s="61"/>
-      <c r="N26" s="54"/>
+      <c r="N26" s="59" t="s">
+        <v>192</v>
+      </c>
       <c r="O26" s="61"/>
       <c r="P26" s="54" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="Q26" s="53" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="R26" s="55">
         <v>11111</v>
@@ -4117,13 +4239,15 @@
       <c r="K27" s="53"/>
       <c r="L27" s="54"/>
       <c r="M27" s="53"/>
-      <c r="N27" s="54"/>
+      <c r="N27" s="59" t="s">
+        <v>194</v>
+      </c>
       <c r="O27" s="53"/>
       <c r="P27" s="54" t="s">
         <v>83</v>
       </c>
       <c r="Q27" s="53" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="R27" s="55">
         <v>11111</v>
@@ -4151,7 +4275,7 @@
         <v>77</v>
       </c>
       <c r="Q28" s="53" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="R28" s="55">
         <v>11111</v>
@@ -4176,10 +4300,10 @@
       <c r="N29" s="53"/>
       <c r="O29" s="53"/>
       <c r="P29" s="59" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="Q29" s="53" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="R29" s="55">
         <v>11111</v>
@@ -4207,7 +4331,7 @@
         <v>31</v>
       </c>
       <c r="Q30" s="53" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="R30" s="55">
         <v>11111</v>
@@ -4235,7 +4359,7 @@
         <v>49</v>
       </c>
       <c r="Q31" s="53" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="R31" s="55">
         <v>11111</v>
@@ -4260,10 +4384,10 @@
       <c r="N32" s="53"/>
       <c r="O32" s="53"/>
       <c r="P32" s="54" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="Q32" s="53" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="R32" s="55">
         <v>11111</v>
@@ -4291,7 +4415,7 @@
         <v>70</v>
       </c>
       <c r="Q33" s="53" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="R33" s="55">
         <v>11111</v>
@@ -4316,10 +4440,10 @@
       <c r="N34" s="53"/>
       <c r="O34" s="53"/>
       <c r="P34" s="54" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="Q34" s="53" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="R34" s="55">
         <v>11111</v>
@@ -4347,7 +4471,7 @@
         <v>66</v>
       </c>
       <c r="Q35" s="53" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="R35" s="55">
         <v>11111</v>
@@ -4371,7 +4495,9 @@
       <c r="M36" s="60"/>
       <c r="N36" s="53"/>
       <c r="O36" s="53"/>
-      <c r="P36" s="54"/>
+      <c r="P36" s="54" t="s">
+        <v>196</v>
+      </c>
       <c r="Q36" s="53"/>
       <c r="R36" s="55"/>
       <c r="S36" s="56"/>
@@ -4386,7 +4512,9 @@
       <c r="I37" s="64"/>
       <c r="L37" s="63"/>
       <c r="M37" s="64"/>
-      <c r="P37" s="63"/>
+      <c r="P37" s="63" t="s">
+        <v>197</v>
+      </c>
       <c r="R37" s="65"/>
       <c r="S37" s="56"/>
       <c r="T37" s="57"/>
@@ -4400,7 +4528,9 @@
       <c r="I38" s="64"/>
       <c r="L38" s="63"/>
       <c r="M38" s="64"/>
-      <c r="P38" s="63"/>
+      <c r="P38" s="63" t="s">
+        <v>198</v>
+      </c>
       <c r="R38" s="65"/>
       <c r="S38" s="56"/>
       <c r="T38" s="57"/>
@@ -4414,7 +4544,9 @@
       <c r="I39" s="64"/>
       <c r="L39" s="63"/>
       <c r="M39" s="64"/>
-      <c r="P39" s="63"/>
+      <c r="P39" s="63" t="s">
+        <v>199</v>
+      </c>
       <c r="R39" s="65"/>
       <c r="S39" s="56"/>
       <c r="T39" s="57"/>
@@ -4428,7 +4560,9 @@
       <c r="I40" s="64"/>
       <c r="L40" s="63"/>
       <c r="M40" s="64"/>
-      <c r="P40" s="63"/>
+      <c r="P40" s="63" t="s">
+        <v>200</v>
+      </c>
       <c r="R40" s="65"/>
       <c r="S40" s="56"/>
       <c r="T40" s="57"/>
@@ -5332,56 +5466,56 @@
         <v>4</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>173</v>
+        <v>201</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>174</v>
+        <v>202</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>175</v>
+        <v>203</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>176</v>
+        <v>204</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>177</v>
+        <v>205</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>178</v>
+        <v>206</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>179</v>
+        <v>207</v>
       </c>
     </row>
     <row r="3" spans="2:15">
       <c r="B3" s="5" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>180</v>
+        <v>208</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>181</v>
+        <v>209</v>
       </c>
       <c r="F3" s="8"/>
       <c r="G3" s="7" t="s">
-        <v>182</v>
+        <v>210</v>
       </c>
       <c r="H3" s="8"/>
       <c r="I3" s="7" t="s">
-        <v>183</v>
+        <v>211</v>
       </c>
       <c r="J3" s="8"/>
       <c r="K3" s="7" t="s">
-        <v>184</v>
+        <v>212</v>
       </c>
       <c r="L3" s="8"/>
       <c r="M3" s="9" t="s">
-        <v>185</v>
+        <v>71</v>
       </c>
       <c r="N3" s="8"/>
       <c r="O3" s="7" t="s">
-        <v>186</v>
+        <v>213</v>
       </c>
     </row>
     <row r="4" spans="2:15">
@@ -5389,115 +5523,115 @@
         <v>84</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>187</v>
+        <v>214</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F4" s="8"/>
       <c r="G4" s="7" t="s">
-        <v>188</v>
+        <v>215</v>
       </c>
       <c r="H4" s="8"/>
       <c r="I4" s="7" t="s">
-        <v>189</v>
+        <v>216</v>
       </c>
       <c r="J4" s="8"/>
       <c r="K4" s="7" t="s">
-        <v>190</v>
+        <v>217</v>
       </c>
       <c r="L4" s="8"/>
       <c r="M4" s="12" t="s">
-        <v>71</v>
+        <v>218</v>
       </c>
       <c r="N4" s="8"/>
       <c r="O4" s="7" t="s">
-        <v>191</v>
+        <v>219</v>
       </c>
     </row>
     <row r="5" spans="2:15">
       <c r="B5" s="13" t="s">
-        <v>192</v>
+        <v>220</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>193</v>
+        <v>221</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>194</v>
+        <v>222</v>
       </c>
       <c r="F5" s="8"/>
       <c r="G5" s="7" t="s">
-        <v>195</v>
+        <v>223</v>
       </c>
       <c r="H5" s="8"/>
       <c r="I5" s="7" t="s">
-        <v>196</v>
+        <v>224</v>
       </c>
       <c r="J5" s="8"/>
       <c r="K5" s="7" t="s">
-        <v>197</v>
+        <v>225</v>
       </c>
       <c r="L5" s="8"/>
       <c r="M5" s="12" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="N5" s="8"/>
       <c r="O5" s="7" t="s">
-        <v>199</v>
+        <v>227</v>
       </c>
     </row>
     <row r="6" spans="2:15">
       <c r="B6" s="15" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>200</v>
+        <v>228</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>201</v>
+        <v>229</v>
       </c>
       <c r="F6" s="8"/>
       <c r="G6" s="17" t="s">
-        <v>202</v>
+        <v>230</v>
       </c>
       <c r="H6" s="8"/>
       <c r="I6" s="17" t="s">
-        <v>203</v>
+        <v>231</v>
       </c>
       <c r="J6" s="8"/>
       <c r="K6" s="17" t="s">
-        <v>204</v>
+        <v>232</v>
       </c>
       <c r="L6" s="8"/>
       <c r="M6" s="18" t="s">
-        <v>205</v>
+        <v>233</v>
       </c>
       <c r="N6" s="8"/>
       <c r="O6" s="17" t="s">
-        <v>206</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7" spans="2:15">
       <c r="B7" s="13" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>207</v>
+        <v>235</v>
       </c>
       <c r="E7" s="17" t="s">
         <v>30</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="17" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="H7" s="8"/>
       <c r="I7" s="17" t="s">
-        <v>208</v>
+        <v>236</v>
       </c>
       <c r="J7" s="8"/>
       <c r="K7" s="17" t="s">
-        <v>209</v>
+        <v>237</v>
       </c>
       <c r="L7" s="8"/>
       <c r="M7" s="18" t="s">
@@ -5505,123 +5639,123 @@
       </c>
       <c r="N7" s="8"/>
       <c r="O7" s="17" t="s">
-        <v>210</v>
+        <v>238</v>
       </c>
     </row>
     <row r="8" spans="2:15">
       <c r="B8" s="15" t="s">
-        <v>211</v>
+        <v>239</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>212</v>
+        <v>240</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="F8" s="8"/>
       <c r="G8" s="17" t="s">
-        <v>214</v>
+        <v>242</v>
       </c>
       <c r="H8" s="8"/>
       <c r="I8" s="17" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J8" s="8"/>
       <c r="K8" s="17" t="s">
-        <v>215</v>
+        <v>243</v>
       </c>
       <c r="L8" s="8"/>
       <c r="M8" s="18" t="s">
-        <v>216</v>
+        <v>244</v>
       </c>
       <c r="N8" s="8"/>
       <c r="O8" s="17" t="s">
-        <v>217</v>
+        <v>245</v>
       </c>
     </row>
     <row r="9" spans="2:15">
       <c r="B9" s="13" t="s">
-        <v>218</v>
+        <v>246</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>219</v>
+        <v>247</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>220</v>
+        <v>248</v>
       </c>
       <c r="F9" s="8"/>
       <c r="G9" s="7" t="s">
-        <v>221</v>
+        <v>249</v>
       </c>
       <c r="H9" s="8"/>
       <c r="I9" s="7" t="s">
-        <v>222</v>
+        <v>250</v>
       </c>
       <c r="J9" s="8"/>
       <c r="K9" s="7" t="s">
-        <v>223</v>
+        <v>251</v>
       </c>
       <c r="L9" s="8"/>
       <c r="M9" s="12" t="s">
-        <v>224</v>
+        <v>252</v>
       </c>
       <c r="N9" s="8"/>
       <c r="O9" s="7" t="s">
-        <v>225</v>
+        <v>253</v>
       </c>
     </row>
     <row r="10" spans="2:15">
       <c r="B10" s="15" t="s">
-        <v>226</v>
+        <v>254</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>227</v>
+        <v>255</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>48</v>
       </c>
       <c r="F10" s="8"/>
       <c r="G10" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="H10" s="8"/>
       <c r="I10" s="7" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="J10" s="8"/>
       <c r="K10" s="7" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="L10" s="8"/>
       <c r="M10" s="12" t="s">
-        <v>228</v>
+        <v>256</v>
       </c>
       <c r="N10" s="8"/>
       <c r="O10" s="7" t="s">
-        <v>229</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11" spans="2:15">
       <c r="B11" s="13" t="s">
-        <v>230</v>
+        <v>258</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>231</v>
+        <v>259</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>232</v>
+        <v>260</v>
       </c>
       <c r="F11" s="8"/>
       <c r="G11" s="7" t="s">
-        <v>233</v>
+        <v>261</v>
       </c>
       <c r="H11" s="8"/>
       <c r="I11" s="7" t="s">
-        <v>234</v>
+        <v>262</v>
       </c>
       <c r="J11" s="8"/>
       <c r="K11" s="7" t="s">
-        <v>235</v>
+        <v>263</v>
       </c>
       <c r="L11" s="8"/>
       <c r="M11" s="12" t="s">
@@ -5629,7 +5763,7 @@
       </c>
       <c r="N11" s="8"/>
       <c r="O11" s="7" t="s">
-        <v>236</v>
+        <v>264</v>
       </c>
     </row>
     <row r="12" spans="2:15">
@@ -5637,14 +5771,14 @@
         <v>46</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>237</v>
+        <v>265</v>
       </c>
       <c r="E12" s="17" t="s">
         <v>69</v>
       </c>
       <c r="F12" s="8"/>
       <c r="G12" s="17" t="s">
-        <v>238</v>
+        <v>266</v>
       </c>
       <c r="H12" s="8"/>
       <c r="I12" s="17" t="s">
@@ -5652,15 +5786,15 @@
       </c>
       <c r="J12" s="8"/>
       <c r="K12" s="17" t="s">
-        <v>239</v>
+        <v>267</v>
       </c>
       <c r="L12" s="8"/>
       <c r="M12" s="18" t="s">
-        <v>240</v>
+        <v>268</v>
       </c>
       <c r="N12" s="8"/>
       <c r="O12" s="17" t="s">
-        <v>241</v>
+        <v>269</v>
       </c>
     </row>
     <row r="13" spans="2:15">
@@ -5668,14 +5802,14 @@
         <v>28</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>242</v>
+        <v>270</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>243</v>
+        <v>271</v>
       </c>
       <c r="F13" s="8"/>
       <c r="G13" s="17" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="H13" s="8"/>
       <c r="I13" s="17" t="s">
@@ -5687,42 +5821,42 @@
       </c>
       <c r="L13" s="8"/>
       <c r="M13" s="18" t="s">
-        <v>244</v>
+        <v>272</v>
       </c>
       <c r="N13" s="8"/>
       <c r="O13" s="17" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" spans="2:15">
       <c r="B14" s="15" t="s">
-        <v>245</v>
+        <v>273</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>246</v>
+        <v>274</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>247</v>
+        <v>275</v>
       </c>
       <c r="F14" s="8"/>
       <c r="G14" s="17" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="H14" s="8"/>
       <c r="I14" s="17" t="s">
-        <v>249</v>
+        <v>277</v>
       </c>
       <c r="J14" s="8"/>
       <c r="K14" s="17" t="s">
-        <v>250</v>
+        <v>278</v>
       </c>
       <c r="L14" s="8"/>
       <c r="M14" s="18" t="s">
-        <v>251</v>
+        <v>279</v>
       </c>
       <c r="N14" s="8"/>
       <c r="O14" s="17" t="s">
-        <v>252</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="2:15">
@@ -5730,76 +5864,76 @@
         <v>67</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>253</v>
+        <v>281</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>254</v>
+        <v>282</v>
       </c>
       <c r="F15" s="8"/>
       <c r="G15" s="7" t="s">
-        <v>255</v>
+        <v>283</v>
       </c>
       <c r="H15" s="8"/>
       <c r="I15" s="7" t="s">
-        <v>256</v>
+        <v>284</v>
       </c>
       <c r="J15" s="8"/>
       <c r="K15" s="7" t="s">
-        <v>257</v>
+        <v>285</v>
       </c>
       <c r="L15" s="8"/>
       <c r="M15" s="12" t="s">
-        <v>258</v>
+        <v>286</v>
       </c>
       <c r="N15" s="8"/>
       <c r="O15" s="7" t="s">
-        <v>259</v>
+        <v>287</v>
       </c>
     </row>
     <row r="16" spans="2:15">
       <c r="B16" s="15" t="s">
-        <v>260</v>
+        <v>288</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>261</v>
+        <v>289</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>262</v>
+        <v>290</v>
       </c>
       <c r="F16" s="8"/>
       <c r="G16" s="7" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="H16" s="8"/>
       <c r="I16" s="7" t="s">
-        <v>263</v>
+        <v>291</v>
       </c>
       <c r="J16" s="8"/>
       <c r="K16" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L16" s="8"/>
       <c r="M16" s="12" t="s">
-        <v>264</v>
+        <v>88</v>
       </c>
       <c r="N16" s="8"/>
       <c r="O16" s="7" t="s">
-        <v>265</v>
+        <v>292</v>
       </c>
     </row>
     <row r="17" spans="2:15">
       <c r="B17" s="19" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>267</v>
+        <v>294</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>268</v>
+        <v>295</v>
       </c>
       <c r="F17" s="8"/>
       <c r="G17" s="7" t="s">
-        <v>269</v>
+        <v>296</v>
       </c>
       <c r="H17" s="8"/>
       <c r="I17" s="7" t="s">
@@ -5807,148 +5941,148 @@
       </c>
       <c r="J17" s="8"/>
       <c r="K17" s="7" t="s">
-        <v>270</v>
+        <v>297</v>
       </c>
       <c r="L17" s="8"/>
       <c r="M17" s="12" t="s">
-        <v>271</v>
+        <v>298</v>
       </c>
       <c r="N17" s="8"/>
       <c r="O17" s="7" t="s">
-        <v>272</v>
+        <v>299</v>
       </c>
     </row>
     <row r="18" ht="14.25" spans="2:15">
       <c r="B18" s="15" t="s">
-        <v>273</v>
+        <v>300</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>274</v>
+        <v>301</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>275</v>
+        <v>302</v>
       </c>
       <c r="F18" s="8"/>
       <c r="G18" s="17" t="s">
-        <v>276</v>
+        <v>303</v>
       </c>
       <c r="H18" s="8"/>
       <c r="I18" s="21" t="s">
-        <v>277</v>
+        <v>304</v>
       </c>
       <c r="J18" s="8"/>
       <c r="K18" s="17" t="s">
-        <v>278</v>
+        <v>305</v>
       </c>
       <c r="L18" s="8"/>
       <c r="M18" s="18" t="s">
-        <v>277</v>
+        <v>304</v>
       </c>
       <c r="N18" s="8"/>
       <c r="O18" s="17" t="s">
-        <v>279</v>
+        <v>306</v>
       </c>
     </row>
     <row r="19" spans="2:15">
       <c r="B19" s="13" t="s">
-        <v>280</v>
+        <v>307</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>281</v>
+        <v>308</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>282</v>
+        <v>309</v>
       </c>
       <c r="F19" s="8"/>
       <c r="G19" s="17" t="s">
-        <v>283</v>
+        <v>310</v>
       </c>
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
       <c r="J19" s="8"/>
       <c r="K19" s="17" t="s">
-        <v>284</v>
+        <v>311</v>
       </c>
       <c r="L19" s="8"/>
       <c r="M19" s="12" t="s">
-        <v>285</v>
+        <v>312</v>
       </c>
       <c r="N19" s="8"/>
       <c r="O19" s="17" t="s">
-        <v>137</v>
+        <v>313</v>
       </c>
     </row>
     <row r="20" spans="2:15">
       <c r="B20" s="15" t="s">
-        <v>286</v>
+        <v>314</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>287</v>
+        <v>315</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>288</v>
+        <v>316</v>
       </c>
       <c r="F20" s="8"/>
       <c r="G20" s="17" t="s">
-        <v>289</v>
+        <v>317</v>
       </c>
       <c r="H20" s="8"/>
       <c r="I20" s="8"/>
       <c r="J20" s="8"/>
       <c r="K20" s="17" t="s">
-        <v>290</v>
+        <v>318</v>
       </c>
       <c r="L20" s="8"/>
       <c r="M20" s="12" t="s">
-        <v>291</v>
+        <v>319</v>
       </c>
       <c r="N20" s="8"/>
       <c r="O20" s="17" t="s">
-        <v>292</v>
+        <v>320</v>
       </c>
     </row>
     <row r="21" ht="14.25" spans="2:15">
       <c r="B21" s="13" t="s">
-        <v>293</v>
+        <v>321</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>281</v>
+        <v>308</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>294</v>
+        <v>322</v>
       </c>
       <c r="F21" s="8"/>
       <c r="G21" s="7" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="H21" s="8"/>
       <c r="I21" s="8"/>
       <c r="J21" s="8"/>
       <c r="K21" s="7" t="s">
-        <v>295</v>
+        <v>323</v>
       </c>
       <c r="L21" s="8"/>
       <c r="M21" s="22" t="s">
-        <v>296</v>
+        <v>324</v>
       </c>
       <c r="N21" s="8"/>
       <c r="O21" s="7" t="s">
-        <v>297</v>
+        <v>325</v>
       </c>
     </row>
     <row r="22" ht="14.25" spans="2:15">
       <c r="B22" s="23" t="s">
-        <v>298</v>
+        <v>326</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>287</v>
+        <v>315</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>299</v>
+        <v>327</v>
       </c>
       <c r="F22" s="8"/>
       <c r="G22" s="7" t="s">
-        <v>300</v>
+        <v>328</v>
       </c>
       <c r="H22" s="8"/>
       <c r="I22" s="8"/>
@@ -5960,49 +6094,49 @@
       <c r="M22" s="8"/>
       <c r="N22" s="8"/>
       <c r="O22" s="7" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="23" spans="2:15">
       <c r="E23" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F23" s="8"/>
       <c r="G23" s="7" t="s">
-        <v>301</v>
+        <v>329</v>
       </c>
       <c r="H23" s="8"/>
       <c r="I23" s="8"/>
       <c r="J23" s="8"/>
       <c r="K23" s="7" t="s">
-        <v>302</v>
+        <v>330</v>
       </c>
       <c r="L23" s="8"/>
       <c r="M23" s="8"/>
       <c r="N23" s="8"/>
       <c r="O23" s="7" t="s">
-        <v>303</v>
+        <v>331</v>
       </c>
     </row>
     <row r="24" spans="2:15">
       <c r="E24" s="17" t="s">
-        <v>304</v>
+        <v>332</v>
       </c>
       <c r="F24" s="8"/>
       <c r="G24" s="17" t="s">
-        <v>305</v>
+        <v>333</v>
       </c>
       <c r="H24" s="8"/>
       <c r="I24" s="8"/>
       <c r="J24" s="8"/>
       <c r="K24" s="17" t="s">
-        <v>306</v>
+        <v>334</v>
       </c>
       <c r="L24" s="8"/>
       <c r="M24" s="8"/>
       <c r="N24" s="8"/>
       <c r="O24" s="17" t="s">
-        <v>307</v>
+        <v>335</v>
       </c>
     </row>
     <row r="25" spans="2:15">
@@ -6011,55 +6145,55 @@
       </c>
       <c r="F25" s="8"/>
       <c r="G25" s="17" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="H25" s="8"/>
       <c r="I25" s="8"/>
       <c r="J25" s="8"/>
       <c r="K25" s="17" t="s">
-        <v>308</v>
+        <v>336</v>
       </c>
       <c r="L25" s="8"/>
       <c r="M25" s="8"/>
       <c r="N25" s="8"/>
       <c r="O25" s="17" t="s">
-        <v>309</v>
+        <v>337</v>
       </c>
     </row>
     <row r="26" ht="14.25" spans="2:15">
       <c r="E26" s="17" t="s">
-        <v>310</v>
+        <v>338</v>
       </c>
       <c r="F26" s="8"/>
       <c r="G26" s="17" t="s">
-        <v>311</v>
+        <v>339</v>
       </c>
       <c r="H26" s="8"/>
       <c r="I26" s="8"/>
       <c r="J26" s="8"/>
       <c r="K26" s="17" t="s">
-        <v>312</v>
+        <v>340</v>
       </c>
       <c r="L26" s="8"/>
       <c r="M26" s="8"/>
       <c r="N26" s="8"/>
       <c r="O26" s="21" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="2:15">
       <c r="E27" s="7" t="s">
-        <v>313</v>
+        <v>341</v>
       </c>
       <c r="F27" s="8"/>
       <c r="G27" s="7" t="s">
-        <v>314</v>
+        <v>342</v>
       </c>
       <c r="H27" s="8"/>
       <c r="I27" s="8"/>
       <c r="J27" s="8"/>
       <c r="K27" s="7" t="s">
-        <v>315</v>
+        <v>343</v>
       </c>
       <c r="L27" s="8"/>
       <c r="M27" s="8"/>
@@ -6068,17 +6202,17 @@
     </row>
     <row r="28" spans="2:15">
       <c r="E28" s="7" t="s">
-        <v>316</v>
+        <v>344</v>
       </c>
       <c r="F28" s="8"/>
       <c r="G28" s="7" t="s">
-        <v>317</v>
+        <v>345</v>
       </c>
       <c r="H28" s="8"/>
       <c r="I28" s="8"/>
       <c r="J28" s="8"/>
       <c r="K28" s="7" t="s">
-        <v>318</v>
+        <v>346</v>
       </c>
       <c r="L28" s="8"/>
       <c r="M28" s="8"/>
@@ -6087,17 +6221,17 @@
     </row>
     <row r="29" ht="14.25" spans="2:15">
       <c r="E29" s="7" t="s">
-        <v>319</v>
+        <v>347</v>
       </c>
       <c r="F29" s="8"/>
       <c r="G29" s="7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H29" s="8"/>
       <c r="I29" s="8"/>
       <c r="J29" s="8"/>
       <c r="K29" s="25" t="s">
-        <v>320</v>
+        <v>348</v>
       </c>
       <c r="L29" s="8"/>
       <c r="M29" s="8"/>
@@ -6106,11 +6240,11 @@
     </row>
     <row r="30" ht="14.25" spans="2:15">
       <c r="E30" s="21" t="s">
-        <v>277</v>
+        <v>304</v>
       </c>
       <c r="F30" s="8"/>
       <c r="G30" s="17" t="s">
-        <v>321</v>
+        <v>349</v>
       </c>
       <c r="H30" s="8"/>
       <c r="I30" s="8"/>
@@ -6125,7 +6259,7 @@
       <c r="E31" s="8"/>
       <c r="F31" s="8"/>
       <c r="G31" s="17" t="s">
-        <v>322</v>
+        <v>350</v>
       </c>
       <c r="H31" s="8"/>
       <c r="I31" s="8"/>
@@ -6155,7 +6289,7 @@
       <c r="E33" s="8"/>
       <c r="F33" s="8"/>
       <c r="G33" s="7" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="H33" s="8"/>
       <c r="I33" s="8"/>
@@ -6170,7 +6304,7 @@
       <c r="E34" s="8"/>
       <c r="F34" s="8"/>
       <c r="G34" s="7" t="s">
-        <v>323</v>
+        <v>351</v>
       </c>
       <c r="H34" s="8"/>
       <c r="I34" s="8"/>
@@ -6185,7 +6319,7 @@
       <c r="E35" s="8"/>
       <c r="F35" s="8"/>
       <c r="G35" s="25" t="s">
-        <v>324</v>
+        <v>352</v>
       </c>
       <c r="H35" s="8"/>
       <c r="I35" s="8"/>

--- a/WIP/月茗/LAN阿斯特莱雅/阿斯特莱雅-军事人员配置表.xlsx
+++ b/WIP/月茗/LAN阿斯特莱雅/阿斯特莱雅-军事人员配置表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" firstSheet="2"/>
+    <workbookView windowWidth="21615" windowHeight="15855" firstSheet="2"/>
   </bookViews>
   <sheets>
     <sheet name="PCR" sheetId="3" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="374">
   <si>
     <t>阿斯特莱雅</t>
   </si>
@@ -114,7 +114,9 @@
     <t>酗酒的会计</t>
   </si>
   <si>
-    <t>已启用墨丘利财团</t>
+    <t>已启用墨丘利财团
+或
+拥有藤堂秋乃</t>
   </si>
   <si>
     <t>阿贺斗紫布菜</t>
@@ -184,12 +186,6 @@
   </si>
   <si>
     <t>陆军机动（大师）</t>
-  </si>
-  <si>
-    <t>出云宫子</t>
-  </si>
-  <si>
-    <t>贸易袭击（奇才）</t>
   </si>
   <si>
     <t>远野帆稀</t>
@@ -253,7 +249,7 @@
     <t>三角千歌</t>
   </si>
   <si>
-    <t>海军航空（专家）</t>
+    <t>海军航空（大师）</t>
   </si>
   <si>
     <t>古蕾雅</t>
@@ -542,10 +538,6 @@
   </si>
   <si>
     <t>财团千金</t>
-  </si>
-  <si>
-    <t>不是当前领导人
-已启用墨丘利财团</t>
   </si>
   <si>
     <t>穗高未奏希</t>
@@ -660,6 +652,9 @@
     <t>海军袭击（奇才）</t>
   </si>
   <si>
+    <t>石桥步美</t>
+  </si>
+  <si>
     <t>露易丝玛丽</t>
   </si>
   <si>
@@ -690,9 +685,18 @@
     <t>织原茉莉</t>
   </si>
   <si>
+    <t>库露露</t>
+  </si>
+  <si>
+    <t>金融硕士</t>
+  </si>
+  <si>
     <t>海军上将</t>
   </si>
   <si>
+    <t>出云宫子</t>
+  </si>
+  <si>
     <t>茜美美</t>
   </si>
   <si>
@@ -702,7 +706,7 @@
     <t>森近铃</t>
   </si>
   <si>
-    <t>库露露</t>
+    <t>鬼道嘉夜</t>
   </si>
   <si>
     <t>远见空花</t>
@@ -711,12 +715,6 @@
     <t>一华牡丹</t>
   </si>
   <si>
-    <t>石桥步美</t>
-  </si>
-  <si>
-    <t>鬼道嘉夜</t>
-  </si>
-  <si>
     <t>对应学说</t>
   </si>
   <si>
@@ -753,6 +751,9 @@
     <t>空军战斗训练（专家）</t>
   </si>
   <si>
+    <t>海军航空（专家）</t>
+  </si>
+  <si>
     <t>反潜作战（专家）</t>
   </si>
   <si>
@@ -768,9 +769,6 @@
     <t>空军战斗训练（大师）</t>
   </si>
   <si>
-    <t>海军航空（大师）</t>
-  </si>
-  <si>
     <t>反潜作战（大师）</t>
   </si>
   <si>
@@ -907,6 +905,9 @@
   </si>
   <si>
     <t>轰炸机拦截（奇才）</t>
+  </si>
+  <si>
+    <t>贸易袭击（奇才）</t>
   </si>
   <si>
     <t>舰队后勤（奇才）</t>
@@ -2364,7 +2365,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2482,9 +2483,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2551,27 +2549,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2600,9 +2589,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3223,2524 +3209,2490 @@
         <v>9</v>
       </c>
       <c r="R3" s="38"/>
-      <c r="S3" s="39"/>
-      <c r="T3" s="40" t="s">
+      <c r="S3" s="35"/>
+      <c r="T3" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="U3" s="40"/>
-      <c r="V3" s="41"/>
-      <c r="X3" s="42" t="s">
+      <c r="U3" s="39"/>
+      <c r="V3" s="40"/>
+      <c r="X3" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="Y3" s="43" t="s">
+      <c r="Y3" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="Z3" s="43" t="s">
+      <c r="Z3" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AA3" s="44" t="s">
+      <c r="AA3" s="43" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="2:27">
-      <c r="B4" s="45" t="s">
+      <c r="B4" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="46" t="s">
+      <c r="C4" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="46" t="s">
+      <c r="D4" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="46" t="s">
+      <c r="E4" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="46" t="s">
+      <c r="F4" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="46" t="s">
+      <c r="G4" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="46" t="s">
+      <c r="H4" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="46" t="s">
+      <c r="I4" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="J4" s="46" t="s">
+      <c r="J4" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="K4" s="46" t="s">
+      <c r="K4" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="L4" s="46" t="s">
+      <c r="L4" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="M4" s="46" t="s">
+      <c r="M4" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="N4" s="46" t="s">
+      <c r="N4" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="O4" s="46" t="s">
+      <c r="O4" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="P4" s="47" t="s">
+      <c r="P4" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="Q4" s="46" t="s">
+      <c r="Q4" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="R4" s="48" t="s">
+      <c r="R4" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="S4" s="49" t="s">
+      <c r="S4" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="T4" s="50" t="s">
+      <c r="T4" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="U4" s="50" t="s">
+      <c r="U4" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="V4" s="51" t="s">
+      <c r="V4" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="X4" s="52" t="s">
+      <c r="X4" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="Y4" s="53" t="s">
+      <c r="Y4" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="Z4" s="53" t="s">
+      <c r="Z4" s="52" t="s">
         <v>22</v>
       </c>
-      <c r="AA4" s="54" t="s">
+      <c r="AA4" s="53" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="2:27">
-      <c r="B5" s="55" t="s">
+      <c r="B5" s="54" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="56" t="s">
+      <c r="C5" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="57" t="s">
+      <c r="D5" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="56" t="s">
+      <c r="E5" s="55" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="56" t="s">
+      <c r="F5" s="55" t="s">
         <v>28</v>
       </c>
-      <c r="G5" s="57" t="s">
+      <c r="G5" s="56" t="s">
         <v>29</v>
       </c>
-      <c r="H5" s="56" t="s">
+      <c r="H5" s="55" t="s">
         <v>30</v>
       </c>
-      <c r="I5" s="57" t="s">
+      <c r="I5" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="J5" s="56" t="s">
+      <c r="J5" s="55" t="s">
         <v>32</v>
       </c>
-      <c r="K5" s="57" t="s">
+      <c r="K5" s="56" t="s">
         <v>33</v>
       </c>
-      <c r="L5" s="56" t="s">
+      <c r="L5" s="55" t="s">
         <v>34</v>
       </c>
-      <c r="M5" s="57" t="s">
+      <c r="M5" s="56" t="s">
         <v>35</v>
       </c>
-      <c r="N5" s="56" t="s">
+      <c r="N5" s="55" t="s">
         <v>36</v>
       </c>
-      <c r="O5" s="57" t="s">
+      <c r="O5" s="56" t="s">
         <v>37</v>
       </c>
-      <c r="P5" s="56" t="s">
+      <c r="P5" s="55" t="s">
         <v>38</v>
       </c>
-      <c r="Q5" s="57" t="s">
+      <c r="Q5" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="R5" s="56" t="s">
+      <c r="R5" s="55" t="s">
         <v>40</v>
       </c>
-      <c r="S5" s="58">
+      <c r="S5" s="57">
+        <v>45431</v>
+      </c>
+      <c r="T5" s="58" t="s">
+        <v>41</v>
+      </c>
+      <c r="U5" s="59" t="s">
+        <v>42</v>
+      </c>
+      <c r="V5" s="60" t="s">
+        <v>43</v>
+      </c>
+      <c r="X5" s="51" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y5" s="52" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z5" s="52" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA5" s="53" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="2:27">
+      <c r="B6" s="54" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="55" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" s="56" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="55" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" s="55"/>
+      <c r="G6" s="56" t="s">
+        <v>48</v>
+      </c>
+      <c r="H6" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="I6" s="56" t="s">
+        <v>50</v>
+      </c>
+      <c r="J6" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="K6" s="61"/>
+      <c r="L6" s="55"/>
+      <c r="M6" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="N6" s="55" t="s">
+        <v>53</v>
+      </c>
+      <c r="O6" s="56" t="s">
+        <v>54</v>
+      </c>
+      <c r="P6" s="55" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q6" s="56" t="s">
+        <v>56</v>
+      </c>
+      <c r="R6" s="55" t="s">
+        <v>40</v>
+      </c>
+      <c r="S6" s="57">
+        <v>52653</v>
+      </c>
+      <c r="T6" s="58" t="s">
+        <v>57</v>
+      </c>
+      <c r="U6" s="59" t="s">
+        <v>58</v>
+      </c>
+      <c r="V6" s="60" t="s">
+        <v>59</v>
+      </c>
+      <c r="X6" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y6" s="52" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z6" s="52" t="s">
+        <v>62</v>
+      </c>
+      <c r="AA6" s="53" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="2:27">
+      <c r="B7" s="54" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="55" t="s">
+        <v>64</v>
+      </c>
+      <c r="D7" s="56" t="s">
+        <v>65</v>
+      </c>
+      <c r="E7" s="55" t="s">
+        <v>66</v>
+      </c>
+      <c r="F7" s="55"/>
+      <c r="G7" s="56" t="s">
+        <v>67</v>
+      </c>
+      <c r="H7" s="55" t="s">
+        <v>68</v>
+      </c>
+      <c r="I7" s="56" t="s">
+        <v>69</v>
+      </c>
+      <c r="J7" s="55" t="s">
+        <v>70</v>
+      </c>
+      <c r="K7" s="56" t="s">
+        <v>71</v>
+      </c>
+      <c r="L7" s="55" t="s">
+        <v>72</v>
+      </c>
+      <c r="M7" s="56" t="s">
+        <v>73</v>
+      </c>
+      <c r="N7" s="55" t="s">
+        <v>74</v>
+      </c>
+      <c r="O7" s="56" t="s">
+        <v>75</v>
+      </c>
+      <c r="P7" s="55" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q7" s="56" t="s">
+        <v>24</v>
+      </c>
+      <c r="R7" s="55" t="s">
+        <v>40</v>
+      </c>
+      <c r="S7" s="57">
+        <v>43361</v>
+      </c>
+      <c r="T7" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="U7" s="59" t="s">
+        <v>42</v>
+      </c>
+      <c r="V7" s="60"/>
+      <c r="X7" s="51" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y7" s="52" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z7" s="52" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA7" s="53" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="2:27">
+      <c r="B8" s="54" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" s="55" t="s">
+        <v>81</v>
+      </c>
+      <c r="D8" s="56" t="s">
+        <v>82</v>
+      </c>
+      <c r="E8" s="55" t="s">
+        <v>83</v>
+      </c>
+      <c r="F8" s="55" t="s">
+        <v>84</v>
+      </c>
+      <c r="G8" s="56" t="s">
+        <v>85</v>
+      </c>
+      <c r="H8" s="55" t="s">
+        <v>86</v>
+      </c>
+      <c r="I8" s="56" t="s">
+        <v>56</v>
+      </c>
+      <c r="J8" s="55" t="s">
+        <v>87</v>
+      </c>
+      <c r="K8" s="62" t="s">
+        <v>88</v>
+      </c>
+      <c r="L8" s="55" t="s">
+        <v>89</v>
+      </c>
+      <c r="M8" s="56" t="s">
+        <v>90</v>
+      </c>
+      <c r="N8" s="55" t="s">
+        <v>91</v>
+      </c>
+      <c r="O8" s="56" t="s">
+        <v>92</v>
+      </c>
+      <c r="P8" s="55" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q8" s="56" t="s">
+        <v>94</v>
+      </c>
+      <c r="R8" s="55" t="s">
+        <v>95</v>
+      </c>
+      <c r="S8" s="57">
+        <v>58322</v>
+      </c>
+      <c r="T8" s="58" t="s">
+        <v>96</v>
+      </c>
+      <c r="U8" s="59" t="s">
+        <v>97</v>
+      </c>
+      <c r="V8" s="60"/>
+      <c r="X8" s="51" t="s">
+        <v>98</v>
+      </c>
+      <c r="Y8" s="52" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z8" s="52" t="s">
+        <v>100</v>
+      </c>
+      <c r="AA8" s="53" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="2:27">
+      <c r="B9" s="54" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" s="55" t="s">
+        <v>101</v>
+      </c>
+      <c r="D9" s="56" t="s">
+        <v>102</v>
+      </c>
+      <c r="E9" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="F9" s="55" t="s">
+        <v>104</v>
+      </c>
+      <c r="G9" s="56" t="s">
+        <v>105</v>
+      </c>
+      <c r="H9" s="55" t="s">
+        <v>106</v>
+      </c>
+      <c r="I9" s="62" t="s">
+        <v>107</v>
+      </c>
+      <c r="J9" s="55" t="s">
+        <v>108</v>
+      </c>
+      <c r="K9" s="56"/>
+      <c r="L9" s="55"/>
+      <c r="M9" s="62" t="s">
+        <v>109</v>
+      </c>
+      <c r="N9" s="55" t="s">
+        <v>110</v>
+      </c>
+      <c r="O9" s="56" t="s">
+        <v>94</v>
+      </c>
+      <c r="P9" s="55" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q9" s="56" t="s">
+        <v>112</v>
+      </c>
+      <c r="R9" s="55" t="s">
+        <v>40</v>
+      </c>
+      <c r="S9" s="57">
+        <v>68443</v>
+      </c>
+      <c r="T9" s="58" t="s">
+        <v>113</v>
+      </c>
+      <c r="U9" s="59" t="s">
+        <v>114</v>
+      </c>
+      <c r="V9" s="60"/>
+      <c r="X9" s="51" t="s">
+        <v>98</v>
+      </c>
+      <c r="Y9" s="52" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z9" s="52" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA9" s="53" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="2:27">
+      <c r="B10" s="54" t="s">
+        <v>117</v>
+      </c>
+      <c r="C10" s="55" t="s">
+        <v>118</v>
+      </c>
+      <c r="D10" s="56" t="s">
+        <v>119</v>
+      </c>
+      <c r="E10" s="55" t="s">
+        <v>120</v>
+      </c>
+      <c r="F10" s="55"/>
+      <c r="G10" s="56" t="s">
+        <v>121</v>
+      </c>
+      <c r="H10" s="55" t="s">
+        <v>122</v>
+      </c>
+      <c r="I10" s="62" t="s">
+        <v>123</v>
+      </c>
+      <c r="J10" s="55" t="s">
+        <v>124</v>
+      </c>
+      <c r="K10" s="56"/>
+      <c r="L10" s="55"/>
+      <c r="M10" s="56"/>
+      <c r="N10" s="55"/>
+      <c r="O10" s="56" t="s">
+        <v>125</v>
+      </c>
+      <c r="P10" s="55" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q10" s="62" t="s">
+        <v>127</v>
+      </c>
+      <c r="R10" s="55" t="s">
+        <v>40</v>
+      </c>
+      <c r="S10" s="57">
+        <v>34222</v>
+      </c>
+      <c r="T10" s="58" t="s">
+        <v>128</v>
+      </c>
+      <c r="U10" s="59" t="s">
+        <v>114</v>
+      </c>
+      <c r="V10" s="60"/>
+      <c r="X10" s="51" t="s">
+        <v>112</v>
+      </c>
+      <c r="Y10" s="52" t="s">
+        <v>129</v>
+      </c>
+      <c r="Z10" s="52" t="s">
+        <v>130</v>
+      </c>
+      <c r="AA10" s="53" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="2:27">
+      <c r="B11" s="54" t="s">
+        <v>78</v>
+      </c>
+      <c r="C11" s="55" t="s">
+        <v>132</v>
+      </c>
+      <c r="D11" s="56" t="s">
+        <v>133</v>
+      </c>
+      <c r="E11" s="55" t="s">
+        <v>134</v>
+      </c>
+      <c r="F11" s="55" t="s">
+        <v>28</v>
+      </c>
+      <c r="G11" s="56" t="s">
+        <v>135</v>
+      </c>
+      <c r="H11" s="55" t="s">
+        <v>136</v>
+      </c>
+      <c r="I11" s="56"/>
+      <c r="J11" s="55"/>
+      <c r="K11" s="56"/>
+      <c r="L11" s="55"/>
+      <c r="M11" s="56"/>
+      <c r="N11" s="55"/>
+      <c r="O11" s="56" t="s">
+        <v>137</v>
+      </c>
+      <c r="P11" s="55" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q11" s="56" t="s">
+        <v>98</v>
+      </c>
+      <c r="R11" s="55" t="s">
+        <v>95</v>
+      </c>
+      <c r="S11" s="57">
         <v>11111</v>
       </c>
-      <c r="T5" s="59" t="s">
-        <v>41</v>
-      </c>
-      <c r="U5" s="60" t="s">
-        <v>42</v>
-      </c>
-      <c r="V5" s="61" t="s">
-        <v>43</v>
-      </c>
-      <c r="X5" s="52" t="s">
+      <c r="T11" s="58"/>
+      <c r="U11" s="59"/>
+      <c r="V11" s="60"/>
+      <c r="X11" s="51" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y11" s="52" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z11" s="52" t="s">
+        <v>100</v>
+      </c>
+      <c r="AA11" s="53" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="2:27">
+      <c r="B12" s="54" t="s">
+        <v>112</v>
+      </c>
+      <c r="C12" s="55" t="s">
+        <v>140</v>
+      </c>
+      <c r="D12" s="56" t="s">
+        <v>98</v>
+      </c>
+      <c r="E12" s="63" t="s">
+        <v>141</v>
+      </c>
+      <c r="F12" s="63" t="s">
+        <v>142</v>
+      </c>
+      <c r="G12" s="56" t="s">
+        <v>143</v>
+      </c>
+      <c r="H12" s="55" t="s">
+        <v>144</v>
+      </c>
+      <c r="I12" s="56"/>
+      <c r="J12" s="55"/>
+      <c r="K12" s="56"/>
+      <c r="L12" s="55"/>
+      <c r="M12" s="56"/>
+      <c r="N12" s="55"/>
+      <c r="O12" s="62" t="s">
+        <v>145</v>
+      </c>
+      <c r="P12" s="55" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q12" s="56"/>
+      <c r="R12" s="55"/>
+      <c r="S12" s="57"/>
+      <c r="T12" s="58"/>
+      <c r="U12" s="59"/>
+      <c r="V12" s="60"/>
+      <c r="X12" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="Y5" s="53" t="s">
-        <v>21</v>
-      </c>
-      <c r="Z5" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="AA5" s="54" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="2:27">
-      <c r="B6" s="55" t="s">
+      <c r="Y12" s="52" t="s">
+        <v>147</v>
+      </c>
+      <c r="Z12" s="52" t="s">
+        <v>148</v>
+      </c>
+      <c r="AA12" s="53" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="2:27">
+      <c r="B13" s="54" t="s">
+        <v>150</v>
+      </c>
+      <c r="C13" s="55"/>
+      <c r="D13" s="56" t="s">
+        <v>151</v>
+      </c>
+      <c r="E13" s="63" t="s">
+        <v>152</v>
+      </c>
+      <c r="F13" s="63" t="s">
+        <v>28</v>
+      </c>
+      <c r="G13" s="56"/>
+      <c r="H13" s="55"/>
+      <c r="I13" s="56"/>
+      <c r="J13" s="55"/>
+      <c r="K13" s="56"/>
+      <c r="L13" s="55"/>
+      <c r="M13" s="56"/>
+      <c r="N13" s="55"/>
+      <c r="O13" s="62" t="s">
+        <v>153</v>
+      </c>
+      <c r="P13" s="55" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q13" s="56" t="s">
+        <v>121</v>
+      </c>
+      <c r="R13" s="55" t="s">
+        <v>95</v>
+      </c>
+      <c r="S13" s="57">
+        <v>44243</v>
+      </c>
+      <c r="T13" s="58"/>
+      <c r="U13" s="59"/>
+      <c r="V13" s="60"/>
+      <c r="X13" s="51"/>
+      <c r="Y13" s="52"/>
+      <c r="Z13" s="52"/>
+      <c r="AA13" s="53"/>
+    </row>
+    <row r="14" customHeight="1" spans="2:27">
+      <c r="B14" s="54" t="s">
+        <v>155</v>
+      </c>
+      <c r="C14" s="55" t="s">
+        <v>156</v>
+      </c>
+      <c r="D14" s="56" t="s">
+        <v>157</v>
+      </c>
+      <c r="E14" s="63" t="s">
+        <v>158</v>
+      </c>
+      <c r="F14" s="64"/>
+      <c r="G14" s="63"/>
+      <c r="H14" s="55"/>
+      <c r="I14" s="56"/>
+      <c r="J14" s="55"/>
+      <c r="K14" s="56"/>
+      <c r="L14" s="55"/>
+      <c r="M14" s="56"/>
+      <c r="N14" s="55"/>
+      <c r="O14" s="62" t="s">
+        <v>159</v>
+      </c>
+      <c r="P14" s="55" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q14" s="56"/>
+      <c r="R14" s="55"/>
+      <c r="S14" s="57"/>
+      <c r="T14" s="58"/>
+      <c r="U14" s="59"/>
+      <c r="V14" s="60"/>
+      <c r="X14" s="51"/>
+      <c r="Y14" s="52"/>
+      <c r="Z14" s="52"/>
+      <c r="AA14" s="53"/>
+    </row>
+    <row r="15" customHeight="1" spans="2:27">
+      <c r="B15" s="54"/>
+      <c r="C15" s="55"/>
+      <c r="D15" s="56" t="s">
+        <v>161</v>
+      </c>
+      <c r="E15" s="63" t="s">
+        <v>162</v>
+      </c>
+      <c r="F15" s="64"/>
+      <c r="G15" s="63"/>
+      <c r="H15" s="55"/>
+      <c r="I15" s="56"/>
+      <c r="J15" s="55"/>
+      <c r="K15" s="56"/>
+      <c r="L15" s="55"/>
+      <c r="M15" s="56"/>
+      <c r="N15" s="55"/>
+      <c r="O15" s="56" t="s">
+        <v>163</v>
+      </c>
+      <c r="P15" s="55" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q15" s="56" t="s">
+        <v>125</v>
+      </c>
+      <c r="R15" s="55" t="s">
+        <v>95</v>
+      </c>
+      <c r="S15" s="57">
+        <v>42416</v>
+      </c>
+      <c r="T15" s="58"/>
+      <c r="U15" s="59"/>
+      <c r="V15" s="60"/>
+      <c r="X15" s="51"/>
+      <c r="Y15" s="52"/>
+      <c r="Z15" s="52"/>
+      <c r="AA15" s="53"/>
+    </row>
+    <row r="16" customHeight="1" spans="2:27">
+      <c r="B16" s="54"/>
+      <c r="C16" s="55"/>
+      <c r="D16" s="56" t="s">
+        <v>165</v>
+      </c>
+      <c r="E16" s="63" t="s">
+        <v>166</v>
+      </c>
+      <c r="F16" s="64"/>
+      <c r="G16" s="63"/>
+      <c r="H16" s="55"/>
+      <c r="I16" s="56"/>
+      <c r="J16" s="55"/>
+      <c r="K16" s="56"/>
+      <c r="L16" s="55"/>
+      <c r="M16" s="56"/>
+      <c r="N16" s="55"/>
+      <c r="O16" s="56" t="s">
+        <v>167</v>
+      </c>
+      <c r="P16" s="55" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q16" s="56" t="s">
+        <v>169</v>
+      </c>
+      <c r="R16" s="55" t="s">
+        <v>95</v>
+      </c>
+      <c r="S16" s="57">
+        <v>33232</v>
+      </c>
+      <c r="T16" s="58"/>
+      <c r="U16" s="59"/>
+      <c r="V16" s="60"/>
+      <c r="X16" s="51"/>
+      <c r="Y16" s="52"/>
+      <c r="Z16" s="52"/>
+      <c r="AA16" s="53"/>
+    </row>
+    <row r="17" customHeight="1" spans="2:27">
+      <c r="B17" s="54"/>
+      <c r="C17" s="55"/>
+      <c r="D17" s="56" t="s">
+        <v>170</v>
+      </c>
+      <c r="E17" s="63" t="s">
+        <v>171</v>
+      </c>
+      <c r="F17" s="64"/>
+      <c r="G17" s="63"/>
+      <c r="H17" s="55"/>
+      <c r="I17" s="56"/>
+      <c r="J17" s="55"/>
+      <c r="K17" s="56"/>
+      <c r="L17" s="55"/>
+      <c r="M17" s="56"/>
+      <c r="N17" s="55"/>
+      <c r="O17" s="56" t="s">
+        <v>172</v>
+      </c>
+      <c r="P17" s="55" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q17" s="56" t="s">
+        <v>174</v>
+      </c>
+      <c r="R17" s="55" t="s">
+        <v>95</v>
+      </c>
+      <c r="S17" s="57">
+        <v>33232</v>
+      </c>
+      <c r="T17" s="58"/>
+      <c r="U17" s="59"/>
+      <c r="V17" s="60"/>
+      <c r="X17" s="51"/>
+      <c r="Y17" s="52"/>
+      <c r="Z17" s="52"/>
+      <c r="AA17" s="53"/>
+    </row>
+    <row r="18" customHeight="1" spans="2:27">
+      <c r="B18" s="54"/>
+      <c r="C18" s="55"/>
+      <c r="D18" s="56" t="s">
         <v>45</v>
       </c>
-      <c r="C6" s="56" t="s">
-        <v>46</v>
-      </c>
-      <c r="D6" s="57" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="56" t="s">
-        <v>47</v>
-      </c>
-      <c r="F6" s="56"/>
-      <c r="G6" s="57" t="s">
-        <v>48</v>
-      </c>
-      <c r="H6" s="56" t="s">
-        <v>49</v>
-      </c>
-      <c r="I6" s="57" t="s">
-        <v>50</v>
-      </c>
-      <c r="J6" s="56" t="s">
-        <v>51</v>
-      </c>
-      <c r="K6" s="62" t="s">
-        <v>52</v>
-      </c>
-      <c r="L6" s="56" t="s">
-        <v>53</v>
-      </c>
-      <c r="M6" s="62" t="s">
-        <v>54</v>
-      </c>
-      <c r="N6" s="56" t="s">
-        <v>55</v>
-      </c>
-      <c r="O6" s="57" t="s">
-        <v>56</v>
-      </c>
-      <c r="P6" s="56" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q6" s="57" t="s">
-        <v>58</v>
-      </c>
-      <c r="R6" s="56" t="s">
-        <v>40</v>
-      </c>
-      <c r="S6" s="58">
+      <c r="E18" s="63" t="s">
+        <v>175</v>
+      </c>
+      <c r="F18" s="64" t="s">
+        <v>176</v>
+      </c>
+      <c r="G18" s="63"/>
+      <c r="H18" s="55"/>
+      <c r="I18" s="56"/>
+      <c r="J18" s="55"/>
+      <c r="K18" s="56"/>
+      <c r="L18" s="55"/>
+      <c r="M18" s="56"/>
+      <c r="N18" s="55"/>
+      <c r="O18" s="62" t="s">
+        <v>177</v>
+      </c>
+      <c r="P18" s="55" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q18" s="56" t="s">
+        <v>179</v>
+      </c>
+      <c r="R18" s="55" t="s">
+        <v>95</v>
+      </c>
+      <c r="S18" s="57">
+        <v>43235</v>
+      </c>
+      <c r="T18" s="58"/>
+      <c r="U18" s="59"/>
+      <c r="V18" s="60"/>
+      <c r="X18" s="51"/>
+      <c r="Y18" s="52"/>
+      <c r="Z18" s="52"/>
+      <c r="AA18" s="53"/>
+    </row>
+    <row r="19" customHeight="1" spans="2:27">
+      <c r="B19" s="54"/>
+      <c r="C19" s="55"/>
+      <c r="D19" s="62" t="s">
+        <v>180</v>
+      </c>
+      <c r="E19" s="63" t="s">
+        <v>181</v>
+      </c>
+      <c r="F19" s="64" t="s">
+        <v>182</v>
+      </c>
+      <c r="G19" s="63"/>
+      <c r="H19" s="55"/>
+      <c r="I19" s="56"/>
+      <c r="J19" s="55"/>
+      <c r="K19" s="56"/>
+      <c r="L19" s="55"/>
+      <c r="M19" s="56"/>
+      <c r="N19" s="55"/>
+      <c r="O19" s="56" t="s">
+        <v>183</v>
+      </c>
+      <c r="P19" s="55" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q19" s="56" t="s">
+        <v>185</v>
+      </c>
+      <c r="R19" s="55" t="s">
+        <v>95</v>
+      </c>
+      <c r="S19" s="57">
+        <v>24111</v>
+      </c>
+      <c r="T19" s="58"/>
+      <c r="U19" s="59"/>
+      <c r="V19" s="60"/>
+      <c r="X19" s="51"/>
+      <c r="Y19" s="52"/>
+      <c r="Z19" s="52"/>
+      <c r="AA19" s="53"/>
+    </row>
+    <row r="20" customHeight="1" spans="2:27">
+      <c r="B20" s="54"/>
+      <c r="C20" s="55"/>
+      <c r="D20" s="62" t="s">
+        <v>186</v>
+      </c>
+      <c r="E20" s="63" t="s">
+        <v>187</v>
+      </c>
+      <c r="F20" s="64"/>
+      <c r="G20" s="63"/>
+      <c r="H20" s="55"/>
+      <c r="I20" s="56"/>
+      <c r="J20" s="55"/>
+      <c r="K20" s="56"/>
+      <c r="L20" s="55"/>
+      <c r="M20" s="56"/>
+      <c r="N20" s="55"/>
+      <c r="O20" s="56" t="s">
+        <v>188</v>
+      </c>
+      <c r="P20" s="55" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q20" s="56" t="s">
+        <v>190</v>
+      </c>
+      <c r="R20" s="55" t="s">
+        <v>95</v>
+      </c>
+      <c r="S20" s="57">
         <v>11111</v>
       </c>
-      <c r="T6" s="59" t="s">
-        <v>59</v>
-      </c>
-      <c r="U6" s="60" t="s">
-        <v>60</v>
-      </c>
-      <c r="V6" s="61" t="s">
-        <v>61</v>
-      </c>
-      <c r="X6" s="52" t="s">
-        <v>62</v>
-      </c>
-      <c r="Y6" s="53" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z6" s="53" t="s">
-        <v>64</v>
-      </c>
-      <c r="AA6" s="54" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="7" customHeight="1" spans="2:27">
-      <c r="B7" s="55" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="56" t="s">
-        <v>66</v>
-      </c>
-      <c r="D7" s="57" t="s">
+      <c r="T20" s="58"/>
+      <c r="U20" s="59"/>
+      <c r="V20" s="60"/>
+      <c r="X20" s="51"/>
+      <c r="Y20" s="52"/>
+      <c r="Z20" s="52"/>
+      <c r="AA20" s="53"/>
+    </row>
+    <row r="21" customHeight="1" spans="2:27">
+      <c r="B21" s="54"/>
+      <c r="C21" s="55"/>
+      <c r="D21" s="56" t="s">
+        <v>191</v>
+      </c>
+      <c r="E21" s="63" t="s">
+        <v>192</v>
+      </c>
+      <c r="F21" s="64"/>
+      <c r="G21" s="63"/>
+      <c r="H21" s="55"/>
+      <c r="I21" s="56"/>
+      <c r="J21" s="55"/>
+      <c r="K21" s="56"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="56"/>
+      <c r="N21" s="55"/>
+      <c r="O21" s="56" t="s">
+        <v>193</v>
+      </c>
+      <c r="P21" s="55" t="s">
+        <v>194</v>
+      </c>
+      <c r="Q21" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="R21" s="55" t="s">
+        <v>95</v>
+      </c>
+      <c r="S21" s="57">
+        <v>43451</v>
+      </c>
+      <c r="T21" s="58"/>
+      <c r="U21" s="59"/>
+      <c r="V21" s="60"/>
+      <c r="X21" s="51"/>
+      <c r="Y21" s="52"/>
+      <c r="Z21" s="52"/>
+      <c r="AA21" s="53"/>
+    </row>
+    <row r="22" customHeight="1" spans="2:27">
+      <c r="B22" s="54"/>
+      <c r="C22" s="55"/>
+      <c r="D22" s="62" t="s">
+        <v>195</v>
+      </c>
+      <c r="E22" s="63" t="s">
+        <v>196</v>
+      </c>
+      <c r="F22" s="64"/>
+      <c r="G22" s="63"/>
+      <c r="H22" s="55"/>
+      <c r="I22" s="56"/>
+      <c r="J22" s="55"/>
+      <c r="K22" s="56"/>
+      <c r="L22" s="55"/>
+      <c r="M22" s="56"/>
+      <c r="N22" s="55"/>
+      <c r="O22" s="62" t="s">
+        <v>197</v>
+      </c>
+      <c r="P22" s="55" t="s">
+        <v>198</v>
+      </c>
+      <c r="Q22" s="56" t="s">
+        <v>183</v>
+      </c>
+      <c r="R22" s="55" t="s">
+        <v>95</v>
+      </c>
+      <c r="S22" s="57">
+        <v>11111</v>
+      </c>
+      <c r="T22" s="58"/>
+      <c r="U22" s="59"/>
+      <c r="V22" s="60"/>
+      <c r="X22" s="51"/>
+      <c r="Y22" s="52"/>
+      <c r="Z22" s="52"/>
+      <c r="AA22" s="53"/>
+    </row>
+    <row r="23" customHeight="1" spans="2:27">
+      <c r="B23" s="54"/>
+      <c r="C23" s="55"/>
+      <c r="D23" s="56" t="s">
+        <v>199</v>
+      </c>
+      <c r="E23" s="63" t="s">
+        <v>200</v>
+      </c>
+      <c r="F23" s="64"/>
+      <c r="G23" s="63"/>
+      <c r="H23" s="55"/>
+      <c r="I23" s="56"/>
+      <c r="J23" s="55"/>
+      <c r="K23" s="56"/>
+      <c r="L23" s="55"/>
+      <c r="M23" s="56"/>
+      <c r="N23" s="55"/>
+      <c r="O23" s="62" t="s">
+        <v>201</v>
+      </c>
+      <c r="P23" s="55" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q23" s="56" t="s">
+        <v>203</v>
+      </c>
+      <c r="R23" s="55" t="s">
+        <v>95</v>
+      </c>
+      <c r="S23" s="57">
+        <v>11111</v>
+      </c>
+      <c r="T23" s="58"/>
+      <c r="U23" s="59"/>
+      <c r="V23" s="60"/>
+      <c r="X23" s="51"/>
+      <c r="Y23" s="52"/>
+      <c r="Z23" s="52"/>
+      <c r="AA23" s="53"/>
+    </row>
+    <row r="24" customHeight="1" spans="2:27">
+      <c r="B24" s="54"/>
+      <c r="C24" s="55"/>
+      <c r="D24" s="56" t="s">
+        <v>204</v>
+      </c>
+      <c r="E24" s="63" t="s">
+        <v>205</v>
+      </c>
+      <c r="F24" s="64"/>
+      <c r="G24" s="63"/>
+      <c r="H24" s="55"/>
+      <c r="I24" s="56"/>
+      <c r="J24" s="55"/>
+      <c r="K24" s="56"/>
+      <c r="L24" s="55"/>
+      <c r="M24" s="56"/>
+      <c r="N24" s="55"/>
+      <c r="O24" s="56"/>
+      <c r="P24" s="55"/>
+      <c r="Q24" s="56" t="s">
+        <v>206</v>
+      </c>
+      <c r="R24" s="55" t="s">
+        <v>95</v>
+      </c>
+      <c r="S24" s="57">
+        <v>32233</v>
+      </c>
+      <c r="T24" s="58"/>
+      <c r="U24" s="59"/>
+      <c r="V24" s="60"/>
+      <c r="X24" s="51"/>
+      <c r="Y24" s="52"/>
+      <c r="Z24" s="52"/>
+      <c r="AA24" s="53"/>
+    </row>
+    <row r="25" customHeight="1" spans="2:27">
+      <c r="B25" s="54"/>
+      <c r="C25" s="63"/>
+      <c r="D25" s="56" t="s">
+        <v>207</v>
+      </c>
+      <c r="E25" s="63" t="s">
+        <v>208</v>
+      </c>
+      <c r="F25" s="64" t="s">
+        <v>209</v>
+      </c>
+      <c r="G25" s="63"/>
+      <c r="H25" s="63"/>
+      <c r="I25" s="56"/>
+      <c r="J25" s="63"/>
+      <c r="K25" s="56"/>
+      <c r="L25" s="63"/>
+      <c r="M25" s="56"/>
+      <c r="N25" s="63"/>
+      <c r="O25" s="56"/>
+      <c r="P25" s="63"/>
+      <c r="Q25" s="56" t="s">
+        <v>75</v>
+      </c>
+      <c r="R25" s="63" t="s">
+        <v>95</v>
+      </c>
+      <c r="S25" s="57">
+        <v>56244</v>
+      </c>
+      <c r="T25" s="58"/>
+      <c r="U25" s="59"/>
+      <c r="V25" s="60"/>
+    </row>
+    <row r="26" customHeight="1" spans="2:27">
+      <c r="B26" s="54"/>
+      <c r="C26" s="63"/>
+      <c r="D26" s="56" t="s">
+        <v>210</v>
+      </c>
+      <c r="E26" s="63" t="s">
+        <v>211</v>
+      </c>
+      <c r="F26" s="64" t="s">
+        <v>212</v>
+      </c>
+      <c r="G26" s="63"/>
+      <c r="H26" s="63"/>
+      <c r="I26" s="56"/>
+      <c r="J26" s="63"/>
+      <c r="K26" s="56"/>
+      <c r="L26" s="63"/>
+      <c r="M26" s="56"/>
+      <c r="N26" s="63"/>
+      <c r="O26" s="56"/>
+      <c r="P26" s="63"/>
+      <c r="Q26" s="56" t="s">
+        <v>213</v>
+      </c>
+      <c r="R26" s="55" t="s">
+        <v>95</v>
+      </c>
+      <c r="S26" s="57">
+        <v>22122</v>
+      </c>
+      <c r="T26" s="58"/>
+      <c r="U26" s="59"/>
+      <c r="V26" s="60"/>
+    </row>
+    <row r="27" customHeight="1" spans="2:27">
+      <c r="B27" s="54"/>
+      <c r="C27" s="55"/>
+      <c r="D27" s="56" t="s">
+        <v>214</v>
+      </c>
+      <c r="E27" s="63" t="s">
+        <v>215</v>
+      </c>
+      <c r="F27" s="64"/>
+      <c r="G27" s="63"/>
+      <c r="H27" s="55"/>
+      <c r="I27" s="56"/>
+      <c r="J27" s="55"/>
+      <c r="K27" s="56"/>
+      <c r="L27" s="55"/>
+      <c r="M27" s="56"/>
+      <c r="N27" s="55"/>
+      <c r="O27" s="56"/>
+      <c r="P27" s="55"/>
+      <c r="Q27" s="56"/>
+      <c r="R27" s="55"/>
+      <c r="S27" s="57"/>
+      <c r="T27" s="58"/>
+      <c r="U27" s="59"/>
+      <c r="V27" s="60"/>
+    </row>
+    <row r="28" customHeight="1" spans="2:27">
+      <c r="B28" s="54"/>
+      <c r="C28" s="55"/>
+      <c r="D28" s="56"/>
+      <c r="E28" s="63"/>
+      <c r="F28" s="64"/>
+      <c r="G28" s="63"/>
+      <c r="H28" s="55"/>
+      <c r="I28" s="56"/>
+      <c r="J28" s="55"/>
+      <c r="K28" s="56"/>
+      <c r="L28" s="55"/>
+      <c r="M28" s="56"/>
+      <c r="N28" s="55"/>
+      <c r="O28" s="56"/>
+      <c r="P28" s="55"/>
+      <c r="Q28" s="56" t="s">
+        <v>78</v>
+      </c>
+      <c r="R28" s="55" t="s">
+        <v>95</v>
+      </c>
+      <c r="S28" s="57">
+        <v>11111</v>
+      </c>
+      <c r="T28" s="58"/>
+      <c r="U28" s="59"/>
+      <c r="V28" s="60"/>
+    </row>
+    <row r="29" customHeight="1" spans="2:27">
+      <c r="B29" s="54"/>
+      <c r="C29" s="55"/>
+      <c r="D29" s="56"/>
+      <c r="E29" s="63"/>
+      <c r="F29" s="64"/>
+      <c r="G29" s="55"/>
+      <c r="H29" s="55"/>
+      <c r="I29" s="56"/>
+      <c r="J29" s="65"/>
+      <c r="K29" s="55"/>
+      <c r="L29" s="55"/>
+      <c r="M29" s="56"/>
+      <c r="N29" s="65"/>
+      <c r="O29" s="55"/>
+      <c r="P29" s="55"/>
+      <c r="Q29" s="62" t="s">
+        <v>153</v>
+      </c>
+      <c r="R29" s="55" t="s">
+        <v>95</v>
+      </c>
+      <c r="S29" s="57">
+        <v>11111</v>
+      </c>
+      <c r="T29" s="58"/>
+      <c r="U29" s="59"/>
+      <c r="V29" s="60"/>
+    </row>
+    <row r="30" customHeight="1" spans="2:27">
+      <c r="B30" s="54"/>
+      <c r="C30" s="55"/>
+      <c r="D30" s="56"/>
+      <c r="E30" s="63"/>
+      <c r="F30" s="64"/>
+      <c r="G30" s="55"/>
+      <c r="H30" s="55"/>
+      <c r="I30" s="56"/>
+      <c r="J30" s="65"/>
+      <c r="K30" s="55"/>
+      <c r="L30" s="55"/>
+      <c r="M30" s="56"/>
+      <c r="N30" s="65"/>
+      <c r="O30" s="55"/>
+      <c r="P30" s="55"/>
+      <c r="Q30" s="56" t="s">
+        <v>33</v>
+      </c>
+      <c r="R30" s="55" t="s">
+        <v>216</v>
+      </c>
+      <c r="S30" s="57">
+        <v>44531</v>
+      </c>
+      <c r="T30" s="58"/>
+      <c r="U30" s="59"/>
+      <c r="V30" s="60"/>
+    </row>
+    <row r="31" customHeight="1" spans="2:27">
+      <c r="B31" s="54"/>
+      <c r="C31" s="55"/>
+      <c r="D31" s="56"/>
+      <c r="E31" s="63"/>
+      <c r="F31" s="64"/>
+      <c r="G31" s="55"/>
+      <c r="H31" s="55"/>
+      <c r="I31" s="56"/>
+      <c r="J31" s="65"/>
+      <c r="K31" s="55"/>
+      <c r="L31" s="55"/>
+      <c r="M31" s="56"/>
+      <c r="N31" s="65"/>
+      <c r="O31" s="55"/>
+      <c r="P31" s="55"/>
+      <c r="Q31" s="62" t="s">
+        <v>217</v>
+      </c>
+      <c r="R31" s="55" t="s">
+        <v>216</v>
+      </c>
+      <c r="S31" s="57">
+        <v>32521</v>
+      </c>
+      <c r="T31" s="58"/>
+      <c r="U31" s="59"/>
+      <c r="V31" s="60"/>
+    </row>
+    <row r="32" customHeight="1" spans="2:27">
+      <c r="B32" s="54"/>
+      <c r="C32" s="55"/>
+      <c r="D32" s="56"/>
+      <c r="E32" s="63"/>
+      <c r="F32" s="64"/>
+      <c r="G32" s="55"/>
+      <c r="H32" s="55"/>
+      <c r="I32" s="56"/>
+      <c r="J32" s="65"/>
+      <c r="K32" s="55"/>
+      <c r="L32" s="55"/>
+      <c r="M32" s="56"/>
+      <c r="N32" s="65"/>
+      <c r="O32" s="55"/>
+      <c r="P32" s="55"/>
+      <c r="Q32" s="56"/>
+      <c r="R32" s="55"/>
+      <c r="S32" s="57"/>
+      <c r="T32" s="58"/>
+      <c r="U32" s="59"/>
+      <c r="V32" s="60"/>
+    </row>
+    <row r="33" customHeight="1" spans="2:22">
+      <c r="B33" s="54"/>
+      <c r="C33" s="55"/>
+      <c r="D33" s="56"/>
+      <c r="E33" s="63"/>
+      <c r="F33" s="64"/>
+      <c r="G33" s="55"/>
+      <c r="H33" s="55"/>
+      <c r="I33" s="56"/>
+      <c r="J33" s="65"/>
+      <c r="K33" s="55"/>
+      <c r="L33" s="55"/>
+      <c r="M33" s="56"/>
+      <c r="N33" s="65"/>
+      <c r="O33" s="55"/>
+      <c r="P33" s="55"/>
+      <c r="Q33" s="56" t="s">
+        <v>71</v>
+      </c>
+      <c r="R33" s="55" t="s">
+        <v>216</v>
+      </c>
+      <c r="S33" s="57">
+        <v>58251</v>
+      </c>
+      <c r="T33" s="58"/>
+      <c r="U33" s="59"/>
+      <c r="V33" s="60"/>
+    </row>
+    <row r="34" customHeight="1" spans="2:22">
+      <c r="B34" s="54"/>
+      <c r="C34" s="55"/>
+      <c r="D34" s="56"/>
+      <c r="E34" s="63"/>
+      <c r="F34" s="64"/>
+      <c r="G34" s="55"/>
+      <c r="H34" s="55"/>
+      <c r="I34" s="56"/>
+      <c r="J34" s="65"/>
+      <c r="K34" s="55"/>
+      <c r="L34" s="55"/>
+      <c r="M34" s="56"/>
+      <c r="N34" s="65"/>
+      <c r="O34" s="55"/>
+      <c r="P34" s="55"/>
+      <c r="Q34" s="56" t="s">
+        <v>218</v>
+      </c>
+      <c r="R34" s="55" t="s">
+        <v>216</v>
+      </c>
+      <c r="S34" s="57">
+        <v>11111</v>
+      </c>
+      <c r="T34" s="58"/>
+      <c r="U34" s="59"/>
+      <c r="V34" s="60"/>
+    </row>
+    <row r="35" customHeight="1" spans="2:22">
+      <c r="B35" s="54"/>
+      <c r="C35" s="55"/>
+      <c r="D35" s="56"/>
+      <c r="E35" s="63"/>
+      <c r="F35" s="64"/>
+      <c r="G35" s="55"/>
+      <c r="H35" s="55"/>
+      <c r="I35" s="56"/>
+      <c r="J35" s="65"/>
+      <c r="K35" s="55"/>
+      <c r="L35" s="55"/>
+      <c r="M35" s="56"/>
+      <c r="N35" s="65"/>
+      <c r="O35" s="55"/>
+      <c r="P35" s="55"/>
+      <c r="Q35" s="56" t="s">
         <v>67</v>
       </c>
-      <c r="E7" s="56" t="s">
-        <v>68</v>
-      </c>
-      <c r="F7" s="56"/>
-      <c r="G7" s="57" t="s">
-        <v>69</v>
-      </c>
-      <c r="H7" s="56" t="s">
-        <v>70</v>
-      </c>
-      <c r="I7" s="57" t="s">
-        <v>71</v>
-      </c>
-      <c r="J7" s="56" t="s">
-        <v>72</v>
-      </c>
-      <c r="K7" s="57" t="s">
-        <v>73</v>
-      </c>
-      <c r="L7" s="56" t="s">
-        <v>74</v>
-      </c>
-      <c r="M7" s="57" t="s">
-        <v>75</v>
-      </c>
-      <c r="N7" s="56" t="s">
-        <v>76</v>
-      </c>
-      <c r="O7" s="57" t="s">
-        <v>77</v>
-      </c>
-      <c r="P7" s="56" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q7" s="57" t="s">
-        <v>24</v>
-      </c>
-      <c r="R7" s="56" t="s">
-        <v>40</v>
-      </c>
-      <c r="S7" s="58">
+      <c r="R35" s="55" t="s">
+        <v>216</v>
+      </c>
+      <c r="S35" s="57">
+        <v>54345</v>
+      </c>
+      <c r="T35" s="58"/>
+      <c r="U35" s="59"/>
+      <c r="V35" s="60"/>
+    </row>
+    <row r="36" customHeight="1" spans="2:22">
+      <c r="B36" s="54"/>
+      <c r="C36" s="55"/>
+      <c r="D36" s="56"/>
+      <c r="E36" s="63"/>
+      <c r="F36" s="64"/>
+      <c r="G36" s="55"/>
+      <c r="H36" s="55"/>
+      <c r="I36" s="56"/>
+      <c r="J36" s="65"/>
+      <c r="K36" s="55"/>
+      <c r="L36" s="55"/>
+      <c r="M36" s="56"/>
+      <c r="N36" s="65"/>
+      <c r="O36" s="55"/>
+      <c r="P36" s="55"/>
+      <c r="Q36" s="56" t="s">
+        <v>219</v>
+      </c>
+      <c r="R36" s="55" t="s">
+        <v>216</v>
+      </c>
+      <c r="S36" s="57">
         <v>11111</v>
       </c>
-      <c r="T7" s="59" t="s">
-        <v>79</v>
-      </c>
-      <c r="U7" s="60" t="s">
-        <v>42</v>
-      </c>
-      <c r="V7" s="61"/>
-      <c r="X7" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="Y7" s="53" t="s">
-        <v>81</v>
-      </c>
-      <c r="Z7" s="53" t="s">
-        <v>82</v>
-      </c>
-      <c r="AA7" s="54" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="2:27">
-      <c r="B8" s="55" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8" s="56" t="s">
-        <v>83</v>
-      </c>
-      <c r="D8" s="57" t="s">
-        <v>84</v>
-      </c>
-      <c r="E8" s="56" t="s">
-        <v>85</v>
-      </c>
-      <c r="F8" s="56" t="s">
-        <v>86</v>
-      </c>
-      <c r="G8" s="57" t="s">
-        <v>87</v>
-      </c>
-      <c r="H8" s="56" t="s">
-        <v>88</v>
-      </c>
-      <c r="I8" s="57" t="s">
-        <v>58</v>
-      </c>
-      <c r="J8" s="56" t="s">
-        <v>89</v>
-      </c>
-      <c r="K8" s="62" t="s">
-        <v>90</v>
-      </c>
-      <c r="L8" s="56" t="s">
-        <v>91</v>
-      </c>
-      <c r="M8" s="57" t="s">
-        <v>92</v>
-      </c>
-      <c r="N8" s="56" t="s">
-        <v>93</v>
-      </c>
-      <c r="O8" s="57" t="s">
-        <v>94</v>
-      </c>
-      <c r="P8" s="56" t="s">
+      <c r="T36" s="58"/>
+      <c r="U36" s="59"/>
+      <c r="V36" s="60"/>
+    </row>
+    <row r="37" customHeight="1" spans="2:22">
+      <c r="B37" s="66"/>
+      <c r="D37" s="67"/>
+      <c r="E37" s="68"/>
+      <c r="F37" s="69"/>
+      <c r="I37" s="67"/>
+      <c r="J37" s="70"/>
+      <c r="M37" s="67"/>
+      <c r="N37" s="70"/>
+      <c r="Q37" s="67" t="s">
+        <v>220</v>
+      </c>
+      <c r="R37" s="55" t="s">
         <v>95</v>
       </c>
-      <c r="Q8" s="57" t="s">
-        <v>96</v>
-      </c>
-      <c r="R8" s="56" t="s">
-        <v>97</v>
-      </c>
-      <c r="S8" s="58">
+      <c r="S37" s="57">
+        <v>22221</v>
+      </c>
+      <c r="T37" s="58"/>
+      <c r="U37" s="59"/>
+      <c r="V37" s="60"/>
+    </row>
+    <row r="38" customHeight="1" spans="2:22">
+      <c r="B38" s="66"/>
+      <c r="D38" s="67"/>
+      <c r="E38" s="68"/>
+      <c r="F38" s="69"/>
+      <c r="I38" s="67"/>
+      <c r="J38" s="70"/>
+      <c r="M38" s="67"/>
+      <c r="N38" s="70"/>
+      <c r="Q38" s="62" t="s">
+        <v>221</v>
+      </c>
+      <c r="R38" s="55" t="s">
+        <v>95</v>
+      </c>
+      <c r="S38" s="57">
+        <v>33412</v>
+      </c>
+      <c r="T38" s="58"/>
+      <c r="U38" s="59"/>
+      <c r="V38" s="60"/>
+    </row>
+    <row r="39" customHeight="1" spans="2:22">
+      <c r="B39" s="66"/>
+      <c r="D39" s="67"/>
+      <c r="E39" s="68"/>
+      <c r="F39" s="69"/>
+      <c r="I39" s="67"/>
+      <c r="J39" s="70"/>
+      <c r="M39" s="67"/>
+      <c r="N39" s="70"/>
+      <c r="Q39" s="67" t="s">
+        <v>222</v>
+      </c>
+      <c r="R39" s="55" t="s">
+        <v>216</v>
+      </c>
+      <c r="S39" s="57">
         <v>11111</v>
       </c>
-      <c r="T8" s="59" t="s">
-        <v>98</v>
-      </c>
-      <c r="U8" s="60" t="s">
-        <v>99</v>
-      </c>
-      <c r="V8" s="61"/>
-      <c r="X8" s="52" t="s">
-        <v>100</v>
-      </c>
-      <c r="Y8" s="53" t="s">
-        <v>101</v>
-      </c>
-      <c r="Z8" s="53" t="s">
-        <v>102</v>
-      </c>
-      <c r="AA8" s="54" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="2:27">
-      <c r="B9" s="55" t="s">
-        <v>100</v>
-      </c>
-      <c r="C9" s="56" t="s">
-        <v>103</v>
-      </c>
-      <c r="D9" s="57" t="s">
-        <v>104</v>
-      </c>
-      <c r="E9" s="56" t="s">
-        <v>105</v>
-      </c>
-      <c r="F9" s="56" t="s">
-        <v>106</v>
-      </c>
-      <c r="G9" s="57" t="s">
-        <v>107</v>
-      </c>
-      <c r="H9" s="56" t="s">
-        <v>108</v>
-      </c>
-      <c r="I9" s="62" t="s">
-        <v>109</v>
-      </c>
-      <c r="J9" s="56" t="s">
-        <v>110</v>
-      </c>
-      <c r="K9" s="57"/>
-      <c r="L9" s="56"/>
-      <c r="M9" s="62" t="s">
-        <v>111</v>
-      </c>
-      <c r="N9" s="56" t="s">
-        <v>112</v>
-      </c>
-      <c r="O9" s="57" t="s">
-        <v>96</v>
-      </c>
-      <c r="P9" s="56" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q9" s="57" t="s">
-        <v>114</v>
-      </c>
-      <c r="R9" s="56" t="s">
-        <v>40</v>
-      </c>
-      <c r="S9" s="58">
-        <v>11111</v>
-      </c>
-      <c r="T9" s="59" t="s">
-        <v>115</v>
-      </c>
-      <c r="U9" s="60" t="s">
-        <v>116</v>
-      </c>
-      <c r="V9" s="61"/>
-      <c r="X9" s="52" t="s">
-        <v>100</v>
-      </c>
-      <c r="Y9" s="53" t="s">
-        <v>101</v>
-      </c>
-      <c r="Z9" s="53" t="s">
-        <v>117</v>
-      </c>
-      <c r="AA9" s="54" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="10" customHeight="1" spans="2:27">
-      <c r="B10" s="55" t="s">
-        <v>119</v>
-      </c>
-      <c r="C10" s="56" t="s">
-        <v>120</v>
-      </c>
-      <c r="D10" s="57" t="s">
-        <v>121</v>
-      </c>
-      <c r="E10" s="56" t="s">
-        <v>122</v>
-      </c>
-      <c r="F10" s="56"/>
-      <c r="G10" s="57" t="s">
-        <v>123</v>
-      </c>
-      <c r="H10" s="56" t="s">
-        <v>124</v>
-      </c>
-      <c r="I10" s="62" t="s">
-        <v>125</v>
-      </c>
-      <c r="J10" s="56" t="s">
-        <v>126</v>
-      </c>
-      <c r="K10" s="57"/>
-      <c r="L10" s="56"/>
-      <c r="M10" s="57"/>
-      <c r="N10" s="56"/>
-      <c r="O10" s="57" t="s">
-        <v>127</v>
-      </c>
-      <c r="P10" s="56" t="s">
-        <v>128</v>
-      </c>
-      <c r="Q10" s="62" t="s">
-        <v>129</v>
-      </c>
-      <c r="R10" s="56" t="s">
-        <v>40</v>
-      </c>
-      <c r="S10" s="58">
-        <v>11111</v>
-      </c>
-      <c r="T10" s="59" t="s">
-        <v>130</v>
-      </c>
-      <c r="U10" s="60" t="s">
-        <v>116</v>
-      </c>
-      <c r="V10" s="61"/>
-      <c r="X10" s="52" t="s">
-        <v>114</v>
-      </c>
-      <c r="Y10" s="53" t="s">
-        <v>131</v>
-      </c>
-      <c r="Z10" s="53" t="s">
-        <v>132</v>
-      </c>
-      <c r="AA10" s="54" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="11" customHeight="1" spans="2:27">
-      <c r="B11" s="55" t="s">
-        <v>80</v>
-      </c>
-      <c r="C11" s="56" t="s">
-        <v>134</v>
-      </c>
-      <c r="D11" s="57" t="s">
-        <v>135</v>
-      </c>
-      <c r="E11" s="56" t="s">
-        <v>136</v>
-      </c>
-      <c r="F11" s="56" t="s">
-        <v>28</v>
-      </c>
-      <c r="G11" s="57" t="s">
-        <v>137</v>
-      </c>
-      <c r="H11" s="56" t="s">
-        <v>138</v>
-      </c>
-      <c r="I11" s="57"/>
-      <c r="J11" s="56"/>
-      <c r="K11" s="57"/>
-      <c r="L11" s="56"/>
-      <c r="M11" s="57"/>
-      <c r="N11" s="56"/>
-      <c r="O11" s="63" t="s">
-        <v>139</v>
-      </c>
-      <c r="P11" s="56" t="s">
-        <v>140</v>
-      </c>
-      <c r="Q11" s="57" t="s">
-        <v>100</v>
-      </c>
-      <c r="R11" s="56" t="s">
-        <v>97</v>
-      </c>
-      <c r="S11" s="58">
-        <v>11111</v>
-      </c>
-      <c r="T11" s="59"/>
-      <c r="U11" s="60"/>
-      <c r="V11" s="61"/>
-      <c r="X11" s="52" t="s">
-        <v>119</v>
-      </c>
-      <c r="Y11" s="53" t="s">
-        <v>101</v>
-      </c>
-      <c r="Z11" s="53" t="s">
-        <v>102</v>
-      </c>
-      <c r="AA11" s="54" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="12" customHeight="1" spans="2:27">
-      <c r="B12" s="55" t="s">
-        <v>114</v>
-      </c>
-      <c r="C12" s="56" t="s">
-        <v>142</v>
-      </c>
-      <c r="D12" s="57" t="s">
-        <v>100</v>
-      </c>
-      <c r="E12" s="64" t="s">
-        <v>143</v>
-      </c>
-      <c r="F12" s="65" t="s">
-        <v>144</v>
-      </c>
-      <c r="G12" s="57" t="s">
-        <v>145</v>
-      </c>
-      <c r="H12" s="56" t="s">
-        <v>146</v>
-      </c>
-      <c r="I12" s="63"/>
-      <c r="J12" s="56"/>
-      <c r="K12" s="57"/>
-      <c r="L12" s="56"/>
-      <c r="M12" s="57"/>
-      <c r="N12" s="56"/>
-      <c r="O12" s="62" t="s">
-        <v>147</v>
-      </c>
-      <c r="P12" s="56" t="s">
-        <v>148</v>
-      </c>
-      <c r="Q12" s="57"/>
-      <c r="R12" s="56" t="s">
-        <v>97</v>
-      </c>
-      <c r="S12" s="58">
-        <v>11111</v>
-      </c>
-      <c r="T12" s="59"/>
-      <c r="U12" s="60"/>
-      <c r="V12" s="61"/>
-      <c r="X12" s="52" t="s">
-        <v>20</v>
-      </c>
-      <c r="Y12" s="53" t="s">
-        <v>149</v>
-      </c>
-      <c r="Z12" s="53" t="s">
-        <v>150</v>
-      </c>
-      <c r="AA12" s="54" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="2:27">
-      <c r="B13" s="55" t="s">
-        <v>152</v>
-      </c>
-      <c r="C13" s="56"/>
-      <c r="D13" s="57" t="s">
-        <v>153</v>
-      </c>
-      <c r="E13" s="64" t="s">
-        <v>154</v>
-      </c>
-      <c r="F13" s="65" t="s">
-        <v>28</v>
-      </c>
-      <c r="G13" s="57"/>
-      <c r="H13" s="56"/>
-      <c r="I13" s="63"/>
-      <c r="J13" s="56"/>
-      <c r="K13" s="57"/>
-      <c r="L13" s="56"/>
-      <c r="M13" s="57"/>
-      <c r="N13" s="56"/>
-      <c r="O13" s="62" t="s">
-        <v>155</v>
-      </c>
-      <c r="P13" s="56" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q13" s="57" t="s">
-        <v>123</v>
-      </c>
-      <c r="R13" s="56" t="s">
-        <v>97</v>
-      </c>
-      <c r="S13" s="58">
-        <v>11111</v>
-      </c>
-      <c r="T13" s="59"/>
-      <c r="U13" s="60"/>
-      <c r="V13" s="61"/>
-      <c r="X13" s="52"/>
-      <c r="Y13" s="53"/>
-      <c r="Z13" s="53"/>
-      <c r="AA13" s="54"/>
-    </row>
-    <row r="14" customHeight="1" spans="2:27">
-      <c r="B14" s="55" t="s">
-        <v>157</v>
-      </c>
-      <c r="C14" s="56" t="s">
-        <v>158</v>
-      </c>
-      <c r="D14" s="57" t="s">
-        <v>159</v>
-      </c>
-      <c r="E14" s="64" t="s">
-        <v>160</v>
-      </c>
-      <c r="F14" s="66"/>
-      <c r="G14" s="67"/>
-      <c r="H14" s="56"/>
-      <c r="I14" s="57"/>
-      <c r="J14" s="56"/>
-      <c r="K14" s="57"/>
-      <c r="L14" s="56"/>
-      <c r="M14" s="57"/>
-      <c r="N14" s="56"/>
-      <c r="O14" s="62" t="s">
-        <v>161</v>
-      </c>
-      <c r="P14" s="56" t="s">
-        <v>162</v>
-      </c>
-      <c r="Q14" s="57" t="s">
-        <v>121</v>
-      </c>
-      <c r="R14" s="56" t="s">
-        <v>97</v>
-      </c>
-      <c r="S14" s="58">
-        <v>11111</v>
-      </c>
-      <c r="T14" s="59"/>
-      <c r="U14" s="60"/>
-      <c r="V14" s="61"/>
-      <c r="X14" s="52"/>
-      <c r="Y14" s="53"/>
-      <c r="Z14" s="53"/>
-      <c r="AA14" s="54"/>
-    </row>
-    <row r="15" customHeight="1" spans="2:27">
-      <c r="B15" s="55"/>
-      <c r="C15" s="56"/>
-      <c r="D15" s="57" t="s">
-        <v>163</v>
-      </c>
-      <c r="E15" s="64" t="s">
-        <v>164</v>
-      </c>
-      <c r="F15" s="66"/>
-      <c r="G15" s="67"/>
-      <c r="H15" s="56"/>
-      <c r="I15" s="57"/>
-      <c r="J15" s="56"/>
-      <c r="K15" s="57"/>
-      <c r="L15" s="56"/>
-      <c r="M15" s="57"/>
-      <c r="N15" s="56"/>
-      <c r="O15" s="57" t="s">
-        <v>165</v>
-      </c>
-      <c r="P15" s="56" t="s">
-        <v>166</v>
-      </c>
-      <c r="Q15" s="57" t="s">
-        <v>127</v>
-      </c>
-      <c r="R15" s="56" t="s">
-        <v>97</v>
-      </c>
-      <c r="S15" s="58">
-        <v>11111</v>
-      </c>
-      <c r="T15" s="59"/>
-      <c r="U15" s="60"/>
-      <c r="V15" s="61"/>
-      <c r="X15" s="52"/>
-      <c r="Y15" s="53"/>
-      <c r="Z15" s="53"/>
-      <c r="AA15" s="54"/>
-    </row>
-    <row r="16" customHeight="1" spans="2:27">
-      <c r="B16" s="55"/>
-      <c r="C16" s="56"/>
-      <c r="D16" s="57" t="s">
-        <v>167</v>
-      </c>
-      <c r="E16" s="64" t="s">
-        <v>168</v>
-      </c>
-      <c r="F16" s="66" t="s">
-        <v>169</v>
-      </c>
-      <c r="G16" s="67"/>
-      <c r="H16" s="56"/>
-      <c r="I16" s="57"/>
-      <c r="J16" s="56"/>
-      <c r="K16" s="57"/>
-      <c r="L16" s="56"/>
-      <c r="M16" s="57"/>
-      <c r="N16" s="56"/>
-      <c r="O16" s="57" t="s">
-        <v>170</v>
-      </c>
-      <c r="P16" s="56" t="s">
-        <v>171</v>
-      </c>
-      <c r="Q16" s="57" t="s">
-        <v>172</v>
-      </c>
-      <c r="R16" s="56" t="s">
-        <v>97</v>
-      </c>
-      <c r="S16" s="58">
-        <v>11111</v>
-      </c>
-      <c r="T16" s="59"/>
-      <c r="U16" s="60"/>
-      <c r="V16" s="61"/>
-      <c r="X16" s="52"/>
-      <c r="Y16" s="53"/>
-      <c r="Z16" s="53"/>
-      <c r="AA16" s="54"/>
-    </row>
-    <row r="17" customHeight="1" spans="2:27">
-      <c r="B17" s="55"/>
-      <c r="C17" s="56"/>
-      <c r="D17" s="57" t="s">
-        <v>173</v>
-      </c>
-      <c r="E17" s="64" t="s">
-        <v>174</v>
-      </c>
-      <c r="F17" s="66"/>
-      <c r="G17" s="67"/>
-      <c r="H17" s="56"/>
-      <c r="I17" s="57"/>
-      <c r="J17" s="56"/>
-      <c r="K17" s="57"/>
-      <c r="L17" s="56"/>
-      <c r="M17" s="57"/>
-      <c r="N17" s="56"/>
-      <c r="O17" s="57" t="s">
-        <v>175</v>
-      </c>
-      <c r="P17" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="Q17" s="57" t="s">
-        <v>177</v>
-      </c>
-      <c r="R17" s="56" t="s">
-        <v>97</v>
-      </c>
-      <c r="S17" s="58">
-        <v>11111</v>
-      </c>
-      <c r="T17" s="59"/>
-      <c r="U17" s="60"/>
-      <c r="V17" s="61"/>
-      <c r="X17" s="52"/>
-      <c r="Y17" s="53"/>
-      <c r="Z17" s="53"/>
-      <c r="AA17" s="54"/>
-    </row>
-    <row r="18" customHeight="1" spans="2:27">
-      <c r="B18" s="55"/>
-      <c r="C18" s="56"/>
-      <c r="D18" s="57" t="s">
-        <v>45</v>
-      </c>
-      <c r="E18" s="64" t="s">
-        <v>178</v>
-      </c>
-      <c r="F18" s="66" t="s">
-        <v>179</v>
-      </c>
-      <c r="G18" s="67"/>
-      <c r="H18" s="56"/>
-      <c r="I18" s="57"/>
-      <c r="J18" s="56"/>
-      <c r="K18" s="57"/>
-      <c r="L18" s="56"/>
-      <c r="M18" s="57"/>
-      <c r="N18" s="56"/>
-      <c r="O18" s="62" t="s">
-        <v>180</v>
-      </c>
-      <c r="P18" s="56" t="s">
-        <v>181</v>
-      </c>
-      <c r="Q18" s="57" t="s">
-        <v>182</v>
-      </c>
-      <c r="R18" s="56" t="s">
-        <v>97</v>
-      </c>
-      <c r="S18" s="58">
-        <v>11111</v>
-      </c>
-      <c r="T18" s="59"/>
-      <c r="U18" s="60"/>
-      <c r="V18" s="61"/>
-      <c r="X18" s="52"/>
-      <c r="Y18" s="53"/>
-      <c r="Z18" s="53"/>
-      <c r="AA18" s="54"/>
-    </row>
-    <row r="19" customHeight="1" spans="2:27">
-      <c r="B19" s="55"/>
-      <c r="C19" s="56"/>
-      <c r="D19" s="62" t="s">
-        <v>183</v>
-      </c>
-      <c r="E19" s="64" t="s">
-        <v>184</v>
-      </c>
-      <c r="F19" s="66" t="s">
-        <v>185</v>
-      </c>
-      <c r="G19" s="67"/>
-      <c r="H19" s="56"/>
-      <c r="I19" s="57"/>
-      <c r="J19" s="56"/>
-      <c r="K19" s="57"/>
-      <c r="L19" s="56"/>
-      <c r="M19" s="57"/>
-      <c r="N19" s="56"/>
-      <c r="O19" s="63" t="s">
-        <v>186</v>
-      </c>
-      <c r="P19" s="56" t="s">
-        <v>187</v>
-      </c>
-      <c r="Q19" s="57" t="s">
-        <v>188</v>
-      </c>
-      <c r="R19" s="56" t="s">
-        <v>97</v>
-      </c>
-      <c r="S19" s="58">
-        <v>11111</v>
-      </c>
-      <c r="T19" s="59"/>
-      <c r="U19" s="60"/>
-      <c r="V19" s="61"/>
-      <c r="X19" s="52"/>
-      <c r="Y19" s="53"/>
-      <c r="Z19" s="53"/>
-      <c r="AA19" s="54"/>
-    </row>
-    <row r="20" customHeight="1" spans="2:27">
-      <c r="B20" s="55"/>
-      <c r="C20" s="56"/>
-      <c r="D20" s="62" t="s">
-        <v>189</v>
-      </c>
-      <c r="E20" s="64" t="s">
-        <v>190</v>
-      </c>
-      <c r="F20" s="66"/>
-      <c r="G20" s="67"/>
-      <c r="H20" s="56"/>
-      <c r="I20" s="57"/>
-      <c r="J20" s="56"/>
-      <c r="K20" s="57"/>
-      <c r="L20" s="56"/>
-      <c r="M20" s="57"/>
-      <c r="N20" s="56"/>
-      <c r="O20" s="63" t="s">
-        <v>191</v>
-      </c>
-      <c r="P20" s="56" t="s">
-        <v>192</v>
-      </c>
-      <c r="Q20" s="57" t="s">
-        <v>193</v>
-      </c>
-      <c r="R20" s="56" t="s">
-        <v>97</v>
-      </c>
-      <c r="S20" s="58">
-        <v>11111</v>
-      </c>
-      <c r="T20" s="59"/>
-      <c r="U20" s="60"/>
-      <c r="V20" s="61"/>
-      <c r="X20" s="52"/>
-      <c r="Y20" s="53"/>
-      <c r="Z20" s="53"/>
-      <c r="AA20" s="54"/>
-    </row>
-    <row r="21" customHeight="1" spans="2:27">
-      <c r="B21" s="55"/>
-      <c r="C21" s="56"/>
-      <c r="D21" s="57" t="s">
-        <v>194</v>
-      </c>
-      <c r="E21" s="64" t="s">
-        <v>195</v>
-      </c>
-      <c r="F21" s="66"/>
-      <c r="G21" s="67"/>
-      <c r="H21" s="56"/>
-      <c r="I21" s="57"/>
-      <c r="J21" s="56"/>
-      <c r="K21" s="57"/>
-      <c r="L21" s="56"/>
-      <c r="M21" s="57"/>
-      <c r="N21" s="56"/>
-      <c r="O21" s="63" t="s">
-        <v>196</v>
-      </c>
-      <c r="P21" s="56" t="s">
-        <v>197</v>
-      </c>
-      <c r="Q21" s="57" t="s">
-        <v>35</v>
-      </c>
-      <c r="R21" s="56" t="s">
-        <v>97</v>
-      </c>
-      <c r="S21" s="58">
-        <v>11111</v>
-      </c>
-      <c r="T21" s="59"/>
-      <c r="U21" s="60"/>
-      <c r="V21" s="61"/>
-      <c r="X21" s="52"/>
-      <c r="Y21" s="53"/>
-      <c r="Z21" s="53"/>
-      <c r="AA21" s="54"/>
-    </row>
-    <row r="22" customHeight="1" spans="2:27">
-      <c r="B22" s="55"/>
-      <c r="C22" s="56"/>
-      <c r="D22" s="62" t="s">
-        <v>198</v>
-      </c>
-      <c r="E22" s="64" t="s">
-        <v>199</v>
-      </c>
-      <c r="F22" s="66"/>
-      <c r="G22" s="67"/>
-      <c r="H22" s="56"/>
-      <c r="I22" s="57"/>
-      <c r="J22" s="56"/>
-      <c r="K22" s="57"/>
-      <c r="L22" s="56"/>
-      <c r="M22" s="57"/>
-      <c r="N22" s="56"/>
-      <c r="O22" s="62" t="s">
-        <v>200</v>
-      </c>
-      <c r="P22" s="56" t="s">
-        <v>201</v>
-      </c>
-      <c r="Q22" s="57" t="s">
-        <v>186</v>
-      </c>
-      <c r="R22" s="56" t="s">
-        <v>97</v>
-      </c>
-      <c r="S22" s="58">
-        <v>11111</v>
-      </c>
-      <c r="T22" s="59"/>
-      <c r="U22" s="60"/>
-      <c r="V22" s="61"/>
-      <c r="X22" s="52"/>
-      <c r="Y22" s="53"/>
-      <c r="Z22" s="53"/>
-      <c r="AA22" s="54"/>
-    </row>
-    <row r="23" customHeight="1" spans="2:27">
-      <c r="B23" s="55"/>
-      <c r="C23" s="56"/>
-      <c r="D23" s="57" t="s">
-        <v>202</v>
-      </c>
-      <c r="E23" s="64" t="s">
-        <v>203</v>
-      </c>
-      <c r="F23" s="66"/>
-      <c r="G23" s="67"/>
-      <c r="H23" s="56"/>
-      <c r="I23" s="57"/>
-      <c r="J23" s="56"/>
-      <c r="K23" s="57"/>
-      <c r="L23" s="56"/>
-      <c r="M23" s="57"/>
-      <c r="N23" s="56"/>
-      <c r="O23" s="62" t="s">
-        <v>204</v>
-      </c>
-      <c r="P23" s="56" t="s">
-        <v>205</v>
-      </c>
-      <c r="Q23" s="57"/>
-      <c r="R23" s="56" t="s">
-        <v>97</v>
-      </c>
-      <c r="S23" s="58">
-        <v>11111</v>
-      </c>
-      <c r="T23" s="59"/>
-      <c r="U23" s="60"/>
-      <c r="V23" s="61"/>
-      <c r="X23" s="52"/>
-      <c r="Y23" s="53"/>
-      <c r="Z23" s="53"/>
-      <c r="AA23" s="54"/>
-    </row>
-    <row r="24" customHeight="1" spans="2:27">
-      <c r="B24" s="55"/>
-      <c r="C24" s="56"/>
-      <c r="D24" s="57" t="s">
-        <v>206</v>
-      </c>
-      <c r="E24" s="64" t="s">
-        <v>207</v>
-      </c>
-      <c r="F24" s="66"/>
-      <c r="G24" s="67"/>
-      <c r="H24" s="56"/>
-      <c r="I24" s="57"/>
-      <c r="J24" s="56"/>
-      <c r="K24" s="57"/>
-      <c r="L24" s="56"/>
-      <c r="M24" s="57"/>
-      <c r="N24" s="56"/>
-      <c r="O24" s="63"/>
-      <c r="P24" s="56"/>
-      <c r="Q24" s="57" t="s">
-        <v>208</v>
-      </c>
-      <c r="R24" s="56" t="s">
-        <v>97</v>
-      </c>
-      <c r="S24" s="58">
-        <v>11111</v>
-      </c>
-      <c r="T24" s="59"/>
-      <c r="U24" s="60"/>
-      <c r="V24" s="61"/>
-      <c r="X24" s="52"/>
-      <c r="Y24" s="53"/>
-      <c r="Z24" s="53"/>
-      <c r="AA24" s="54"/>
-    </row>
-    <row r="25" customHeight="1" spans="2:27">
-      <c r="B25" s="55"/>
-      <c r="C25" s="67"/>
-      <c r="D25" s="63" t="s">
-        <v>209</v>
-      </c>
-      <c r="E25" s="64" t="s">
-        <v>210</v>
-      </c>
-      <c r="F25" s="66" t="s">
-        <v>211</v>
-      </c>
-      <c r="G25" s="67"/>
-      <c r="H25" s="67"/>
-      <c r="I25" s="57"/>
-      <c r="J25" s="67"/>
-      <c r="K25" s="57"/>
-      <c r="L25" s="67"/>
-      <c r="M25" s="57"/>
-      <c r="N25" s="67"/>
-      <c r="O25" s="63"/>
-      <c r="P25" s="67"/>
-      <c r="Q25" s="57" t="s">
-        <v>77</v>
-      </c>
-      <c r="R25" s="67" t="s">
-        <v>97</v>
-      </c>
-      <c r="S25" s="58">
-        <v>51111</v>
-      </c>
-      <c r="T25" s="59"/>
-      <c r="U25" s="60"/>
-      <c r="V25" s="61"/>
-    </row>
-    <row r="26" customHeight="1" spans="2:27">
-      <c r="B26" s="55"/>
-      <c r="C26" s="67"/>
-      <c r="D26" s="63" t="s">
-        <v>212</v>
-      </c>
-      <c r="E26" s="64" t="s">
-        <v>213</v>
-      </c>
-      <c r="F26" s="66" t="s">
-        <v>214</v>
-      </c>
-      <c r="G26" s="67"/>
-      <c r="H26" s="67"/>
-      <c r="I26" s="57"/>
-      <c r="J26" s="67"/>
-      <c r="K26" s="57"/>
-      <c r="L26" s="67"/>
-      <c r="M26" s="57"/>
-      <c r="N26" s="67"/>
-      <c r="O26" s="63"/>
-      <c r="P26" s="67"/>
-      <c r="Q26" s="57" t="s">
-        <v>215</v>
-      </c>
-      <c r="R26" s="56" t="s">
-        <v>97</v>
-      </c>
-      <c r="S26" s="58">
-        <v>11111</v>
-      </c>
-      <c r="T26" s="59"/>
-      <c r="U26" s="60"/>
-      <c r="V26" s="61"/>
-    </row>
-    <row r="27" customHeight="1" spans="2:27">
-      <c r="B27" s="55"/>
-      <c r="C27" s="56"/>
-      <c r="D27" s="57"/>
-      <c r="E27" s="64"/>
-      <c r="F27" s="66"/>
-      <c r="G27" s="67"/>
-      <c r="H27" s="56"/>
-      <c r="I27" s="57"/>
-      <c r="J27" s="56"/>
-      <c r="K27" s="57"/>
-      <c r="L27" s="56"/>
-      <c r="M27" s="57"/>
-      <c r="N27" s="56"/>
-      <c r="O27" s="63"/>
-      <c r="P27" s="56"/>
-      <c r="Q27" s="57" t="s">
-        <v>87</v>
-      </c>
-      <c r="R27" s="56" t="s">
-        <v>97</v>
-      </c>
-      <c r="S27" s="58">
-        <v>11111</v>
-      </c>
-      <c r="T27" s="59"/>
-      <c r="U27" s="60"/>
-      <c r="V27" s="61"/>
-    </row>
-    <row r="28" customHeight="1" spans="2:27">
-      <c r="B28" s="55"/>
-      <c r="C28" s="56"/>
-      <c r="D28" s="57"/>
-      <c r="E28" s="64"/>
-      <c r="F28" s="66"/>
-      <c r="G28" s="67"/>
-      <c r="H28" s="56"/>
-      <c r="I28" s="57"/>
-      <c r="J28" s="56"/>
-      <c r="K28" s="57"/>
-      <c r="L28" s="56"/>
-      <c r="M28" s="57"/>
-      <c r="N28" s="56"/>
-      <c r="O28" s="57"/>
-      <c r="P28" s="56"/>
-      <c r="Q28" s="57" t="s">
-        <v>80</v>
-      </c>
-      <c r="R28" s="56" t="s">
-        <v>97</v>
-      </c>
-      <c r="S28" s="58">
-        <v>11111</v>
-      </c>
-      <c r="T28" s="59"/>
-      <c r="U28" s="60"/>
-      <c r="V28" s="61"/>
-    </row>
-    <row r="29" customHeight="1" spans="2:27">
-      <c r="B29" s="55"/>
-      <c r="C29" s="56"/>
-      <c r="D29" s="57"/>
-      <c r="E29" s="64"/>
-      <c r="F29" s="68"/>
-      <c r="G29" s="56"/>
-      <c r="H29" s="56"/>
-      <c r="I29" s="57"/>
-      <c r="J29" s="69"/>
-      <c r="K29" s="56"/>
-      <c r="L29" s="56"/>
-      <c r="M29" s="57"/>
-      <c r="N29" s="69"/>
-      <c r="O29" s="56"/>
-      <c r="P29" s="56"/>
-      <c r="Q29" s="62" t="s">
-        <v>155</v>
-      </c>
-      <c r="R29" s="56" t="s">
-        <v>97</v>
-      </c>
-      <c r="S29" s="58">
-        <v>11111</v>
-      </c>
-      <c r="T29" s="59"/>
-      <c r="U29" s="60"/>
-      <c r="V29" s="61"/>
-    </row>
-    <row r="30" customHeight="1" spans="2:27">
-      <c r="B30" s="55"/>
-      <c r="C30" s="56"/>
-      <c r="D30" s="57"/>
-      <c r="E30" s="64"/>
-      <c r="F30" s="68"/>
-      <c r="G30" s="56"/>
-      <c r="H30" s="56"/>
-      <c r="I30" s="57"/>
-      <c r="J30" s="69"/>
-      <c r="K30" s="56"/>
-      <c r="L30" s="56"/>
-      <c r="M30" s="57"/>
-      <c r="N30" s="69"/>
-      <c r="O30" s="56"/>
-      <c r="P30" s="56"/>
-      <c r="Q30" s="57" t="s">
-        <v>33</v>
-      </c>
-      <c r="R30" s="56" t="s">
-        <v>216</v>
-      </c>
-      <c r="S30" s="58">
-        <v>11111</v>
-      </c>
-      <c r="T30" s="59"/>
-      <c r="U30" s="60"/>
-      <c r="V30" s="61"/>
-    </row>
-    <row r="31" customHeight="1" spans="2:27">
-      <c r="B31" s="55"/>
-      <c r="C31" s="56"/>
-      <c r="D31" s="57"/>
-      <c r="E31" s="64"/>
-      <c r="F31" s="68"/>
-      <c r="G31" s="56"/>
-      <c r="H31" s="56"/>
-      <c r="I31" s="57"/>
-      <c r="J31" s="69"/>
-      <c r="K31" s="56"/>
-      <c r="L31" s="56"/>
-      <c r="M31" s="57"/>
-      <c r="N31" s="69"/>
-      <c r="O31" s="56"/>
-      <c r="P31" s="56"/>
-      <c r="Q31" s="62" t="s">
-        <v>52</v>
-      </c>
-      <c r="R31" s="56" t="s">
-        <v>216</v>
-      </c>
-      <c r="S31" s="58">
-        <v>11111</v>
-      </c>
-      <c r="T31" s="59"/>
-      <c r="U31" s="60"/>
-      <c r="V31" s="61"/>
-    </row>
-    <row r="32" customHeight="1" spans="2:27">
-      <c r="B32" s="55"/>
-      <c r="C32" s="56"/>
-      <c r="D32" s="57"/>
-      <c r="E32" s="64"/>
-      <c r="F32" s="68"/>
-      <c r="G32" s="56"/>
-      <c r="H32" s="56"/>
-      <c r="I32" s="57"/>
-      <c r="J32" s="69"/>
-      <c r="K32" s="56"/>
-      <c r="L32" s="56"/>
-      <c r="M32" s="57"/>
-      <c r="N32" s="69"/>
-      <c r="O32" s="56"/>
-      <c r="P32" s="56"/>
-      <c r="Q32" s="57" t="s">
-        <v>153</v>
-      </c>
-      <c r="R32" s="56" t="s">
-        <v>216</v>
-      </c>
-      <c r="S32" s="58">
-        <v>11111</v>
-      </c>
-      <c r="T32" s="59"/>
-      <c r="U32" s="60"/>
-      <c r="V32" s="61"/>
-    </row>
-    <row r="33" customHeight="1" spans="2:22">
-      <c r="B33" s="55"/>
-      <c r="C33" s="56"/>
-      <c r="D33" s="57"/>
-      <c r="E33" s="64"/>
-      <c r="F33" s="68"/>
-      <c r="G33" s="56"/>
-      <c r="H33" s="56"/>
-      <c r="I33" s="57"/>
-      <c r="J33" s="69"/>
-      <c r="K33" s="56"/>
-      <c r="L33" s="56"/>
-      <c r="M33" s="57"/>
-      <c r="N33" s="69"/>
-      <c r="O33" s="56"/>
-      <c r="P33" s="56"/>
-      <c r="Q33" s="57" t="s">
-        <v>73</v>
-      </c>
-      <c r="R33" s="56" t="s">
-        <v>216</v>
-      </c>
-      <c r="S33" s="58">
-        <v>11111</v>
-      </c>
-      <c r="T33" s="59"/>
-      <c r="U33" s="60"/>
-      <c r="V33" s="61"/>
-    </row>
-    <row r="34" customHeight="1" spans="2:22">
-      <c r="B34" s="55"/>
-      <c r="C34" s="56"/>
-      <c r="D34" s="57"/>
-      <c r="E34" s="64"/>
-      <c r="F34" s="68"/>
-      <c r="G34" s="56"/>
-      <c r="H34" s="56"/>
-      <c r="I34" s="57"/>
-      <c r="J34" s="69"/>
-      <c r="K34" s="56"/>
-      <c r="L34" s="56"/>
-      <c r="M34" s="57"/>
-      <c r="N34" s="69"/>
-      <c r="O34" s="56"/>
-      <c r="P34" s="56"/>
-      <c r="Q34" s="57" t="s">
-        <v>217</v>
-      </c>
-      <c r="R34" s="56" t="s">
-        <v>216</v>
-      </c>
-      <c r="S34" s="58">
-        <v>11111</v>
-      </c>
-      <c r="T34" s="59"/>
-      <c r="U34" s="60"/>
-      <c r="V34" s="61"/>
-    </row>
-    <row r="35" customHeight="1" spans="2:22">
-      <c r="B35" s="55"/>
-      <c r="C35" s="56"/>
-      <c r="D35" s="57"/>
-      <c r="E35" s="64"/>
-      <c r="F35" s="68"/>
-      <c r="G35" s="56"/>
-      <c r="H35" s="56"/>
-      <c r="I35" s="57"/>
-      <c r="J35" s="69"/>
-      <c r="K35" s="56"/>
-      <c r="L35" s="56"/>
-      <c r="M35" s="57"/>
-      <c r="N35" s="69"/>
-      <c r="O35" s="56"/>
-      <c r="P35" s="56"/>
-      <c r="Q35" s="57" t="s">
-        <v>69</v>
-      </c>
-      <c r="R35" s="56" t="s">
-        <v>216</v>
-      </c>
-      <c r="S35" s="58">
-        <v>11111</v>
-      </c>
-      <c r="T35" s="59"/>
-      <c r="U35" s="60"/>
-      <c r="V35" s="61"/>
-    </row>
-    <row r="36" customHeight="1" spans="2:22">
-      <c r="B36" s="55"/>
-      <c r="C36" s="56"/>
-      <c r="D36" s="57"/>
-      <c r="E36" s="64"/>
-      <c r="F36" s="68"/>
-      <c r="G36" s="56"/>
-      <c r="H36" s="56"/>
-      <c r="I36" s="57"/>
-      <c r="J36" s="69"/>
-      <c r="K36" s="56"/>
-      <c r="L36" s="56"/>
-      <c r="M36" s="57"/>
-      <c r="N36" s="69"/>
-      <c r="O36" s="56"/>
-      <c r="P36" s="56"/>
-      <c r="Q36" s="57" t="s">
-        <v>218</v>
-      </c>
-      <c r="R36" s="56" t="s">
-        <v>216</v>
-      </c>
-      <c r="S36" s="58">
-        <v>11111</v>
-      </c>
-      <c r="T36" s="59"/>
-      <c r="U36" s="60"/>
-      <c r="V36" s="61"/>
-    </row>
-    <row r="37" customHeight="1" spans="2:22">
-      <c r="B37" s="70"/>
-      <c r="D37" s="71"/>
-      <c r="E37" s="72"/>
-      <c r="F37" s="73"/>
-      <c r="I37" s="71"/>
-      <c r="J37" s="74"/>
-      <c r="M37" s="71"/>
-      <c r="N37" s="74"/>
-      <c r="Q37" s="71" t="s">
-        <v>219</v>
-      </c>
-      <c r="R37" s="56" t="s">
-        <v>97</v>
-      </c>
-      <c r="S37" s="58">
-        <v>11111</v>
-      </c>
-      <c r="T37" s="59"/>
-      <c r="U37" s="60"/>
-      <c r="V37" s="61"/>
-    </row>
-    <row r="38" customHeight="1" spans="2:22">
-      <c r="B38" s="70"/>
-      <c r="D38" s="71"/>
-      <c r="E38" s="72"/>
-      <c r="F38" s="73"/>
-      <c r="I38" s="71"/>
-      <c r="J38" s="74"/>
-      <c r="M38" s="71"/>
-      <c r="N38" s="74"/>
-      <c r="Q38" s="71" t="s">
-        <v>220</v>
-      </c>
-      <c r="R38" s="56" t="s">
-        <v>97</v>
-      </c>
-      <c r="S38" s="58">
-        <v>11111</v>
-      </c>
-      <c r="T38" s="59"/>
-      <c r="U38" s="60"/>
-      <c r="V38" s="61"/>
-    </row>
-    <row r="39" customHeight="1" spans="2:22">
-      <c r="B39" s="70"/>
-      <c r="D39" s="71"/>
-      <c r="E39" s="72"/>
-      <c r="F39" s="73"/>
-      <c r="I39" s="71"/>
-      <c r="J39" s="74"/>
-      <c r="M39" s="71"/>
-      <c r="N39" s="74"/>
-      <c r="Q39" s="71" t="s">
-        <v>221</v>
-      </c>
-      <c r="R39" s="56" t="s">
-        <v>216</v>
-      </c>
-      <c r="S39" s="58">
-        <v>11111</v>
-      </c>
-      <c r="T39" s="59"/>
-      <c r="U39" s="60"/>
-      <c r="V39" s="61"/>
+      <c r="T39" s="58"/>
+      <c r="U39" s="59"/>
+      <c r="V39" s="60"/>
     </row>
     <row r="40" customHeight="1" spans="2:22">
-      <c r="B40" s="70"/>
-      <c r="D40" s="71"/>
-      <c r="E40" s="72"/>
-      <c r="F40" s="73"/>
-      <c r="I40" s="71"/>
-      <c r="J40" s="74"/>
-      <c r="M40" s="71"/>
-      <c r="N40" s="74"/>
+      <c r="B40" s="66"/>
+      <c r="D40" s="67"/>
+      <c r="E40" s="68"/>
+      <c r="F40" s="69"/>
+      <c r="I40" s="67"/>
+      <c r="J40" s="70"/>
+      <c r="M40" s="67"/>
+      <c r="N40" s="70"/>
       <c r="Q40" s="62" t="s">
-        <v>222</v>
-      </c>
-      <c r="R40" s="56" t="s">
-        <v>97</v>
-      </c>
-      <c r="S40" s="58">
-        <v>11111</v>
-      </c>
-      <c r="T40" s="59"/>
-      <c r="U40" s="60"/>
-      <c r="V40" s="61"/>
+        <v>223</v>
+      </c>
+      <c r="R40" s="55" t="s">
+        <v>95</v>
+      </c>
+      <c r="S40" s="57">
+        <v>23121</v>
+      </c>
+      <c r="T40" s="58"/>
+      <c r="U40" s="59"/>
+      <c r="V40" s="60"/>
     </row>
     <row r="41" customHeight="1" spans="2:22">
-      <c r="B41" s="70"/>
-      <c r="D41" s="71"/>
-      <c r="E41" s="72"/>
-      <c r="F41" s="73"/>
-      <c r="I41" s="71"/>
-      <c r="J41" s="74"/>
-      <c r="M41" s="71"/>
-      <c r="N41" s="74"/>
-      <c r="Q41" s="71" t="s">
-        <v>223</v>
-      </c>
-      <c r="R41" s="56" t="s">
-        <v>97</v>
-      </c>
-      <c r="S41" s="58">
-        <v>11111</v>
-      </c>
-      <c r="T41" s="59"/>
-      <c r="U41" s="60"/>
-      <c r="V41" s="61"/>
+      <c r="B41" s="66"/>
+      <c r="D41" s="67"/>
+      <c r="E41" s="68"/>
+      <c r="F41" s="69"/>
+      <c r="I41" s="67"/>
+      <c r="J41" s="70"/>
+      <c r="M41" s="67"/>
+      <c r="N41" s="70"/>
+      <c r="Q41" s="67"/>
+      <c r="R41" s="55"/>
+      <c r="S41" s="57"/>
+      <c r="T41" s="58"/>
+      <c r="U41" s="59"/>
+      <c r="V41" s="60"/>
     </row>
     <row r="42" customHeight="1" spans="2:22">
-      <c r="B42" s="70"/>
-      <c r="D42" s="71"/>
-      <c r="E42" s="72"/>
-      <c r="F42" s="73"/>
-      <c r="I42" s="71"/>
-      <c r="J42" s="74"/>
-      <c r="M42" s="71"/>
-      <c r="N42" s="74"/>
-      <c r="Q42" s="62" t="s">
-        <v>224</v>
-      </c>
-      <c r="R42" s="56" t="s">
-        <v>97</v>
-      </c>
-      <c r="S42" s="58">
-        <v>11111</v>
-      </c>
-      <c r="T42" s="59"/>
-      <c r="U42" s="60"/>
-      <c r="V42" s="61"/>
+      <c r="B42" s="66"/>
+      <c r="D42" s="67"/>
+      <c r="E42" s="68"/>
+      <c r="F42" s="69"/>
+      <c r="I42" s="67"/>
+      <c r="J42" s="70"/>
+      <c r="M42" s="67"/>
+      <c r="N42" s="70"/>
+      <c r="Q42" s="61"/>
+      <c r="R42" s="55"/>
+      <c r="S42" s="57"/>
+      <c r="T42" s="58"/>
+      <c r="U42" s="59"/>
+      <c r="V42" s="60"/>
     </row>
     <row r="43" customHeight="1" spans="2:22">
-      <c r="B43" s="70"/>
-      <c r="D43" s="71"/>
-      <c r="E43" s="72"/>
-      <c r="F43" s="73"/>
-      <c r="I43" s="71"/>
-      <c r="J43" s="74"/>
-      <c r="M43" s="71"/>
-      <c r="N43" s="74"/>
-      <c r="Q43" s="71"/>
+      <c r="B43" s="66"/>
+      <c r="D43" s="67"/>
+      <c r="E43" s="68"/>
+      <c r="F43" s="69"/>
+      <c r="I43" s="67"/>
+      <c r="J43" s="70"/>
+      <c r="M43" s="67"/>
+      <c r="N43" s="70"/>
+      <c r="Q43" s="67"/>
       <c r="R43"/>
-      <c r="S43" s="75"/>
-      <c r="T43" s="59"/>
-      <c r="U43" s="60"/>
-      <c r="V43" s="61"/>
+      <c r="S43" s="71"/>
+      <c r="T43" s="58"/>
+      <c r="U43" s="59"/>
+      <c r="V43" s="60"/>
     </row>
     <row r="44" customHeight="1" spans="2:22">
-      <c r="B44" s="70"/>
-      <c r="D44" s="71"/>
-      <c r="E44" s="72"/>
-      <c r="F44" s="73"/>
-      <c r="I44" s="71"/>
-      <c r="J44" s="74"/>
-      <c r="M44" s="71"/>
-      <c r="N44" s="74"/>
-      <c r="Q44" s="71"/>
-      <c r="S44" s="75"/>
-      <c r="T44" s="59"/>
-      <c r="U44" s="60"/>
-      <c r="V44" s="61"/>
+      <c r="B44" s="66"/>
+      <c r="D44" s="67"/>
+      <c r="E44" s="68"/>
+      <c r="F44" s="69"/>
+      <c r="I44" s="67"/>
+      <c r="J44" s="70"/>
+      <c r="M44" s="67"/>
+      <c r="N44" s="70"/>
+      <c r="Q44" s="67"/>
+      <c r="S44" s="71"/>
+      <c r="T44" s="58"/>
+      <c r="U44" s="59"/>
+      <c r="V44" s="60"/>
     </row>
     <row r="45" customHeight="1" spans="2:22">
-      <c r="B45" s="70"/>
-      <c r="D45" s="71"/>
-      <c r="E45" s="72"/>
-      <c r="F45" s="73"/>
-      <c r="I45" s="71"/>
-      <c r="J45" s="74"/>
-      <c r="M45" s="71"/>
-      <c r="N45" s="74"/>
-      <c r="Q45" s="71"/>
-      <c r="S45" s="75"/>
-      <c r="T45" s="59"/>
-      <c r="U45" s="60"/>
-      <c r="V45" s="61"/>
+      <c r="B45" s="66"/>
+      <c r="D45" s="67"/>
+      <c r="E45" s="68"/>
+      <c r="F45" s="69"/>
+      <c r="I45" s="67"/>
+      <c r="J45" s="70"/>
+      <c r="M45" s="67"/>
+      <c r="N45" s="70"/>
+      <c r="Q45" s="67"/>
+      <c r="S45" s="71"/>
+      <c r="T45" s="58"/>
+      <c r="U45" s="59"/>
+      <c r="V45" s="60"/>
     </row>
     <row r="46" customHeight="1" spans="2:22">
-      <c r="B46" s="70"/>
-      <c r="D46" s="71"/>
-      <c r="E46" s="72"/>
-      <c r="F46" s="73"/>
-      <c r="I46" s="71"/>
-      <c r="J46" s="74"/>
-      <c r="M46" s="71"/>
-      <c r="N46" s="74"/>
-      <c r="Q46" s="71"/>
-      <c r="S46" s="75"/>
-      <c r="T46" s="59"/>
-      <c r="U46" s="60"/>
-      <c r="V46" s="61"/>
+      <c r="B46" s="66"/>
+      <c r="D46" s="67"/>
+      <c r="E46" s="68"/>
+      <c r="F46" s="69"/>
+      <c r="I46" s="67"/>
+      <c r="J46" s="70"/>
+      <c r="M46" s="67"/>
+      <c r="N46" s="70"/>
+      <c r="Q46" s="67"/>
+      <c r="S46" s="71"/>
+      <c r="T46" s="58"/>
+      <c r="U46" s="59"/>
+      <c r="V46" s="60"/>
     </row>
     <row r="47" customHeight="1" spans="2:22">
-      <c r="B47" s="70"/>
-      <c r="D47" s="71"/>
-      <c r="E47" s="72"/>
-      <c r="F47" s="73"/>
-      <c r="I47" s="71"/>
-      <c r="J47" s="74"/>
-      <c r="M47" s="71"/>
-      <c r="N47" s="74"/>
-      <c r="Q47" s="71"/>
-      <c r="S47" s="75"/>
-      <c r="T47" s="59"/>
-      <c r="U47" s="60"/>
-      <c r="V47" s="61"/>
+      <c r="B47" s="66"/>
+      <c r="D47" s="67"/>
+      <c r="E47" s="68"/>
+      <c r="F47" s="69"/>
+      <c r="I47" s="67"/>
+      <c r="J47" s="70"/>
+      <c r="M47" s="67"/>
+      <c r="N47" s="70"/>
+      <c r="Q47" s="67"/>
+      <c r="S47" s="71"/>
+      <c r="T47" s="58"/>
+      <c r="U47" s="59"/>
+      <c r="V47" s="60"/>
     </row>
     <row r="48" customHeight="1" spans="2:22">
-      <c r="B48" s="70"/>
-      <c r="D48" s="71"/>
-      <c r="E48" s="72"/>
-      <c r="F48" s="73"/>
-      <c r="I48" s="71"/>
-      <c r="J48" s="74"/>
-      <c r="M48" s="71"/>
-      <c r="N48" s="74"/>
-      <c r="Q48" s="71"/>
-      <c r="S48" s="75"/>
-      <c r="T48" s="59"/>
-      <c r="U48" s="60"/>
-      <c r="V48" s="61"/>
+      <c r="B48" s="66"/>
+      <c r="D48" s="67"/>
+      <c r="E48" s="68"/>
+      <c r="F48" s="69"/>
+      <c r="I48" s="67"/>
+      <c r="J48" s="70"/>
+      <c r="M48" s="67"/>
+      <c r="N48" s="70"/>
+      <c r="Q48" s="67"/>
+      <c r="S48" s="71"/>
+      <c r="T48" s="58"/>
+      <c r="U48" s="59"/>
+      <c r="V48" s="60"/>
     </row>
     <row r="49" customHeight="1" spans="2:22">
-      <c r="B49" s="70"/>
-      <c r="D49" s="71"/>
-      <c r="E49" s="72"/>
-      <c r="F49" s="73"/>
-      <c r="I49" s="71"/>
-      <c r="J49" s="74"/>
-      <c r="M49" s="71"/>
-      <c r="N49" s="74"/>
-      <c r="Q49" s="71"/>
-      <c r="S49" s="75"/>
-      <c r="T49" s="59"/>
-      <c r="U49" s="60"/>
-      <c r="V49" s="61"/>
+      <c r="B49" s="66"/>
+      <c r="D49" s="67"/>
+      <c r="E49" s="68"/>
+      <c r="F49" s="69"/>
+      <c r="I49" s="67"/>
+      <c r="J49" s="70"/>
+      <c r="M49" s="67"/>
+      <c r="N49" s="70"/>
+      <c r="Q49" s="67"/>
+      <c r="S49" s="71"/>
+      <c r="T49" s="58"/>
+      <c r="U49" s="59"/>
+      <c r="V49" s="60"/>
     </row>
     <row r="50" customHeight="1" spans="2:22">
-      <c r="B50" s="70"/>
-      <c r="D50" s="71"/>
-      <c r="E50" s="72"/>
-      <c r="F50" s="73"/>
-      <c r="I50" s="71"/>
-      <c r="J50" s="74"/>
-      <c r="M50" s="71"/>
-      <c r="N50" s="74"/>
-      <c r="Q50" s="71"/>
-      <c r="S50" s="75"/>
-      <c r="T50" s="59"/>
-      <c r="U50" s="60"/>
-      <c r="V50" s="61"/>
+      <c r="B50" s="66"/>
+      <c r="D50" s="67"/>
+      <c r="E50" s="68"/>
+      <c r="F50" s="69"/>
+      <c r="I50" s="67"/>
+      <c r="J50" s="70"/>
+      <c r="M50" s="67"/>
+      <c r="N50" s="70"/>
+      <c r="Q50" s="67"/>
+      <c r="S50" s="71"/>
+      <c r="T50" s="58"/>
+      <c r="U50" s="59"/>
+      <c r="V50" s="60"/>
     </row>
     <row r="51" customHeight="1" spans="2:22">
-      <c r="B51" s="70"/>
-      <c r="D51" s="71"/>
-      <c r="E51" s="72"/>
-      <c r="F51" s="73"/>
-      <c r="I51" s="71"/>
-      <c r="J51" s="74"/>
-      <c r="M51" s="71"/>
-      <c r="N51" s="74"/>
-      <c r="Q51" s="71"/>
-      <c r="S51" s="75"/>
-      <c r="T51" s="59"/>
-      <c r="U51" s="60"/>
-      <c r="V51" s="61"/>
+      <c r="B51" s="66"/>
+      <c r="D51" s="67"/>
+      <c r="E51" s="68"/>
+      <c r="F51" s="69"/>
+      <c r="I51" s="67"/>
+      <c r="J51" s="70"/>
+      <c r="M51" s="67"/>
+      <c r="N51" s="70"/>
+      <c r="Q51" s="67"/>
+      <c r="S51" s="71"/>
+      <c r="T51" s="58"/>
+      <c r="U51" s="59"/>
+      <c r="V51" s="60"/>
     </row>
     <row r="52" customHeight="1" spans="2:22">
-      <c r="B52" s="70"/>
-      <c r="D52" s="71"/>
-      <c r="E52" s="72"/>
-      <c r="F52" s="73"/>
-      <c r="I52" s="71"/>
-      <c r="J52" s="74"/>
-      <c r="M52" s="71"/>
-      <c r="N52" s="74"/>
-      <c r="Q52" s="71"/>
-      <c r="S52" s="75"/>
-      <c r="T52" s="59"/>
-      <c r="U52" s="60"/>
-      <c r="V52" s="61"/>
+      <c r="B52" s="66"/>
+      <c r="D52" s="67"/>
+      <c r="E52" s="68"/>
+      <c r="F52" s="69"/>
+      <c r="I52" s="67"/>
+      <c r="J52" s="70"/>
+      <c r="M52" s="67"/>
+      <c r="N52" s="70"/>
+      <c r="Q52" s="67"/>
+      <c r="S52" s="71"/>
+      <c r="T52" s="58"/>
+      <c r="U52" s="59"/>
+      <c r="V52" s="60"/>
     </row>
     <row r="53" customHeight="1" spans="2:22">
-      <c r="B53" s="70"/>
-      <c r="D53" s="71"/>
-      <c r="E53" s="72"/>
-      <c r="F53" s="73"/>
-      <c r="I53" s="71"/>
-      <c r="J53" s="74"/>
-      <c r="M53" s="71"/>
-      <c r="N53" s="74"/>
-      <c r="Q53" s="71"/>
-      <c r="S53" s="75"/>
-      <c r="T53" s="59"/>
-      <c r="U53" s="60"/>
-      <c r="V53" s="61"/>
+      <c r="B53" s="66"/>
+      <c r="D53" s="67"/>
+      <c r="E53" s="68"/>
+      <c r="F53" s="69"/>
+      <c r="I53" s="67"/>
+      <c r="J53" s="70"/>
+      <c r="M53" s="67"/>
+      <c r="N53" s="70"/>
+      <c r="Q53" s="67"/>
+      <c r="S53" s="71"/>
+      <c r="T53" s="58"/>
+      <c r="U53" s="59"/>
+      <c r="V53" s="60"/>
     </row>
     <row r="54" customHeight="1" spans="2:22">
-      <c r="B54" s="70"/>
-      <c r="D54" s="71"/>
-      <c r="E54" s="72"/>
-      <c r="F54" s="73"/>
-      <c r="I54" s="71"/>
-      <c r="J54" s="74"/>
-      <c r="M54" s="71"/>
-      <c r="N54" s="74"/>
-      <c r="Q54" s="71"/>
-      <c r="S54" s="75"/>
-      <c r="T54" s="59"/>
-      <c r="U54" s="60"/>
-      <c r="V54" s="61"/>
+      <c r="B54" s="66"/>
+      <c r="D54" s="67"/>
+      <c r="E54" s="68"/>
+      <c r="F54" s="69"/>
+      <c r="I54" s="67"/>
+      <c r="J54" s="70"/>
+      <c r="M54" s="67"/>
+      <c r="N54" s="70"/>
+      <c r="Q54" s="67"/>
+      <c r="S54" s="71"/>
+      <c r="T54" s="58"/>
+      <c r="U54" s="59"/>
+      <c r="V54" s="60"/>
     </row>
     <row r="55" customHeight="1" spans="2:22">
-      <c r="B55" s="70"/>
-      <c r="D55" s="71"/>
-      <c r="E55" s="72"/>
-      <c r="F55" s="73"/>
-      <c r="I55" s="71"/>
-      <c r="J55" s="74"/>
-      <c r="M55" s="71"/>
-      <c r="N55" s="74"/>
-      <c r="Q55" s="71"/>
-      <c r="S55" s="75"/>
-      <c r="T55" s="59"/>
-      <c r="U55" s="60"/>
-      <c r="V55" s="61"/>
+      <c r="B55" s="66"/>
+      <c r="D55" s="67"/>
+      <c r="E55" s="68"/>
+      <c r="F55" s="69"/>
+      <c r="I55" s="67"/>
+      <c r="J55" s="70"/>
+      <c r="M55" s="67"/>
+      <c r="N55" s="70"/>
+      <c r="Q55" s="67"/>
+      <c r="S55" s="71"/>
+      <c r="T55" s="58"/>
+      <c r="U55" s="59"/>
+      <c r="V55" s="60"/>
     </row>
     <row r="56" customHeight="1" spans="2:22">
-      <c r="B56" s="70"/>
-      <c r="D56" s="71"/>
-      <c r="E56" s="72"/>
-      <c r="F56" s="73"/>
-      <c r="I56" s="71"/>
-      <c r="J56" s="74"/>
-      <c r="M56" s="71"/>
-      <c r="N56" s="74"/>
-      <c r="Q56" s="71"/>
-      <c r="S56" s="75"/>
-      <c r="T56" s="59"/>
-      <c r="U56" s="60"/>
-      <c r="V56" s="61"/>
+      <c r="B56" s="66"/>
+      <c r="D56" s="67"/>
+      <c r="E56" s="68"/>
+      <c r="F56" s="69"/>
+      <c r="I56" s="67"/>
+      <c r="J56" s="70"/>
+      <c r="M56" s="67"/>
+      <c r="N56" s="70"/>
+      <c r="Q56" s="67"/>
+      <c r="S56" s="71"/>
+      <c r="T56" s="58"/>
+      <c r="U56" s="59"/>
+      <c r="V56" s="60"/>
     </row>
     <row r="57" customHeight="1" spans="2:22">
-      <c r="B57" s="70"/>
-      <c r="D57" s="71"/>
-      <c r="E57" s="72"/>
-      <c r="F57" s="73"/>
-      <c r="I57" s="71"/>
-      <c r="J57" s="74"/>
-      <c r="M57" s="71"/>
-      <c r="N57" s="74"/>
-      <c r="Q57" s="71"/>
-      <c r="S57" s="75"/>
-      <c r="T57" s="59"/>
-      <c r="U57" s="60"/>
-      <c r="V57" s="61"/>
+      <c r="B57" s="66"/>
+      <c r="D57" s="67"/>
+      <c r="E57" s="68"/>
+      <c r="F57" s="69"/>
+      <c r="I57" s="67"/>
+      <c r="J57" s="70"/>
+      <c r="M57" s="67"/>
+      <c r="N57" s="70"/>
+      <c r="Q57" s="67"/>
+      <c r="S57" s="71"/>
+      <c r="T57" s="58"/>
+      <c r="U57" s="59"/>
+      <c r="V57" s="60"/>
     </row>
     <row r="58" customHeight="1" spans="2:22">
-      <c r="B58" s="70"/>
-      <c r="D58" s="71"/>
-      <c r="E58" s="72"/>
-      <c r="F58" s="73"/>
-      <c r="I58" s="71"/>
-      <c r="J58" s="74"/>
-      <c r="M58" s="71"/>
-      <c r="N58" s="74"/>
-      <c r="Q58" s="71"/>
-      <c r="S58" s="75"/>
-      <c r="T58" s="59"/>
-      <c r="U58" s="60"/>
-      <c r="V58" s="61"/>
+      <c r="B58" s="66"/>
+      <c r="D58" s="67"/>
+      <c r="E58" s="68"/>
+      <c r="F58" s="69"/>
+      <c r="I58" s="67"/>
+      <c r="J58" s="70"/>
+      <c r="M58" s="67"/>
+      <c r="N58" s="70"/>
+      <c r="Q58" s="67"/>
+      <c r="S58" s="71"/>
+      <c r="T58" s="58"/>
+      <c r="U58" s="59"/>
+      <c r="V58" s="60"/>
     </row>
     <row r="59" customHeight="1" spans="2:22">
-      <c r="B59" s="70"/>
-      <c r="D59" s="71"/>
-      <c r="E59" s="72"/>
-      <c r="F59" s="73"/>
-      <c r="I59" s="71"/>
-      <c r="J59" s="74"/>
-      <c r="M59" s="71"/>
-      <c r="N59" s="74"/>
-      <c r="Q59" s="71"/>
-      <c r="S59" s="75"/>
-      <c r="T59" s="59"/>
-      <c r="U59" s="60"/>
-      <c r="V59" s="61"/>
+      <c r="B59" s="66"/>
+      <c r="D59" s="67"/>
+      <c r="E59" s="68"/>
+      <c r="F59" s="69"/>
+      <c r="I59" s="67"/>
+      <c r="J59" s="70"/>
+      <c r="M59" s="67"/>
+      <c r="N59" s="70"/>
+      <c r="Q59" s="67"/>
+      <c r="S59" s="71"/>
+      <c r="T59" s="58"/>
+      <c r="U59" s="59"/>
+      <c r="V59" s="60"/>
     </row>
     <row r="60" customHeight="1" spans="2:22">
-      <c r="B60" s="70"/>
-      <c r="D60" s="71"/>
-      <c r="E60" s="72"/>
-      <c r="F60" s="73"/>
-      <c r="I60" s="71"/>
-      <c r="J60" s="74"/>
-      <c r="M60" s="71"/>
-      <c r="N60" s="74"/>
-      <c r="Q60" s="71"/>
-      <c r="S60" s="75"/>
-      <c r="T60" s="59"/>
-      <c r="U60" s="60"/>
-      <c r="V60" s="61"/>
+      <c r="B60" s="66"/>
+      <c r="D60" s="67"/>
+      <c r="E60" s="68"/>
+      <c r="F60" s="69"/>
+      <c r="I60" s="67"/>
+      <c r="J60" s="70"/>
+      <c r="M60" s="67"/>
+      <c r="N60" s="70"/>
+      <c r="Q60" s="67"/>
+      <c r="S60" s="71"/>
+      <c r="T60" s="58"/>
+      <c r="U60" s="59"/>
+      <c r="V60" s="60"/>
     </row>
     <row r="61" customHeight="1" spans="2:22">
-      <c r="B61" s="70"/>
-      <c r="D61" s="71"/>
-      <c r="E61" s="72"/>
-      <c r="F61" s="73"/>
-      <c r="I61" s="71"/>
-      <c r="J61" s="74"/>
-      <c r="M61" s="71"/>
-      <c r="N61" s="74"/>
-      <c r="Q61" s="71"/>
-      <c r="S61" s="75"/>
-      <c r="T61" s="59"/>
-      <c r="U61" s="60"/>
-      <c r="V61" s="61"/>
+      <c r="B61" s="66"/>
+      <c r="D61" s="67"/>
+      <c r="E61" s="68"/>
+      <c r="F61" s="69"/>
+      <c r="I61" s="67"/>
+      <c r="J61" s="70"/>
+      <c r="M61" s="67"/>
+      <c r="N61" s="70"/>
+      <c r="Q61" s="67"/>
+      <c r="S61" s="71"/>
+      <c r="T61" s="58"/>
+      <c r="U61" s="59"/>
+      <c r="V61" s="60"/>
     </row>
     <row r="62" customHeight="1" spans="2:22">
-      <c r="B62" s="70"/>
-      <c r="D62" s="71"/>
-      <c r="E62" s="72"/>
-      <c r="F62" s="73"/>
-      <c r="I62" s="71"/>
-      <c r="J62" s="74"/>
-      <c r="M62" s="71"/>
-      <c r="N62" s="74"/>
-      <c r="Q62" s="71"/>
-      <c r="S62" s="75"/>
-      <c r="T62" s="59"/>
-      <c r="U62" s="60"/>
-      <c r="V62" s="61"/>
+      <c r="B62" s="66"/>
+      <c r="D62" s="67"/>
+      <c r="E62" s="68"/>
+      <c r="F62" s="69"/>
+      <c r="I62" s="67"/>
+      <c r="J62" s="70"/>
+      <c r="M62" s="67"/>
+      <c r="N62" s="70"/>
+      <c r="Q62" s="67"/>
+      <c r="S62" s="71"/>
+      <c r="T62" s="58"/>
+      <c r="U62" s="59"/>
+      <c r="V62" s="60"/>
     </row>
     <row r="63" customHeight="1" spans="2:22">
-      <c r="B63" s="70"/>
-      <c r="D63" s="71"/>
-      <c r="E63" s="72"/>
-      <c r="F63" s="73"/>
-      <c r="I63" s="71"/>
-      <c r="J63" s="74"/>
-      <c r="M63" s="71"/>
-      <c r="N63" s="74"/>
-      <c r="Q63" s="71"/>
-      <c r="S63" s="75"/>
-      <c r="T63" s="59"/>
-      <c r="U63" s="60"/>
-      <c r="V63" s="61"/>
+      <c r="B63" s="66"/>
+      <c r="D63" s="67"/>
+      <c r="E63" s="68"/>
+      <c r="F63" s="69"/>
+      <c r="I63" s="67"/>
+      <c r="J63" s="70"/>
+      <c r="M63" s="67"/>
+      <c r="N63" s="70"/>
+      <c r="Q63" s="67"/>
+      <c r="S63" s="71"/>
+      <c r="T63" s="58"/>
+      <c r="U63" s="59"/>
+      <c r="V63" s="60"/>
     </row>
     <row r="64" customHeight="1" spans="2:22">
-      <c r="B64" s="70"/>
-      <c r="D64" s="71"/>
-      <c r="E64" s="72"/>
-      <c r="F64" s="73"/>
-      <c r="I64" s="71"/>
-      <c r="J64" s="74"/>
-      <c r="M64" s="71"/>
-      <c r="N64" s="74"/>
-      <c r="Q64" s="71"/>
-      <c r="S64" s="75"/>
-      <c r="T64" s="59"/>
-      <c r="U64" s="60"/>
-      <c r="V64" s="61"/>
+      <c r="B64" s="66"/>
+      <c r="D64" s="67"/>
+      <c r="E64" s="68"/>
+      <c r="F64" s="69"/>
+      <c r="I64" s="67"/>
+      <c r="J64" s="70"/>
+      <c r="M64" s="67"/>
+      <c r="N64" s="70"/>
+      <c r="Q64" s="67"/>
+      <c r="S64" s="71"/>
+      <c r="T64" s="58"/>
+      <c r="U64" s="59"/>
+      <c r="V64" s="60"/>
     </row>
     <row r="65" customHeight="1" spans="2:22">
-      <c r="B65" s="70"/>
-      <c r="D65" s="71"/>
-      <c r="E65" s="72"/>
-      <c r="F65" s="73"/>
-      <c r="I65" s="71"/>
-      <c r="J65" s="74"/>
-      <c r="M65" s="71"/>
-      <c r="N65" s="74"/>
-      <c r="Q65" s="71"/>
-      <c r="S65" s="75"/>
-      <c r="T65" s="59"/>
-      <c r="U65" s="60"/>
-      <c r="V65" s="61"/>
+      <c r="B65" s="66"/>
+      <c r="D65" s="67"/>
+      <c r="E65" s="68"/>
+      <c r="F65" s="69"/>
+      <c r="I65" s="67"/>
+      <c r="J65" s="70"/>
+      <c r="M65" s="67"/>
+      <c r="N65" s="70"/>
+      <c r="Q65" s="67"/>
+      <c r="S65" s="71"/>
+      <c r="T65" s="58"/>
+      <c r="U65" s="59"/>
+      <c r="V65" s="60"/>
     </row>
     <row r="66" customHeight="1" spans="2:22">
-      <c r="B66" s="70"/>
-      <c r="D66" s="71"/>
-      <c r="E66" s="72"/>
-      <c r="F66" s="73"/>
-      <c r="I66" s="71"/>
-      <c r="J66" s="74"/>
-      <c r="M66" s="71"/>
-      <c r="N66" s="74"/>
-      <c r="Q66" s="71"/>
-      <c r="S66" s="75"/>
-      <c r="T66" s="59"/>
-      <c r="U66" s="60"/>
-      <c r="V66" s="61"/>
+      <c r="B66" s="66"/>
+      <c r="D66" s="67"/>
+      <c r="E66" s="68"/>
+      <c r="F66" s="69"/>
+      <c r="I66" s="67"/>
+      <c r="J66" s="70"/>
+      <c r="M66" s="67"/>
+      <c r="N66" s="70"/>
+      <c r="Q66" s="67"/>
+      <c r="S66" s="71"/>
+      <c r="T66" s="58"/>
+      <c r="U66" s="59"/>
+      <c r="V66" s="60"/>
     </row>
     <row r="67" customHeight="1" spans="2:22">
-      <c r="B67" s="70"/>
-      <c r="D67" s="71"/>
-      <c r="E67" s="72"/>
-      <c r="F67" s="73"/>
-      <c r="I67" s="71"/>
-      <c r="J67" s="74"/>
-      <c r="M67" s="71"/>
-      <c r="N67" s="74"/>
-      <c r="Q67" s="71"/>
-      <c r="S67" s="75"/>
-      <c r="T67" s="59"/>
-      <c r="U67" s="60"/>
-      <c r="V67" s="61"/>
+      <c r="B67" s="66"/>
+      <c r="D67" s="67"/>
+      <c r="E67" s="68"/>
+      <c r="F67" s="69"/>
+      <c r="I67" s="67"/>
+      <c r="J67" s="70"/>
+      <c r="M67" s="67"/>
+      <c r="N67" s="70"/>
+      <c r="Q67" s="67"/>
+      <c r="S67" s="71"/>
+      <c r="T67" s="58"/>
+      <c r="U67" s="59"/>
+      <c r="V67" s="60"/>
     </row>
     <row r="68" customHeight="1" spans="2:22">
-      <c r="B68" s="70"/>
-      <c r="D68" s="71"/>
-      <c r="E68" s="72"/>
-      <c r="F68" s="73"/>
-      <c r="I68" s="71"/>
-      <c r="J68" s="74"/>
-      <c r="M68" s="71"/>
-      <c r="N68" s="74"/>
-      <c r="Q68" s="71"/>
-      <c r="S68" s="75"/>
-      <c r="T68" s="59"/>
-      <c r="U68" s="60"/>
-      <c r="V68" s="61"/>
+      <c r="B68" s="66"/>
+      <c r="D68" s="67"/>
+      <c r="E68" s="68"/>
+      <c r="F68" s="69"/>
+      <c r="I68" s="67"/>
+      <c r="J68" s="70"/>
+      <c r="M68" s="67"/>
+      <c r="N68" s="70"/>
+      <c r="Q68" s="67"/>
+      <c r="S68" s="71"/>
+      <c r="T68" s="58"/>
+      <c r="U68" s="59"/>
+      <c r="V68" s="60"/>
     </row>
     <row r="69" customHeight="1" spans="2:22">
-      <c r="B69" s="70"/>
-      <c r="D69" s="71"/>
-      <c r="E69" s="72"/>
-      <c r="F69" s="73"/>
-      <c r="I69" s="71"/>
-      <c r="J69" s="74"/>
-      <c r="M69" s="71"/>
-      <c r="N69" s="74"/>
-      <c r="Q69" s="71"/>
-      <c r="S69" s="75"/>
-      <c r="T69" s="59"/>
-      <c r="U69" s="60"/>
-      <c r="V69" s="61"/>
+      <c r="B69" s="66"/>
+      <c r="D69" s="67"/>
+      <c r="E69" s="68"/>
+      <c r="F69" s="69"/>
+      <c r="I69" s="67"/>
+      <c r="J69" s="70"/>
+      <c r="M69" s="67"/>
+      <c r="N69" s="70"/>
+      <c r="Q69" s="67"/>
+      <c r="S69" s="71"/>
+      <c r="T69" s="58"/>
+      <c r="U69" s="59"/>
+      <c r="V69" s="60"/>
     </row>
     <row r="70" customHeight="1" spans="2:22">
-      <c r="B70" s="70"/>
-      <c r="D70" s="71"/>
-      <c r="E70" s="72"/>
-      <c r="F70" s="73"/>
-      <c r="I70" s="71"/>
-      <c r="J70" s="74"/>
-      <c r="M70" s="71"/>
-      <c r="N70" s="74"/>
-      <c r="Q70" s="71"/>
-      <c r="S70" s="75"/>
-      <c r="T70" s="59"/>
-      <c r="U70" s="60"/>
-      <c r="V70" s="61"/>
+      <c r="B70" s="66"/>
+      <c r="D70" s="67"/>
+      <c r="E70" s="68"/>
+      <c r="F70" s="69"/>
+      <c r="I70" s="67"/>
+      <c r="J70" s="70"/>
+      <c r="M70" s="67"/>
+      <c r="N70" s="70"/>
+      <c r="Q70" s="67"/>
+      <c r="S70" s="71"/>
+      <c r="T70" s="58"/>
+      <c r="U70" s="59"/>
+      <c r="V70" s="60"/>
     </row>
     <row r="71" customHeight="1" spans="2:22">
-      <c r="B71" s="70"/>
-      <c r="D71" s="71"/>
-      <c r="E71" s="72"/>
-      <c r="F71" s="73"/>
-      <c r="I71" s="71"/>
-      <c r="J71" s="74"/>
-      <c r="M71" s="71"/>
-      <c r="N71" s="74"/>
-      <c r="Q71" s="71"/>
-      <c r="S71" s="75"/>
-      <c r="T71" s="59"/>
-      <c r="U71" s="60"/>
-      <c r="V71" s="61"/>
+      <c r="B71" s="66"/>
+      <c r="D71" s="67"/>
+      <c r="E71" s="68"/>
+      <c r="F71" s="69"/>
+      <c r="I71" s="67"/>
+      <c r="J71" s="70"/>
+      <c r="M71" s="67"/>
+      <c r="N71" s="70"/>
+      <c r="Q71" s="67"/>
+      <c r="S71" s="71"/>
+      <c r="T71" s="58"/>
+      <c r="U71" s="59"/>
+      <c r="V71" s="60"/>
     </row>
     <row r="72" customHeight="1" spans="2:22">
-      <c r="B72" s="70"/>
-      <c r="D72" s="71"/>
-      <c r="E72" s="72"/>
-      <c r="F72" s="73"/>
-      <c r="I72" s="71"/>
-      <c r="J72" s="74"/>
-      <c r="M72" s="71"/>
-      <c r="N72" s="74"/>
-      <c r="Q72" s="71"/>
-      <c r="S72" s="75"/>
-      <c r="T72" s="59"/>
-      <c r="U72" s="60"/>
-      <c r="V72" s="61"/>
+      <c r="B72" s="66"/>
+      <c r="D72" s="67"/>
+      <c r="E72" s="68"/>
+      <c r="F72" s="69"/>
+      <c r="I72" s="67"/>
+      <c r="J72" s="70"/>
+      <c r="M72" s="67"/>
+      <c r="N72" s="70"/>
+      <c r="Q72" s="67"/>
+      <c r="S72" s="71"/>
+      <c r="T72" s="58"/>
+      <c r="U72" s="59"/>
+      <c r="V72" s="60"/>
     </row>
     <row r="73" customHeight="1" spans="2:22">
-      <c r="B73" s="70"/>
-      <c r="D73" s="71"/>
-      <c r="E73" s="72"/>
-      <c r="F73" s="73"/>
-      <c r="I73" s="71"/>
-      <c r="J73" s="74"/>
-      <c r="M73" s="71"/>
-      <c r="N73" s="74"/>
-      <c r="Q73" s="71"/>
-      <c r="S73" s="75"/>
-      <c r="T73" s="59"/>
-      <c r="U73" s="60"/>
-      <c r="V73" s="61"/>
+      <c r="B73" s="66"/>
+      <c r="D73" s="67"/>
+      <c r="E73" s="68"/>
+      <c r="F73" s="69"/>
+      <c r="I73" s="67"/>
+      <c r="J73" s="70"/>
+      <c r="M73" s="67"/>
+      <c r="N73" s="70"/>
+      <c r="Q73" s="67"/>
+      <c r="S73" s="71"/>
+      <c r="T73" s="58"/>
+      <c r="U73" s="59"/>
+      <c r="V73" s="60"/>
     </row>
     <row r="74" customHeight="1" spans="2:22">
-      <c r="B74" s="70"/>
-      <c r="D74" s="71"/>
-      <c r="E74" s="72"/>
-      <c r="F74" s="73"/>
-      <c r="I74" s="71"/>
-      <c r="J74" s="74"/>
-      <c r="M74" s="71"/>
-      <c r="N74" s="74"/>
-      <c r="Q74" s="71"/>
-      <c r="S74" s="75"/>
-      <c r="T74" s="59"/>
-      <c r="U74" s="60"/>
-      <c r="V74" s="61"/>
+      <c r="B74" s="66"/>
+      <c r="D74" s="67"/>
+      <c r="E74" s="68"/>
+      <c r="F74" s="69"/>
+      <c r="I74" s="67"/>
+      <c r="J74" s="70"/>
+      <c r="M74" s="67"/>
+      <c r="N74" s="70"/>
+      <c r="Q74" s="67"/>
+      <c r="S74" s="71"/>
+      <c r="T74" s="58"/>
+      <c r="U74" s="59"/>
+      <c r="V74" s="60"/>
     </row>
     <row r="75" customHeight="1" spans="2:22">
-      <c r="B75" s="70"/>
-      <c r="D75" s="71"/>
-      <c r="E75" s="72"/>
-      <c r="F75" s="73"/>
-      <c r="I75" s="71"/>
-      <c r="J75" s="74"/>
-      <c r="M75" s="71"/>
-      <c r="N75" s="74"/>
-      <c r="Q75" s="71"/>
-      <c r="S75" s="75"/>
-      <c r="T75" s="59"/>
-      <c r="U75" s="60"/>
-      <c r="V75" s="61"/>
+      <c r="B75" s="66"/>
+      <c r="D75" s="67"/>
+      <c r="E75" s="68"/>
+      <c r="F75" s="69"/>
+      <c r="I75" s="67"/>
+      <c r="J75" s="70"/>
+      <c r="M75" s="67"/>
+      <c r="N75" s="70"/>
+      <c r="Q75" s="67"/>
+      <c r="S75" s="71"/>
+      <c r="T75" s="58"/>
+      <c r="U75" s="59"/>
+      <c r="V75" s="60"/>
     </row>
     <row r="76" customHeight="1" spans="2:22">
-      <c r="B76" s="70"/>
-      <c r="D76" s="71"/>
-      <c r="E76" s="72"/>
-      <c r="F76" s="73"/>
-      <c r="I76" s="71"/>
-      <c r="J76" s="74"/>
-      <c r="M76" s="71"/>
-      <c r="N76" s="74"/>
-      <c r="Q76" s="71"/>
-      <c r="S76" s="75"/>
-      <c r="T76" s="59"/>
-      <c r="U76" s="60"/>
-      <c r="V76" s="61"/>
+      <c r="B76" s="66"/>
+      <c r="D76" s="67"/>
+      <c r="E76" s="68"/>
+      <c r="F76" s="69"/>
+      <c r="I76" s="67"/>
+      <c r="J76" s="70"/>
+      <c r="M76" s="67"/>
+      <c r="N76" s="70"/>
+      <c r="Q76" s="67"/>
+      <c r="S76" s="71"/>
+      <c r="T76" s="58"/>
+      <c r="U76" s="59"/>
+      <c r="V76" s="60"/>
     </row>
     <row r="77" customHeight="1" spans="2:22">
-      <c r="B77" s="70"/>
-      <c r="D77" s="71"/>
-      <c r="E77" s="72"/>
-      <c r="F77" s="73"/>
-      <c r="I77" s="71"/>
-      <c r="J77" s="74"/>
-      <c r="M77" s="71"/>
-      <c r="N77" s="74"/>
-      <c r="Q77" s="71"/>
-      <c r="S77" s="75"/>
-      <c r="T77" s="59"/>
-      <c r="U77" s="60"/>
-      <c r="V77" s="61"/>
+      <c r="B77" s="66"/>
+      <c r="D77" s="67"/>
+      <c r="E77" s="68"/>
+      <c r="F77" s="69"/>
+      <c r="I77" s="67"/>
+      <c r="J77" s="70"/>
+      <c r="M77" s="67"/>
+      <c r="N77" s="70"/>
+      <c r="Q77" s="67"/>
+      <c r="S77" s="71"/>
+      <c r="T77" s="58"/>
+      <c r="U77" s="59"/>
+      <c r="V77" s="60"/>
     </row>
     <row r="78" customHeight="1" spans="2:22">
-      <c r="B78" s="70"/>
-      <c r="D78" s="71"/>
-      <c r="E78" s="72"/>
-      <c r="F78" s="73"/>
-      <c r="I78" s="71"/>
-      <c r="J78" s="74"/>
-      <c r="M78" s="71"/>
-      <c r="N78" s="74"/>
-      <c r="Q78" s="71"/>
-      <c r="S78" s="75"/>
-      <c r="T78" s="59"/>
-      <c r="U78" s="60"/>
-      <c r="V78" s="61"/>
+      <c r="B78" s="66"/>
+      <c r="D78" s="67"/>
+      <c r="E78" s="68"/>
+      <c r="F78" s="69"/>
+      <c r="I78" s="67"/>
+      <c r="J78" s="70"/>
+      <c r="M78" s="67"/>
+      <c r="N78" s="70"/>
+      <c r="Q78" s="67"/>
+      <c r="S78" s="71"/>
+      <c r="T78" s="58"/>
+      <c r="U78" s="59"/>
+      <c r="V78" s="60"/>
     </row>
     <row r="79" customHeight="1" spans="2:22">
-      <c r="B79" s="70"/>
-      <c r="D79" s="71"/>
-      <c r="E79" s="72"/>
-      <c r="F79" s="73"/>
-      <c r="I79" s="71"/>
-      <c r="J79" s="74"/>
-      <c r="M79" s="71"/>
-      <c r="N79" s="74"/>
-      <c r="Q79" s="71"/>
-      <c r="S79" s="75"/>
-      <c r="T79" s="59"/>
-      <c r="U79" s="60"/>
-      <c r="V79" s="61"/>
+      <c r="B79" s="66"/>
+      <c r="D79" s="67"/>
+      <c r="E79" s="68"/>
+      <c r="F79" s="69"/>
+      <c r="I79" s="67"/>
+      <c r="J79" s="70"/>
+      <c r="M79" s="67"/>
+      <c r="N79" s="70"/>
+      <c r="Q79" s="67"/>
+      <c r="S79" s="71"/>
+      <c r="T79" s="58"/>
+      <c r="U79" s="59"/>
+      <c r="V79" s="60"/>
     </row>
     <row r="80" customHeight="1" spans="2:22">
-      <c r="B80" s="70"/>
-      <c r="D80" s="71"/>
-      <c r="E80" s="72"/>
-      <c r="F80" s="73"/>
-      <c r="I80" s="71"/>
-      <c r="J80" s="74"/>
-      <c r="M80" s="71"/>
-      <c r="N80" s="74"/>
-      <c r="Q80" s="71"/>
-      <c r="S80" s="75"/>
-      <c r="T80" s="59"/>
-      <c r="U80" s="60"/>
-      <c r="V80" s="61"/>
+      <c r="B80" s="66"/>
+      <c r="D80" s="67"/>
+      <c r="E80" s="68"/>
+      <c r="F80" s="69"/>
+      <c r="I80" s="67"/>
+      <c r="J80" s="70"/>
+      <c r="M80" s="67"/>
+      <c r="N80" s="70"/>
+      <c r="Q80" s="67"/>
+      <c r="S80" s="71"/>
+      <c r="T80" s="58"/>
+      <c r="U80" s="59"/>
+      <c r="V80" s="60"/>
     </row>
     <row r="81" customHeight="1" spans="2:22">
-      <c r="B81" s="70"/>
-      <c r="D81" s="71"/>
-      <c r="E81" s="72"/>
-      <c r="F81" s="73"/>
-      <c r="I81" s="71"/>
-      <c r="J81" s="74"/>
-      <c r="M81" s="71"/>
-      <c r="N81" s="74"/>
-      <c r="Q81" s="71"/>
-      <c r="S81" s="75"/>
-      <c r="T81" s="59"/>
-      <c r="U81" s="60"/>
-      <c r="V81" s="61"/>
+      <c r="B81" s="66"/>
+      <c r="D81" s="67"/>
+      <c r="E81" s="68"/>
+      <c r="F81" s="69"/>
+      <c r="I81" s="67"/>
+      <c r="J81" s="70"/>
+      <c r="M81" s="67"/>
+      <c r="N81" s="70"/>
+      <c r="Q81" s="67"/>
+      <c r="S81" s="71"/>
+      <c r="T81" s="58"/>
+      <c r="U81" s="59"/>
+      <c r="V81" s="60"/>
     </row>
     <row r="82" customHeight="1" spans="2:22">
-      <c r="B82" s="70"/>
-      <c r="D82" s="71"/>
-      <c r="E82" s="72"/>
-      <c r="F82" s="73"/>
-      <c r="I82" s="71"/>
-      <c r="J82" s="74"/>
-      <c r="M82" s="71"/>
-      <c r="N82" s="74"/>
-      <c r="Q82" s="71"/>
-      <c r="S82" s="75"/>
-      <c r="T82" s="59"/>
-      <c r="U82" s="60"/>
-      <c r="V82" s="61"/>
+      <c r="B82" s="66"/>
+      <c r="D82" s="67"/>
+      <c r="E82" s="68"/>
+      <c r="F82" s="69"/>
+      <c r="I82" s="67"/>
+      <c r="J82" s="70"/>
+      <c r="M82" s="67"/>
+      <c r="N82" s="70"/>
+      <c r="Q82" s="67"/>
+      <c r="S82" s="71"/>
+      <c r="T82" s="58"/>
+      <c r="U82" s="59"/>
+      <c r="V82" s="60"/>
     </row>
     <row r="83" customHeight="1" spans="2:22">
-      <c r="B83" s="70"/>
-      <c r="D83" s="71"/>
-      <c r="E83" s="72"/>
-      <c r="F83" s="73"/>
-      <c r="I83" s="71"/>
-      <c r="J83" s="74"/>
-      <c r="M83" s="71"/>
-      <c r="N83" s="74"/>
-      <c r="Q83" s="71"/>
-      <c r="S83" s="75"/>
-      <c r="T83" s="59"/>
-      <c r="U83" s="60"/>
-      <c r="V83" s="61"/>
+      <c r="B83" s="66"/>
+      <c r="D83" s="67"/>
+      <c r="E83" s="68"/>
+      <c r="F83" s="69"/>
+      <c r="I83" s="67"/>
+      <c r="J83" s="70"/>
+      <c r="M83" s="67"/>
+      <c r="N83" s="70"/>
+      <c r="Q83" s="67"/>
+      <c r="S83" s="71"/>
+      <c r="T83" s="58"/>
+      <c r="U83" s="59"/>
+      <c r="V83" s="60"/>
     </row>
     <row r="84" customHeight="1" spans="2:22">
-      <c r="B84" s="70"/>
-      <c r="D84" s="71"/>
-      <c r="E84" s="72"/>
-      <c r="F84" s="73"/>
-      <c r="I84" s="71"/>
-      <c r="J84" s="74"/>
-      <c r="M84" s="71"/>
-      <c r="N84" s="74"/>
-      <c r="Q84" s="71"/>
-      <c r="S84" s="75"/>
-      <c r="T84" s="59"/>
-      <c r="U84" s="60"/>
-      <c r="V84" s="61"/>
+      <c r="B84" s="66"/>
+      <c r="D84" s="67"/>
+      <c r="E84" s="68"/>
+      <c r="F84" s="69"/>
+      <c r="I84" s="67"/>
+      <c r="J84" s="70"/>
+      <c r="M84" s="67"/>
+      <c r="N84" s="70"/>
+      <c r="Q84" s="67"/>
+      <c r="S84" s="71"/>
+      <c r="T84" s="58"/>
+      <c r="U84" s="59"/>
+      <c r="V84" s="60"/>
     </row>
     <row r="85" customHeight="1" spans="2:22">
-      <c r="B85" s="70"/>
-      <c r="D85" s="71"/>
-      <c r="E85" s="72"/>
-      <c r="F85" s="73"/>
-      <c r="I85" s="71"/>
-      <c r="J85" s="74"/>
-      <c r="M85" s="71"/>
-      <c r="N85" s="74"/>
-      <c r="Q85" s="71"/>
-      <c r="S85" s="75"/>
-      <c r="T85" s="59"/>
-      <c r="U85" s="60"/>
-      <c r="V85" s="61"/>
+      <c r="B85" s="66"/>
+      <c r="D85" s="67"/>
+      <c r="E85" s="68"/>
+      <c r="F85" s="69"/>
+      <c r="I85" s="67"/>
+      <c r="J85" s="70"/>
+      <c r="M85" s="67"/>
+      <c r="N85" s="70"/>
+      <c r="Q85" s="67"/>
+      <c r="S85" s="71"/>
+      <c r="T85" s="58"/>
+      <c r="U85" s="59"/>
+      <c r="V85" s="60"/>
     </row>
     <row r="86" customHeight="1" spans="2:22">
-      <c r="B86" s="70"/>
-      <c r="D86" s="71"/>
-      <c r="E86" s="72"/>
-      <c r="F86" s="73"/>
-      <c r="I86" s="71"/>
-      <c r="J86" s="74"/>
-      <c r="M86" s="71"/>
-      <c r="N86" s="74"/>
-      <c r="Q86" s="71"/>
-      <c r="S86" s="75"/>
-      <c r="T86" s="59"/>
-      <c r="U86" s="60"/>
-      <c r="V86" s="61"/>
+      <c r="B86" s="66"/>
+      <c r="D86" s="67"/>
+      <c r="E86" s="68"/>
+      <c r="F86" s="69"/>
+      <c r="I86" s="67"/>
+      <c r="J86" s="70"/>
+      <c r="M86" s="67"/>
+      <c r="N86" s="70"/>
+      <c r="Q86" s="67"/>
+      <c r="S86" s="71"/>
+      <c r="T86" s="58"/>
+      <c r="U86" s="59"/>
+      <c r="V86" s="60"/>
     </row>
     <row r="87" customHeight="1" spans="2:22">
-      <c r="B87" s="70"/>
-      <c r="D87" s="71"/>
-      <c r="E87" s="72"/>
-      <c r="F87" s="73"/>
-      <c r="I87" s="71"/>
-      <c r="J87" s="74"/>
-      <c r="M87" s="71"/>
-      <c r="N87" s="74"/>
-      <c r="Q87" s="71"/>
-      <c r="S87" s="75"/>
-      <c r="T87" s="59"/>
-      <c r="U87" s="60"/>
-      <c r="V87" s="61"/>
+      <c r="B87" s="66"/>
+      <c r="D87" s="67"/>
+      <c r="E87" s="68"/>
+      <c r="F87" s="69"/>
+      <c r="I87" s="67"/>
+      <c r="J87" s="70"/>
+      <c r="M87" s="67"/>
+      <c r="N87" s="70"/>
+      <c r="Q87" s="67"/>
+      <c r="S87" s="71"/>
+      <c r="T87" s="58"/>
+      <c r="U87" s="59"/>
+      <c r="V87" s="60"/>
     </row>
     <row r="88" customHeight="1" spans="2:22">
-      <c r="B88" s="70"/>
-      <c r="D88" s="71"/>
-      <c r="E88" s="72"/>
-      <c r="F88" s="73"/>
-      <c r="I88" s="71"/>
-      <c r="J88" s="74"/>
-      <c r="M88" s="71"/>
-      <c r="N88" s="74"/>
-      <c r="Q88" s="71"/>
-      <c r="S88" s="75"/>
-      <c r="T88" s="59"/>
-      <c r="U88" s="60"/>
-      <c r="V88" s="61"/>
+      <c r="B88" s="66"/>
+      <c r="D88" s="67"/>
+      <c r="E88" s="68"/>
+      <c r="F88" s="69"/>
+      <c r="I88" s="67"/>
+      <c r="J88" s="70"/>
+      <c r="M88" s="67"/>
+      <c r="N88" s="70"/>
+      <c r="Q88" s="67"/>
+      <c r="S88" s="71"/>
+      <c r="T88" s="58"/>
+      <c r="U88" s="59"/>
+      <c r="V88" s="60"/>
     </row>
     <row r="89" customHeight="1" spans="2:22">
-      <c r="B89" s="70"/>
-      <c r="D89" s="71"/>
-      <c r="E89" s="72"/>
-      <c r="F89" s="73"/>
-      <c r="I89" s="71"/>
-      <c r="J89" s="74"/>
-      <c r="M89" s="71"/>
-      <c r="N89" s="74"/>
-      <c r="Q89" s="71"/>
-      <c r="S89" s="75"/>
-      <c r="T89" s="59"/>
-      <c r="U89" s="60"/>
-      <c r="V89" s="61"/>
+      <c r="B89" s="66"/>
+      <c r="D89" s="67"/>
+      <c r="E89" s="68"/>
+      <c r="F89" s="69"/>
+      <c r="I89" s="67"/>
+      <c r="J89" s="70"/>
+      <c r="M89" s="67"/>
+      <c r="N89" s="70"/>
+      <c r="Q89" s="67"/>
+      <c r="S89" s="71"/>
+      <c r="T89" s="58"/>
+      <c r="U89" s="59"/>
+      <c r="V89" s="60"/>
     </row>
     <row r="90" customHeight="1" spans="2:22">
-      <c r="B90" s="70"/>
-      <c r="D90" s="71"/>
-      <c r="E90" s="72"/>
-      <c r="F90" s="73"/>
-      <c r="I90" s="71"/>
-      <c r="J90" s="74"/>
-      <c r="M90" s="71"/>
-      <c r="N90" s="74"/>
-      <c r="Q90" s="71"/>
-      <c r="S90" s="75"/>
-      <c r="T90" s="59"/>
-      <c r="U90" s="60"/>
-      <c r="V90" s="61"/>
+      <c r="B90" s="66"/>
+      <c r="D90" s="67"/>
+      <c r="E90" s="68"/>
+      <c r="F90" s="69"/>
+      <c r="I90" s="67"/>
+      <c r="J90" s="70"/>
+      <c r="M90" s="67"/>
+      <c r="N90" s="70"/>
+      <c r="Q90" s="67"/>
+      <c r="S90" s="71"/>
+      <c r="T90" s="58"/>
+      <c r="U90" s="59"/>
+      <c r="V90" s="60"/>
     </row>
     <row r="91" customHeight="1" spans="2:22">
-      <c r="B91" s="70"/>
-      <c r="D91" s="71"/>
-      <c r="E91" s="72"/>
-      <c r="F91" s="73"/>
-      <c r="I91" s="71"/>
-      <c r="J91" s="74"/>
-      <c r="M91" s="71"/>
-      <c r="N91" s="74"/>
-      <c r="Q91" s="71"/>
-      <c r="S91" s="75"/>
-      <c r="T91" s="59"/>
-      <c r="U91" s="60"/>
-      <c r="V91" s="61"/>
+      <c r="B91" s="66"/>
+      <c r="D91" s="67"/>
+      <c r="E91" s="68"/>
+      <c r="F91" s="69"/>
+      <c r="I91" s="67"/>
+      <c r="J91" s="70"/>
+      <c r="M91" s="67"/>
+      <c r="N91" s="70"/>
+      <c r="Q91" s="67"/>
+      <c r="S91" s="71"/>
+      <c r="T91" s="58"/>
+      <c r="U91" s="59"/>
+      <c r="V91" s="60"/>
     </row>
     <row r="92" customHeight="1" spans="2:22">
-      <c r="B92" s="70"/>
-      <c r="D92" s="71"/>
-      <c r="E92" s="72"/>
-      <c r="F92" s="73"/>
-      <c r="I92" s="71"/>
-      <c r="J92" s="74"/>
-      <c r="M92" s="71"/>
-      <c r="N92" s="74"/>
-      <c r="Q92" s="71"/>
-      <c r="S92" s="75"/>
-      <c r="T92" s="59"/>
-      <c r="U92" s="60"/>
-      <c r="V92" s="61"/>
+      <c r="B92" s="66"/>
+      <c r="D92" s="67"/>
+      <c r="E92" s="68"/>
+      <c r="F92" s="69"/>
+      <c r="I92" s="67"/>
+      <c r="J92" s="70"/>
+      <c r="M92" s="67"/>
+      <c r="N92" s="70"/>
+      <c r="Q92" s="67"/>
+      <c r="S92" s="71"/>
+      <c r="T92" s="58"/>
+      <c r="U92" s="59"/>
+      <c r="V92" s="60"/>
     </row>
     <row r="93" customHeight="1" spans="2:22">
-      <c r="B93" s="70"/>
-      <c r="D93" s="71"/>
-      <c r="E93" s="72"/>
-      <c r="F93" s="73"/>
-      <c r="I93" s="71"/>
-      <c r="J93" s="74"/>
-      <c r="M93" s="71"/>
-      <c r="N93" s="74"/>
-      <c r="Q93" s="71"/>
-      <c r="S93" s="75"/>
-      <c r="T93" s="59"/>
-      <c r="U93" s="60"/>
-      <c r="V93" s="61"/>
+      <c r="B93" s="66"/>
+      <c r="D93" s="67"/>
+      <c r="E93" s="68"/>
+      <c r="F93" s="69"/>
+      <c r="I93" s="67"/>
+      <c r="J93" s="70"/>
+      <c r="M93" s="67"/>
+      <c r="N93" s="70"/>
+      <c r="Q93" s="67"/>
+      <c r="S93" s="71"/>
+      <c r="T93" s="58"/>
+      <c r="U93" s="59"/>
+      <c r="V93" s="60"/>
     </row>
     <row r="94" customHeight="1" spans="2:22">
-      <c r="B94" s="70"/>
-      <c r="D94" s="71"/>
-      <c r="E94" s="72"/>
-      <c r="F94" s="73"/>
-      <c r="I94" s="71"/>
-      <c r="J94" s="74"/>
-      <c r="M94" s="71"/>
-      <c r="N94" s="74"/>
-      <c r="Q94" s="71"/>
-      <c r="S94" s="75"/>
-      <c r="T94" s="59"/>
-      <c r="U94" s="60"/>
-      <c r="V94" s="61"/>
+      <c r="B94" s="66"/>
+      <c r="D94" s="67"/>
+      <c r="E94" s="68"/>
+      <c r="F94" s="69"/>
+      <c r="I94" s="67"/>
+      <c r="J94" s="70"/>
+      <c r="M94" s="67"/>
+      <c r="N94" s="70"/>
+      <c r="Q94" s="67"/>
+      <c r="S94" s="71"/>
+      <c r="T94" s="58"/>
+      <c r="U94" s="59"/>
+      <c r="V94" s="60"/>
     </row>
     <row r="95" customHeight="1" spans="2:22">
-      <c r="B95" s="70"/>
-      <c r="D95" s="71"/>
-      <c r="E95" s="72"/>
-      <c r="F95" s="73"/>
-      <c r="I95" s="71"/>
-      <c r="J95" s="74"/>
-      <c r="M95" s="71"/>
-      <c r="N95" s="74"/>
-      <c r="Q95" s="71"/>
-      <c r="S95" s="75"/>
-      <c r="T95" s="59"/>
-      <c r="U95" s="60"/>
-      <c r="V95" s="61"/>
+      <c r="B95" s="66"/>
+      <c r="D95" s="67"/>
+      <c r="E95" s="68"/>
+      <c r="F95" s="69"/>
+      <c r="I95" s="67"/>
+      <c r="J95" s="70"/>
+      <c r="M95" s="67"/>
+      <c r="N95" s="70"/>
+      <c r="Q95" s="67"/>
+      <c r="S95" s="71"/>
+      <c r="T95" s="58"/>
+      <c r="U95" s="59"/>
+      <c r="V95" s="60"/>
     </row>
     <row r="96" customHeight="1" spans="2:22">
-      <c r="B96" s="70"/>
-      <c r="D96" s="71"/>
-      <c r="E96" s="72"/>
-      <c r="F96" s="73"/>
-      <c r="I96" s="71"/>
-      <c r="J96" s="74"/>
-      <c r="M96" s="71"/>
-      <c r="N96" s="74"/>
-      <c r="Q96" s="71"/>
-      <c r="S96" s="75"/>
-      <c r="T96" s="59"/>
-      <c r="U96" s="60"/>
-      <c r="V96" s="61"/>
+      <c r="B96" s="66"/>
+      <c r="D96" s="67"/>
+      <c r="E96" s="68"/>
+      <c r="F96" s="69"/>
+      <c r="I96" s="67"/>
+      <c r="J96" s="70"/>
+      <c r="M96" s="67"/>
+      <c r="N96" s="70"/>
+      <c r="Q96" s="67"/>
+      <c r="S96" s="71"/>
+      <c r="T96" s="58"/>
+      <c r="U96" s="59"/>
+      <c r="V96" s="60"/>
     </row>
     <row r="97" customHeight="1" spans="2:22">
-      <c r="B97" s="70"/>
-      <c r="D97" s="71"/>
-      <c r="E97" s="72"/>
-      <c r="F97" s="73"/>
-      <c r="I97" s="71"/>
-      <c r="J97" s="74"/>
-      <c r="M97" s="71"/>
-      <c r="N97" s="74"/>
-      <c r="Q97" s="71"/>
-      <c r="S97" s="75"/>
-      <c r="T97" s="59"/>
-      <c r="U97" s="60"/>
-      <c r="V97" s="61"/>
+      <c r="B97" s="66"/>
+      <c r="D97" s="67"/>
+      <c r="E97" s="68"/>
+      <c r="F97" s="69"/>
+      <c r="I97" s="67"/>
+      <c r="J97" s="70"/>
+      <c r="M97" s="67"/>
+      <c r="N97" s="70"/>
+      <c r="Q97" s="67"/>
+      <c r="S97" s="71"/>
+      <c r="T97" s="58"/>
+      <c r="U97" s="59"/>
+      <c r="V97" s="60"/>
     </row>
     <row r="98" customHeight="1" spans="2:22">
-      <c r="B98" s="70"/>
-      <c r="D98" s="71"/>
-      <c r="E98" s="72"/>
-      <c r="F98" s="73"/>
-      <c r="I98" s="71"/>
-      <c r="J98" s="74"/>
-      <c r="M98" s="71"/>
-      <c r="N98" s="74"/>
-      <c r="Q98" s="71"/>
-      <c r="S98" s="75"/>
-      <c r="T98" s="59"/>
-      <c r="U98" s="60"/>
-      <c r="V98" s="61"/>
+      <c r="B98" s="66"/>
+      <c r="D98" s="67"/>
+      <c r="E98" s="68"/>
+      <c r="F98" s="69"/>
+      <c r="I98" s="67"/>
+      <c r="J98" s="70"/>
+      <c r="M98" s="67"/>
+      <c r="N98" s="70"/>
+      <c r="Q98" s="67"/>
+      <c r="S98" s="71"/>
+      <c r="T98" s="58"/>
+      <c r="U98" s="59"/>
+      <c r="V98" s="60"/>
     </row>
     <row r="99" customHeight="1" spans="2:22">
-      <c r="B99" s="70"/>
-      <c r="D99" s="71"/>
-      <c r="E99" s="72"/>
-      <c r="F99" s="73"/>
-      <c r="I99" s="71"/>
-      <c r="J99" s="74"/>
-      <c r="M99" s="71"/>
-      <c r="N99" s="74"/>
-      <c r="Q99" s="71"/>
-      <c r="S99" s="75"/>
-      <c r="T99" s="59"/>
-      <c r="U99" s="60"/>
-      <c r="V99" s="61"/>
+      <c r="B99" s="66"/>
+      <c r="D99" s="67"/>
+      <c r="E99" s="68"/>
+      <c r="F99" s="69"/>
+      <c r="I99" s="67"/>
+      <c r="J99" s="70"/>
+      <c r="M99" s="67"/>
+      <c r="N99" s="70"/>
+      <c r="Q99" s="67"/>
+      <c r="S99" s="71"/>
+      <c r="T99" s="58"/>
+      <c r="U99" s="59"/>
+      <c r="V99" s="60"/>
     </row>
     <row r="100" customHeight="1" spans="2:22">
-      <c r="B100" s="76"/>
-      <c r="C100" s="77"/>
-      <c r="D100" s="78"/>
-      <c r="E100" s="79"/>
-      <c r="F100" s="80"/>
-      <c r="G100" s="77"/>
-      <c r="H100" s="77"/>
-      <c r="I100" s="78"/>
-      <c r="J100" s="81"/>
-      <c r="K100" s="77"/>
-      <c r="L100" s="77"/>
-      <c r="M100" s="78"/>
-      <c r="N100" s="81"/>
-      <c r="O100" s="77"/>
-      <c r="P100" s="77"/>
-      <c r="Q100" s="78"/>
-      <c r="R100" s="77"/>
-      <c r="S100" s="82"/>
-      <c r="T100" s="83"/>
-      <c r="U100" s="82"/>
-      <c r="V100" s="84"/>
+      <c r="B100" s="72"/>
+      <c r="C100" s="73"/>
+      <c r="D100" s="74"/>
+      <c r="E100" s="73"/>
+      <c r="F100" s="75"/>
+      <c r="G100" s="73"/>
+      <c r="H100" s="73"/>
+      <c r="I100" s="74"/>
+      <c r="J100" s="76"/>
+      <c r="K100" s="73"/>
+      <c r="L100" s="73"/>
+      <c r="M100" s="74"/>
+      <c r="N100" s="76"/>
+      <c r="O100" s="73"/>
+      <c r="P100" s="73"/>
+      <c r="Q100" s="74"/>
+      <c r="R100" s="73"/>
+      <c r="S100" s="77"/>
+      <c r="T100" s="78"/>
+      <c r="U100" s="77"/>
+      <c r="V100" s="79"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -5757,7 +5709,7 @@
     <mergeCell ref="T3:V3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R5:R34 R35:R42">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R5:R42">
       <formula1>"陆军上将,陆军元帅,海军上将"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5792,52 +5744,52 @@
         <v>4</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="I2" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="K2" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="M2" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="O2" s="3" t="s">
         <v>230</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="3" spans="2:15">
       <c r="B3" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C3" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>232</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>233</v>
       </c>
       <c r="F3" s="8"/>
       <c r="G3" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H3" s="8"/>
       <c r="I3" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J3" s="8"/>
       <c r="K3" s="7" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="L3" s="8"/>
       <c r="M3" s="9" t="s">
-        <v>74</v>
+        <v>236</v>
       </c>
       <c r="N3" s="8"/>
       <c r="O3" s="7" t="s">
@@ -5846,13 +5798,13 @@
     </row>
     <row r="4" spans="2:15">
       <c r="B4" s="10" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>238</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F4" s="8"/>
       <c r="G4" s="7" t="s">
@@ -5868,96 +5820,96 @@
       </c>
       <c r="L4" s="8"/>
       <c r="M4" s="12" t="s">
-        <v>242</v>
+        <v>72</v>
       </c>
       <c r="N4" s="8"/>
       <c r="O4" s="7" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="5" spans="2:15">
       <c r="B5" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="C5" s="14" t="s">
         <v>244</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="E5" s="7" t="s">
         <v>245</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>246</v>
       </c>
       <c r="F5" s="8"/>
       <c r="G5" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H5" s="8"/>
       <c r="I5" s="7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="J5" s="8"/>
       <c r="K5" s="7" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="L5" s="8"/>
       <c r="M5" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="N5" s="8"/>
       <c r="O5" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="6" spans="2:15">
       <c r="B6" s="15" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E6" s="17" t="s">
         <v>32</v>
       </c>
       <c r="F6" s="8"/>
       <c r="G6" s="17" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H6" s="8"/>
       <c r="I6" s="17" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J6" s="8"/>
       <c r="K6" s="17" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="L6" s="8"/>
       <c r="M6" s="18" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="N6" s="8"/>
       <c r="O6" s="17" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="7" spans="2:15">
       <c r="B7" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="E7" s="17" t="s">
         <v>124</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>258</v>
-      </c>
-      <c r="E7" s="17" t="s">
-        <v>126</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="17" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H7" s="8"/>
       <c r="I7" s="17" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J7" s="8"/>
       <c r="K7" s="17" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="L7" s="8"/>
       <c r="M7" s="18" t="s">
@@ -5965,127 +5917,127 @@
       </c>
       <c r="N7" s="8"/>
       <c r="O7" s="17" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="8" spans="2:15">
       <c r="B8" s="15" t="s">
+        <v>261</v>
+      </c>
+      <c r="C8" s="16" t="s">
         <v>262</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="E8" s="17" t="s">
         <v>263</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>264</v>
       </c>
       <c r="F8" s="8"/>
       <c r="G8" s="17" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H8" s="8"/>
       <c r="I8" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="J8" s="8"/>
       <c r="K8" s="17" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="L8" s="8"/>
       <c r="M8" s="18" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="N8" s="8"/>
       <c r="O8" s="17" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="9" spans="2:15">
       <c r="B9" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="C9" s="14" t="s">
         <v>268</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="E9" s="7" t="s">
         <v>269</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>270</v>
       </c>
       <c r="F9" s="8"/>
       <c r="G9" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H9" s="8"/>
       <c r="I9" s="7" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J9" s="8"/>
       <c r="K9" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="L9" s="8"/>
       <c r="M9" s="12" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="N9" s="8"/>
       <c r="O9" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="2:15">
       <c r="B10" s="15" t="s">
+        <v>275</v>
+      </c>
+      <c r="C10" s="16" t="s">
         <v>276</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="E10" s="7" t="s">
         <v>277</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>278</v>
       </c>
       <c r="F10" s="8"/>
       <c r="G10" s="7" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H10" s="8"/>
       <c r="I10" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="J10" s="8"/>
       <c r="K10" s="7" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="L10" s="8"/>
       <c r="M10" s="12" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="N10" s="8"/>
       <c r="O10" s="7" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="11" spans="2:15">
       <c r="B11" s="13" t="s">
+        <v>282</v>
+      </c>
+      <c r="C11" s="14" t="s">
         <v>283</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="E11" s="7" t="s">
         <v>284</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>285</v>
       </c>
       <c r="F11" s="8"/>
       <c r="G11" s="7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H11" s="8"/>
       <c r="I11" s="7" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="J11" s="8"/>
       <c r="K11" s="7" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L11" s="8"/>
       <c r="M11" s="12" t="s">
-        <v>53</v>
+        <v>288</v>
       </c>
       <c r="N11" s="8"/>
       <c r="O11" s="7" t="s">
@@ -6108,7 +6060,7 @@
       </c>
       <c r="H12" s="8"/>
       <c r="I12" s="17" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="J12" s="8"/>
       <c r="K12" s="17" t="s">
@@ -6135,7 +6087,7 @@
       </c>
       <c r="F13" s="8"/>
       <c r="G13" s="17" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H13" s="8"/>
       <c r="I13" s="17" t="s">
@@ -6143,7 +6095,7 @@
       </c>
       <c r="J13" s="8"/>
       <c r="K13" s="17" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="L13" s="8"/>
       <c r="M13" s="18" t="s">
@@ -6151,12 +6103,12 @@
       </c>
       <c r="N13" s="8"/>
       <c r="O13" s="17" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14" spans="2:15">
       <c r="B14" s="15" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C14" s="16" t="s">
         <v>300</v>
@@ -6170,7 +6122,7 @@
       </c>
       <c r="H14" s="8"/>
       <c r="I14" s="17" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="J14" s="8"/>
       <c r="K14" s="17" t="s">
@@ -6187,7 +6139,7 @@
     </row>
     <row r="15" spans="2:15">
       <c r="B15" s="13" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C15" s="14" t="s">
         <v>306</v>
@@ -6197,7 +6149,7 @@
       </c>
       <c r="F15" s="8"/>
       <c r="G15" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H15" s="8"/>
       <c r="I15" s="7" t="s">
@@ -6213,7 +6165,7 @@
       </c>
       <c r="N15" s="8"/>
       <c r="O15" s="7" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="16" spans="2:15">
@@ -6236,11 +6188,11 @@
       </c>
       <c r="J16" s="8"/>
       <c r="K16" s="7" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="L16" s="8"/>
       <c r="M16" s="12" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="N16" s="8"/>
       <c r="O16" s="7" t="s">
@@ -6356,7 +6308,7 @@
       <c r="I20" s="8"/>
       <c r="J20" s="8"/>
       <c r="K20" s="17" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="L20" s="8"/>
       <c r="M20" s="12" t="s">
@@ -6404,7 +6356,7 @@
         <v>339</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F22" s="8"/>
       <c r="G22" s="7" t="s">
@@ -6414,18 +6366,18 @@
       <c r="I22" s="8"/>
       <c r="J22" s="8"/>
       <c r="K22" s="7" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="L22" s="8"/>
       <c r="M22" s="8"/>
       <c r="N22" s="8"/>
       <c r="O22" s="7" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="23" spans="2:15">
       <c r="E23" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F23" s="8"/>
       <c r="G23" s="7" t="s">
@@ -6471,7 +6423,7 @@
       </c>
       <c r="F25" s="8"/>
       <c r="G25" s="17" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H25" s="8"/>
       <c r="I25" s="8"/>
@@ -6504,7 +6456,7 @@
       <c r="M26" s="8"/>
       <c r="N26" s="8"/>
       <c r="O26" s="21" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="27" spans="2:15">
@@ -6551,7 +6503,7 @@
       </c>
       <c r="F29" s="8"/>
       <c r="G29" s="7" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H29" s="8"/>
       <c r="I29" s="8"/>
@@ -6585,7 +6537,7 @@
       <c r="E31" s="8"/>
       <c r="F31" s="8"/>
       <c r="G31" s="17" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H31" s="8"/>
       <c r="I31" s="8"/>
@@ -6600,7 +6552,7 @@
       <c r="E32" s="8"/>
       <c r="F32" s="8"/>
       <c r="G32" s="17" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H32" s="8"/>
       <c r="I32" s="8"/>
@@ -6615,7 +6567,7 @@
       <c r="E33" s="8"/>
       <c r="F33" s="8"/>
       <c r="G33" s="7" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H33" s="8"/>
       <c r="I33" s="8"/>

--- a/WIP/月茗/LAN阿斯特莱雅/阿斯特莱雅-军事人员配置表.xlsx
+++ b/WIP/月茗/LAN阿斯特莱雅/阿斯特莱雅-军事人员配置表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21615" windowHeight="15855" firstSheet="2"/>
+    <workbookView windowWidth="13545" windowHeight="12375" firstSheet="2"/>
   </bookViews>
   <sheets>
     <sheet name="PCR" sheetId="3" r:id="rId1"/>
@@ -2365,7 +2365,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2548,9 +2548,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3408,9 +3405,9 @@
       <c r="J6" s="55" t="s">
         <v>51</v>
       </c>
-      <c r="K6" s="61"/>
+      <c r="K6" s="56"/>
       <c r="L6" s="55"/>
-      <c r="M6" s="62" t="s">
+      <c r="M6" s="61" t="s">
         <v>52</v>
       </c>
       <c r="N6" s="55" t="s">
@@ -3554,7 +3551,7 @@
       <c r="J8" s="55" t="s">
         <v>87</v>
       </c>
-      <c r="K8" s="62" t="s">
+      <c r="K8" s="61" t="s">
         <v>88</v>
       </c>
       <c r="L8" s="55" t="s">
@@ -3623,7 +3620,7 @@
       <c r="H9" s="55" t="s">
         <v>106</v>
       </c>
-      <c r="I9" s="62" t="s">
+      <c r="I9" s="61" t="s">
         <v>107</v>
       </c>
       <c r="J9" s="55" t="s">
@@ -3631,7 +3628,7 @@
       </c>
       <c r="K9" s="56"/>
       <c r="L9" s="55"/>
-      <c r="M9" s="62" t="s">
+      <c r="M9" s="61" t="s">
         <v>109</v>
       </c>
       <c r="N9" s="55" t="s">
@@ -3692,7 +3689,7 @@
       <c r="H10" s="55" t="s">
         <v>122</v>
       </c>
-      <c r="I10" s="62" t="s">
+      <c r="I10" s="61" t="s">
         <v>123</v>
       </c>
       <c r="J10" s="55" t="s">
@@ -3708,7 +3705,7 @@
       <c r="P10" s="55" t="s">
         <v>126</v>
       </c>
-      <c r="Q10" s="62" t="s">
+      <c r="Q10" s="61" t="s">
         <v>127</v>
       </c>
       <c r="R10" s="55" t="s">
@@ -3806,10 +3803,10 @@
       <c r="D12" s="56" t="s">
         <v>98</v>
       </c>
-      <c r="E12" s="63" t="s">
+      <c r="E12" s="62" t="s">
         <v>141</v>
       </c>
-      <c r="F12" s="63" t="s">
+      <c r="F12" s="62" t="s">
         <v>142</v>
       </c>
       <c r="G12" s="56" t="s">
@@ -3824,7 +3821,7 @@
       <c r="L12" s="55"/>
       <c r="M12" s="56"/>
       <c r="N12" s="55"/>
-      <c r="O12" s="62" t="s">
+      <c r="O12" s="61" t="s">
         <v>145</v>
       </c>
       <c r="P12" s="55" t="s">
@@ -3857,10 +3854,10 @@
       <c r="D13" s="56" t="s">
         <v>151</v>
       </c>
-      <c r="E13" s="63" t="s">
+      <c r="E13" s="62" t="s">
         <v>152</v>
       </c>
-      <c r="F13" s="63" t="s">
+      <c r="F13" s="62" t="s">
         <v>28</v>
       </c>
       <c r="G13" s="56"/>
@@ -3871,7 +3868,7 @@
       <c r="L13" s="55"/>
       <c r="M13" s="56"/>
       <c r="N13" s="55"/>
-      <c r="O13" s="62" t="s">
+      <c r="O13" s="61" t="s">
         <v>153</v>
       </c>
       <c r="P13" s="55" t="s">
@@ -3904,11 +3901,11 @@
       <c r="D14" s="56" t="s">
         <v>157</v>
       </c>
-      <c r="E14" s="63" t="s">
+      <c r="E14" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="F14" s="64"/>
-      <c r="G14" s="63"/>
+      <c r="F14" s="63"/>
+      <c r="G14" s="62"/>
       <c r="H14" s="55"/>
       <c r="I14" s="56"/>
       <c r="J14" s="55"/>
@@ -3916,7 +3913,7 @@
       <c r="L14" s="55"/>
       <c r="M14" s="56"/>
       <c r="N14" s="55"/>
-      <c r="O14" s="62" t="s">
+      <c r="O14" s="61" t="s">
         <v>159</v>
       </c>
       <c r="P14" s="55" t="s">
@@ -3939,11 +3936,11 @@
       <c r="D15" s="56" t="s">
         <v>161</v>
       </c>
-      <c r="E15" s="63" t="s">
+      <c r="E15" s="62" t="s">
         <v>162</v>
       </c>
-      <c r="F15" s="64"/>
-      <c r="G15" s="63"/>
+      <c r="F15" s="63"/>
+      <c r="G15" s="62"/>
       <c r="H15" s="55"/>
       <c r="I15" s="56"/>
       <c r="J15" s="55"/>
@@ -3980,11 +3977,11 @@
       <c r="D16" s="56" t="s">
         <v>165</v>
       </c>
-      <c r="E16" s="63" t="s">
+      <c r="E16" s="62" t="s">
         <v>166</v>
       </c>
-      <c r="F16" s="64"/>
-      <c r="G16" s="63"/>
+      <c r="F16" s="63"/>
+      <c r="G16" s="62"/>
       <c r="H16" s="55"/>
       <c r="I16" s="56"/>
       <c r="J16" s="55"/>
@@ -4021,11 +4018,11 @@
       <c r="D17" s="56" t="s">
         <v>170</v>
       </c>
-      <c r="E17" s="63" t="s">
+      <c r="E17" s="62" t="s">
         <v>171</v>
       </c>
-      <c r="F17" s="64"/>
-      <c r="G17" s="63"/>
+      <c r="F17" s="63"/>
+      <c r="G17" s="62"/>
       <c r="H17" s="55"/>
       <c r="I17" s="56"/>
       <c r="J17" s="55"/>
@@ -4062,13 +4059,13 @@
       <c r="D18" s="56" t="s">
         <v>45</v>
       </c>
-      <c r="E18" s="63" t="s">
+      <c r="E18" s="62" t="s">
         <v>175</v>
       </c>
-      <c r="F18" s="64" t="s">
+      <c r="F18" s="63" t="s">
         <v>176</v>
       </c>
-      <c r="G18" s="63"/>
+      <c r="G18" s="62"/>
       <c r="H18" s="55"/>
       <c r="I18" s="56"/>
       <c r="J18" s="55"/>
@@ -4076,7 +4073,7 @@
       <c r="L18" s="55"/>
       <c r="M18" s="56"/>
       <c r="N18" s="55"/>
-      <c r="O18" s="62" t="s">
+      <c r="O18" s="61" t="s">
         <v>177</v>
       </c>
       <c r="P18" s="55" t="s">
@@ -4102,16 +4099,16 @@
     <row r="19" customHeight="1" spans="2:27">
       <c r="B19" s="54"/>
       <c r="C19" s="55"/>
-      <c r="D19" s="62" t="s">
+      <c r="D19" s="61" t="s">
         <v>180</v>
       </c>
-      <c r="E19" s="63" t="s">
+      <c r="E19" s="62" t="s">
         <v>181</v>
       </c>
-      <c r="F19" s="64" t="s">
+      <c r="F19" s="63" t="s">
         <v>182</v>
       </c>
-      <c r="G19" s="63"/>
+      <c r="G19" s="62"/>
       <c r="H19" s="55"/>
       <c r="I19" s="56"/>
       <c r="J19" s="55"/>
@@ -4145,14 +4142,14 @@
     <row r="20" customHeight="1" spans="2:27">
       <c r="B20" s="54"/>
       <c r="C20" s="55"/>
-      <c r="D20" s="62" t="s">
+      <c r="D20" s="61" t="s">
         <v>186</v>
       </c>
-      <c r="E20" s="63" t="s">
+      <c r="E20" s="62" t="s">
         <v>187</v>
       </c>
-      <c r="F20" s="64"/>
-      <c r="G20" s="63"/>
+      <c r="F20" s="63"/>
+      <c r="G20" s="62"/>
       <c r="H20" s="55"/>
       <c r="I20" s="56"/>
       <c r="J20" s="55"/>
@@ -4189,11 +4186,11 @@
       <c r="D21" s="56" t="s">
         <v>191</v>
       </c>
-      <c r="E21" s="63" t="s">
+      <c r="E21" s="62" t="s">
         <v>192</v>
       </c>
-      <c r="F21" s="64"/>
-      <c r="G21" s="63"/>
+      <c r="F21" s="63"/>
+      <c r="G21" s="62"/>
       <c r="H21" s="55"/>
       <c r="I21" s="56"/>
       <c r="J21" s="55"/>
@@ -4227,14 +4224,14 @@
     <row r="22" customHeight="1" spans="2:27">
       <c r="B22" s="54"/>
       <c r="C22" s="55"/>
-      <c r="D22" s="62" t="s">
+      <c r="D22" s="61" t="s">
         <v>195</v>
       </c>
-      <c r="E22" s="63" t="s">
+      <c r="E22" s="62" t="s">
         <v>196</v>
       </c>
-      <c r="F22" s="64"/>
-      <c r="G22" s="63"/>
+      <c r="F22" s="63"/>
+      <c r="G22" s="62"/>
       <c r="H22" s="55"/>
       <c r="I22" s="56"/>
       <c r="J22" s="55"/>
@@ -4242,7 +4239,7 @@
       <c r="L22" s="55"/>
       <c r="M22" s="56"/>
       <c r="N22" s="55"/>
-      <c r="O22" s="62" t="s">
+      <c r="O22" s="61" t="s">
         <v>197</v>
       </c>
       <c r="P22" s="55" t="s">
@@ -4271,11 +4268,11 @@
       <c r="D23" s="56" t="s">
         <v>199</v>
       </c>
-      <c r="E23" s="63" t="s">
+      <c r="E23" s="62" t="s">
         <v>200</v>
       </c>
-      <c r="F23" s="64"/>
-      <c r="G23" s="63"/>
+      <c r="F23" s="63"/>
+      <c r="G23" s="62"/>
       <c r="H23" s="55"/>
       <c r="I23" s="56"/>
       <c r="J23" s="55"/>
@@ -4283,7 +4280,7 @@
       <c r="L23" s="55"/>
       <c r="M23" s="56"/>
       <c r="N23" s="55"/>
-      <c r="O23" s="62" t="s">
+      <c r="O23" s="61" t="s">
         <v>201</v>
       </c>
       <c r="P23" s="55" t="s">
@@ -4312,11 +4309,11 @@
       <c r="D24" s="56" t="s">
         <v>204</v>
       </c>
-      <c r="E24" s="63" t="s">
+      <c r="E24" s="62" t="s">
         <v>205</v>
       </c>
-      <c r="F24" s="64"/>
-      <c r="G24" s="63"/>
+      <c r="F24" s="63"/>
+      <c r="G24" s="62"/>
       <c r="H24" s="55"/>
       <c r="I24" s="56"/>
       <c r="J24" s="55"/>
@@ -4345,30 +4342,30 @@
     </row>
     <row r="25" customHeight="1" spans="2:27">
       <c r="B25" s="54"/>
-      <c r="C25" s="63"/>
+      <c r="C25" s="62"/>
       <c r="D25" s="56" t="s">
         <v>207</v>
       </c>
-      <c r="E25" s="63" t="s">
+      <c r="E25" s="62" t="s">
         <v>208</v>
       </c>
-      <c r="F25" s="64" t="s">
+      <c r="F25" s="63" t="s">
         <v>209</v>
       </c>
-      <c r="G25" s="63"/>
-      <c r="H25" s="63"/>
+      <c r="G25" s="62"/>
+      <c r="H25" s="62"/>
       <c r="I25" s="56"/>
-      <c r="J25" s="63"/>
+      <c r="J25" s="62"/>
       <c r="K25" s="56"/>
-      <c r="L25" s="63"/>
+      <c r="L25" s="62"/>
       <c r="M25" s="56"/>
-      <c r="N25" s="63"/>
+      <c r="N25" s="62"/>
       <c r="O25" s="56"/>
-      <c r="P25" s="63"/>
+      <c r="P25" s="62"/>
       <c r="Q25" s="56" t="s">
         <v>75</v>
       </c>
-      <c r="R25" s="63" t="s">
+      <c r="R25" s="62" t="s">
         <v>95</v>
       </c>
       <c r="S25" s="57">
@@ -4380,26 +4377,26 @@
     </row>
     <row r="26" customHeight="1" spans="2:27">
       <c r="B26" s="54"/>
-      <c r="C26" s="63"/>
+      <c r="C26" s="62"/>
       <c r="D26" s="56" t="s">
         <v>210</v>
       </c>
-      <c r="E26" s="63" t="s">
+      <c r="E26" s="62" t="s">
         <v>211</v>
       </c>
-      <c r="F26" s="64" t="s">
+      <c r="F26" s="63" t="s">
         <v>212</v>
       </c>
-      <c r="G26" s="63"/>
-      <c r="H26" s="63"/>
+      <c r="G26" s="62"/>
+      <c r="H26" s="62"/>
       <c r="I26" s="56"/>
-      <c r="J26" s="63"/>
+      <c r="J26" s="62"/>
       <c r="K26" s="56"/>
-      <c r="L26" s="63"/>
+      <c r="L26" s="62"/>
       <c r="M26" s="56"/>
-      <c r="N26" s="63"/>
+      <c r="N26" s="62"/>
       <c r="O26" s="56"/>
-      <c r="P26" s="63"/>
+      <c r="P26" s="62"/>
       <c r="Q26" s="56" t="s">
         <v>213</v>
       </c>
@@ -4419,11 +4416,11 @@
       <c r="D27" s="56" t="s">
         <v>214</v>
       </c>
-      <c r="E27" s="63" t="s">
+      <c r="E27" s="62" t="s">
         <v>215</v>
       </c>
-      <c r="F27" s="64"/>
-      <c r="G27" s="63"/>
+      <c r="F27" s="63"/>
+      <c r="G27" s="62"/>
       <c r="H27" s="55"/>
       <c r="I27" s="56"/>
       <c r="J27" s="55"/>
@@ -4444,9 +4441,9 @@
       <c r="B28" s="54"/>
       <c r="C28" s="55"/>
       <c r="D28" s="56"/>
-      <c r="E28" s="63"/>
-      <c r="F28" s="64"/>
-      <c r="G28" s="63"/>
+      <c r="E28" s="62"/>
+      <c r="F28" s="63"/>
+      <c r="G28" s="62"/>
       <c r="H28" s="55"/>
       <c r="I28" s="56"/>
       <c r="J28" s="55"/>
@@ -4473,19 +4470,19 @@
       <c r="B29" s="54"/>
       <c r="C29" s="55"/>
       <c r="D29" s="56"/>
-      <c r="E29" s="63"/>
-      <c r="F29" s="64"/>
+      <c r="E29" s="62"/>
+      <c r="F29" s="63"/>
       <c r="G29" s="55"/>
       <c r="H29" s="55"/>
       <c r="I29" s="56"/>
-      <c r="J29" s="65"/>
+      <c r="J29" s="64"/>
       <c r="K29" s="55"/>
       <c r="L29" s="55"/>
       <c r="M29" s="56"/>
-      <c r="N29" s="65"/>
+      <c r="N29" s="64"/>
       <c r="O29" s="55"/>
       <c r="P29" s="55"/>
-      <c r="Q29" s="62" t="s">
+      <c r="Q29" s="61" t="s">
         <v>153</v>
       </c>
       <c r="R29" s="55" t="s">
@@ -4502,16 +4499,16 @@
       <c r="B30" s="54"/>
       <c r="C30" s="55"/>
       <c r="D30" s="56"/>
-      <c r="E30" s="63"/>
-      <c r="F30" s="64"/>
+      <c r="E30" s="62"/>
+      <c r="F30" s="63"/>
       <c r="G30" s="55"/>
       <c r="H30" s="55"/>
       <c r="I30" s="56"/>
-      <c r="J30" s="65"/>
+      <c r="J30" s="64"/>
       <c r="K30" s="55"/>
       <c r="L30" s="55"/>
       <c r="M30" s="56"/>
-      <c r="N30" s="65"/>
+      <c r="N30" s="64"/>
       <c r="O30" s="55"/>
       <c r="P30" s="55"/>
       <c r="Q30" s="56" t="s">
@@ -4531,19 +4528,19 @@
       <c r="B31" s="54"/>
       <c r="C31" s="55"/>
       <c r="D31" s="56"/>
-      <c r="E31" s="63"/>
-      <c r="F31" s="64"/>
+      <c r="E31" s="62"/>
+      <c r="F31" s="63"/>
       <c r="G31" s="55"/>
       <c r="H31" s="55"/>
       <c r="I31" s="56"/>
-      <c r="J31" s="65"/>
+      <c r="J31" s="64"/>
       <c r="K31" s="55"/>
       <c r="L31" s="55"/>
       <c r="M31" s="56"/>
-      <c r="N31" s="65"/>
+      <c r="N31" s="64"/>
       <c r="O31" s="55"/>
       <c r="P31" s="55"/>
-      <c r="Q31" s="62" t="s">
+      <c r="Q31" s="61" t="s">
         <v>217</v>
       </c>
       <c r="R31" s="55" t="s">
@@ -4560,16 +4557,16 @@
       <c r="B32" s="54"/>
       <c r="C32" s="55"/>
       <c r="D32" s="56"/>
-      <c r="E32" s="63"/>
-      <c r="F32" s="64"/>
+      <c r="E32" s="62"/>
+      <c r="F32" s="63"/>
       <c r="G32" s="55"/>
       <c r="H32" s="55"/>
       <c r="I32" s="56"/>
-      <c r="J32" s="65"/>
+      <c r="J32" s="64"/>
       <c r="K32" s="55"/>
       <c r="L32" s="55"/>
       <c r="M32" s="56"/>
-      <c r="N32" s="65"/>
+      <c r="N32" s="64"/>
       <c r="O32" s="55"/>
       <c r="P32" s="55"/>
       <c r="Q32" s="56"/>
@@ -4583,16 +4580,16 @@
       <c r="B33" s="54"/>
       <c r="C33" s="55"/>
       <c r="D33" s="56"/>
-      <c r="E33" s="63"/>
-      <c r="F33" s="64"/>
+      <c r="E33" s="62"/>
+      <c r="F33" s="63"/>
       <c r="G33" s="55"/>
       <c r="H33" s="55"/>
       <c r="I33" s="56"/>
-      <c r="J33" s="65"/>
+      <c r="J33" s="64"/>
       <c r="K33" s="55"/>
       <c r="L33" s="55"/>
       <c r="M33" s="56"/>
-      <c r="N33" s="65"/>
+      <c r="N33" s="64"/>
       <c r="O33" s="55"/>
       <c r="P33" s="55"/>
       <c r="Q33" s="56" t="s">
@@ -4612,16 +4609,16 @@
       <c r="B34" s="54"/>
       <c r="C34" s="55"/>
       <c r="D34" s="56"/>
-      <c r="E34" s="63"/>
-      <c r="F34" s="64"/>
+      <c r="E34" s="62"/>
+      <c r="F34" s="63"/>
       <c r="G34" s="55"/>
       <c r="H34" s="55"/>
       <c r="I34" s="56"/>
-      <c r="J34" s="65"/>
+      <c r="J34" s="64"/>
       <c r="K34" s="55"/>
       <c r="L34" s="55"/>
       <c r="M34" s="56"/>
-      <c r="N34" s="65"/>
+      <c r="N34" s="64"/>
       <c r="O34" s="55"/>
       <c r="P34" s="55"/>
       <c r="Q34" s="56" t="s">
@@ -4641,16 +4638,16 @@
       <c r="B35" s="54"/>
       <c r="C35" s="55"/>
       <c r="D35" s="56"/>
-      <c r="E35" s="63"/>
-      <c r="F35" s="64"/>
+      <c r="E35" s="62"/>
+      <c r="F35" s="63"/>
       <c r="G35" s="55"/>
       <c r="H35" s="55"/>
       <c r="I35" s="56"/>
-      <c r="J35" s="65"/>
+      <c r="J35" s="64"/>
       <c r="K35" s="55"/>
       <c r="L35" s="55"/>
       <c r="M35" s="56"/>
-      <c r="N35" s="65"/>
+      <c r="N35" s="64"/>
       <c r="O35" s="55"/>
       <c r="P35" s="55"/>
       <c r="Q35" s="56" t="s">
@@ -4670,16 +4667,16 @@
       <c r="B36" s="54"/>
       <c r="C36" s="55"/>
       <c r="D36" s="56"/>
-      <c r="E36" s="63"/>
-      <c r="F36" s="64"/>
+      <c r="E36" s="62"/>
+      <c r="F36" s="63"/>
       <c r="G36" s="55"/>
       <c r="H36" s="55"/>
       <c r="I36" s="56"/>
-      <c r="J36" s="65"/>
+      <c r="J36" s="64"/>
       <c r="K36" s="55"/>
       <c r="L36" s="55"/>
       <c r="M36" s="56"/>
-      <c r="N36" s="65"/>
+      <c r="N36" s="64"/>
       <c r="O36" s="55"/>
       <c r="P36" s="55"/>
       <c r="Q36" s="56" t="s">
@@ -4696,15 +4693,15 @@
       <c r="V36" s="60"/>
     </row>
     <row r="37" customHeight="1" spans="2:22">
-      <c r="B37" s="66"/>
-      <c r="D37" s="67"/>
-      <c r="E37" s="68"/>
-      <c r="F37" s="69"/>
-      <c r="I37" s="67"/>
-      <c r="J37" s="70"/>
-      <c r="M37" s="67"/>
-      <c r="N37" s="70"/>
-      <c r="Q37" s="67" t="s">
+      <c r="B37" s="65"/>
+      <c r="D37" s="66"/>
+      <c r="E37" s="67"/>
+      <c r="F37" s="68"/>
+      <c r="I37" s="66"/>
+      <c r="J37" s="69"/>
+      <c r="M37" s="66"/>
+      <c r="N37" s="69"/>
+      <c r="Q37" s="66" t="s">
         <v>220</v>
       </c>
       <c r="R37" s="55" t="s">
@@ -4718,15 +4715,15 @@
       <c r="V37" s="60"/>
     </row>
     <row r="38" customHeight="1" spans="2:22">
-      <c r="B38" s="66"/>
-      <c r="D38" s="67"/>
-      <c r="E38" s="68"/>
-      <c r="F38" s="69"/>
-      <c r="I38" s="67"/>
-      <c r="J38" s="70"/>
-      <c r="M38" s="67"/>
-      <c r="N38" s="70"/>
-      <c r="Q38" s="62" t="s">
+      <c r="B38" s="65"/>
+      <c r="D38" s="66"/>
+      <c r="E38" s="67"/>
+      <c r="F38" s="68"/>
+      <c r="I38" s="66"/>
+      <c r="J38" s="69"/>
+      <c r="M38" s="66"/>
+      <c r="N38" s="69"/>
+      <c r="Q38" s="61" t="s">
         <v>221</v>
       </c>
       <c r="R38" s="55" t="s">
@@ -4740,15 +4737,15 @@
       <c r="V38" s="60"/>
     </row>
     <row r="39" customHeight="1" spans="2:22">
-      <c r="B39" s="66"/>
-      <c r="D39" s="67"/>
-      <c r="E39" s="68"/>
-      <c r="F39" s="69"/>
-      <c r="I39" s="67"/>
-      <c r="J39" s="70"/>
-      <c r="M39" s="67"/>
-      <c r="N39" s="70"/>
-      <c r="Q39" s="67" t="s">
+      <c r="B39" s="65"/>
+      <c r="D39" s="66"/>
+      <c r="E39" s="67"/>
+      <c r="F39" s="68"/>
+      <c r="I39" s="66"/>
+      <c r="J39" s="69"/>
+      <c r="M39" s="66"/>
+      <c r="N39" s="69"/>
+      <c r="Q39" s="66" t="s">
         <v>222</v>
       </c>
       <c r="R39" s="55" t="s">
@@ -4762,15 +4759,15 @@
       <c r="V39" s="60"/>
     </row>
     <row r="40" customHeight="1" spans="2:22">
-      <c r="B40" s="66"/>
-      <c r="D40" s="67"/>
-      <c r="E40" s="68"/>
-      <c r="F40" s="69"/>
-      <c r="I40" s="67"/>
-      <c r="J40" s="70"/>
-      <c r="M40" s="67"/>
-      <c r="N40" s="70"/>
-      <c r="Q40" s="62" t="s">
+      <c r="B40" s="65"/>
+      <c r="D40" s="66"/>
+      <c r="E40" s="67"/>
+      <c r="F40" s="68"/>
+      <c r="I40" s="66"/>
+      <c r="J40" s="69"/>
+      <c r="M40" s="66"/>
+      <c r="N40" s="69"/>
+      <c r="Q40" s="61" t="s">
         <v>223</v>
       </c>
       <c r="R40" s="55" t="s">
@@ -4784,15 +4781,15 @@
       <c r="V40" s="60"/>
     </row>
     <row r="41" customHeight="1" spans="2:22">
-      <c r="B41" s="66"/>
-      <c r="D41" s="67"/>
-      <c r="E41" s="68"/>
-      <c r="F41" s="69"/>
-      <c r="I41" s="67"/>
-      <c r="J41" s="70"/>
-      <c r="M41" s="67"/>
-      <c r="N41" s="70"/>
-      <c r="Q41" s="67"/>
+      <c r="B41" s="65"/>
+      <c r="D41" s="66"/>
+      <c r="E41" s="67"/>
+      <c r="F41" s="68"/>
+      <c r="I41" s="66"/>
+      <c r="J41" s="69"/>
+      <c r="M41" s="66"/>
+      <c r="N41" s="69"/>
+      <c r="Q41" s="66"/>
       <c r="R41" s="55"/>
       <c r="S41" s="57"/>
       <c r="T41" s="58"/>
@@ -4800,15 +4797,15 @@
       <c r="V41" s="60"/>
     </row>
     <row r="42" customHeight="1" spans="2:22">
-      <c r="B42" s="66"/>
-      <c r="D42" s="67"/>
-      <c r="E42" s="68"/>
-      <c r="F42" s="69"/>
-      <c r="I42" s="67"/>
-      <c r="J42" s="70"/>
-      <c r="M42" s="67"/>
-      <c r="N42" s="70"/>
-      <c r="Q42" s="61"/>
+      <c r="B42" s="65"/>
+      <c r="D42" s="66"/>
+      <c r="E42" s="67"/>
+      <c r="F42" s="68"/>
+      <c r="I42" s="66"/>
+      <c r="J42" s="69"/>
+      <c r="M42" s="66"/>
+      <c r="N42" s="69"/>
+      <c r="Q42" s="56"/>
       <c r="R42" s="55"/>
       <c r="S42" s="57"/>
       <c r="T42" s="58"/>
@@ -4816,883 +4813,883 @@
       <c r="V42" s="60"/>
     </row>
     <row r="43" customHeight="1" spans="2:22">
-      <c r="B43" s="66"/>
-      <c r="D43" s="67"/>
-      <c r="E43" s="68"/>
-      <c r="F43" s="69"/>
-      <c r="I43" s="67"/>
-      <c r="J43" s="70"/>
-      <c r="M43" s="67"/>
-      <c r="N43" s="70"/>
-      <c r="Q43" s="67"/>
+      <c r="B43" s="65"/>
+      <c r="D43" s="66"/>
+      <c r="E43" s="67"/>
+      <c r="F43" s="68"/>
+      <c r="I43" s="66"/>
+      <c r="J43" s="69"/>
+      <c r="M43" s="66"/>
+      <c r="N43" s="69"/>
+      <c r="Q43" s="66"/>
       <c r="R43"/>
-      <c r="S43" s="71"/>
+      <c r="S43" s="70"/>
       <c r="T43" s="58"/>
       <c r="U43" s="59"/>
       <c r="V43" s="60"/>
     </row>
     <row r="44" customHeight="1" spans="2:22">
-      <c r="B44" s="66"/>
-      <c r="D44" s="67"/>
-      <c r="E44" s="68"/>
-      <c r="F44" s="69"/>
-      <c r="I44" s="67"/>
-      <c r="J44" s="70"/>
-      <c r="M44" s="67"/>
-      <c r="N44" s="70"/>
-      <c r="Q44" s="67"/>
-      <c r="S44" s="71"/>
+      <c r="B44" s="65"/>
+      <c r="D44" s="66"/>
+      <c r="E44" s="67"/>
+      <c r="F44" s="68"/>
+      <c r="I44" s="66"/>
+      <c r="J44" s="69"/>
+      <c r="M44" s="66"/>
+      <c r="N44" s="69"/>
+      <c r="Q44" s="66"/>
+      <c r="S44" s="70"/>
       <c r="T44" s="58"/>
       <c r="U44" s="59"/>
       <c r="V44" s="60"/>
     </row>
     <row r="45" customHeight="1" spans="2:22">
-      <c r="B45" s="66"/>
-      <c r="D45" s="67"/>
-      <c r="E45" s="68"/>
-      <c r="F45" s="69"/>
-      <c r="I45" s="67"/>
-      <c r="J45" s="70"/>
-      <c r="M45" s="67"/>
-      <c r="N45" s="70"/>
-      <c r="Q45" s="67"/>
-      <c r="S45" s="71"/>
+      <c r="B45" s="65"/>
+      <c r="D45" s="66"/>
+      <c r="E45" s="67"/>
+      <c r="F45" s="68"/>
+      <c r="I45" s="66"/>
+      <c r="J45" s="69"/>
+      <c r="M45" s="66"/>
+      <c r="N45" s="69"/>
+      <c r="Q45" s="66"/>
+      <c r="S45" s="70"/>
       <c r="T45" s="58"/>
       <c r="U45" s="59"/>
       <c r="V45" s="60"/>
     </row>
     <row r="46" customHeight="1" spans="2:22">
-      <c r="B46" s="66"/>
-      <c r="D46" s="67"/>
-      <c r="E46" s="68"/>
-      <c r="F46" s="69"/>
-      <c r="I46" s="67"/>
-      <c r="J46" s="70"/>
-      <c r="M46" s="67"/>
-      <c r="N46" s="70"/>
-      <c r="Q46" s="67"/>
-      <c r="S46" s="71"/>
+      <c r="B46" s="65"/>
+      <c r="D46" s="66"/>
+      <c r="E46" s="67"/>
+      <c r="F46" s="68"/>
+      <c r="I46" s="66"/>
+      <c r="J46" s="69"/>
+      <c r="M46" s="66"/>
+      <c r="N46" s="69"/>
+      <c r="Q46" s="66"/>
+      <c r="S46" s="70"/>
       <c r="T46" s="58"/>
       <c r="U46" s="59"/>
       <c r="V46" s="60"/>
     </row>
     <row r="47" customHeight="1" spans="2:22">
-      <c r="B47" s="66"/>
-      <c r="D47" s="67"/>
-      <c r="E47" s="68"/>
-      <c r="F47" s="69"/>
-      <c r="I47" s="67"/>
-      <c r="J47" s="70"/>
-      <c r="M47" s="67"/>
-      <c r="N47" s="70"/>
-      <c r="Q47" s="67"/>
-      <c r="S47" s="71"/>
+      <c r="B47" s="65"/>
+      <c r="D47" s="66"/>
+      <c r="E47" s="67"/>
+      <c r="F47" s="68"/>
+      <c r="I47" s="66"/>
+      <c r="J47" s="69"/>
+      <c r="M47" s="66"/>
+      <c r="N47" s="69"/>
+      <c r="Q47" s="66"/>
+      <c r="S47" s="70"/>
       <c r="T47" s="58"/>
       <c r="U47" s="59"/>
       <c r="V47" s="60"/>
     </row>
     <row r="48" customHeight="1" spans="2:22">
-      <c r="B48" s="66"/>
-      <c r="D48" s="67"/>
-      <c r="E48" s="68"/>
-      <c r="F48" s="69"/>
-      <c r="I48" s="67"/>
-      <c r="J48" s="70"/>
-      <c r="M48" s="67"/>
-      <c r="N48" s="70"/>
-      <c r="Q48" s="67"/>
-      <c r="S48" s="71"/>
+      <c r="B48" s="65"/>
+      <c r="D48" s="66"/>
+      <c r="E48" s="67"/>
+      <c r="F48" s="68"/>
+      <c r="I48" s="66"/>
+      <c r="J48" s="69"/>
+      <c r="M48" s="66"/>
+      <c r="N48" s="69"/>
+      <c r="Q48" s="66"/>
+      <c r="S48" s="70"/>
       <c r="T48" s="58"/>
       <c r="U48" s="59"/>
       <c r="V48" s="60"/>
     </row>
     <row r="49" customHeight="1" spans="2:22">
-      <c r="B49" s="66"/>
-      <c r="D49" s="67"/>
-      <c r="E49" s="68"/>
-      <c r="F49" s="69"/>
-      <c r="I49" s="67"/>
-      <c r="J49" s="70"/>
-      <c r="M49" s="67"/>
-      <c r="N49" s="70"/>
-      <c r="Q49" s="67"/>
-      <c r="S49" s="71"/>
+      <c r="B49" s="65"/>
+      <c r="D49" s="66"/>
+      <c r="E49" s="67"/>
+      <c r="F49" s="68"/>
+      <c r="I49" s="66"/>
+      <c r="J49" s="69"/>
+      <c r="M49" s="66"/>
+      <c r="N49" s="69"/>
+      <c r="Q49" s="66"/>
+      <c r="S49" s="70"/>
       <c r="T49" s="58"/>
       <c r="U49" s="59"/>
       <c r="V49" s="60"/>
     </row>
     <row r="50" customHeight="1" spans="2:22">
-      <c r="B50" s="66"/>
-      <c r="D50" s="67"/>
-      <c r="E50" s="68"/>
-      <c r="F50" s="69"/>
-      <c r="I50" s="67"/>
-      <c r="J50" s="70"/>
-      <c r="M50" s="67"/>
-      <c r="N50" s="70"/>
-      <c r="Q50" s="67"/>
-      <c r="S50" s="71"/>
+      <c r="B50" s="65"/>
+      <c r="D50" s="66"/>
+      <c r="E50" s="67"/>
+      <c r="F50" s="68"/>
+      <c r="I50" s="66"/>
+      <c r="J50" s="69"/>
+      <c r="M50" s="66"/>
+      <c r="N50" s="69"/>
+      <c r="Q50" s="66"/>
+      <c r="S50" s="70"/>
       <c r="T50" s="58"/>
       <c r="U50" s="59"/>
       <c r="V50" s="60"/>
     </row>
     <row r="51" customHeight="1" spans="2:22">
-      <c r="B51" s="66"/>
-      <c r="D51" s="67"/>
-      <c r="E51" s="68"/>
-      <c r="F51" s="69"/>
-      <c r="I51" s="67"/>
-      <c r="J51" s="70"/>
-      <c r="M51" s="67"/>
-      <c r="N51" s="70"/>
-      <c r="Q51" s="67"/>
-      <c r="S51" s="71"/>
+      <c r="B51" s="65"/>
+      <c r="D51" s="66"/>
+      <c r="E51" s="67"/>
+      <c r="F51" s="68"/>
+      <c r="I51" s="66"/>
+      <c r="J51" s="69"/>
+      <c r="M51" s="66"/>
+      <c r="N51" s="69"/>
+      <c r="Q51" s="66"/>
+      <c r="S51" s="70"/>
       <c r="T51" s="58"/>
       <c r="U51" s="59"/>
       <c r="V51" s="60"/>
     </row>
     <row r="52" customHeight="1" spans="2:22">
-      <c r="B52" s="66"/>
-      <c r="D52" s="67"/>
-      <c r="E52" s="68"/>
-      <c r="F52" s="69"/>
-      <c r="I52" s="67"/>
-      <c r="J52" s="70"/>
-      <c r="M52" s="67"/>
-      <c r="N52" s="70"/>
-      <c r="Q52" s="67"/>
-      <c r="S52" s="71"/>
+      <c r="B52" s="65"/>
+      <c r="D52" s="66"/>
+      <c r="E52" s="67"/>
+      <c r="F52" s="68"/>
+      <c r="I52" s="66"/>
+      <c r="J52" s="69"/>
+      <c r="M52" s="66"/>
+      <c r="N52" s="69"/>
+      <c r="Q52" s="66"/>
+      <c r="S52" s="70"/>
       <c r="T52" s="58"/>
       <c r="U52" s="59"/>
       <c r="V52" s="60"/>
     </row>
     <row r="53" customHeight="1" spans="2:22">
-      <c r="B53" s="66"/>
-      <c r="D53" s="67"/>
-      <c r="E53" s="68"/>
-      <c r="F53" s="69"/>
-      <c r="I53" s="67"/>
-      <c r="J53" s="70"/>
-      <c r="M53" s="67"/>
-      <c r="N53" s="70"/>
-      <c r="Q53" s="67"/>
-      <c r="S53" s="71"/>
+      <c r="B53" s="65"/>
+      <c r="D53" s="66"/>
+      <c r="E53" s="67"/>
+      <c r="F53" s="68"/>
+      <c r="I53" s="66"/>
+      <c r="J53" s="69"/>
+      <c r="M53" s="66"/>
+      <c r="N53" s="69"/>
+      <c r="Q53" s="66"/>
+      <c r="S53" s="70"/>
       <c r="T53" s="58"/>
       <c r="U53" s="59"/>
       <c r="V53" s="60"/>
     </row>
     <row r="54" customHeight="1" spans="2:22">
-      <c r="B54" s="66"/>
-      <c r="D54" s="67"/>
-      <c r="E54" s="68"/>
-      <c r="F54" s="69"/>
-      <c r="I54" s="67"/>
-      <c r="J54" s="70"/>
-      <c r="M54" s="67"/>
-      <c r="N54" s="70"/>
-      <c r="Q54" s="67"/>
-      <c r="S54" s="71"/>
+      <c r="B54" s="65"/>
+      <c r="D54" s="66"/>
+      <c r="E54" s="67"/>
+      <c r="F54" s="68"/>
+      <c r="I54" s="66"/>
+      <c r="J54" s="69"/>
+      <c r="M54" s="66"/>
+      <c r="N54" s="69"/>
+      <c r="Q54" s="66"/>
+      <c r="S54" s="70"/>
       <c r="T54" s="58"/>
       <c r="U54" s="59"/>
       <c r="V54" s="60"/>
     </row>
     <row r="55" customHeight="1" spans="2:22">
-      <c r="B55" s="66"/>
-      <c r="D55" s="67"/>
-      <c r="E55" s="68"/>
-      <c r="F55" s="69"/>
-      <c r="I55" s="67"/>
-      <c r="J55" s="70"/>
-      <c r="M55" s="67"/>
-      <c r="N55" s="70"/>
-      <c r="Q55" s="67"/>
-      <c r="S55" s="71"/>
+      <c r="B55" s="65"/>
+      <c r="D55" s="66"/>
+      <c r="E55" s="67"/>
+      <c r="F55" s="68"/>
+      <c r="I55" s="66"/>
+      <c r="J55" s="69"/>
+      <c r="M55" s="66"/>
+      <c r="N55" s="69"/>
+      <c r="Q55" s="66"/>
+      <c r="S55" s="70"/>
       <c r="T55" s="58"/>
       <c r="U55" s="59"/>
       <c r="V55" s="60"/>
     </row>
     <row r="56" customHeight="1" spans="2:22">
-      <c r="B56" s="66"/>
-      <c r="D56" s="67"/>
-      <c r="E56" s="68"/>
-      <c r="F56" s="69"/>
-      <c r="I56" s="67"/>
-      <c r="J56" s="70"/>
-      <c r="M56" s="67"/>
-      <c r="N56" s="70"/>
-      <c r="Q56" s="67"/>
-      <c r="S56" s="71"/>
+      <c r="B56" s="65"/>
+      <c r="D56" s="66"/>
+      <c r="E56" s="67"/>
+      <c r="F56" s="68"/>
+      <c r="I56" s="66"/>
+      <c r="J56" s="69"/>
+      <c r="M56" s="66"/>
+      <c r="N56" s="69"/>
+      <c r="Q56" s="66"/>
+      <c r="S56" s="70"/>
       <c r="T56" s="58"/>
       <c r="U56" s="59"/>
       <c r="V56" s="60"/>
     </row>
     <row r="57" customHeight="1" spans="2:22">
-      <c r="B57" s="66"/>
-      <c r="D57" s="67"/>
-      <c r="E57" s="68"/>
-      <c r="F57" s="69"/>
-      <c r="I57" s="67"/>
-      <c r="J57" s="70"/>
-      <c r="M57" s="67"/>
-      <c r="N57" s="70"/>
-      <c r="Q57" s="67"/>
-      <c r="S57" s="71"/>
+      <c r="B57" s="65"/>
+      <c r="D57" s="66"/>
+      <c r="E57" s="67"/>
+      <c r="F57" s="68"/>
+      <c r="I57" s="66"/>
+      <c r="J57" s="69"/>
+      <c r="M57" s="66"/>
+      <c r="N57" s="69"/>
+      <c r="Q57" s="66"/>
+      <c r="S57" s="70"/>
       <c r="T57" s="58"/>
       <c r="U57" s="59"/>
       <c r="V57" s="60"/>
     </row>
     <row r="58" customHeight="1" spans="2:22">
-      <c r="B58" s="66"/>
-      <c r="D58" s="67"/>
-      <c r="E58" s="68"/>
-      <c r="F58" s="69"/>
-      <c r="I58" s="67"/>
-      <c r="J58" s="70"/>
-      <c r="M58" s="67"/>
-      <c r="N58" s="70"/>
-      <c r="Q58" s="67"/>
-      <c r="S58" s="71"/>
+      <c r="B58" s="65"/>
+      <c r="D58" s="66"/>
+      <c r="E58" s="67"/>
+      <c r="F58" s="68"/>
+      <c r="I58" s="66"/>
+      <c r="J58" s="69"/>
+      <c r="M58" s="66"/>
+      <c r="N58" s="69"/>
+      <c r="Q58" s="66"/>
+      <c r="S58" s="70"/>
       <c r="T58" s="58"/>
       <c r="U58" s="59"/>
       <c r="V58" s="60"/>
     </row>
     <row r="59" customHeight="1" spans="2:22">
-      <c r="B59" s="66"/>
-      <c r="D59" s="67"/>
-      <c r="E59" s="68"/>
-      <c r="F59" s="69"/>
-      <c r="I59" s="67"/>
-      <c r="J59" s="70"/>
-      <c r="M59" s="67"/>
-      <c r="N59" s="70"/>
-      <c r="Q59" s="67"/>
-      <c r="S59" s="71"/>
+      <c r="B59" s="65"/>
+      <c r="D59" s="66"/>
+      <c r="E59" s="67"/>
+      <c r="F59" s="68"/>
+      <c r="I59" s="66"/>
+      <c r="J59" s="69"/>
+      <c r="M59" s="66"/>
+      <c r="N59" s="69"/>
+      <c r="Q59" s="66"/>
+      <c r="S59" s="70"/>
       <c r="T59" s="58"/>
       <c r="U59" s="59"/>
       <c r="V59" s="60"/>
     </row>
     <row r="60" customHeight="1" spans="2:22">
-      <c r="B60" s="66"/>
-      <c r="D60" s="67"/>
-      <c r="E60" s="68"/>
-      <c r="F60" s="69"/>
-      <c r="I60" s="67"/>
-      <c r="J60" s="70"/>
-      <c r="M60" s="67"/>
-      <c r="N60" s="70"/>
-      <c r="Q60" s="67"/>
-      <c r="S60" s="71"/>
+      <c r="B60" s="65"/>
+      <c r="D60" s="66"/>
+      <c r="E60" s="67"/>
+      <c r="F60" s="68"/>
+      <c r="I60" s="66"/>
+      <c r="J60" s="69"/>
+      <c r="M60" s="66"/>
+      <c r="N60" s="69"/>
+      <c r="Q60" s="66"/>
+      <c r="S60" s="70"/>
       <c r="T60" s="58"/>
       <c r="U60" s="59"/>
       <c r="V60" s="60"/>
     </row>
     <row r="61" customHeight="1" spans="2:22">
-      <c r="B61" s="66"/>
-      <c r="D61" s="67"/>
-      <c r="E61" s="68"/>
-      <c r="F61" s="69"/>
-      <c r="I61" s="67"/>
-      <c r="J61" s="70"/>
-      <c r="M61" s="67"/>
-      <c r="N61" s="70"/>
-      <c r="Q61" s="67"/>
-      <c r="S61" s="71"/>
+      <c r="B61" s="65"/>
+      <c r="D61" s="66"/>
+      <c r="E61" s="67"/>
+      <c r="F61" s="68"/>
+      <c r="I61" s="66"/>
+      <c r="J61" s="69"/>
+      <c r="M61" s="66"/>
+      <c r="N61" s="69"/>
+      <c r="Q61" s="66"/>
+      <c r="S61" s="70"/>
       <c r="T61" s="58"/>
       <c r="U61" s="59"/>
       <c r="V61" s="60"/>
     </row>
     <row r="62" customHeight="1" spans="2:22">
-      <c r="B62" s="66"/>
-      <c r="D62" s="67"/>
-      <c r="E62" s="68"/>
-      <c r="F62" s="69"/>
-      <c r="I62" s="67"/>
-      <c r="J62" s="70"/>
-      <c r="M62" s="67"/>
-      <c r="N62" s="70"/>
-      <c r="Q62" s="67"/>
-      <c r="S62" s="71"/>
+      <c r="B62" s="65"/>
+      <c r="D62" s="66"/>
+      <c r="E62" s="67"/>
+      <c r="F62" s="68"/>
+      <c r="I62" s="66"/>
+      <c r="J62" s="69"/>
+      <c r="M62" s="66"/>
+      <c r="N62" s="69"/>
+      <c r="Q62" s="66"/>
+      <c r="S62" s="70"/>
       <c r="T62" s="58"/>
       <c r="U62" s="59"/>
       <c r="V62" s="60"/>
     </row>
     <row r="63" customHeight="1" spans="2:22">
-      <c r="B63" s="66"/>
-      <c r="D63" s="67"/>
-      <c r="E63" s="68"/>
-      <c r="F63" s="69"/>
-      <c r="I63" s="67"/>
-      <c r="J63" s="70"/>
-      <c r="M63" s="67"/>
-      <c r="N63" s="70"/>
-      <c r="Q63" s="67"/>
-      <c r="S63" s="71"/>
+      <c r="B63" s="65"/>
+      <c r="D63" s="66"/>
+      <c r="E63" s="67"/>
+      <c r="F63" s="68"/>
+      <c r="I63" s="66"/>
+      <c r="J63" s="69"/>
+      <c r="M63" s="66"/>
+      <c r="N63" s="69"/>
+      <c r="Q63" s="66"/>
+      <c r="S63" s="70"/>
       <c r="T63" s="58"/>
       <c r="U63" s="59"/>
       <c r="V63" s="60"/>
     </row>
     <row r="64" customHeight="1" spans="2:22">
-      <c r="B64" s="66"/>
-      <c r="D64" s="67"/>
-      <c r="E64" s="68"/>
-      <c r="F64" s="69"/>
-      <c r="I64" s="67"/>
-      <c r="J64" s="70"/>
-      <c r="M64" s="67"/>
-      <c r="N64" s="70"/>
-      <c r="Q64" s="67"/>
-      <c r="S64" s="71"/>
+      <c r="B64" s="65"/>
+      <c r="D64" s="66"/>
+      <c r="E64" s="67"/>
+      <c r="F64" s="68"/>
+      <c r="I64" s="66"/>
+      <c r="J64" s="69"/>
+      <c r="M64" s="66"/>
+      <c r="N64" s="69"/>
+      <c r="Q64" s="66"/>
+      <c r="S64" s="70"/>
       <c r="T64" s="58"/>
       <c r="U64" s="59"/>
       <c r="V64" s="60"/>
     </row>
     <row r="65" customHeight="1" spans="2:22">
-      <c r="B65" s="66"/>
-      <c r="D65" s="67"/>
-      <c r="E65" s="68"/>
-      <c r="F65" s="69"/>
-      <c r="I65" s="67"/>
-      <c r="J65" s="70"/>
-      <c r="M65" s="67"/>
-      <c r="N65" s="70"/>
-      <c r="Q65" s="67"/>
-      <c r="S65" s="71"/>
+      <c r="B65" s="65"/>
+      <c r="D65" s="66"/>
+      <c r="E65" s="67"/>
+      <c r="F65" s="68"/>
+      <c r="I65" s="66"/>
+      <c r="J65" s="69"/>
+      <c r="M65" s="66"/>
+      <c r="N65" s="69"/>
+      <c r="Q65" s="66"/>
+      <c r="S65" s="70"/>
       <c r="T65" s="58"/>
       <c r="U65" s="59"/>
       <c r="V65" s="60"/>
     </row>
     <row r="66" customHeight="1" spans="2:22">
-      <c r="B66" s="66"/>
-      <c r="D66" s="67"/>
-      <c r="E66" s="68"/>
-      <c r="F66" s="69"/>
-      <c r="I66" s="67"/>
-      <c r="J66" s="70"/>
-      <c r="M66" s="67"/>
-      <c r="N66" s="70"/>
-      <c r="Q66" s="67"/>
-      <c r="S66" s="71"/>
+      <c r="B66" s="65"/>
+      <c r="D66" s="66"/>
+      <c r="E66" s="67"/>
+      <c r="F66" s="68"/>
+      <c r="I66" s="66"/>
+      <c r="J66" s="69"/>
+      <c r="M66" s="66"/>
+      <c r="N66" s="69"/>
+      <c r="Q66" s="66"/>
+      <c r="S66" s="70"/>
       <c r="T66" s="58"/>
       <c r="U66" s="59"/>
       <c r="V66" s="60"/>
     </row>
     <row r="67" customHeight="1" spans="2:22">
-      <c r="B67" s="66"/>
-      <c r="D67" s="67"/>
-      <c r="E67" s="68"/>
-      <c r="F67" s="69"/>
-      <c r="I67" s="67"/>
-      <c r="J67" s="70"/>
-      <c r="M67" s="67"/>
-      <c r="N67" s="70"/>
-      <c r="Q67" s="67"/>
-      <c r="S67" s="71"/>
+      <c r="B67" s="65"/>
+      <c r="D67" s="66"/>
+      <c r="E67" s="67"/>
+      <c r="F67" s="68"/>
+      <c r="I67" s="66"/>
+      <c r="J67" s="69"/>
+      <c r="M67" s="66"/>
+      <c r="N67" s="69"/>
+      <c r="Q67" s="66"/>
+      <c r="S67" s="70"/>
       <c r="T67" s="58"/>
       <c r="U67" s="59"/>
       <c r="V67" s="60"/>
     </row>
     <row r="68" customHeight="1" spans="2:22">
-      <c r="B68" s="66"/>
-      <c r="D68" s="67"/>
-      <c r="E68" s="68"/>
-      <c r="F68" s="69"/>
-      <c r="I68" s="67"/>
-      <c r="J68" s="70"/>
-      <c r="M68" s="67"/>
-      <c r="N68" s="70"/>
-      <c r="Q68" s="67"/>
-      <c r="S68" s="71"/>
+      <c r="B68" s="65"/>
+      <c r="D68" s="66"/>
+      <c r="E68" s="67"/>
+      <c r="F68" s="68"/>
+      <c r="I68" s="66"/>
+      <c r="J68" s="69"/>
+      <c r="M68" s="66"/>
+      <c r="N68" s="69"/>
+      <c r="Q68" s="66"/>
+      <c r="S68" s="70"/>
       <c r="T68" s="58"/>
       <c r="U68" s="59"/>
       <c r="V68" s="60"/>
     </row>
     <row r="69" customHeight="1" spans="2:22">
-      <c r="B69" s="66"/>
-      <c r="D69" s="67"/>
-      <c r="E69" s="68"/>
-      <c r="F69" s="69"/>
-      <c r="I69" s="67"/>
-      <c r="J69" s="70"/>
-      <c r="M69" s="67"/>
-      <c r="N69" s="70"/>
-      <c r="Q69" s="67"/>
-      <c r="S69" s="71"/>
+      <c r="B69" s="65"/>
+      <c r="D69" s="66"/>
+      <c r="E69" s="67"/>
+      <c r="F69" s="68"/>
+      <c r="I69" s="66"/>
+      <c r="J69" s="69"/>
+      <c r="M69" s="66"/>
+      <c r="N69" s="69"/>
+      <c r="Q69" s="66"/>
+      <c r="S69" s="70"/>
       <c r="T69" s="58"/>
       <c r="U69" s="59"/>
       <c r="V69" s="60"/>
     </row>
     <row r="70" customHeight="1" spans="2:22">
-      <c r="B70" s="66"/>
-      <c r="D70" s="67"/>
-      <c r="E70" s="68"/>
-      <c r="F70" s="69"/>
-      <c r="I70" s="67"/>
-      <c r="J70" s="70"/>
-      <c r="M70" s="67"/>
-      <c r="N70" s="70"/>
-      <c r="Q70" s="67"/>
-      <c r="S70" s="71"/>
+      <c r="B70" s="65"/>
+      <c r="D70" s="66"/>
+      <c r="E70" s="67"/>
+      <c r="F70" s="68"/>
+      <c r="I70" s="66"/>
+      <c r="J70" s="69"/>
+      <c r="M70" s="66"/>
+      <c r="N70" s="69"/>
+      <c r="Q70" s="66"/>
+      <c r="S70" s="70"/>
       <c r="T70" s="58"/>
       <c r="U70" s="59"/>
       <c r="V70" s="60"/>
     </row>
     <row r="71" customHeight="1" spans="2:22">
-      <c r="B71" s="66"/>
-      <c r="D71" s="67"/>
-      <c r="E71" s="68"/>
-      <c r="F71" s="69"/>
-      <c r="I71" s="67"/>
-      <c r="J71" s="70"/>
-      <c r="M71" s="67"/>
-      <c r="N71" s="70"/>
-      <c r="Q71" s="67"/>
-      <c r="S71" s="71"/>
+      <c r="B71" s="65"/>
+      <c r="D71" s="66"/>
+      <c r="E71" s="67"/>
+      <c r="F71" s="68"/>
+      <c r="I71" s="66"/>
+      <c r="J71" s="69"/>
+      <c r="M71" s="66"/>
+      <c r="N71" s="69"/>
+      <c r="Q71" s="66"/>
+      <c r="S71" s="70"/>
       <c r="T71" s="58"/>
       <c r="U71" s="59"/>
       <c r="V71" s="60"/>
     </row>
     <row r="72" customHeight="1" spans="2:22">
-      <c r="B72" s="66"/>
-      <c r="D72" s="67"/>
-      <c r="E72" s="68"/>
-      <c r="F72" s="69"/>
-      <c r="I72" s="67"/>
-      <c r="J72" s="70"/>
-      <c r="M72" s="67"/>
-      <c r="N72" s="70"/>
-      <c r="Q72" s="67"/>
-      <c r="S72" s="71"/>
+      <c r="B72" s="65"/>
+      <c r="D72" s="66"/>
+      <c r="E72" s="67"/>
+      <c r="F72" s="68"/>
+      <c r="I72" s="66"/>
+      <c r="J72" s="69"/>
+      <c r="M72" s="66"/>
+      <c r="N72" s="69"/>
+      <c r="Q72" s="66"/>
+      <c r="S72" s="70"/>
       <c r="T72" s="58"/>
       <c r="U72" s="59"/>
       <c r="V72" s="60"/>
     </row>
     <row r="73" customHeight="1" spans="2:22">
-      <c r="B73" s="66"/>
-      <c r="D73" s="67"/>
-      <c r="E73" s="68"/>
-      <c r="F73" s="69"/>
-      <c r="I73" s="67"/>
-      <c r="J73" s="70"/>
-      <c r="M73" s="67"/>
-      <c r="N73" s="70"/>
-      <c r="Q73" s="67"/>
-      <c r="S73" s="71"/>
+      <c r="B73" s="65"/>
+      <c r="D73" s="66"/>
+      <c r="E73" s="67"/>
+      <c r="F73" s="68"/>
+      <c r="I73" s="66"/>
+      <c r="J73" s="69"/>
+      <c r="M73" s="66"/>
+      <c r="N73" s="69"/>
+      <c r="Q73" s="66"/>
+      <c r="S73" s="70"/>
       <c r="T73" s="58"/>
       <c r="U73" s="59"/>
       <c r="V73" s="60"/>
     </row>
     <row r="74" customHeight="1" spans="2:22">
-      <c r="B74" s="66"/>
-      <c r="D74" s="67"/>
-      <c r="E74" s="68"/>
-      <c r="F74" s="69"/>
-      <c r="I74" s="67"/>
-      <c r="J74" s="70"/>
-      <c r="M74" s="67"/>
-      <c r="N74" s="70"/>
-      <c r="Q74" s="67"/>
-      <c r="S74" s="71"/>
+      <c r="B74" s="65"/>
+      <c r="D74" s="66"/>
+      <c r="E74" s="67"/>
+      <c r="F74" s="68"/>
+      <c r="I74" s="66"/>
+      <c r="J74" s="69"/>
+      <c r="M74" s="66"/>
+      <c r="N74" s="69"/>
+      <c r="Q74" s="66"/>
+      <c r="S74" s="70"/>
       <c r="T74" s="58"/>
       <c r="U74" s="59"/>
       <c r="V74" s="60"/>
     </row>
     <row r="75" customHeight="1" spans="2:22">
-      <c r="B75" s="66"/>
-      <c r="D75" s="67"/>
-      <c r="E75" s="68"/>
-      <c r="F75" s="69"/>
-      <c r="I75" s="67"/>
-      <c r="J75" s="70"/>
-      <c r="M75" s="67"/>
-      <c r="N75" s="70"/>
-      <c r="Q75" s="67"/>
-      <c r="S75" s="71"/>
+      <c r="B75" s="65"/>
+      <c r="D75" s="66"/>
+      <c r="E75" s="67"/>
+      <c r="F75" s="68"/>
+      <c r="I75" s="66"/>
+      <c r="J75" s="69"/>
+      <c r="M75" s="66"/>
+      <c r="N75" s="69"/>
+      <c r="Q75" s="66"/>
+      <c r="S75" s="70"/>
       <c r="T75" s="58"/>
       <c r="U75" s="59"/>
       <c r="V75" s="60"/>
     </row>
     <row r="76" customHeight="1" spans="2:22">
-      <c r="B76" s="66"/>
-      <c r="D76" s="67"/>
-      <c r="E76" s="68"/>
-      <c r="F76" s="69"/>
-      <c r="I76" s="67"/>
-      <c r="J76" s="70"/>
-      <c r="M76" s="67"/>
-      <c r="N76" s="70"/>
-      <c r="Q76" s="67"/>
-      <c r="S76" s="71"/>
+      <c r="B76" s="65"/>
+      <c r="D76" s="66"/>
+      <c r="E76" s="67"/>
+      <c r="F76" s="68"/>
+      <c r="I76" s="66"/>
+      <c r="J76" s="69"/>
+      <c r="M76" s="66"/>
+      <c r="N76" s="69"/>
+      <c r="Q76" s="66"/>
+      <c r="S76" s="70"/>
       <c r="T76" s="58"/>
       <c r="U76" s="59"/>
       <c r="V76" s="60"/>
     </row>
     <row r="77" customHeight="1" spans="2:22">
-      <c r="B77" s="66"/>
-      <c r="D77" s="67"/>
-      <c r="E77" s="68"/>
-      <c r="F77" s="69"/>
-      <c r="I77" s="67"/>
-      <c r="J77" s="70"/>
-      <c r="M77" s="67"/>
-      <c r="N77" s="70"/>
-      <c r="Q77" s="67"/>
-      <c r="S77" s="71"/>
+      <c r="B77" s="65"/>
+      <c r="D77" s="66"/>
+      <c r="E77" s="67"/>
+      <c r="F77" s="68"/>
+      <c r="I77" s="66"/>
+      <c r="J77" s="69"/>
+      <c r="M77" s="66"/>
+      <c r="N77" s="69"/>
+      <c r="Q77" s="66"/>
+      <c r="S77" s="70"/>
       <c r="T77" s="58"/>
       <c r="U77" s="59"/>
       <c r="V77" s="60"/>
     </row>
     <row r="78" customHeight="1" spans="2:22">
-      <c r="B78" s="66"/>
-      <c r="D78" s="67"/>
-      <c r="E78" s="68"/>
-      <c r="F78" s="69"/>
-      <c r="I78" s="67"/>
-      <c r="J78" s="70"/>
-      <c r="M78" s="67"/>
-      <c r="N78" s="70"/>
-      <c r="Q78" s="67"/>
-      <c r="S78" s="71"/>
+      <c r="B78" s="65"/>
+      <c r="D78" s="66"/>
+      <c r="E78" s="67"/>
+      <c r="F78" s="68"/>
+      <c r="I78" s="66"/>
+      <c r="J78" s="69"/>
+      <c r="M78" s="66"/>
+      <c r="N78" s="69"/>
+      <c r="Q78" s="66"/>
+      <c r="S78" s="70"/>
       <c r="T78" s="58"/>
       <c r="U78" s="59"/>
       <c r="V78" s="60"/>
     </row>
     <row r="79" customHeight="1" spans="2:22">
-      <c r="B79" s="66"/>
-      <c r="D79" s="67"/>
-      <c r="E79" s="68"/>
-      <c r="F79" s="69"/>
-      <c r="I79" s="67"/>
-      <c r="J79" s="70"/>
-      <c r="M79" s="67"/>
-      <c r="N79" s="70"/>
-      <c r="Q79" s="67"/>
-      <c r="S79" s="71"/>
+      <c r="B79" s="65"/>
+      <c r="D79" s="66"/>
+      <c r="E79" s="67"/>
+      <c r="F79" s="68"/>
+      <c r="I79" s="66"/>
+      <c r="J79" s="69"/>
+      <c r="M79" s="66"/>
+      <c r="N79" s="69"/>
+      <c r="Q79" s="66"/>
+      <c r="S79" s="70"/>
       <c r="T79" s="58"/>
       <c r="U79" s="59"/>
       <c r="V79" s="60"/>
     </row>
     <row r="80" customHeight="1" spans="2:22">
-      <c r="B80" s="66"/>
-      <c r="D80" s="67"/>
-      <c r="E80" s="68"/>
-      <c r="F80" s="69"/>
-      <c r="I80" s="67"/>
-      <c r="J80" s="70"/>
-      <c r="M80" s="67"/>
-      <c r="N80" s="70"/>
-      <c r="Q80" s="67"/>
-      <c r="S80" s="71"/>
+      <c r="B80" s="65"/>
+      <c r="D80" s="66"/>
+      <c r="E80" s="67"/>
+      <c r="F80" s="68"/>
+      <c r="I80" s="66"/>
+      <c r="J80" s="69"/>
+      <c r="M80" s="66"/>
+      <c r="N80" s="69"/>
+      <c r="Q80" s="66"/>
+      <c r="S80" s="70"/>
       <c r="T80" s="58"/>
       <c r="U80" s="59"/>
       <c r="V80" s="60"/>
     </row>
     <row r="81" customHeight="1" spans="2:22">
-      <c r="B81" s="66"/>
-      <c r="D81" s="67"/>
-      <c r="E81" s="68"/>
-      <c r="F81" s="69"/>
-      <c r="I81" s="67"/>
-      <c r="J81" s="70"/>
-      <c r="M81" s="67"/>
-      <c r="N81" s="70"/>
-      <c r="Q81" s="67"/>
-      <c r="S81" s="71"/>
+      <c r="B81" s="65"/>
+      <c r="D81" s="66"/>
+      <c r="E81" s="67"/>
+      <c r="F81" s="68"/>
+      <c r="I81" s="66"/>
+      <c r="J81" s="69"/>
+      <c r="M81" s="66"/>
+      <c r="N81" s="69"/>
+      <c r="Q81" s="66"/>
+      <c r="S81" s="70"/>
       <c r="T81" s="58"/>
       <c r="U81" s="59"/>
       <c r="V81" s="60"/>
     </row>
     <row r="82" customHeight="1" spans="2:22">
-      <c r="B82" s="66"/>
-      <c r="D82" s="67"/>
-      <c r="E82" s="68"/>
-      <c r="F82" s="69"/>
-      <c r="I82" s="67"/>
-      <c r="J82" s="70"/>
-      <c r="M82" s="67"/>
-      <c r="N82" s="70"/>
-      <c r="Q82" s="67"/>
-      <c r="S82" s="71"/>
+      <c r="B82" s="65"/>
+      <c r="D82" s="66"/>
+      <c r="E82" s="67"/>
+      <c r="F82" s="68"/>
+      <c r="I82" s="66"/>
+      <c r="J82" s="69"/>
+      <c r="M82" s="66"/>
+      <c r="N82" s="69"/>
+      <c r="Q82" s="66"/>
+      <c r="S82" s="70"/>
       <c r="T82" s="58"/>
       <c r="U82" s="59"/>
       <c r="V82" s="60"/>
     </row>
     <row r="83" customHeight="1" spans="2:22">
-      <c r="B83" s="66"/>
-      <c r="D83" s="67"/>
-      <c r="E83" s="68"/>
-      <c r="F83" s="69"/>
-      <c r="I83" s="67"/>
-      <c r="J83" s="70"/>
-      <c r="M83" s="67"/>
-      <c r="N83" s="70"/>
-      <c r="Q83" s="67"/>
-      <c r="S83" s="71"/>
+      <c r="B83" s="65"/>
+      <c r="D83" s="66"/>
+      <c r="E83" s="67"/>
+      <c r="F83" s="68"/>
+      <c r="I83" s="66"/>
+      <c r="J83" s="69"/>
+      <c r="M83" s="66"/>
+      <c r="N83" s="69"/>
+      <c r="Q83" s="66"/>
+      <c r="S83" s="70"/>
       <c r="T83" s="58"/>
       <c r="U83" s="59"/>
       <c r="V83" s="60"/>
     </row>
     <row r="84" customHeight="1" spans="2:22">
-      <c r="B84" s="66"/>
-      <c r="D84" s="67"/>
-      <c r="E84" s="68"/>
-      <c r="F84" s="69"/>
-      <c r="I84" s="67"/>
-      <c r="J84" s="70"/>
-      <c r="M84" s="67"/>
-      <c r="N84" s="70"/>
-      <c r="Q84" s="67"/>
-      <c r="S84" s="71"/>
+      <c r="B84" s="65"/>
+      <c r="D84" s="66"/>
+      <c r="E84" s="67"/>
+      <c r="F84" s="68"/>
+      <c r="I84" s="66"/>
+      <c r="J84" s="69"/>
+      <c r="M84" s="66"/>
+      <c r="N84" s="69"/>
+      <c r="Q84" s="66"/>
+      <c r="S84" s="70"/>
       <c r="T84" s="58"/>
       <c r="U84" s="59"/>
       <c r="V84" s="60"/>
     </row>
     <row r="85" customHeight="1" spans="2:22">
-      <c r="B85" s="66"/>
-      <c r="D85" s="67"/>
-      <c r="E85" s="68"/>
-      <c r="F85" s="69"/>
-      <c r="I85" s="67"/>
-      <c r="J85" s="70"/>
-      <c r="M85" s="67"/>
-      <c r="N85" s="70"/>
-      <c r="Q85" s="67"/>
-      <c r="S85" s="71"/>
+      <c r="B85" s="65"/>
+      <c r="D85" s="66"/>
+      <c r="E85" s="67"/>
+      <c r="F85" s="68"/>
+      <c r="I85" s="66"/>
+      <c r="J85" s="69"/>
+      <c r="M85" s="66"/>
+      <c r="N85" s="69"/>
+      <c r="Q85" s="66"/>
+      <c r="S85" s="70"/>
       <c r="T85" s="58"/>
       <c r="U85" s="59"/>
       <c r="V85" s="60"/>
     </row>
     <row r="86" customHeight="1" spans="2:22">
-      <c r="B86" s="66"/>
-      <c r="D86" s="67"/>
-      <c r="E86" s="68"/>
-      <c r="F86" s="69"/>
-      <c r="I86" s="67"/>
-      <c r="J86" s="70"/>
-      <c r="M86" s="67"/>
-      <c r="N86" s="70"/>
-      <c r="Q86" s="67"/>
-      <c r="S86" s="71"/>
+      <c r="B86" s="65"/>
+      <c r="D86" s="66"/>
+      <c r="E86" s="67"/>
+      <c r="F86" s="68"/>
+      <c r="I86" s="66"/>
+      <c r="J86" s="69"/>
+      <c r="M86" s="66"/>
+      <c r="N86" s="69"/>
+      <c r="Q86" s="66"/>
+      <c r="S86" s="70"/>
       <c r="T86" s="58"/>
       <c r="U86" s="59"/>
       <c r="V86" s="60"/>
     </row>
     <row r="87" customHeight="1" spans="2:22">
-      <c r="B87" s="66"/>
-      <c r="D87" s="67"/>
-      <c r="E87" s="68"/>
-      <c r="F87" s="69"/>
-      <c r="I87" s="67"/>
-      <c r="J87" s="70"/>
-      <c r="M87" s="67"/>
-      <c r="N87" s="70"/>
-      <c r="Q87" s="67"/>
-      <c r="S87" s="71"/>
+      <c r="B87" s="65"/>
+      <c r="D87" s="66"/>
+      <c r="E87" s="67"/>
+      <c r="F87" s="68"/>
+      <c r="I87" s="66"/>
+      <c r="J87" s="69"/>
+      <c r="M87" s="66"/>
+      <c r="N87" s="69"/>
+      <c r="Q87" s="66"/>
+      <c r="S87" s="70"/>
       <c r="T87" s="58"/>
       <c r="U87" s="59"/>
       <c r="V87" s="60"/>
     </row>
     <row r="88" customHeight="1" spans="2:22">
-      <c r="B88" s="66"/>
-      <c r="D88" s="67"/>
-      <c r="E88" s="68"/>
-      <c r="F88" s="69"/>
-      <c r="I88" s="67"/>
-      <c r="J88" s="70"/>
-      <c r="M88" s="67"/>
-      <c r="N88" s="70"/>
-      <c r="Q88" s="67"/>
-      <c r="S88" s="71"/>
+      <c r="B88" s="65"/>
+      <c r="D88" s="66"/>
+      <c r="E88" s="67"/>
+      <c r="F88" s="68"/>
+      <c r="I88" s="66"/>
+      <c r="J88" s="69"/>
+      <c r="M88" s="66"/>
+      <c r="N88" s="69"/>
+      <c r="Q88" s="66"/>
+      <c r="S88" s="70"/>
       <c r="T88" s="58"/>
       <c r="U88" s="59"/>
       <c r="V88" s="60"/>
     </row>
     <row r="89" customHeight="1" spans="2:22">
-      <c r="B89" s="66"/>
-      <c r="D89" s="67"/>
-      <c r="E89" s="68"/>
-      <c r="F89" s="69"/>
-      <c r="I89" s="67"/>
-      <c r="J89" s="70"/>
-      <c r="M89" s="67"/>
-      <c r="N89" s="70"/>
-      <c r="Q89" s="67"/>
-      <c r="S89" s="71"/>
+      <c r="B89" s="65"/>
+      <c r="D89" s="66"/>
+      <c r="E89" s="67"/>
+      <c r="F89" s="68"/>
+      <c r="I89" s="66"/>
+      <c r="J89" s="69"/>
+      <c r="M89" s="66"/>
+      <c r="N89" s="69"/>
+      <c r="Q89" s="66"/>
+      <c r="S89" s="70"/>
       <c r="T89" s="58"/>
       <c r="U89" s="59"/>
       <c r="V89" s="60"/>
     </row>
     <row r="90" customHeight="1" spans="2:22">
-      <c r="B90" s="66"/>
-      <c r="D90" s="67"/>
-      <c r="E90" s="68"/>
-      <c r="F90" s="69"/>
-      <c r="I90" s="67"/>
-      <c r="J90" s="70"/>
-      <c r="M90" s="67"/>
-      <c r="N90" s="70"/>
-      <c r="Q90" s="67"/>
-      <c r="S90" s="71"/>
+      <c r="B90" s="65"/>
+      <c r="D90" s="66"/>
+      <c r="E90" s="67"/>
+      <c r="F90" s="68"/>
+      <c r="I90" s="66"/>
+      <c r="J90" s="69"/>
+      <c r="M90" s="66"/>
+      <c r="N90" s="69"/>
+      <c r="Q90" s="66"/>
+      <c r="S90" s="70"/>
       <c r="T90" s="58"/>
       <c r="U90" s="59"/>
       <c r="V90" s="60"/>
     </row>
     <row r="91" customHeight="1" spans="2:22">
-      <c r="B91" s="66"/>
-      <c r="D91" s="67"/>
-      <c r="E91" s="68"/>
-      <c r="F91" s="69"/>
-      <c r="I91" s="67"/>
-      <c r="J91" s="70"/>
-      <c r="M91" s="67"/>
-      <c r="N91" s="70"/>
-      <c r="Q91" s="67"/>
-      <c r="S91" s="71"/>
+      <c r="B91" s="65"/>
+      <c r="D91" s="66"/>
+      <c r="E91" s="67"/>
+      <c r="F91" s="68"/>
+      <c r="I91" s="66"/>
+      <c r="J91" s="69"/>
+      <c r="M91" s="66"/>
+      <c r="N91" s="69"/>
+      <c r="Q91" s="66"/>
+      <c r="S91" s="70"/>
       <c r="T91" s="58"/>
       <c r="U91" s="59"/>
       <c r="V91" s="60"/>
     </row>
     <row r="92" customHeight="1" spans="2:22">
-      <c r="B92" s="66"/>
-      <c r="D92" s="67"/>
-      <c r="E92" s="68"/>
-      <c r="F92" s="69"/>
-      <c r="I92" s="67"/>
-      <c r="J92" s="70"/>
-      <c r="M92" s="67"/>
-      <c r="N92" s="70"/>
-      <c r="Q92" s="67"/>
-      <c r="S92" s="71"/>
+      <c r="B92" s="65"/>
+      <c r="D92" s="66"/>
+      <c r="E92" s="67"/>
+      <c r="F92" s="68"/>
+      <c r="I92" s="66"/>
+      <c r="J92" s="69"/>
+      <c r="M92" s="66"/>
+      <c r="N92" s="69"/>
+      <c r="Q92" s="66"/>
+      <c r="S92" s="70"/>
       <c r="T92" s="58"/>
       <c r="U92" s="59"/>
       <c r="V92" s="60"/>
     </row>
     <row r="93" customHeight="1" spans="2:22">
-      <c r="B93" s="66"/>
-      <c r="D93" s="67"/>
-      <c r="E93" s="68"/>
-      <c r="F93" s="69"/>
-      <c r="I93" s="67"/>
-      <c r="J93" s="70"/>
-      <c r="M93" s="67"/>
-      <c r="N93" s="70"/>
-      <c r="Q93" s="67"/>
-      <c r="S93" s="71"/>
+      <c r="B93" s="65"/>
+      <c r="D93" s="66"/>
+      <c r="E93" s="67"/>
+      <c r="F93" s="68"/>
+      <c r="I93" s="66"/>
+      <c r="J93" s="69"/>
+      <c r="M93" s="66"/>
+      <c r="N93" s="69"/>
+      <c r="Q93" s="66"/>
+      <c r="S93" s="70"/>
       <c r="T93" s="58"/>
       <c r="U93" s="59"/>
       <c r="V93" s="60"/>
     </row>
     <row r="94" customHeight="1" spans="2:22">
-      <c r="B94" s="66"/>
-      <c r="D94" s="67"/>
-      <c r="E94" s="68"/>
-      <c r="F94" s="69"/>
-      <c r="I94" s="67"/>
-      <c r="J94" s="70"/>
-      <c r="M94" s="67"/>
-      <c r="N94" s="70"/>
-      <c r="Q94" s="67"/>
-      <c r="S94" s="71"/>
+      <c r="B94" s="65"/>
+      <c r="D94" s="66"/>
+      <c r="E94" s="67"/>
+      <c r="F94" s="68"/>
+      <c r="I94" s="66"/>
+      <c r="J94" s="69"/>
+      <c r="M94" s="66"/>
+      <c r="N94" s="69"/>
+      <c r="Q94" s="66"/>
+      <c r="S94" s="70"/>
       <c r="T94" s="58"/>
       <c r="U94" s="59"/>
       <c r="V94" s="60"/>
     </row>
     <row r="95" customHeight="1" spans="2:22">
-      <c r="B95" s="66"/>
-      <c r="D95" s="67"/>
-      <c r="E95" s="68"/>
-      <c r="F95" s="69"/>
-      <c r="I95" s="67"/>
-      <c r="J95" s="70"/>
-      <c r="M95" s="67"/>
-      <c r="N95" s="70"/>
-      <c r="Q95" s="67"/>
-      <c r="S95" s="71"/>
+      <c r="B95" s="65"/>
+      <c r="D95" s="66"/>
+      <c r="E95" s="67"/>
+      <c r="F95" s="68"/>
+      <c r="I95" s="66"/>
+      <c r="J95" s="69"/>
+      <c r="M95" s="66"/>
+      <c r="N95" s="69"/>
+      <c r="Q95" s="66"/>
+      <c r="S95" s="70"/>
       <c r="T95" s="58"/>
       <c r="U95" s="59"/>
       <c r="V95" s="60"/>
     </row>
     <row r="96" customHeight="1" spans="2:22">
-      <c r="B96" s="66"/>
-      <c r="D96" s="67"/>
-      <c r="E96" s="68"/>
-      <c r="F96" s="69"/>
-      <c r="I96" s="67"/>
-      <c r="J96" s="70"/>
-      <c r="M96" s="67"/>
-      <c r="N96" s="70"/>
-      <c r="Q96" s="67"/>
-      <c r="S96" s="71"/>
+      <c r="B96" s="65"/>
+      <c r="D96" s="66"/>
+      <c r="E96" s="67"/>
+      <c r="F96" s="68"/>
+      <c r="I96" s="66"/>
+      <c r="J96" s="69"/>
+      <c r="M96" s="66"/>
+      <c r="N96" s="69"/>
+      <c r="Q96" s="66"/>
+      <c r="S96" s="70"/>
       <c r="T96" s="58"/>
       <c r="U96" s="59"/>
       <c r="V96" s="60"/>
     </row>
     <row r="97" customHeight="1" spans="2:22">
-      <c r="B97" s="66"/>
-      <c r="D97" s="67"/>
-      <c r="E97" s="68"/>
-      <c r="F97" s="69"/>
-      <c r="I97" s="67"/>
-      <c r="J97" s="70"/>
-      <c r="M97" s="67"/>
-      <c r="N97" s="70"/>
-      <c r="Q97" s="67"/>
-      <c r="S97" s="71"/>
+      <c r="B97" s="65"/>
+      <c r="D97" s="66"/>
+      <c r="E97" s="67"/>
+      <c r="F97" s="68"/>
+      <c r="I97" s="66"/>
+      <c r="J97" s="69"/>
+      <c r="M97" s="66"/>
+      <c r="N97" s="69"/>
+      <c r="Q97" s="66"/>
+      <c r="S97" s="70"/>
       <c r="T97" s="58"/>
       <c r="U97" s="59"/>
       <c r="V97" s="60"/>
     </row>
     <row r="98" customHeight="1" spans="2:22">
-      <c r="B98" s="66"/>
-      <c r="D98" s="67"/>
-      <c r="E98" s="68"/>
-      <c r="F98" s="69"/>
-      <c r="I98" s="67"/>
-      <c r="J98" s="70"/>
-      <c r="M98" s="67"/>
-      <c r="N98" s="70"/>
-      <c r="Q98" s="67"/>
-      <c r="S98" s="71"/>
+      <c r="B98" s="65"/>
+      <c r="D98" s="66"/>
+      <c r="E98" s="67"/>
+      <c r="F98" s="68"/>
+      <c r="I98" s="66"/>
+      <c r="J98" s="69"/>
+      <c r="M98" s="66"/>
+      <c r="N98" s="69"/>
+      <c r="Q98" s="66"/>
+      <c r="S98" s="70"/>
       <c r="T98" s="58"/>
       <c r="U98" s="59"/>
       <c r="V98" s="60"/>
     </row>
     <row r="99" customHeight="1" spans="2:22">
-      <c r="B99" s="66"/>
-      <c r="D99" s="67"/>
-      <c r="E99" s="68"/>
-      <c r="F99" s="69"/>
-      <c r="I99" s="67"/>
-      <c r="J99" s="70"/>
-      <c r="M99" s="67"/>
-      <c r="N99" s="70"/>
-      <c r="Q99" s="67"/>
-      <c r="S99" s="71"/>
+      <c r="B99" s="65"/>
+      <c r="D99" s="66"/>
+      <c r="E99" s="67"/>
+      <c r="F99" s="68"/>
+      <c r="I99" s="66"/>
+      <c r="J99" s="69"/>
+      <c r="M99" s="66"/>
+      <c r="N99" s="69"/>
+      <c r="Q99" s="66"/>
+      <c r="S99" s="70"/>
       <c r="T99" s="58"/>
       <c r="U99" s="59"/>
       <c r="V99" s="60"/>
     </row>
     <row r="100" customHeight="1" spans="2:22">
-      <c r="B100" s="72"/>
-      <c r="C100" s="73"/>
-      <c r="D100" s="74"/>
-      <c r="E100" s="73"/>
-      <c r="F100" s="75"/>
-      <c r="G100" s="73"/>
-      <c r="H100" s="73"/>
-      <c r="I100" s="74"/>
-      <c r="J100" s="76"/>
-      <c r="K100" s="73"/>
-      <c r="L100" s="73"/>
-      <c r="M100" s="74"/>
-      <c r="N100" s="76"/>
-      <c r="O100" s="73"/>
-      <c r="P100" s="73"/>
-      <c r="Q100" s="74"/>
-      <c r="R100" s="73"/>
-      <c r="S100" s="77"/>
-      <c r="T100" s="78"/>
-      <c r="U100" s="77"/>
-      <c r="V100" s="79"/>
+      <c r="B100" s="71"/>
+      <c r="C100" s="72"/>
+      <c r="D100" s="73"/>
+      <c r="E100" s="72"/>
+      <c r="F100" s="74"/>
+      <c r="G100" s="72"/>
+      <c r="H100" s="72"/>
+      <c r="I100" s="73"/>
+      <c r="J100" s="75"/>
+      <c r="K100" s="72"/>
+      <c r="L100" s="72"/>
+      <c r="M100" s="73"/>
+      <c r="N100" s="75"/>
+      <c r="O100" s="72"/>
+      <c r="P100" s="72"/>
+      <c r="Q100" s="73"/>
+      <c r="R100" s="72"/>
+      <c r="S100" s="76"/>
+      <c r="T100" s="77"/>
+      <c r="U100" s="76"/>
+      <c r="V100" s="78"/>
     </row>
   </sheetData>
   <mergeCells count="11">
